--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="865">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">1.74538791179657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69254732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245504379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68429100513458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67603480815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66612684726715</t>
+    <t xml:space="preserve">1.69254720211029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245480537415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67603468894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66612696647644</t>
   </si>
   <si>
     <t xml:space="preserve">1.63888120651245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61163532733917</t>
+    <t xml:space="preserve">1.61163520812988</t>
   </si>
   <si>
     <t xml:space="preserve">1.59347140789032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48613905906677</t>
+    <t xml:space="preserve">1.48613917827606</t>
   </si>
   <si>
     <t xml:space="preserve">1.59264576435089</t>
@@ -80,67 +80,67 @@
     <t xml:space="preserve">1.59182000160217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58604061603546</t>
+    <t xml:space="preserve">1.58604073524475</t>
   </si>
   <si>
     <t xml:space="preserve">1.6017279624939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58521509170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56044614315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51255917549133</t>
+    <t xml:space="preserve">1.58521521091461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56044590473175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51255929470062</t>
   </si>
   <si>
     <t xml:space="preserve">1.53980529308319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56539976596832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53567707538605</t>
+    <t xml:space="preserve">1.56539988517761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53567719459534</t>
   </si>
   <si>
     <t xml:space="preserve">1.45311379432678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50595426559448</t>
+    <t xml:space="preserve">1.50595438480377</t>
   </si>
   <si>
     <t xml:space="preserve">1.46137022972107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44238066673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51833868026733</t>
+    <t xml:space="preserve">1.4423805475235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51833879947662</t>
   </si>
   <si>
     <t xml:space="preserve">1.65126574039459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63475298881531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65621960163116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64300918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63723003864288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64218366146088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63970673084259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6677782535553</t>
+    <t xml:space="preserve">1.63475286960602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65621948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64300930500031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6372298002243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64218378067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63970685005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66777837276459</t>
   </si>
   <si>
     <t xml:space="preserve">1.60503041744232</t>
@@ -149,85 +149,85 @@
     <t xml:space="preserve">1.5984251499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56870245933533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227617740631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60255336761475</t>
+    <t xml:space="preserve">1.56870234012604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053237438202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227593898773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60255324840546</t>
   </si>
   <si>
     <t xml:space="preserve">1.57283055782318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58934330940247</t>
+    <t xml:space="preserve">1.58934319019318</t>
   </si>
   <si>
     <t xml:space="preserve">1.58438944816589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56787693500519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55714356899261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53402590751648</t>
+    <t xml:space="preserve">1.56787669658661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5571436882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53402602672577</t>
   </si>
   <si>
     <t xml:space="preserve">1.54310786724091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55466651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962061882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55218970775604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55053853988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50265169143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4869647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861622810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237450122833</t>
+    <t xml:space="preserve">1.55466639995575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5596204996109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55218958854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55053842067719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50265181064606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696482181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237462043762</t>
   </si>
   <si>
     <t xml:space="preserve">1.49026727676392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5150363445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779058456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623145580292</t>
+    <t xml:space="preserve">1.51503622531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779046535492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47623157501221</t>
   </si>
   <si>
     <t xml:space="preserve">1.50760555267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5010005235672</t>
+    <t xml:space="preserve">1.50100040435791</t>
   </si>
   <si>
     <t xml:space="preserve">1.49439549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48366212844849</t>
+    <t xml:space="preserve">1.48366224765778</t>
   </si>
   <si>
     <t xml:space="preserve">1.45971882343292</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.45299983024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46223831176758</t>
+    <t xml:space="preserve">1.46223855018616</t>
   </si>
   <si>
     <t xml:space="preserve">1.43284261226654</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">1.41100549697876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44040167331696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43620204925537</t>
+    <t xml:space="preserve">1.44040155410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43620216846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.4429212808609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44880032539368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47819626331329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460093975067</t>
+    <t xml:space="preserve">1.44880044460297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47819638252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460082054138</t>
   </si>
   <si>
     <t xml:space="preserve">1.42360389232635</t>
@@ -290,43 +290,43 @@
     <t xml:space="preserve">1.4084860086441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37825012207031</t>
+    <t xml:space="preserve">1.37825000286102</t>
   </si>
   <si>
     <t xml:space="preserve">1.42444384098053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604495048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46979761123657</t>
+    <t xml:space="preserve">1.41604483127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46979749202728</t>
   </si>
   <si>
     <t xml:space="preserve">1.42780315876007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42192411422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47567653656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44796049594879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735619544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43368256092072</t>
+    <t xml:space="preserve">1.42192399501801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47567689418793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4479603767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735631465912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43368244171143</t>
   </si>
   <si>
     <t xml:space="preserve">1.45803892612457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45216000080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48491537570953</t>
+    <t xml:space="preserve">1.45216012001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48491513729095</t>
   </si>
   <si>
     <t xml:space="preserve">1.46391832828522</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">1.46643805503845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46895754337311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48575532436371</t>
+    <t xml:space="preserve">1.46895742416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.485755443573</t>
   </si>
   <si>
     <t xml:space="preserve">1.45887899398804</t>
@@ -350,49 +350,49 @@
     <t xml:space="preserve">1.45719921588898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48827493190765</t>
+    <t xml:space="preserve">1.48827469348907</t>
   </si>
   <si>
     <t xml:space="preserve">1.43956160545349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.473996758461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46727788448334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49835360050201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50927197933197</t>
+    <t xml:space="preserve">1.47399687767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46727776527405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49835348129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50927209854126</t>
   </si>
   <si>
     <t xml:space="preserve">1.5033928155899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49499404430389</t>
+    <t xml:space="preserve">1.49499380588531</t>
   </si>
   <si>
     <t xml:space="preserve">1.48743498325348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51011192798615</t>
+    <t xml:space="preserve">1.51011180877686</t>
   </si>
   <si>
     <t xml:space="preserve">1.4991934299469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179182529449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45047998428345</t>
+    <t xml:space="preserve">1.51179170608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45048010349274</t>
   </si>
   <si>
     <t xml:space="preserve">1.44628059864044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4387218952179</t>
+    <t xml:space="preserve">1.43872165679932</t>
   </si>
   <si>
     <t xml:space="preserve">1.50003325939178</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">1.48071587085724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48155581951141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51095187664032</t>
+    <t xml:space="preserve">1.48155570030212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51095163822174</t>
   </si>
   <si>
     <t xml:space="preserve">1.49583387374878</t>
@@ -413,16 +413,16 @@
     <t xml:space="preserve">1.50759208202362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49667382240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47231698036194</t>
+    <t xml:space="preserve">1.49667358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47231709957123</t>
   </si>
   <si>
     <t xml:space="preserve">1.49331426620483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47147727012634</t>
+    <t xml:space="preserve">1.47147715091705</t>
   </si>
   <si>
     <t xml:space="preserve">1.50087320804596</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">1.53194892406464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52690958976746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355003356934</t>
+    <t xml:space="preserve">1.52690947055817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52354991436005</t>
   </si>
   <si>
     <t xml:space="preserve">1.50423264503479</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">1.51263165473938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454708099365</t>
+    <t xml:space="preserve">1.54454696178436</t>
   </si>
   <si>
     <t xml:space="preserve">1.54538714885712</t>
@@ -458,28 +458,28 @@
     <t xml:space="preserve">1.52019059658051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5084320306778</t>
+    <t xml:space="preserve">1.50843214988708</t>
   </si>
   <si>
     <t xml:space="preserve">1.59578001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53446841239929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56050515174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53026914596558</t>
+    <t xml:space="preserve">1.53446865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56050503253937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53026902675629</t>
   </si>
   <si>
     <t xml:space="preserve">1.53110897541046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55126631259918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55210602283478</t>
+    <t xml:space="preserve">1.55126619338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55210614204407</t>
   </si>
   <si>
     <t xml:space="preserve">1.55378580093384</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">1.58654141426086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56218492984772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56974387168884</t>
+    <t xml:space="preserve">1.56218481063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56974375247955</t>
   </si>
   <si>
     <t xml:space="preserve">1.57058358192444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60333907604218</t>
+    <t xml:space="preserve">1.60333919525146</t>
   </si>
   <si>
     <t xml:space="preserve">1.54958653450012</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">1.55798530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57142353057861</t>
+    <t xml:space="preserve">1.5714236497879</t>
   </si>
   <si>
     <t xml:space="preserve">1.56470429897308</t>
@@ -524,46 +524,46 @@
     <t xml:space="preserve">1.62517607212067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62097668647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61257779598236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5932605266571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58822095394135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60753846168518</t>
+    <t xml:space="preserve">1.62097656726837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61257791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59326040744781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58822107315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60753834247589</t>
   </si>
   <si>
     <t xml:space="preserve">1.63105547428131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61425769329071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71504366397858</t>
+    <t xml:space="preserve">1.61425757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71504378318787</t>
   </si>
   <si>
     <t xml:space="preserve">1.77215564250946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7654367685318</t>
+    <t xml:space="preserve">1.76543664932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.75367856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72512221336365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74527943134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72176277637482</t>
+    <t xml:space="preserve">1.72512209415436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74527955055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72176265716553</t>
   </si>
   <si>
     <t xml:space="preserve">1.70664489269257</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">1.73856043815613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69992578029633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67892861366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69656610488892</t>
+    <t xml:space="preserve">1.69992589950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67892849445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69656622409821</t>
   </si>
   <si>
     <t xml:space="preserve">1.69320666790009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70496511459351</t>
+    <t xml:space="preserve">1.70496499538422</t>
   </si>
   <si>
     <t xml:space="preserve">1.77383553981781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75871789455414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68984723091125</t>
+    <t xml:space="preserve">1.75871777534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68984699249268</t>
   </si>
   <si>
     <t xml:space="preserve">1.69152677059174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66800999641418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68816733360291</t>
+    <t xml:space="preserve">1.66801011562347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68816745281219</t>
   </si>
   <si>
     <t xml:space="preserve">1.71336376667023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73184144496918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535809993744</t>
+    <t xml:space="preserve">1.7318412065506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535798072815</t>
   </si>
   <si>
     <t xml:space="preserve">1.7100043296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71672344207764</t>
+    <t xml:space="preserve">1.71672332286835</t>
   </si>
   <si>
     <t xml:space="preserve">1.73016154766083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047610282898</t>
+    <t xml:space="preserve">1.74695932865143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77047622203827</t>
   </si>
   <si>
     <t xml:space="preserve">1.76375687122345</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">1.75031900405884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78895366191864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7402400970459</t>
+    <t xml:space="preserve">1.78895354270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74024033546448</t>
   </si>
   <si>
     <t xml:space="preserve">1.76207721233368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73352110385895</t>
+    <t xml:space="preserve">1.73352098464966</t>
   </si>
   <si>
     <t xml:space="preserve">1.79903209209442</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">1.78055465221405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82254874706268</t>
+    <t xml:space="preserve">1.82254886627197</t>
   </si>
   <si>
     <t xml:space="preserve">1.86958241462708</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">2.36482620239258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32223200798035</t>
+    <t xml:space="preserve">2.32223224639893</t>
   </si>
   <si>
     <t xml:space="preserve">2.34608435630798</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">2.2489697933197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20296859741211</t>
+    <t xml:space="preserve">2.20296835899353</t>
   </si>
   <si>
     <t xml:space="preserve">2.14163279533386</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">2.00192403793335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02407312393188</t>
+    <t xml:space="preserve">2.02407288551331</t>
   </si>
   <si>
     <t xml:space="preserve">2.06155610084534</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.04111075401306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9797750711441</t>
+    <t xml:space="preserve">1.97977530956268</t>
   </si>
   <si>
     <t xml:space="preserve">1.99340498447418</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">1.97636759281158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97125625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466385364532</t>
+    <t xml:space="preserve">1.97125601768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9746640920639</t>
   </si>
   <si>
     <t xml:space="preserve">1.95081150531769</t>
@@ -767,13 +767,13 @@
     <t xml:space="preserve">1.92525470256805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92695844173431</t>
+    <t xml:space="preserve">1.92695868015289</t>
   </si>
   <si>
     <t xml:space="preserve">1.94229221343994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95762598514557</t>
+    <t xml:space="preserve">1.95762622356415</t>
   </si>
   <si>
     <t xml:space="preserve">1.93718099594116</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">2.00703549385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01555418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98829424381256</t>
+    <t xml:space="preserve">2.01555442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98829400539398</t>
   </si>
   <si>
     <t xml:space="preserve">1.93206977844238</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">1.93377375602722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94058871269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822555541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2557852268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22341322898865</t>
+    <t xml:space="preserve">1.94058895111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822531700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25578546524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22341346740723</t>
   </si>
   <si>
     <t xml:space="preserve">2.35971450805664</t>
@@ -830,19 +830,19 @@
     <t xml:space="preserve">2.41593885421753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41253161430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3682336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30860161781311</t>
+    <t xml:space="preserve">2.41253137588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36823391914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30860185623169</t>
   </si>
   <si>
     <t xml:space="preserve">2.31200933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31541681289673</t>
+    <t xml:space="preserve">2.31541705131531</t>
   </si>
   <si>
     <t xml:space="preserve">2.28986048698425</t>
@@ -851,37 +851,37 @@
     <t xml:space="preserve">2.42445802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41423535346985</t>
+    <t xml:space="preserve">2.41423559188843</t>
   </si>
   <si>
     <t xml:space="preserve">2.36993741989136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39719748497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35801124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30519413948059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32052850723267</t>
+    <t xml:space="preserve">2.39719772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35801100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30519437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32052826881409</t>
   </si>
   <si>
     <t xml:space="preserve">2.32904720306396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31882452964783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3477885723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36312198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3443808555603</t>
+    <t xml:space="preserve">2.31882429122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34778833389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36312222480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
     <t xml:space="preserve">2.32563972473145</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">2.36652994155884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37675285339355</t>
+    <t xml:space="preserve">2.37675261497498</t>
   </si>
   <si>
     <t xml:space="preserve">2.38356781005859</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">2.12800240516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31712102890015</t>
+    <t xml:space="preserve">2.31712079048157</t>
   </si>
   <si>
     <t xml:space="preserve">2.28304553031921</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">2.29667592048645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28815698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21659827232361</t>
+    <t xml:space="preserve">2.28815674781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21659851074219</t>
   </si>
   <si>
     <t xml:space="preserve">2.23874735832214</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">2.29156446456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39379024505615</t>
+    <t xml:space="preserve">2.39379000663757</t>
   </si>
   <si>
     <t xml:space="preserve">2.41934633255005</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">2.5726854801178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54712915420532</t>
+    <t xml:space="preserve">2.5471293926239</t>
   </si>
   <si>
     <t xml:space="preserve">2.5812041759491</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">2.41082787513733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30008316040039</t>
+    <t xml:space="preserve">2.30008292198181</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342206954956</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">2.60676097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61527967453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64935493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787386894226</t>
+    <t xml:space="preserve">2.61527943611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6493546962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787410736084</t>
   </si>
   <si>
     <t xml:space="preserve">2.43638443946838</t>
@@ -1034,22 +1034,22 @@
     <t xml:space="preserve">2.53861021995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55564785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48749709129333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4449028968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26600813865662</t>
+    <t xml:space="preserve">2.55564761161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48749732971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44490265846252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26600790023804</t>
   </si>
   <si>
     <t xml:space="preserve">2.1467444896698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19671058654785</t>
+    <t xml:space="preserve">2.19671034812927</t>
   </si>
   <si>
     <t xml:space="preserve">2.1185667514801</t>
@@ -1067,22 +1067,22 @@
     <t xml:space="preserve">2.24880623817444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26617121696472</t>
+    <t xml:space="preserve">2.2661714553833</t>
   </si>
   <si>
     <t xml:space="preserve">2.27485394477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34431552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35299801826477</t>
+    <t xml:space="preserve">2.34431529045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35299825668335</t>
   </si>
   <si>
     <t xml:space="preserve">2.30090236663818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3095850944519</t>
+    <t xml:space="preserve">2.30958485603333</t>
   </si>
   <si>
     <t xml:space="preserve">2.32695007324219</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">2.21407580375671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17934536933899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20539283752441</t>
+    <t xml:space="preserve">2.17934513092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20539307594299</t>
   </si>
   <si>
     <t xml:space="preserve">2.15329718589783</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">1.93623089790344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87545251846313</t>
+    <t xml:space="preserve">1.87545239925385</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281761646271</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">1.82335638999939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81467378139496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77994322776794</t>
+    <t xml:space="preserve">1.81467366218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77994310855865</t>
   </si>
   <si>
     <t xml:space="preserve">1.71916460990906</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">1.62799692153931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63233804702759</t>
+    <t xml:space="preserve">1.6323379278183</t>
   </si>
   <si>
     <t xml:space="preserve">1.67575132846832</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">1.68443417549133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71048200130463</t>
+    <t xml:space="preserve">1.71048212051392</t>
   </si>
   <si>
     <t xml:space="preserve">1.68877530097961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71482336521149</t>
+    <t xml:space="preserve">1.7148232460022</t>
   </si>
   <si>
     <t xml:space="preserve">1.69745814800262</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">1.59760761260986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60629022121429</t>
+    <t xml:space="preserve">1.60629034042358</t>
   </si>
   <si>
     <t xml:space="preserve">1.6193140745163</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">1.61497271060944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63667941093445</t>
+    <t xml:space="preserve">1.63667953014374</t>
   </si>
   <si>
     <t xml:space="preserve">1.64970350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68009257316589</t>
+    <t xml:space="preserve">1.68009269237518</t>
   </si>
   <si>
     <t xml:space="preserve">1.65838611125946</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">1.67141008377075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66706871986389</t>
+    <t xml:space="preserve">1.66706883907318</t>
   </si>
   <si>
     <t xml:space="preserve">1.57155954837799</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">1.66272723674774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72784721851349</t>
+    <t xml:space="preserve">1.72784733772278</t>
   </si>
   <si>
     <t xml:space="preserve">1.76257789134979</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">1.78862583637238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80599105358124</t>
+    <t xml:space="preserve">1.80599117279053</t>
   </si>
   <si>
     <t xml:space="preserve">1.77126038074493</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.97096157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91886532306671</t>
+    <t xml:space="preserve">1.91886556148529</t>
   </si>
   <si>
     <t xml:space="preserve">1.92754828929901</t>
@@ -2604,6 +2604,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.23000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26999998092651</t>
   </si>
 </sst>
 </file>
@@ -67656,7 +67659,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6494907407</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>3805</v>
@@ -67677,6 +67680,32 @@
         <v>857</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6496412037</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>47</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>864</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034153461456</t>
+    <t xml:space="preserve">1.75034165382385</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538791179657</t>
+    <t xml:space="preserve">1.74538803100586</t>
   </si>
   <si>
     <t xml:space="preserve">1.69254720211029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70245492458344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6760345697403</t>
+    <t xml:space="preserve">1.70245516300201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68429100513458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67603468894958</t>
   </si>
   <si>
     <t xml:space="preserve">1.66612708568573</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">1.63888120651245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61163544654846</t>
+    <t xml:space="preserve">1.61163532733917</t>
   </si>
   <si>
     <t xml:space="preserve">1.59347140789032</t>
@@ -74,28 +74,28 @@
     <t xml:space="preserve">1.48613905906677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59264588356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59182012081146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58604085445404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172784328461</t>
+    <t xml:space="preserve">1.59264576435089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59182024002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58604061603546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172760486603</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521497249603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56044602394104</t>
+    <t xml:space="preserve">1.56044614315033</t>
   </si>
   <si>
     <t xml:space="preserve">1.51255941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53980529308319</t>
+    <t xml:space="preserve">1.53980553150177</t>
   </si>
   <si>
     <t xml:space="preserve">1.56539988517761</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">1.4423805475235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51833868026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6512656211853</t>
+    <t xml:space="preserve">1.51833891868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65126574039459</t>
   </si>
   <si>
     <t xml:space="preserve">1.63475286960602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65621960163116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64300930500031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6372298002243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64218366146088</t>
+    <t xml:space="preserve">1.65621948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64300942420959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63722991943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64218378067017</t>
   </si>
   <si>
     <t xml:space="preserve">1.63970685005188</t>
@@ -143,22 +143,22 @@
     <t xml:space="preserve">1.66777837276459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60503029823303</t>
+    <t xml:space="preserve">1.60503017902374</t>
   </si>
   <si>
     <t xml:space="preserve">1.5984251499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56870234012604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6405326128006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227617740631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60255336761475</t>
+    <t xml:space="preserve">1.56870210170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227593898773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60255324840546</t>
   </si>
   <si>
     <t xml:space="preserve">1.57283055782318</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">1.58934319019318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58438944816589</t>
+    <t xml:space="preserve">1.58438956737518</t>
   </si>
   <si>
     <t xml:space="preserve">1.56787693500519</t>
@@ -179,16 +179,16 @@
     <t xml:space="preserve">1.53402578830719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54310774803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962061882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55218958854675</t>
+    <t xml:space="preserve">1.54310762882233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466663837433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962038040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55218970775604</t>
   </si>
   <si>
     <t xml:space="preserve">1.55053842067719</t>
@@ -200,70 +200,70 @@
     <t xml:space="preserve">1.4869647026062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48861622810364</t>
+    <t xml:space="preserve">1.48861610889435</t>
   </si>
   <si>
     <t xml:space="preserve">1.53237450122833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49026727676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5150363445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623145580292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50760567188263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50100040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49439525604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48366224765778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45971870422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45971882343292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45299983024597</t>
+    <t xml:space="preserve">1.49026739597321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51503622531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47623157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50760555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50100064277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49439549446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48366212844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45971894264221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4597190618515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45299971103668</t>
   </si>
   <si>
     <t xml:space="preserve">1.46223866939545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43284261226654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43536221981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43200266361237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42612338066101</t>
+    <t xml:space="preserve">1.43284273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4353621006012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43200278282166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4261234998703</t>
   </si>
   <si>
     <t xml:space="preserve">1.41100549697876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44040155410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43620204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4429212808609</t>
+    <t xml:space="preserve">1.44040143489838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43620216846466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44292116165161</t>
   </si>
   <si>
     <t xml:space="preserve">1.44880044460297</t>
@@ -272,88 +272,88 @@
     <t xml:space="preserve">1.47819626331329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44460082054138</t>
+    <t xml:space="preserve">1.44460105895996</t>
   </si>
   <si>
     <t xml:space="preserve">1.42360401153564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4303230047226</t>
+    <t xml:space="preserve">1.43032276630402</t>
   </si>
   <si>
     <t xml:space="preserve">1.46139860153198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40260660648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40848588943481</t>
+    <t xml:space="preserve">1.40260672569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40848612785339</t>
   </si>
   <si>
     <t xml:space="preserve">1.37825000286102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42444384098053</t>
+    <t xml:space="preserve">1.42444360256195</t>
   </si>
   <si>
     <t xml:space="preserve">1.41604483127594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46979737281799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42780315876007</t>
+    <t xml:space="preserve">1.46979761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42780327796936</t>
   </si>
   <si>
     <t xml:space="preserve">1.42192399501801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47567653656006</t>
+    <t xml:space="preserve">1.47567677497864</t>
   </si>
   <si>
     <t xml:space="preserve">1.44796049594879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735619544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43368232250214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45803916454315</t>
+    <t xml:space="preserve">1.47735643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43368244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45803892612457</t>
   </si>
   <si>
     <t xml:space="preserve">1.4521598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48491537570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46391832828522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46643817424774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46895742416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48575520515442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45887899398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45635914802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45719921588898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48827481269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4395614862442</t>
+    <t xml:space="preserve">1.48491525650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46391820907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46643793582916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46895754337311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48575532436371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45887875556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4563592672348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45719933509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48827493190765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43956160545349</t>
   </si>
   <si>
     <t xml:space="preserve">1.47399687767029</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">1.49835360050201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50927197933197</t>
+    <t xml:space="preserve">1.50927209854126</t>
   </si>
   <si>
     <t xml:space="preserve">1.5033928155899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4949939250946</t>
+    <t xml:space="preserve">1.49499380588531</t>
   </si>
   <si>
     <t xml:space="preserve">1.48743498325348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51011192798615</t>
+    <t xml:space="preserve">1.51011180877686</t>
   </si>
   <si>
     <t xml:space="preserve">1.4991934299469</t>
@@ -386,28 +386,28 @@
     <t xml:space="preserve">1.51179158687592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45048010349274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44628083705902</t>
+    <t xml:space="preserve">1.45048022270203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44628047943115</t>
   </si>
   <si>
     <t xml:space="preserve">1.4387218952179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50003325939178</t>
+    <t xml:space="preserve">1.50003337860107</t>
   </si>
   <si>
     <t xml:space="preserve">1.48071610927582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48155570030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51095175743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49583375453949</t>
+    <t xml:space="preserve">1.4815559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51095187664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49583387374878</t>
   </si>
   <si>
     <t xml:space="preserve">1.50759220123291</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">1.49667382240295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47231733798981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49331402778625</t>
+    <t xml:space="preserve">1.47231721878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49331438541412</t>
   </si>
   <si>
     <t xml:space="preserve">1.47147715091705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50087308883667</t>
+    <t xml:space="preserve">1.50087296962738</t>
   </si>
   <si>
     <t xml:space="preserve">1.52774941921234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53194892406464</t>
+    <t xml:space="preserve">1.53194880485535</t>
   </si>
   <si>
     <t xml:space="preserve">1.52690947055817</t>
@@ -440,70 +440,70 @@
     <t xml:space="preserve">1.52355015277863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50423276424408</t>
+    <t xml:space="preserve">1.50423288345337</t>
   </si>
   <si>
     <t xml:space="preserve">1.51263153553009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454684257507</t>
+    <t xml:space="preserve">1.54454731941223</t>
   </si>
   <si>
     <t xml:space="preserve">1.54538714885712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55294573307037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52019035816193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50843214988708</t>
+    <t xml:space="preserve">1.55294597148895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52019059658051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50843226909637</t>
   </si>
   <si>
     <t xml:space="preserve">1.59578001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53446853160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56050503253937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53026914596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53110897541046</t>
+    <t xml:space="preserve">1.53446865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56050515174866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53026926517487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53110885620117</t>
   </si>
   <si>
     <t xml:space="preserve">1.55126619338989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55210626125336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55378603935242</t>
+    <t xml:space="preserve">1.55210614204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55378592014313</t>
   </si>
   <si>
     <t xml:space="preserve">1.58654141426086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56218469142914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56974375247955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57058346271515</t>
+    <t xml:space="preserve">1.56218457221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56974363327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57058358192444</t>
   </si>
   <si>
     <t xml:space="preserve">1.60333907604218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54958665370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55798554420471</t>
+    <t xml:space="preserve">1.54958653450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55798518657684</t>
   </si>
   <si>
     <t xml:space="preserve">1.57142353057861</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">1.56470441818237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6108980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6117377281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60417890548706</t>
+    <t xml:space="preserve">1.61089789867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61173796653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60417902469635</t>
   </si>
   <si>
     <t xml:space="preserve">1.62517607212067</t>
@@ -527,28 +527,28 @@
     <t xml:space="preserve">1.62097668647766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61257767677307</t>
+    <t xml:space="preserve">1.61257791519165</t>
   </si>
   <si>
     <t xml:space="preserve">1.59326040744781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58822119235992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60753846168518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63105535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61425769329071</t>
+    <t xml:space="preserve">1.58822107315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60753858089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63105511665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61425757408142</t>
   </si>
   <si>
     <t xml:space="preserve">1.71504366397858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77215540409088</t>
+    <t xml:space="preserve">1.77215564250946</t>
   </si>
   <si>
     <t xml:space="preserve">1.76543664932251</t>
@@ -557,25 +557,25 @@
     <t xml:space="preserve">1.75367844104767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72512209415436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74527966976166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72176265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70664489269257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73856031894684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69992566108704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67892849445343</t>
+    <t xml:space="preserve">1.72512233257294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74527955055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72176253795624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70664477348328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73856043815613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69992578029633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67892861366272</t>
   </si>
   <si>
     <t xml:space="preserve">1.69656622409821</t>
@@ -584,40 +584,40 @@
     <t xml:space="preserve">1.69320666790009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70496487617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7738356590271</t>
+    <t xml:space="preserve">1.70496499538422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77383553981781</t>
   </si>
   <si>
     <t xml:space="preserve">1.75871777534485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68984723091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69152677059174</t>
+    <t xml:space="preserve">1.68984699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69152688980103</t>
   </si>
   <si>
     <t xml:space="preserve">1.66801011562347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68816733360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71336376667023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73184132575989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535786151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71000444889069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71672332286835</t>
+    <t xml:space="preserve">1.68816745281219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71336400508881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73184156417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535798072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7100043296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71672320365906</t>
   </si>
   <si>
     <t xml:space="preserve">1.73016166687012</t>
@@ -626,61 +626,61 @@
     <t xml:space="preserve">1.74695909023285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77047610282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375710964203</t>
+    <t xml:space="preserve">1.77047598361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375699043274</t>
   </si>
   <si>
     <t xml:space="preserve">1.75031888484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78895342350006</t>
+    <t xml:space="preserve">1.78895378112793</t>
   </si>
   <si>
     <t xml:space="preserve">1.74024021625519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76207709312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73352086544037</t>
+    <t xml:space="preserve">1.76207733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73352098464966</t>
   </si>
   <si>
     <t xml:space="preserve">1.79903221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78055453300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254886627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86958265304565</t>
+    <t xml:space="preserve">1.78055465221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254862785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86958241462708</t>
   </si>
   <si>
     <t xml:space="preserve">1.86454296112061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84774553775787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391408920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90480971336365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98488664627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34267711639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35119605064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24045157432556</t>
+    <t xml:space="preserve">1.84774541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391432762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90480983257294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98488640785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34267735481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3511962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24045133590698</t>
   </si>
   <si>
     <t xml:space="preserve">2.180819272995</t>
@@ -695,22 +695,22 @@
     <t xml:space="preserve">2.34608459472656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33415865898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24897003173828</t>
+    <t xml:space="preserve">2.33415818214417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2489697933197</t>
   </si>
   <si>
     <t xml:space="preserve">2.20296859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14163255691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07007479667664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01896166801453</t>
+    <t xml:space="preserve">2.14163303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07007503509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01896142959595</t>
   </si>
   <si>
     <t xml:space="preserve">1.95932984352112</t>
@@ -719,34 +719,34 @@
     <t xml:space="preserve">2.01044297218323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00192403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02407312393188</t>
+    <t xml:space="preserve">2.06496357917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00192427635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02407288551331</t>
   </si>
   <si>
     <t xml:space="preserve">2.06155610084534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04451847076416</t>
+    <t xml:space="preserve">2.04451823234558</t>
   </si>
   <si>
     <t xml:space="preserve">2.0683708190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303740501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111075401306</t>
+    <t xml:space="preserve">2.05303716659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04111051559448</t>
   </si>
   <si>
     <t xml:space="preserve">1.9797750711441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99340510368347</t>
+    <t xml:space="preserve">1.99340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">1.97636747360229</t>
@@ -755,43 +755,43 @@
     <t xml:space="preserve">1.97125613689423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97466385364532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95081126689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.938884973526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92525446414948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92695844173431</t>
+    <t xml:space="preserve">1.97466421127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9508113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93888485431671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92525482177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9269585609436</t>
   </si>
   <si>
     <t xml:space="preserve">1.94229221343994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95762622356415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718111515045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866230010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97296023368835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00703525543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01555442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98829400539398</t>
+    <t xml:space="preserve">1.95762646198273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718087673187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866218090057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97296035289764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00703549385071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01555418968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98829424381256</t>
   </si>
   <si>
     <t xml:space="preserve">1.93206977844238</t>
@@ -800,43 +800,43 @@
     <t xml:space="preserve">1.91673588752747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91332852840424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90821695327759</t>
+    <t xml:space="preserve">1.91332817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90821707248688</t>
   </si>
   <si>
     <t xml:space="preserve">1.93377363681793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94058859348297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822555541992</t>
+    <t xml:space="preserve">1.94058847427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822531700134</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578498840332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22341370582581</t>
+    <t xml:space="preserve">2.22341346740723</t>
   </si>
   <si>
     <t xml:space="preserve">2.35971474647522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27452683448792</t>
+    <t xml:space="preserve">2.27452659606934</t>
   </si>
   <si>
     <t xml:space="preserve">2.41593909263611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41253161430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36823344230652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30860185623169</t>
+    <t xml:space="preserve">2.41253185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3682336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30860209465027</t>
   </si>
   <si>
     <t xml:space="preserve">2.31200933456421</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">2.31541681289673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28986024856567</t>
+    <t xml:space="preserve">2.28986048698425</t>
   </si>
   <si>
     <t xml:space="preserve">2.42445802688599</t>
@@ -854,43 +854,43 @@
     <t xml:space="preserve">2.41423535346985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36993741989136</t>
+    <t xml:space="preserve">2.36993765830994</t>
   </si>
   <si>
     <t xml:space="preserve">2.39719772338867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35801076889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30519461631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32052803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32904672622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31882429122925</t>
+    <t xml:space="preserve">2.35801100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30519437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32052826881409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32904696464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31882452964783</t>
   </si>
   <si>
     <t xml:space="preserve">2.3477885723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36312246322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34438133239746</t>
+    <t xml:space="preserve">2.36312222480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
     <t xml:space="preserve">2.32563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33927011489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36652994155884</t>
+    <t xml:space="preserve">2.3392698764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36653017997742</t>
   </si>
   <si>
     <t xml:space="preserve">2.3767523765564</t>
@@ -905,58 +905,58 @@
     <t xml:space="preserve">2.25408148765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09392714500427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15696716308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10585379600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10414981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12800240516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31712079048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28304529190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30349040031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29667568206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28815674781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21659851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23874735832214</t>
+    <t xml:space="preserve">2.09392762184143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15696692466736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10585331916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10415029525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12800288200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31712055206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28304553031921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30349063873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29667544364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28815698623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21659874916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23874759674072</t>
   </si>
   <si>
     <t xml:space="preserve">2.21489453315735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25748896598816</t>
+    <t xml:space="preserve">2.25748920440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.24556255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2319324016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933844566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26260018348694</t>
+    <t xml:space="preserve">2.23193264007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933820724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26260042190552</t>
   </si>
   <si>
     <t xml:space="preserve">2.22511720657349</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">2.23363614082336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23022842407227</t>
+    <t xml:space="preserve">2.23022866249084</t>
   </si>
   <si>
     <t xml:space="preserve">2.20637583732605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29156446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39379000663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41934680938721</t>
+    <t xml:space="preserve">2.29156422615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39379024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41934633255005</t>
   </si>
   <si>
     <t xml:space="preserve">2.53009128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57268524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54712891578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58120441436768</t>
+    <t xml:space="preserve">2.57268571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54712915420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58120465278625</t>
   </si>
   <si>
     <t xml:space="preserve">2.50453495979309</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">2.41082787513733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30008292198181</t>
+    <t xml:space="preserve">2.30008339881897</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342206954956</t>
@@ -1016,43 +1016,43 @@
     <t xml:space="preserve">2.60676074028015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61527991294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6493546962738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4363842010498</t>
+    <t xml:space="preserve">2.61527967453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64935493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787386894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43638396263123</t>
   </si>
   <si>
     <t xml:space="preserve">2.52157258987427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53860998153687</t>
+    <t xml:space="preserve">2.53861045837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.55564785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48749709129333</t>
+    <t xml:space="preserve">2.48749732971191</t>
   </si>
   <si>
     <t xml:space="preserve">2.4449028968811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26600766181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1467444896698</t>
+    <t xml:space="preserve">2.26600813865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14674401283264</t>
   </si>
   <si>
     <t xml:space="preserve">2.19671010971069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1185667514801</t>
+    <t xml:space="preserve">2.11856651306152</t>
   </si>
   <si>
     <t xml:space="preserve">2.17066240310669</t>
@@ -1061,19 +1061,22 @@
     <t xml:space="preserve">2.29221963882446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24880623817444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26617169380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27485394477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34431552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35299801826477</t>
+    <t xml:space="preserve">2.25748872756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24880599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2661714553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27485418319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34431576728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35299825668335</t>
   </si>
   <si>
     <t xml:space="preserve">2.3009021282196</t>
@@ -1082,70 +1085,70 @@
     <t xml:space="preserve">2.30958485603333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32695007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28353714942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21407580375671</t>
+    <t xml:space="preserve">2.32694983482361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28353691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21407604217529</t>
   </si>
   <si>
     <t xml:space="preserve">2.17934513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20539283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15329718589783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13593173027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1098837852478</t>
+    <t xml:space="preserve">2.20539307594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15329694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13593196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10988402366638</t>
   </si>
   <si>
     <t xml:space="preserve">2.18802785873413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09251880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22275805473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07515335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0838360786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10120177268982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04042267799377</t>
+    <t xml:space="preserve">2.09251856803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2227578163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07515358924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08383584022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10120129585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0404224395752</t>
   </si>
   <si>
     <t xml:space="preserve">2.01437449455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05778789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06647086143494</t>
+    <t xml:space="preserve">2.05778765678406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06647062301636</t>
   </si>
   <si>
     <t xml:space="preserve">1.99700927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00569200515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964406013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96227860450745</t>
+    <t xml:space="preserve">2.00569224357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964417934418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96227872371674</t>
   </si>
   <si>
     <t xml:space="preserve">2.02305722236633</t>
@@ -1154,37 +1157,37 @@
     <t xml:space="preserve">2.0491054058075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03173971176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93623077869415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87545239925385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.892817735672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82335650920868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81467366218567</t>
+    <t xml:space="preserve">2.03173995018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93623101711273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87545228004456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281761646271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82335638999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81467354297638</t>
   </si>
   <si>
     <t xml:space="preserve">1.77994310855865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71916460990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69311678409576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62799680233002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63233804702759</t>
+    <t xml:space="preserve">1.71916472911835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69311666488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62799668312073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63233816623688</t>
   </si>
   <si>
     <t xml:space="preserve">1.67575132846832</t>
@@ -1193,13 +1196,13 @@
     <t xml:space="preserve">1.68443417549133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71048212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68877530097961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7148232460022</t>
+    <t xml:space="preserve">1.71048200130463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6887754201889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71482336521149</t>
   </si>
   <si>
     <t xml:space="preserve">1.69745814800262</t>
@@ -1211,13 +1214,13 @@
     <t xml:space="preserve">1.59760761260986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60629022121429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6193140745163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61497294902802</t>
+    <t xml:space="preserve">1.60629034042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61931419372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61497282981873</t>
   </si>
   <si>
     <t xml:space="preserve">1.63667941093445</t>
@@ -1229,13 +1232,13 @@
     <t xml:space="preserve">1.68009269237518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65838611125946</t>
+    <t xml:space="preserve">1.65838599205017</t>
   </si>
   <si>
     <t xml:space="preserve">1.7017993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67141008377075</t>
+    <t xml:space="preserve">1.67140996456146</t>
   </si>
   <si>
     <t xml:space="preserve">1.66706871986389</t>
@@ -1244,13 +1247,13 @@
     <t xml:space="preserve">1.57155954837799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52814626693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51078116893768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551160335541</t>
+    <t xml:space="preserve">1.52814650535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51078104972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551148414612</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287693977356</t>
@@ -1259,79 +1262,79 @@
     <t xml:space="preserve">1.6540447473526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66272723674774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72784733772278</t>
+    <t xml:space="preserve">1.66272735595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72784721851349</t>
   </si>
   <si>
     <t xml:space="preserve">1.7625777721405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75389516353607</t>
+    <t xml:space="preserve">1.75389528274536</t>
   </si>
   <si>
     <t xml:space="preserve">1.78862583637238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80599117279053</t>
+    <t xml:space="preserve">1.80599105358124</t>
   </si>
   <si>
     <t xml:space="preserve">1.77126049995422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74521255493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83203887939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79730844497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84072172641754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86676967144012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91018319129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359623432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94491338729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98832702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97096145153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91886568069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92754828929901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85808706283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84940421581268</t>
+    <t xml:space="preserve">1.74521267414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83203899860382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7973085641861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84072160720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86676979064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91018307209015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359635353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94491350650787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98832666873932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97096157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91886556148529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92754817008972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85808718204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84940457344055</t>
   </si>
   <si>
     <t xml:space="preserve">1.88413500785828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62365531921387</t>
+    <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
     <t xml:space="preserve">1.6504191160202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61919498443604</t>
+    <t xml:space="preserve">1.61919510364532</t>
   </si>
   <si>
     <t xml:space="preserve">1.6013525724411</t>
@@ -1346,46 +1349,43 @@
     <t xml:space="preserve">1.65487957000732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62365543842316</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.6459584236145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64149796962738</t>
+    <t xml:space="preserve">1.64149785041809</t>
   </si>
   <si>
     <t xml:space="preserve">1.65934026241302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66826128959656</t>
+    <t xml:space="preserve">1.66826140880585</t>
   </si>
   <si>
     <t xml:space="preserve">1.68610382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68164324760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63257670402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60581302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62811613082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61473417282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58351016044617</t>
+    <t xml:space="preserve">1.68164312839508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63257682323456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60581314563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62811625003815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61473441123962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58351027965546</t>
   </si>
   <si>
     <t xml:space="preserve">1.57904970645905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55228590965271</t>
+    <t xml:space="preserve">1.55228614807129</t>
   </si>
   <si>
     <t xml:space="preserve">1.54336476325989</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">1.56120717525482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53890430927277</t>
+    <t xml:space="preserve">1.53890419006348</t>
   </si>
   <si>
     <t xml:space="preserve">1.55674660205841</t>
@@ -1406,40 +1406,40 @@
     <t xml:space="preserve">1.57012856006622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58797085285187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57458901405334</t>
+    <t xml:space="preserve">1.58797073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57458889484406</t>
   </si>
   <si>
     <t xml:space="preserve">1.59689199924469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53444361686707</t>
+    <t xml:space="preserve">1.53444385528564</t>
   </si>
   <si>
     <t xml:space="preserve">1.66380083560944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56566774845123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54782545566559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52552258968353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5076801776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738938331604</t>
+    <t xml:space="preserve">1.56566786766052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54782557487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52552247047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50768005847931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738962173462</t>
   </si>
   <si>
     <t xml:space="preserve">1.51660144329071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48983776569366</t>
+    <t xml:space="preserve">1.48983764648438</t>
   </si>
   <si>
     <t xml:space="preserve">1.34263813495636</t>
@@ -1448,31 +1448,31 @@
     <t xml:space="preserve">1.34709882736206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32479596138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19097816944122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26680815219879</t>
+    <t xml:space="preserve">1.32479584217072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19097805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2668080329895</t>
   </si>
   <si>
     <t xml:space="preserve">1.24450528621674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29803228378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20435988903046</t>
+    <t xml:space="preserve">1.29803240299225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20436000823975</t>
   </si>
   <si>
     <t xml:space="preserve">1.27572929859161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28465056419373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30695354938507</t>
+    <t xml:space="preserve">1.28465044498444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30695343017578</t>
   </si>
   <si>
     <t xml:space="preserve">1.30249285697937</t>
@@ -1484,58 +1484,58 @@
     <t xml:space="preserve">1.36494112014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35601997375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36048066616058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40508639812469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44969248771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45415318012238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44523179531097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43631052970886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41846823692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4630743265152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39170467853546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40062606334686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41400754451752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38278341293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38724410533905</t>
+    <t xml:space="preserve">1.35602009296417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36048054695129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40508663654327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44969236850739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4541529417038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44523191452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43631076812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41846835613251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46307420730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39170479774475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40062594413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41400766372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38278353214264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38724422454834</t>
   </si>
   <si>
     <t xml:space="preserve">1.33817768096924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35155928134918</t>
+    <t xml:space="preserve">1.35155940055847</t>
   </si>
   <si>
     <t xml:space="preserve">1.29357171058655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32925653457642</t>
+    <t xml:space="preserve">1.32925641536713</t>
   </si>
   <si>
     <t xml:space="preserve">1.33371710777283</t>
@@ -1544,64 +1544,64 @@
     <t xml:space="preserve">1.31587469577789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37386226654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31141400337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32033538818359</t>
+    <t xml:space="preserve">1.37386238574982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31141412258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3203352689743</t>
   </si>
   <si>
     <t xml:space="preserve">1.28018987178802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4095470905304</t>
+    <t xml:space="preserve">1.40954720973969</t>
   </si>
   <si>
     <t xml:space="preserve">1.39616537094116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45861375331879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37832295894623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42292881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28911113739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2712687253952</t>
+    <t xml:space="preserve">1.45861351490021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37832283973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42292892932892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28911101818085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27126860618591</t>
   </si>
   <si>
     <t xml:space="preserve">1.26234757900238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24896585941315</t>
+    <t xml:space="preserve">1.24896574020386</t>
   </si>
   <si>
     <t xml:space="preserve">1.46753478050232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44077122211456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48091661930084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49429833889008</t>
+    <t xml:space="preserve">1.44077134132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48091650009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49429821968079</t>
   </si>
   <si>
     <t xml:space="preserve">1.5032194852829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52998316287994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49875891208649</t>
+    <t xml:space="preserve">1.52998304367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49875903129578</t>
   </si>
   <si>
     <t xml:space="preserve">1.51214075088501</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">1.48537719249725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52106201648712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72178864479065</t>
+    <t xml:space="preserve">1.52106189727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72178840637207</t>
   </si>
   <si>
     <t xml:space="preserve">1.76639449596405</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">1.83776390552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423678874969</t>
+    <t xml:space="preserve">1.78423690795898</t>
   </si>
   <si>
     <t xml:space="preserve">1.77531564235687</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">1.77085506916046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72624921798706</t>
+    <t xml:space="preserve">1.72624909877777</t>
   </si>
   <si>
     <t xml:space="preserve">1.73070979118347</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">1.74855220317841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79315793514252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71732807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74409151077271</t>
+    <t xml:space="preserve">1.79315805435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71732783317566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74409162998199</t>
   </si>
   <si>
     <t xml:space="preserve">1.77977633476257</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">1.84668505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86452734470367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80207908153534</t>
+    <t xml:space="preserve">1.86452722549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80207931995392</t>
   </si>
   <si>
     <t xml:space="preserve">1.75747334957123</t>
@@ -1688,31 +1688,31 @@
     <t xml:space="preserve">2.0251088142395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96266043186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92697584629059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98050272464752</t>
+    <t xml:space="preserve">1.96266055107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9269757270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98050284385681</t>
   </si>
   <si>
     <t xml:space="preserve">2.07863593101501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10539937019348</t>
+    <t xml:space="preserve">2.10539960861206</t>
   </si>
   <si>
     <t xml:space="preserve">2.05187225341797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06079339981079</t>
+    <t xml:space="preserve">2.06079363822937</t>
   </si>
   <si>
     <t xml:space="preserve">2.09647822380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43548321723938</t>
+    <t xml:space="preserve">2.43548345565796</t>
   </si>
   <si>
     <t xml:space="preserve">2.46224689483643</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">2.60498571395874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65005469322205</t>
+    <t xml:space="preserve">2.65005493164062</t>
   </si>
   <si>
     <t xml:space="preserve">2.61399960517883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64104104042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74019265174866</t>
+    <t xml:space="preserve">2.64104080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74019289016724</t>
   </si>
   <si>
     <t xml:space="preserve">2.78526163101196</t>
@@ -1751,10 +1751,10 @@
     <t xml:space="preserve">3.10074424743652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99257898330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92948246002197</t>
+    <t xml:space="preserve">2.99257874488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92948269844055</t>
   </si>
   <si>
     <t xml:space="preserve">2.84835815429688</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">2.76723408699036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83934426307678</t>
+    <t xml:space="preserve">2.83934450149536</t>
   </si>
   <si>
     <t xml:space="preserve">2.87539935112</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">2.60498595237732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58695816993713</t>
+    <t xml:space="preserve">2.58695793151855</t>
   </si>
   <si>
     <t xml:space="preserve">2.65906858444214</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.67709636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5238618850708</t>
+    <t xml:space="preserve">2.52386164665222</t>
   </si>
   <si>
     <t xml:space="preserve">2.62301349639893</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">2.57794427871704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597206115723</t>
+    <t xml:space="preserve">2.59597182273865</t>
   </si>
   <si>
     <t xml:space="preserve">2.55090308189392</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">2.56893062591553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79427528381348</t>
+    <t xml:space="preserve">2.79427552223206</t>
   </si>
   <si>
     <t xml:space="preserve">2.83033084869385</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">3.0015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09173083305359</t>
+    <t xml:space="preserve">3.09173059463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.96553754806519</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">2.93849635124207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81230282783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54188942909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4787929058075</t>
+    <t xml:space="preserve">2.81230306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54188919067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47879266738892</t>
   </si>
   <si>
     <t xml:space="preserve">2.63202714920044</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">2.95652389526367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01060652732849</t>
+    <t xml:space="preserve">3.01060628890991</t>
   </si>
   <si>
     <t xml:space="preserve">3.01962018013</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">2.98356509208679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88441324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94751024246216</t>
+    <t xml:space="preserve">2.88441348075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94751000404358</t>
   </si>
   <si>
     <t xml:space="preserve">2.92046856880188</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">2.75822019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68611025810242</t>
+    <t xml:space="preserve">2.68611001968384</t>
   </si>
   <si>
     <t xml:space="preserve">2.23542046546936</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">2.36161327362061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50583434104919</t>
+    <t xml:space="preserve">2.50583410263062</t>
   </si>
   <si>
     <t xml:space="preserve">2.48780655860901</t>
@@ -1928,22 +1928,22 @@
     <t xml:space="preserve">2.37964105606079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3706271648407</t>
+    <t xml:space="preserve">2.37062740325928</t>
   </si>
   <si>
     <t xml:space="preserve">2.27147555351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26246190071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28950309753418</t>
+    <t xml:space="preserve">2.26246166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28950333595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555794715881</t>
+    <t xml:space="preserve">2.32555818557739</t>
   </si>
   <si>
     <t xml:space="preserve">2.29851698875427</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">2.343585729599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21739292144775</t>
+    <t xml:space="preserve">2.21739268302917</t>
   </si>
   <si>
     <t xml:space="preserve">2.20837903022766</t>
@@ -19005,7 +19005,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G618" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19031,7 +19031,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G619" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19057,7 +19057,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G620" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19083,7 +19083,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G621" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19109,7 +19109,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19135,7 +19135,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G623" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19161,7 +19161,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G624" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19187,7 +19187,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G625" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19213,7 +19213,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G626" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G627" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19265,7 +19265,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G628" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19291,7 +19291,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G629" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19317,7 +19317,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G630" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19343,7 +19343,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G631" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19369,7 +19369,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G632" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19395,7 +19395,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G633" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19421,7 +19421,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G634" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19447,7 +19447,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G635" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19473,7 +19473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G636" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19525,7 +19525,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G639" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G640" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G641" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G642" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G644" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G645" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G646" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G649" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G655" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G656" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G657" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G658" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G660" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G661" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G662" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G663" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G665" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G666" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G667" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G668" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G670" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20383,7 +20383,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G671" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20409,7 +20409,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G672" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G673" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G674" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G675" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G676" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G677" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G678" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G680" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G682" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G684" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G685" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G686" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G687" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G688" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G690" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G691" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G692" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G693" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G694" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G695" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G697" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G698" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G699" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G700" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G702" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G703" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G704" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G706" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G707" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G708" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G709" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>1.875</v>
       </c>
       <c r="G710" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G711" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G712" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G713" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21501,7 +21501,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21527,7 +21527,7 @@
         <v>1.875</v>
       </c>
       <c r="G715" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G716" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G717" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G718" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G719" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G720" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G721" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G722" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21735,7 +21735,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G723" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21761,7 +21761,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G724" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G725" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G726" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21839,7 +21839,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G727" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G728" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G729" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21917,7 +21917,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G730" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G731" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G732" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G734" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G735" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G736" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G737" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G738" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G739" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G740" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G741" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G742" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G743" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G744" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G745" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G746" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G747" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G748" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G749" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G750" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G751" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G752" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G754" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G755" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G756" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G757" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G758" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G759" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G760" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G761" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G762" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G763" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G764" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G765" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G766" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G767" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G768" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G769" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G770" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G771" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G772" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G773" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G774" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G775" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G776" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G777" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G779" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G781" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G782" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G783" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G784" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G785" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G786" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G787" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G788" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G789" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G790" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G791" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G792" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G793" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G794" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G795" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G796" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G797" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G798" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G799" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G801" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G802" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G803" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G804" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G805" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G806" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>2.25</v>
       </c>
       <c r="G807" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>2.25</v>
       </c>
       <c r="G809" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>2.25</v>
       </c>
       <c r="G811" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G812" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G814" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G817" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G818" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G822" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G823" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G824" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G825" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>2.25</v>
       </c>
       <c r="G826" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G828" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G829" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>2.25</v>
       </c>
       <c r="G830" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G831" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G832" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G834" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G835" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G836" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G837" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G838" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G839" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G840" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G841" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G842" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G843" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G844" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G845" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G846" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G847" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G848" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G850" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G851" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G852" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G853" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G854" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G855" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G856" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G857" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>1.875</v>
       </c>
       <c r="G858" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G859" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G860" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G861" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G862" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G863" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G864" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G865" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G866" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G867" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G868" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G869" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G872" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G873" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G875" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G876" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25895,7 +25895,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G883" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25921,7 +25921,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G884" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G887" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G889" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G893" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G900" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G905" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26935,7 +26935,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27039,7 +27039,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G927" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G928" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G933" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27481,7 +27481,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G944" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28001,7 +28001,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G964" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28027,7 +28027,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G965" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28131,7 +28131,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G969" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G971" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28287,7 +28287,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G975" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28313,7 +28313,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G976" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28443,7 +28443,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G981" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G982" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28495,7 +28495,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G983" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28807,7 +28807,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G995" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28833,7 +28833,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G996" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28859,7 +28859,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G997" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1000" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1001" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1003" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29067,7 +29067,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1005" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1006" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29171,7 +29171,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1009" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29431,7 +29431,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1019" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -36737,7 +36737,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1300" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -67789,7 +67789,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6347337963</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>4811</v>
@@ -67810,6 +67810,32 @@
         <v>857</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6424421296</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>4348</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>858</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -44,58 +44,58 @@
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69254720211029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245516300201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68429100513458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67603468894958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66612708568573</t>
+    <t xml:space="preserve">1.74538791179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69254744052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245504379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6760345697403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66612684726715</t>
   </si>
   <si>
     <t xml:space="preserve">1.63888120651245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61163532733917</t>
+    <t xml:space="preserve">1.61163520812988</t>
   </si>
   <si>
     <t xml:space="preserve">1.59347140789032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48613905906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59264576435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59182024002075</t>
+    <t xml:space="preserve">1.48613917827606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59182012081146</t>
   </si>
   <si>
     <t xml:space="preserve">1.58604061603546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172760486603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521497249603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56044614315033</t>
+    <t xml:space="preserve">1.60172772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521509170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56044602394104</t>
   </si>
   <si>
     <t xml:space="preserve">1.51255941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53980553150177</t>
+    <t xml:space="preserve">1.53980529308319</t>
   </si>
   <si>
     <t xml:space="preserve">1.56539988517761</t>
@@ -107,37 +107,37 @@
     <t xml:space="preserve">1.45311379432678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50595438480377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46137011051178</t>
+    <t xml:space="preserve">1.50595426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46137022972107</t>
   </si>
   <si>
     <t xml:space="preserve">1.4423805475235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51833891868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65126574039459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63475286960602</t>
+    <t xml:space="preserve">1.51833879947662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6512656211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6347531080246</t>
   </si>
   <si>
     <t xml:space="preserve">1.65621948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64300942420959</t>
+    <t xml:space="preserve">1.64300930500031</t>
   </si>
   <si>
     <t xml:space="preserve">1.63722991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64218378067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63970685005188</t>
+    <t xml:space="preserve">1.64218366146088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6397066116333</t>
   </si>
   <si>
     <t xml:space="preserve">1.66777837276459</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">1.60503017902374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5984251499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870210170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227593898773</t>
+    <t xml:space="preserve">1.59842526912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870222091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053237438202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227617740631</t>
   </si>
   <si>
     <t xml:space="preserve">1.60255324840546</t>
@@ -167,73 +167,73 @@
     <t xml:space="preserve">1.58934319019318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58438956737518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56787693500519</t>
+    <t xml:space="preserve">1.58438944816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5678768157959</t>
   </si>
   <si>
     <t xml:space="preserve">1.55714356899261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53402578830719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54310762882233</t>
+    <t xml:space="preserve">1.53402602672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54310774803162</t>
   </si>
   <si>
     <t xml:space="preserve">1.55466663837433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55962038040161</t>
+    <t xml:space="preserve">1.5596204996109</t>
   </si>
   <si>
     <t xml:space="preserve">1.55218970775604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55053842067719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50265169143677</t>
+    <t xml:space="preserve">1.55053853988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50265181064606</t>
   </si>
   <si>
     <t xml:space="preserve">1.4869647026062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48861610889435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237450122833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49026739597321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51503622531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779058456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623157501221</t>
+    <t xml:space="preserve">1.48861622810364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237438201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49026727676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51503610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779046535492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47623145580292</t>
   </si>
   <si>
     <t xml:space="preserve">1.50760555267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50100064277649</t>
+    <t xml:space="preserve">1.5010005235672</t>
   </si>
   <si>
     <t xml:space="preserve">1.49439549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48366212844849</t>
+    <t xml:space="preserve">1.48366236686707</t>
   </si>
   <si>
     <t xml:space="preserve">1.45971894264221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4597190618515</t>
+    <t xml:space="preserve">1.45971882343292</t>
   </si>
   <si>
     <t xml:space="preserve">1.45299971103668</t>
@@ -242,58 +242,58 @@
     <t xml:space="preserve">1.46223866939545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43284273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4353621006012</t>
+    <t xml:space="preserve">1.43284249305725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43536233901978</t>
   </si>
   <si>
     <t xml:space="preserve">1.43200278282166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4261234998703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41100549697876</t>
+    <t xml:space="preserve">1.42612361907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41100573539734</t>
   </si>
   <si>
     <t xml:space="preserve">1.44040143489838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43620216846466</t>
+    <t xml:space="preserve">1.43620204925537</t>
   </si>
   <si>
     <t xml:space="preserve">1.44292116165161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44880044460297</t>
+    <t xml:space="preserve">1.44880056381226</t>
   </si>
   <si>
     <t xml:space="preserve">1.47819626331329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44460105895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42360401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43032276630402</t>
+    <t xml:space="preserve">1.44460093975067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42360377311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43032288551331</t>
   </si>
   <si>
     <t xml:space="preserve">1.46139860153198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40260672569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40848612785339</t>
+    <t xml:space="preserve">1.40260660648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40848588943481</t>
   </si>
   <si>
     <t xml:space="preserve">1.37825000286102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42444360256195</t>
+    <t xml:space="preserve">1.42444372177124</t>
   </si>
   <si>
     <t xml:space="preserve">1.41604483127594</t>
@@ -308,28 +308,28 @@
     <t xml:space="preserve">1.42192399501801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47567677497864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44796049594879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735643386841</t>
+    <t xml:space="preserve">1.47567653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44796061515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735631465912</t>
   </si>
   <si>
     <t xml:space="preserve">1.43368244171143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45803892612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4521598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48491525650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46391820907593</t>
+    <t xml:space="preserve">1.45803904533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45215976238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48491549491882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46391844749451</t>
   </si>
   <si>
     <t xml:space="preserve">1.46643793582916</t>
@@ -338,25 +338,25 @@
     <t xml:space="preserve">1.46895754337311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48575532436371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45887875556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4563592672348</t>
+    <t xml:space="preserve">1.485755443573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45887899398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45635938644409</t>
   </si>
   <si>
     <t xml:space="preserve">1.45719933509827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48827493190765</t>
+    <t xml:space="preserve">1.48827481269836</t>
   </si>
   <si>
     <t xml:space="preserve">1.43956160545349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47399687767029</t>
+    <t xml:space="preserve">1.47399699687958</t>
   </si>
   <si>
     <t xml:space="preserve">1.46727776527405</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">1.49835360050201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50927209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5033928155899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49499380588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48743498325348</t>
+    <t xml:space="preserve">1.50927221775055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50339269638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4949939250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48743522167206</t>
   </si>
   <si>
     <t xml:space="preserve">1.51011180877686</t>
@@ -383,130 +383,130 @@
     <t xml:space="preserve">1.4991934299469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179158687592</t>
+    <t xml:space="preserve">1.51179170608521</t>
   </si>
   <si>
     <t xml:space="preserve">1.45048022270203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44628047943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4387218952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50003337860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48071610927582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4815559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51095187664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49583387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50759220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49667382240295</t>
+    <t xml:space="preserve">1.44628059864044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43872177600861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50003349781036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48071599006653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48155581951141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51095175743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49583399295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50759208202362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49667370319366</t>
   </si>
   <si>
     <t xml:space="preserve">1.47231721878052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49331438541412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147715091705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50087296962738</t>
+    <t xml:space="preserve">1.49331414699554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147727012634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50087320804596</t>
   </si>
   <si>
     <t xml:space="preserve">1.52774941921234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53194880485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690947055817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355015277863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50423288345337</t>
+    <t xml:space="preserve">1.53194892406464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690958976746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50423264503479</t>
   </si>
   <si>
     <t xml:space="preserve">1.51263153553009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454731941223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54538714885712</t>
+    <t xml:space="preserve">1.54454720020294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54538702964783</t>
   </si>
   <si>
     <t xml:space="preserve">1.55294597148895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52019059658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50843226909637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59578001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53446865081787</t>
+    <t xml:space="preserve">1.52019047737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5084320306778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59577989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53446853160858</t>
   </si>
   <si>
     <t xml:space="preserve">1.56050515174866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53026926517487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53110885620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55126619338989</t>
+    <t xml:space="preserve">1.53026914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53110897541046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55126643180847</t>
   </si>
   <si>
     <t xml:space="preserve">1.55210614204407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55378592014313</t>
+    <t xml:space="preserve">1.55378580093384</t>
   </si>
   <si>
     <t xml:space="preserve">1.58654141426086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56218457221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56974363327026</t>
+    <t xml:space="preserve">1.56218469142914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56974351406097</t>
   </si>
   <si>
     <t xml:space="preserve">1.57058358192444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60333907604218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54958653450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55798518657684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57142353057861</t>
+    <t xml:space="preserve">1.60333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54958641529083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55798542499542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57142341136932</t>
   </si>
   <si>
     <t xml:space="preserve">1.56470441818237</t>
@@ -518,124 +518,124 @@
     <t xml:space="preserve">1.61173796653748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60417902469635</t>
+    <t xml:space="preserve">1.60417890548706</t>
   </si>
   <si>
     <t xml:space="preserve">1.62517607212067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62097668647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61257791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59326040744781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58822107315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60753858089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63105511665344</t>
+    <t xml:space="preserve">1.62097656726837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61257779598236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5932605266571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58822119235992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60753846168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63105535507202</t>
   </si>
   <si>
     <t xml:space="preserve">1.61425757408142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71504366397858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77215564250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76543664932251</t>
+    <t xml:space="preserve">1.71504378318787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77215552330017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7654367685318</t>
   </si>
   <si>
     <t xml:space="preserve">1.75367844104767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72512233257294</t>
+    <t xml:space="preserve">1.72512221336365</t>
   </si>
   <si>
     <t xml:space="preserve">1.74527955055237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72176253795624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70664477348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73856043815613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69992578029633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67892861366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69656622409821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69320666790009</t>
+    <t xml:space="preserve">1.72176277637482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70664489269257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73856055736542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69992566108704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67892873287201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69656610488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69320678710938</t>
   </si>
   <si>
     <t xml:space="preserve">1.70496499538422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77383553981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75871777534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68984699249268</t>
+    <t xml:space="preserve">1.77383542060852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75871765613556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68984723091125</t>
   </si>
   <si>
     <t xml:space="preserve">1.69152688980103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66801011562347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68816745281219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71336400508881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73184156417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535798072815</t>
+    <t xml:space="preserve">1.6680098772049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68816757202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71336376667023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73184144496918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535786151886</t>
   </si>
   <si>
     <t xml:space="preserve">1.7100043296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71672320365906</t>
+    <t xml:space="preserve">1.71672332286835</t>
   </si>
   <si>
     <t xml:space="preserve">1.73016166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74695909023285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047598361969</t>
+    <t xml:space="preserve">1.74695920944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7704758644104</t>
   </si>
   <si>
     <t xml:space="preserve">1.76375699043274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75031888484955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78895378112793</t>
+    <t xml:space="preserve">1.75031912326813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78895366191864</t>
   </si>
   <si>
     <t xml:space="preserve">1.74024021625519</t>
@@ -650,70 +650,70 @@
     <t xml:space="preserve">1.79903221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78055465221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254862785339</t>
+    <t xml:space="preserve">1.78055477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254874706268</t>
   </si>
   <si>
     <t xml:space="preserve">1.86958241462708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86454296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84774541854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391432762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90480983257294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98488640785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34267735481262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3511962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24045133590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.180819272995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.364825963974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32223224639893</t>
+    <t xml:space="preserve">1.86454284191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84774553775787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391408920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90480947494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98488688468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34267687797546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35119605064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24045157432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18081951141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36482620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32223200798035</t>
   </si>
   <si>
     <t xml:space="preserve">2.34608459472656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33415818214417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2489697933197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20296859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14163303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07007503509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01896142959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95932984352112</t>
+    <t xml:space="preserve">2.33415842056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24897003173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20296812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14163279533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07007479667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01896166801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9593300819397</t>
   </si>
   <si>
     <t xml:space="preserve">2.01044297218323</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">2.06496357917786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00192427635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02407288551331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06155610084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04451823234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0683708190918</t>
+    <t xml:space="preserve">2.00192403793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02407312393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06155633926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04451847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837105751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.05303716659546</t>
@@ -743,43 +743,43 @@
     <t xml:space="preserve">2.04111051559448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9797750711441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99340534210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97636747360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97125613689423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466421127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9508113861084</t>
+    <t xml:space="preserve">1.97977519035339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99340498447418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97636759281158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97125637531281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97466397285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95081126689911</t>
   </si>
   <si>
     <t xml:space="preserve">1.93888485431671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92525482177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9269585609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94229221343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95762646198273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718087673187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866218090057</t>
+    <t xml:space="preserve">1.92525470256805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92695844173431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94229257106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95762634277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718099594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866206169128</t>
   </si>
   <si>
     <t xml:space="preserve">1.97296035289764</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">2.00703549385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01555418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98829424381256</t>
+    <t xml:space="preserve">2.01555442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98829400539398</t>
   </si>
   <si>
     <t xml:space="preserve">1.93206977844238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91673588752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91332817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90821707248688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93377363681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94058847427368</t>
+    <t xml:space="preserve">1.91673600673676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91332852840424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90821695327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93377327919006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94058871269226</t>
   </si>
   <si>
     <t xml:space="preserve">2.13822531700134</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">2.35971474647522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27452659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41593909263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41253185272217</t>
+    <t xml:space="preserve">2.27452635765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41593933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41253137588501</t>
   </si>
   <si>
     <t xml:space="preserve">2.3682336807251</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">2.30860209465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31200933456421</t>
+    <t xml:space="preserve">2.31200957298279</t>
   </si>
   <si>
     <t xml:space="preserve">2.31541681289673</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">2.41423535346985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36993765830994</t>
+    <t xml:space="preserve">2.36993741989136</t>
   </si>
   <si>
     <t xml:space="preserve">2.39719772338867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35801100730896</t>
+    <t xml:space="preserve">2.35801124572754</t>
   </si>
   <si>
     <t xml:space="preserve">2.30519437789917</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">2.32052826881409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32904696464539</t>
+    <t xml:space="preserve">2.32904720306396</t>
   </si>
   <si>
     <t xml:space="preserve">2.31882452964783</t>
@@ -878,43 +878,43 @@
     <t xml:space="preserve">2.3477885723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36312222480774</t>
+    <t xml:space="preserve">2.36312246322632</t>
   </si>
   <si>
     <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32563972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3392698764801</t>
+    <t xml:space="preserve">2.32563948631287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33926963806152</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653017997742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3767523765564</t>
+    <t xml:space="preserve">2.37675261497498</t>
   </si>
   <si>
     <t xml:space="preserve">2.38356757164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27111864089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25408148765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09392762184143</t>
+    <t xml:space="preserve">2.2711193561554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25408124923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09392738342285</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696692466736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10585331916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10415029525757</t>
+    <t xml:space="preserve">2.10585355758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10415005683899</t>
   </si>
   <si>
     <t xml:space="preserve">2.12800288200378</t>
@@ -926,46 +926,46 @@
     <t xml:space="preserve">2.28304553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30349063873291</t>
+    <t xml:space="preserve">2.30349087715149</t>
   </si>
   <si>
     <t xml:space="preserve">2.29667544364929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28815698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21659874916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23874759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21489453315735</t>
+    <t xml:space="preserve">2.28815674781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21659851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2387478351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21489524841309</t>
   </si>
   <si>
     <t xml:space="preserve">2.25748920440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24556255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23193264007568</t>
+    <t xml:space="preserve">2.24556279182434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23193216323853</t>
   </si>
   <si>
     <t xml:space="preserve">2.18933820724487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26260042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22511720657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23363614082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23022866249084</t>
+    <t xml:space="preserve">2.26260018348694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22511744499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23363637924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23022842407227</t>
   </si>
   <si>
     <t xml:space="preserve">2.20637583732605</t>
@@ -974,22 +974,22 @@
     <t xml:space="preserve">2.29156422615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39379024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41934633255005</t>
+    <t xml:space="preserve">2.39379000663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41934657096863</t>
   </si>
   <si>
     <t xml:space="preserve">2.53009128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57268571853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54712915420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58120465278625</t>
+    <t xml:space="preserve">2.5726854801178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5471293926239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58120393753052</t>
   </si>
   <si>
     <t xml:space="preserve">2.50453495979309</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">2.47045946121216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46194076538086</t>
+    <t xml:space="preserve">2.46194124221802</t>
   </si>
   <si>
     <t xml:space="preserve">2.3852710723877</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">2.41082787513733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30008339881897</t>
+    <t xml:space="preserve">2.30008316040039</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342206954956</t>
@@ -1019,37 +1019,37 @@
     <t xml:space="preserve">2.61527967453003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64935493469238</t>
+    <t xml:space="preserve">2.6493546962738</t>
   </si>
   <si>
     <t xml:space="preserve">2.65787386894226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43638396263123</t>
+    <t xml:space="preserve">2.43638443946838</t>
   </si>
   <si>
     <t xml:space="preserve">2.52157258987427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53861045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55564785003662</t>
+    <t xml:space="preserve">2.53861021995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55564761161804</t>
   </si>
   <si>
     <t xml:space="preserve">2.48749732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4449028968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26600813865662</t>
+    <t xml:space="preserve">2.44490265846252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26600790023804</t>
   </si>
   <si>
     <t xml:space="preserve">2.14674401283264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19671010971069</t>
+    <t xml:space="preserve">2.19671058654785</t>
   </si>
   <si>
     <t xml:space="preserve">2.11856651306152</t>
@@ -1061,79 +1061,76 @@
     <t xml:space="preserve">2.29221963882446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25748872756958</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.24880599975586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2661714553833</t>
+    <t xml:space="preserve">2.26617121696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.27485418319702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34431576728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35299825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3009021282196</t>
+    <t xml:space="preserve">2.34431552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35299801826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30090236663818</t>
   </si>
   <si>
     <t xml:space="preserve">2.30958485603333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32694983482361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28353691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21407604217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17934513092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20539307594299</t>
+    <t xml:space="preserve">2.32695007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28353714942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21407556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17934489250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20539283752441</t>
   </si>
   <si>
     <t xml:space="preserve">2.15329694747925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13593196868896</t>
+    <t xml:space="preserve">2.13593173027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.10988402366638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18802785873413</t>
+    <t xml:space="preserve">2.18802738189697</t>
   </si>
   <si>
     <t xml:space="preserve">2.09251856803894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2227578163147</t>
+    <t xml:space="preserve">2.22275853157043</t>
   </si>
   <si>
     <t xml:space="preserve">2.07515358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08383584022522</t>
+    <t xml:space="preserve">2.0838360786438</t>
   </si>
   <si>
     <t xml:space="preserve">2.10120129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0404224395752</t>
+    <t xml:space="preserve">2.04042267799377</t>
   </si>
   <si>
     <t xml:space="preserve">2.01437449455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05778765678406</t>
+    <t xml:space="preserve">2.05778789520264</t>
   </si>
   <si>
     <t xml:space="preserve">2.06647062301636</t>
@@ -1142,22 +1139,22 @@
     <t xml:space="preserve">1.99700927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00569224357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964417934418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96227872371674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02305722236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0491054058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03173995018005</t>
+    <t xml:space="preserve">2.00569200515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964429855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96227884292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02305769920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04910516738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03173971176147</t>
   </si>
   <si>
     <t xml:space="preserve">1.93623101711273</t>
@@ -1166,19 +1163,19 @@
     <t xml:space="preserve">1.87545228004456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89281761646271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82335638999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81467354297638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77994310855865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71916472911835</t>
+    <t xml:space="preserve">1.89281797409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82335650920868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81467366218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77994322776794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71916460990906</t>
   </si>
   <si>
     <t xml:space="preserve">1.69311666488647</t>
@@ -1190,10 +1187,10 @@
     <t xml:space="preserve">1.63233816623688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67575132846832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68443417549133</t>
+    <t xml:space="preserve">1.67575144767761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68443405628204</t>
   </si>
   <si>
     <t xml:space="preserve">1.71048200130463</t>
@@ -1205,16 +1202,16 @@
     <t xml:space="preserve">1.71482336521149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69745814800262</t>
+    <t xml:space="preserve">1.69745802879333</t>
   </si>
   <si>
     <t xml:space="preserve">1.64536213874817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59760761260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60629034042358</t>
+    <t xml:space="preserve">1.59760749340057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60629022121429</t>
   </si>
   <si>
     <t xml:space="preserve">1.61931419372559</t>
@@ -1226,7 +1223,7 @@
     <t xml:space="preserve">1.63667941093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64970338344574</t>
+    <t xml:space="preserve">1.64970326423645</t>
   </si>
   <si>
     <t xml:space="preserve">1.68009269237518</t>
@@ -1241,34 +1238,34 @@
     <t xml:space="preserve">1.67140996456146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66706871986389</t>
+    <t xml:space="preserve">1.6670686006546</t>
   </si>
   <si>
     <t xml:space="preserve">1.57155954837799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52814650535583</t>
+    <t xml:space="preserve">1.52814626693726</t>
   </si>
   <si>
     <t xml:space="preserve">1.51078104972839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54551148414612</t>
+    <t xml:space="preserve">1.54551160335541</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6540447473526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66272735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72784721851349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7625777721405</t>
+    <t xml:space="preserve">1.65404486656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66272747516632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7278470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76257801055908</t>
   </si>
   <si>
     <t xml:space="preserve">1.75389528274536</t>
@@ -1277,7 +1274,7 @@
     <t xml:space="preserve">1.78862583637238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80599105358124</t>
+    <t xml:space="preserve">1.80599117279053</t>
   </si>
   <si>
     <t xml:space="preserve">1.77126049995422</t>
@@ -1286,13 +1283,13 @@
     <t xml:space="preserve">1.74521267414093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83203899860382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7973085641861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84072160720825</t>
+    <t xml:space="preserve">1.83203887939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79730844497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84072184562683</t>
   </si>
   <si>
     <t xml:space="preserve">1.86676979064941</t>
@@ -1301,7 +1298,7 @@
     <t xml:space="preserve">1.91018307209015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359635353088</t>
+    <t xml:space="preserve">1.95359623432159</t>
   </si>
   <si>
     <t xml:space="preserve">1.94491350650787</t>
@@ -1310,45 +1307,48 @@
     <t xml:space="preserve">1.98832666873932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97096157073975</t>
+    <t xml:space="preserve">1.97096121311188</t>
   </si>
   <si>
     <t xml:space="preserve">1.91886556148529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92754817008972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85808718204498</t>
+    <t xml:space="preserve">1.92754805088043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8580869436264</t>
   </si>
   <si>
     <t xml:space="preserve">1.84940457344055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88413500785828</t>
+    <t xml:space="preserve">1.88413488864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62365543842316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6504191160202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61919498443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60135233402252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61027383804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63703727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6548798084259</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6504191160202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61919510364532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6013525724411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61027371883392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63703727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65487957000732</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.6459584236145</t>
   </si>
   <si>
@@ -1367,43 +1367,43 @@
     <t xml:space="preserve">1.68164312839508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63257682323456</t>
+    <t xml:space="preserve">1.63257670402527</t>
   </si>
   <si>
     <t xml:space="preserve">1.60581314563751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62811625003815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61473441123962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58351027965546</t>
+    <t xml:space="preserve">1.62811613082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61473429203033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58351016044617</t>
   </si>
   <si>
     <t xml:space="preserve">1.57904970645905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55228614807129</t>
+    <t xml:space="preserve">1.552286028862</t>
   </si>
   <si>
     <t xml:space="preserve">1.54336476325989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59243130683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56120717525482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53890419006348</t>
+    <t xml:space="preserve">1.59243142604828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56120729446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53890442848206</t>
   </si>
   <si>
     <t xml:space="preserve">1.55674660205841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57012856006622</t>
+    <t xml:space="preserve">1.57012832164764</t>
   </si>
   <si>
     <t xml:space="preserve">1.58797073364258</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">1.59689199924469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53444385528564</t>
+    <t xml:space="preserve">1.53444373607635</t>
   </si>
   <si>
     <t xml:space="preserve">1.66380083560944</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">1.52552247047424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50768005847931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738962173462</t>
+    <t xml:space="preserve">1.5076801776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738950252533</t>
   </si>
   <si>
     <t xml:space="preserve">1.51660144329071</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">1.48983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34263813495636</t>
+    <t xml:space="preserve">1.34263825416565</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709882736206</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">1.19097805023193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2668080329895</t>
+    <t xml:space="preserve">1.26680815219879</t>
   </si>
   <si>
     <t xml:space="preserve">1.24450528621674</t>
@@ -1463,22 +1463,22 @@
     <t xml:space="preserve">1.29803240299225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20436000823975</t>
+    <t xml:space="preserve">1.20435988903046</t>
   </si>
   <si>
     <t xml:space="preserve">1.27572929859161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28465044498444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30695343017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30249285697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36940181255341</t>
+    <t xml:space="preserve">1.28465056419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30695331096649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30249297618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36940169334412</t>
   </si>
   <si>
     <t xml:space="preserve">1.36494112014771</t>
@@ -1487,25 +1487,25 @@
     <t xml:space="preserve">1.35602009296417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36048054695129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40508663654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44969236850739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4541529417038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44523191452026</t>
+    <t xml:space="preserve">1.36048066616058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40508675575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44969248771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45415306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44523179531097</t>
   </si>
   <si>
     <t xml:space="preserve">1.43631076812744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41846835613251</t>
+    <t xml:space="preserve">1.41846823692322</t>
   </si>
   <si>
     <t xml:space="preserve">1.46307420730591</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">1.38278353214264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33817768096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35155940055847</t>
+    <t xml:space="preserve">1.38724398612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33817756175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35155928134918</t>
   </si>
   <si>
     <t xml:space="preserve">1.29357171058655</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">1.32925641536713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33371710777283</t>
+    <t xml:space="preserve">1.33371722698212</t>
   </si>
   <si>
     <t xml:space="preserve">1.31587469577789</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">1.3203352689743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28018987178802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40954720973969</t>
+    <t xml:space="preserve">1.28018975257874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4095470905304</t>
   </si>
   <si>
     <t xml:space="preserve">1.39616537094116</t>
@@ -1565,34 +1565,34 @@
     <t xml:space="preserve">1.45861351490021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37832283973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42292892932892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28911101818085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27126860618591</t>
+    <t xml:space="preserve">1.37832295894623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42292881011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28911125659943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2712687253952</t>
   </si>
   <si>
     <t xml:space="preserve">1.26234757900238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24896574020386</t>
+    <t xml:space="preserve">1.24896562099457</t>
   </si>
   <si>
     <t xml:space="preserve">1.46753478050232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44077134132385</t>
+    <t xml:space="preserve">1.44077122211456</t>
   </si>
   <si>
     <t xml:space="preserve">1.48091650009155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49429821968079</t>
+    <t xml:space="preserve">1.49429833889008</t>
   </si>
   <si>
     <t xml:space="preserve">1.5032194852829</t>
@@ -1601,19 +1601,19 @@
     <t xml:space="preserve">1.52998304367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49875903129578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51214075088501</t>
+    <t xml:space="preserve">1.49875891208649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51214063167572</t>
   </si>
   <si>
     <t xml:space="preserve">1.48537719249725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52106189727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72178840637207</t>
+    <t xml:space="preserve">1.52106201648712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72178864479065</t>
   </si>
   <si>
     <t xml:space="preserve">1.76639449596405</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">1.73963093757629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81992161273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87344861030579</t>
+    <t xml:space="preserve">1.81992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87344872951508</t>
   </si>
   <si>
     <t xml:space="preserve">1.82884275913239</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">1.83776390552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77531564235687</t>
+    <t xml:space="preserve">1.78423678874969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77531552314758</t>
   </si>
   <si>
     <t xml:space="preserve">1.73517036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085506916046</t>
+    <t xml:space="preserve">1.77085518836975</t>
   </si>
   <si>
     <t xml:space="preserve">1.72624909877777</t>
@@ -1661,73 +1661,73 @@
     <t xml:space="preserve">1.71732783317566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74409162998199</t>
+    <t xml:space="preserve">1.74409151077271</t>
   </si>
   <si>
     <t xml:space="preserve">1.77977633476257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81100034713745</t>
+    <t xml:space="preserve">1.81100046634674</t>
   </si>
   <si>
     <t xml:space="preserve">1.84668505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86452722549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80207931995392</t>
+    <t xml:space="preserve">1.86452734470367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80207920074463</t>
   </si>
   <si>
     <t xml:space="preserve">1.75747334957123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03402996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0251088142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96266055107117</t>
+    <t xml:space="preserve">2.0340301990509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02510857582092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96266067028046</t>
   </si>
   <si>
     <t xml:space="preserve">1.9269757270813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050284385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07863593101501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10539960861206</t>
+    <t xml:space="preserve">1.98050272464752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07863616943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10539937019348</t>
   </si>
   <si>
     <t xml:space="preserve">2.05187225341797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06079363822937</t>
+    <t xml:space="preserve">2.06079339981079</t>
   </si>
   <si>
     <t xml:space="preserve">2.09647822380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43548345565796</t>
+    <t xml:space="preserve">2.43548321723938</t>
   </si>
   <si>
     <t xml:space="preserve">2.46224689483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39087748527527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56037974357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60498571395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65005493164062</t>
+    <t xml:space="preserve">2.39087724685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56037950515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60498595237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6500551700592</t>
   </si>
   <si>
     <t xml:space="preserve">2.61399960517883</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">2.73117876052856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90244078636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10074424743652</t>
+    <t xml:space="preserve">2.90244102478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1007444858551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99257874488831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92948269844055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84835815429688</t>
+    <t xml:space="preserve">2.92948246002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84835839271545</t>
   </si>
   <si>
     <t xml:space="preserve">2.76723408699036</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">2.83934450149536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87539935112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82131695747375</t>
+    <t xml:space="preserve">2.87539958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82131671905518</t>
   </si>
   <si>
     <t xml:space="preserve">2.77624773979187</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">2.53287553787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60498595237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58695793151855</t>
+    <t xml:space="preserve">2.6049861907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58695816993713</t>
   </si>
   <si>
     <t xml:space="preserve">2.65906858444214</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">2.67709636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52386164665222</t>
+    <t xml:space="preserve">2.52386140823364</t>
   </si>
   <si>
     <t xml:space="preserve">2.62301349639893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57794427871704</t>
+    <t xml:space="preserve">2.57794451713562</t>
   </si>
   <si>
     <t xml:space="preserve">2.59597182273865</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">2.51484799385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56893062591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79427552223206</t>
+    <t xml:space="preserve">2.56893038749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79427528381348</t>
   </si>
   <si>
     <t xml:space="preserve">2.83033084869385</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">3.0015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09173059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96553754806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93849635124207</t>
+    <t xml:space="preserve">3.09173035621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96553730964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93849611282349</t>
   </si>
   <si>
     <t xml:space="preserve">2.81230306625366</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">2.47879266738892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63202714920044</t>
+    <t xml:space="preserve">2.63202738761902</t>
   </si>
   <si>
     <t xml:space="preserve">2.91145467758179</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">2.9745512008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95652389526367</t>
+    <t xml:space="preserve">2.95652365684509</t>
   </si>
   <si>
     <t xml:space="preserve">3.01060628890991</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">2.92046856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85737180709839</t>
+    <t xml:space="preserve">2.85737204551697</t>
   </si>
   <si>
     <t xml:space="preserve">2.75822019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68611001968384</t>
+    <t xml:space="preserve">2.68610978126526</t>
   </si>
   <si>
     <t xml:space="preserve">2.23542046546936</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">2.28048944473267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41569638252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3165442943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36161327362061</t>
+    <t xml:space="preserve">2.415696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31654453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36161351203918</t>
   </si>
   <si>
     <t xml:space="preserve">2.50583410263062</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">2.4427375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37964105606079</t>
+    <t xml:space="preserve">2.37964129447937</t>
   </si>
   <si>
     <t xml:space="preserve">2.37062740325928</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">2.32555818557739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29851698875427</t>
+    <t xml:space="preserve">2.29851675033569</t>
   </si>
   <si>
     <t xml:space="preserve">2.343585729599</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">2.24518537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18077421188354</t>
+    <t xml:space="preserve">2.18077397346497</t>
   </si>
   <si>
     <t xml:space="preserve">2.16237092018127</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">2.11636304855347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08875823020935</t>
+    <t xml:space="preserve">2.08875846862793</t>
   </si>
   <si>
     <t xml:space="preserve">2.07035541534424</t>
@@ -2009,31 +2009,31 @@
     <t xml:space="preserve">2.07955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09796023368835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13476634025574</t>
+    <t xml:space="preserve">2.09795999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13476610183716</t>
   </si>
   <si>
     <t xml:space="preserve">2.10716152191162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18997573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14396810531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12556457519531</t>
+    <t xml:space="preserve">2.18997597694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14396786689758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12556481361389</t>
   </si>
   <si>
     <t xml:space="preserve">1.99674272537231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96913802623749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95073473453522</t>
+    <t xml:space="preserve">1.9691379070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95073485374451</t>
   </si>
   <si>
     <t xml:space="preserve">2.00594425201416</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">1.93233156204224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91392827033997</t>
+    <t xml:space="preserve">1.91392838954926</t>
   </si>
   <si>
     <t xml:space="preserve">1.90472686290741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92312979698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94153308868408</t>
+    <t xml:space="preserve">1.9231299161911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94153296947479</t>
   </si>
   <si>
     <t xml:space="preserve">1.88632369041443</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">1.87712204456329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83111429214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80350947380066</t>
+    <t xml:space="preserve">1.83111417293549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271111965179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80350959300995</t>
   </si>
   <si>
     <t xml:space="preserve">1.79430794715881</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">1.8357150554657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82651340961456</t>
+    <t xml:space="preserve">1.82651352882385</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031581878662</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">2.02434754371643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31879806518555</t>
+    <t xml:space="preserve">2.31879782676697</t>
   </si>
   <si>
     <t xml:space="preserve">2.3740074634552</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">2.28199172019958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26358819007874</t>
+    <t xml:space="preserve">2.26358842849731</t>
   </si>
   <si>
     <t xml:space="preserve">2.30039477348328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27279019355774</t>
+    <t xml:space="preserve">2.27278995513916</t>
   </si>
   <si>
     <t xml:space="preserve">2.33720111846924</t>
@@ -19005,7 +19005,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G618" t="s">
-        <v>349</v>
+        <v>310</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19031,7 +19031,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G619" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19057,7 +19057,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G620" t="s">
-        <v>349</v>
+        <v>310</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19083,7 +19083,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G621" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19109,7 +19109,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19135,7 +19135,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G623" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19161,7 +19161,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G624" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19187,7 +19187,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G625" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19213,7 +19213,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G626" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G627" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19265,7 +19265,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G628" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19291,7 +19291,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G629" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19317,7 +19317,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G630" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19343,7 +19343,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G631" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19369,7 +19369,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G632" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19395,7 +19395,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G633" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19421,7 +19421,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G634" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19447,7 +19447,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G635" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19473,7 +19473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G636" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>349</v>
+        <v>310</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19525,7 +19525,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>349</v>
+        <v>310</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G639" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G640" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G641" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G642" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G644" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G645" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G646" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G649" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G655" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G656" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G657" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G658" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>349</v>
+        <v>310</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G660" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G661" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G662" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G663" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G665" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G666" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G667" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G668" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G670" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20383,7 +20383,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G671" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20409,7 +20409,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G672" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G673" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G674" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G675" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G676" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G677" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G678" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G680" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G682" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G684" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G685" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G686" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G687" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G688" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G690" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G691" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G692" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G693" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G694" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G695" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G697" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G698" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G699" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G700" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G702" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G703" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G704" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G706" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G707" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G708" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G709" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>1.875</v>
       </c>
       <c r="G710" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G711" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G712" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G713" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21501,7 +21501,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21527,7 +21527,7 @@
         <v>1.875</v>
       </c>
       <c r="G715" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G716" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G717" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G718" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G719" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G720" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G721" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G722" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21735,7 +21735,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G723" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21761,7 +21761,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G724" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G725" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G726" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21839,7 +21839,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G727" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G728" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G729" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21917,7 +21917,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G730" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G731" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G732" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G734" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G735" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G736" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G737" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G738" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G739" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G740" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G741" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G742" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G743" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G744" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G745" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G746" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G747" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G748" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G749" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G750" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G751" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G752" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G754" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G755" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G756" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G757" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G758" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G759" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G760" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G761" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G762" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G763" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G764" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G765" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G766" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G767" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G768" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G769" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G770" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G771" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G772" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G773" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G774" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G775" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G776" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G777" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G779" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G781" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G782" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G783" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G784" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G785" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G786" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G787" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G788" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G789" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G790" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G791" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G792" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G793" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G794" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G795" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G796" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G797" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G798" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G799" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G801" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G802" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G803" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G804" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G805" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G806" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>2.25</v>
       </c>
       <c r="G807" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>2.25</v>
       </c>
       <c r="G809" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>2.25</v>
       </c>
       <c r="G811" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G812" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G814" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G817" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G818" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G822" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G823" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G824" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G825" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>2.25</v>
       </c>
       <c r="G826" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G828" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G829" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>2.25</v>
       </c>
       <c r="G830" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G831" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G832" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G834" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G835" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G836" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G837" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G838" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G839" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G840" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G841" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G842" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G843" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G844" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G845" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G846" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G847" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G848" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G850" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G851" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G852" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G853" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G854" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G855" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G856" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G857" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>1.875</v>
       </c>
       <c r="G858" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G859" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G860" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G861" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G862" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G863" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G864" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G865" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G866" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G867" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G868" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G869" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G872" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G873" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G875" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G876" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25895,7 +25895,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G883" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25921,7 +25921,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G884" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G887" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G889" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G893" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G900" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G905" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26935,7 +26935,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27039,7 +27039,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G927" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G928" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G933" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27481,7 +27481,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G944" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28001,7 +28001,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G964" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28027,7 +28027,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G965" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28131,7 +28131,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G969" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G971" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28287,7 +28287,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G975" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28313,7 +28313,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G976" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28443,7 +28443,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G981" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G982" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28495,7 +28495,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G983" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28807,7 +28807,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G995" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28833,7 +28833,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G996" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28859,7 +28859,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G997" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1000" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1001" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1003" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29067,7 +29067,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1005" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1006" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29171,7 +29171,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1009" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29431,7 +29431,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1019" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -36737,7 +36737,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1300" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -67815,7 +67815,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6424421296</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>4348</v>
@@ -67836,6 +67836,32 @@
         <v>858</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.431087963</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>4113</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>2.17000007629395</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>859</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="864">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538791179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69254732131958</t>
+    <t xml:space="preserve">1.74538779258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69254720211029</t>
   </si>
   <si>
     <t xml:space="preserve">1.70245492458344</t>
@@ -56,37 +56,37 @@
     <t xml:space="preserve">1.68429100513458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67603480815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66612696647644</t>
+    <t xml:space="preserve">1.67603468894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66612708568573</t>
   </si>
   <si>
     <t xml:space="preserve">1.63888120651245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61163544654846</t>
+    <t xml:space="preserve">1.61163532733917</t>
   </si>
   <si>
     <t xml:space="preserve">1.59347128868103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48613917827606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59264576435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59182000160217</t>
+    <t xml:space="preserve">1.48613905906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59182024002075</t>
   </si>
   <si>
     <t xml:space="preserve">1.58604073524475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172784328461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521509170532</t>
+    <t xml:space="preserve">1.60172772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521485328674</t>
   </si>
   <si>
     <t xml:space="preserve">1.56044602394104</t>
@@ -95,40 +95,40 @@
     <t xml:space="preserve">1.51255941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53980529308319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5654000043869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53567707538605</t>
+    <t xml:space="preserve">1.53980541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56539988517761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53567719459534</t>
   </si>
   <si>
     <t xml:space="preserve">1.45311379432678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50595414638519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46137011051178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44238066673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51833868026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65126574039459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63475298881531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65621948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64300930500031</t>
+    <t xml:space="preserve">1.50595438480377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46136999130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4423805475235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51833891868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6512656211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6347531080246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65621960163116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64300942420959</t>
   </si>
   <si>
     <t xml:space="preserve">1.63722991943359</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">1.60503017902374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59842526912689</t>
+    <t xml:space="preserve">1.5984251499176</t>
   </si>
   <si>
     <t xml:space="preserve">1.56870234012604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6405326128006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227617740631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60255336761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57283067703247</t>
+    <t xml:space="preserve">1.64053249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227641582489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60255324840546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57283043861389</t>
   </si>
   <si>
     <t xml:space="preserve">1.58934330940247</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">1.55714344978333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53402602672577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54310750961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466675758362</t>
+    <t xml:space="preserve">1.53402578830719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54310762882233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466663837433</t>
   </si>
   <si>
     <t xml:space="preserve">1.5596204996109</t>
@@ -194,31 +194,31 @@
     <t xml:space="preserve">1.55053853988647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50265192985535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696482181549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237450122833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49026715755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51503622531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779058456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623145580292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50760567188263</t>
+    <t xml:space="preserve">1.50265181064606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4869647026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861575126648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237462043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49026727676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5150363445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779046535492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4762316942215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50760555267334</t>
   </si>
   <si>
     <t xml:space="preserve">1.50100040435791</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">1.49439549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48366248607635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45971894264221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45299983024597</t>
+    <t xml:space="preserve">1.48366224765778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45971882343292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45299971103668</t>
   </si>
   <si>
     <t xml:space="preserve">1.46223855018616</t>
@@ -242,34 +242,34 @@
     <t xml:space="preserve">1.43284261226654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4353621006012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43200278282166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42612338066101</t>
+    <t xml:space="preserve">1.43536221981049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43200266361237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4261234998703</t>
   </si>
   <si>
     <t xml:space="preserve">1.41100549697876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44040143489838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43620216846466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44292116165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44880044460297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.478196144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460105895996</t>
+    <t xml:space="preserve">1.44040155410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43620204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4429212808609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44880032539368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47819626331329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460093975067</t>
   </si>
   <si>
     <t xml:space="preserve">1.42360401153564</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">1.43032288551331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139872074127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40260672569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4084860086441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37825012207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42444372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41604495048523</t>
+    <t xml:space="preserve">1.46139860153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40260660648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40848588943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37825000286102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42444384098053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41604483127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.46979749202728</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">1.42192399501801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47567653656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44796049594879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735643386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43368232250214</t>
+    <t xml:space="preserve">1.47567677497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4479603767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735631465912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43368244171143</t>
   </si>
   <si>
     <t xml:space="preserve">1.45803904533386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45216000080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48491537570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46391820907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46643793582916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46895778179169</t>
+    <t xml:space="preserve">1.4521598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48491525650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46391808986664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46643805503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46895754337311</t>
   </si>
   <si>
     <t xml:space="preserve">1.48575520515442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45887887477875</t>
+    <t xml:space="preserve">1.45887899398804</t>
   </si>
   <si>
     <t xml:space="preserve">1.4563592672348</t>
@@ -350,37 +350,37 @@
     <t xml:space="preserve">1.48827493190765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43956160545349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47399699687958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46727788448334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49835360050201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50927209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5033928155899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4949939250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48743498325348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51011180877686</t>
+    <t xml:space="preserve">1.4395614862442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47399687767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46727776527405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4983537197113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50927197933197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50339293479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49499380588531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48743510246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51011204719543</t>
   </si>
   <si>
     <t xml:space="preserve">1.49919331073761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179170608521</t>
+    <t xml:space="preserve">1.51179158687592</t>
   </si>
   <si>
     <t xml:space="preserve">1.45048022270203</t>
@@ -389,46 +389,46 @@
     <t xml:space="preserve">1.44628059864044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43872165679932</t>
+    <t xml:space="preserve">1.4387218952179</t>
   </si>
   <si>
     <t xml:space="preserve">1.50003325939178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48071575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4815559387207</t>
+    <t xml:space="preserve">1.48071587085724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48155581951141</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095175743103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49583411216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50759220123291</t>
+    <t xml:space="preserve">1.49583387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5075923204422</t>
   </si>
   <si>
     <t xml:space="preserve">1.49667382240295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47231721878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49331438541412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147738933563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50087320804596</t>
+    <t xml:space="preserve">1.47231709957123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49331426620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147727012634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50087296962738</t>
   </si>
   <si>
     <t xml:space="preserve">1.52774941921234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53194880485535</t>
+    <t xml:space="preserve">1.53194904327393</t>
   </si>
   <si>
     <t xml:space="preserve">1.52690958976746</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">1.52355003356934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50423264503479</t>
+    <t xml:space="preserve">1.50423276424408</t>
   </si>
   <si>
     <t xml:space="preserve">1.51263165473938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454720020294</t>
+    <t xml:space="preserve">1.54454731941223</t>
   </si>
   <si>
     <t xml:space="preserve">1.54538702964783</t>
@@ -455,40 +455,40 @@
     <t xml:space="preserve">1.52019047737122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50843214988708</t>
+    <t xml:space="preserve">1.50843238830566</t>
   </si>
   <si>
     <t xml:space="preserve">1.59578013420105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53446865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56050503253937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53026902675629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53110885620117</t>
+    <t xml:space="preserve">1.53446853160858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56050491333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53026914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53110909461975</t>
   </si>
   <si>
     <t xml:space="preserve">1.55126631259918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55210602283478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55378580093384</t>
+    <t xml:space="preserve">1.55210614204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55378592014313</t>
   </si>
   <si>
     <t xml:space="preserve">1.58654141426086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56218469142914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56974351406097</t>
+    <t xml:space="preserve">1.56218457221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56974363327026</t>
   </si>
   <si>
     <t xml:space="preserve">1.57058358192444</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">1.60333907604218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54958641529083</t>
+    <t xml:space="preserve">1.54958653450012</t>
   </si>
   <si>
     <t xml:space="preserve">1.55798518657684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57142341136932</t>
+    <t xml:space="preserve">1.5714236497879</t>
   </si>
   <si>
     <t xml:space="preserve">1.56470441818237</t>
@@ -512,40 +512,40 @@
     <t xml:space="preserve">1.6108980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61173796653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60417902469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62517607212067</t>
+    <t xml:space="preserve">1.61173784732819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60417890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62517595291138</t>
   </si>
   <si>
     <t xml:space="preserve">1.62097656726837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61257791519165</t>
+    <t xml:space="preserve">1.61257779598236</t>
   </si>
   <si>
     <t xml:space="preserve">1.59326040744781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58822119235992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60753858089447</t>
+    <t xml:space="preserve">1.58822107315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60753846168518</t>
   </si>
   <si>
     <t xml:space="preserve">1.63105535507202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61425757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71504366397858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77215576171875</t>
+    <t xml:space="preserve">1.61425769329071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71504378318787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77215564250946</t>
   </si>
   <si>
     <t xml:space="preserve">1.7654367685318</t>
@@ -560,31 +560,31 @@
     <t xml:space="preserve">1.74527966976166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72176277637482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70664477348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73856019973755</t>
+    <t xml:space="preserve">1.72176265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70664489269257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73856008052826</t>
   </si>
   <si>
     <t xml:space="preserve">1.69992566108704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67892861366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69656622409821</t>
+    <t xml:space="preserve">1.67892849445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69656610488892</t>
   </si>
   <si>
     <t xml:space="preserve">1.69320666790009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70496511459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77383553981781</t>
+    <t xml:space="preserve">1.70496487617493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77383577823639</t>
   </si>
   <si>
     <t xml:space="preserve">1.75871765613556</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">1.68816733360291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71336388587952</t>
+    <t xml:space="preserve">1.71336400508881</t>
   </si>
   <si>
     <t xml:space="preserve">1.73184132575989</t>
@@ -614,79 +614,79 @@
     <t xml:space="preserve">1.7100043296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71672344207764</t>
+    <t xml:space="preserve">1.71672356128693</t>
   </si>
   <si>
     <t xml:space="preserve">1.73016154766083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047598361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375675201416</t>
+    <t xml:space="preserve">1.74695909023285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77047574520111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375687122345</t>
   </si>
   <si>
     <t xml:space="preserve">1.75031888484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78895354270935</t>
+    <t xml:space="preserve">1.78895366191864</t>
   </si>
   <si>
     <t xml:space="preserve">1.74024033546448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76207709312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73352110385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78055453300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254886627197</t>
+    <t xml:space="preserve">1.76207733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73352098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903209209442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78055441379547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254898548126</t>
   </si>
   <si>
     <t xml:space="preserve">1.86958253383636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86454284191132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84774529933929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391432762146</t>
+    <t xml:space="preserve">1.8645430803299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84774541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391420841217</t>
   </si>
   <si>
     <t xml:space="preserve">1.90480959415436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98488664627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34267711639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35119605064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24045133590698</t>
+    <t xml:space="preserve">1.98488640785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34267735481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3511962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2404510974884</t>
   </si>
   <si>
     <t xml:space="preserve">2.18081951141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36482620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32223200798035</t>
+    <t xml:space="preserve">2.364825963974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32223224639893</t>
   </si>
   <si>
     <t xml:space="preserve">2.34608483314514</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">2.33415818214417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24897027015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20296835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14163279533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07007455825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01896190643311</t>
+    <t xml:space="preserve">2.2489697933197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20296859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14163303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07007479667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01896166801453</t>
   </si>
   <si>
     <t xml:space="preserve">1.95933020114899</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">2.01044297218323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496334075928</t>
+    <t xml:space="preserve">2.06496357917786</t>
   </si>
   <si>
     <t xml:space="preserve">2.00192427635193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02407312393188</t>
+    <t xml:space="preserve">2.02407288551331</t>
   </si>
   <si>
     <t xml:space="preserve">2.06155633926392</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">2.04451823234558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06837105751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303740501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111051559448</t>
+    <t xml:space="preserve">2.0683708190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303716659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04111075401306</t>
   </si>
   <si>
     <t xml:space="preserve">1.97977519035339</t>
@@ -746,43 +746,43 @@
     <t xml:space="preserve">1.99340534210205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97636783123016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97125601768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466385364532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95081114768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93888521194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92525470256805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9269585609436</t>
+    <t xml:space="preserve">1.97636759281158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97125625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97466433048248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9508113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93888485431671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92525482177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92695844173431</t>
   </si>
   <si>
     <t xml:space="preserve">1.94229233264923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95762634277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718087673187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866230010986</t>
+    <t xml:space="preserve">1.95762658119202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718075752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866218090057</t>
   </si>
   <si>
     <t xml:space="preserve">1.97295999526978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00703525543213</t>
+    <t xml:space="preserve">2.00703573226929</t>
   </si>
   <si>
     <t xml:space="preserve">2.01555418968201</t>
@@ -791,46 +791,46 @@
     <t xml:space="preserve">1.98829400539398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93206965923309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673564910889</t>
+    <t xml:space="preserve">1.93206977844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673576831818</t>
   </si>
   <si>
     <t xml:space="preserve">1.91332828998566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9082168340683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93377327919006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94058859348297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822507858276</t>
+    <t xml:space="preserve">1.90821695327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93377375602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94058871269226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822555541992</t>
   </si>
   <si>
     <t xml:space="preserve">2.2557852268219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22341370582581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3597149848938</t>
+    <t xml:space="preserve">2.22341346740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35971474647522</t>
   </si>
   <si>
     <t xml:space="preserve">2.27452635765076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41593933105469</t>
+    <t xml:space="preserve">2.41593885421753</t>
   </si>
   <si>
     <t xml:space="preserve">2.41253161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3682336807251</t>
+    <t xml:space="preserve">2.36823391914368</t>
   </si>
   <si>
     <t xml:space="preserve">2.30860161781311</t>
@@ -839,70 +839,70 @@
     <t xml:space="preserve">2.31200933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31541705131531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28986048698425</t>
+    <t xml:space="preserve">2.31541728973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28986072540283</t>
   </si>
   <si>
     <t xml:space="preserve">2.42445802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41423559188843</t>
+    <t xml:space="preserve">2.41423535346985</t>
   </si>
   <si>
     <t xml:space="preserve">2.36993741989136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39719748497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35801124572754</t>
+    <t xml:space="preserve">2.39719772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35801100730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.30519437789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32052850723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32904696464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31882452964783</t>
+    <t xml:space="preserve">2.32052826881409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32904720306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31882429122925</t>
   </si>
   <si>
     <t xml:space="preserve">2.3477885723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36312198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3443808555603</t>
+    <t xml:space="preserve">2.36312246322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
     <t xml:space="preserve">2.32563924789429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3392698764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36652994155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37675261497498</t>
+    <t xml:space="preserve">2.33927011489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36653017997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3767523765564</t>
   </si>
   <si>
     <t xml:space="preserve">2.38356757164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27111887931824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25408124923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09392762184143</t>
+    <t xml:space="preserve">2.27111911773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25408148765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09392738342285</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696692466736</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">2.10585379600525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10414981842041</t>
+    <t xml:space="preserve">2.10415005683899</t>
   </si>
   <si>
     <t xml:space="preserve">2.12800264358521</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">2.31712079048157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28304553031921</t>
+    <t xml:space="preserve">2.28304529190063</t>
   </si>
   <si>
     <t xml:space="preserve">2.30349063873291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29667568206787</t>
+    <t xml:space="preserve">2.29667544364929</t>
   </si>
   <si>
     <t xml:space="preserve">2.28815698623657</t>
@@ -935,31 +935,31 @@
     <t xml:space="preserve">2.21659827232361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23874711990356</t>
+    <t xml:space="preserve">2.23874759674072</t>
   </si>
   <si>
     <t xml:space="preserve">2.21489500999451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25748896598816</t>
+    <t xml:space="preserve">2.25748920440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.24556255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23193216323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933844566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26260018348694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22511720657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23363590240479</t>
+    <t xml:space="preserve">2.2319324016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933820724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26260042190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22511696815491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23363637924194</t>
   </si>
   <si>
     <t xml:space="preserve">2.23022866249084</t>
@@ -968,40 +968,40 @@
     <t xml:space="preserve">2.20637607574463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29156398773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39379048347473</t>
+    <t xml:space="preserve">2.29156446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39379024505615</t>
   </si>
   <si>
     <t xml:space="preserve">2.41934680938721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53009128570557</t>
+    <t xml:space="preserve">2.53009152412415</t>
   </si>
   <si>
     <t xml:space="preserve">2.5726854801178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54712915420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58120465278625</t>
+    <t xml:space="preserve">2.54712891578674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58120393753052</t>
   </si>
   <si>
     <t xml:space="preserve">2.50453495979309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47045969963074</t>
+    <t xml:space="preserve">2.47045993804932</t>
   </si>
   <si>
     <t xml:space="preserve">2.46194100379944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38527154922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41082787513733</t>
+    <t xml:space="preserve">2.38527131080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41082811355591</t>
   </si>
   <si>
     <t xml:space="preserve">2.30008292198181</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">2.60676074028015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61527967453003</t>
+    <t xml:space="preserve">2.61527943611145</t>
   </si>
   <si>
     <t xml:space="preserve">2.64935493469238</t>
@@ -1022,40 +1022,40 @@
     <t xml:space="preserve">2.65787363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43638396263123</t>
+    <t xml:space="preserve">2.4363842010498</t>
   </si>
   <si>
     <t xml:space="preserve">2.52157282829285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53860998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55564785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48749732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4449028968811</t>
+    <t xml:space="preserve">2.53861021995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55564761161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48749756813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44490313529968</t>
   </si>
   <si>
     <t xml:space="preserve">2.26600790023804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14674425125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671034812927</t>
+    <t xml:space="preserve">2.1467444896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671058654785</t>
   </si>
   <si>
     <t xml:space="preserve">2.11856651306152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17066240310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29221963882446</t>
+    <t xml:space="preserve">2.17066264152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29221940040588</t>
   </si>
   <si>
     <t xml:space="preserve">2.24880647659302</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">2.27485394477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34431529045105</t>
+    <t xml:space="preserve">2.34431505203247</t>
   </si>
   <si>
     <t xml:space="preserve">2.35299777984619</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">2.32695007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28353691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21407580375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17934489250183</t>
+    <t xml:space="preserve">2.28353667259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21407556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17934513092041</t>
   </si>
   <si>
     <t xml:space="preserve">2.20539283752441</t>
@@ -1100,61 +1100,61 @@
     <t xml:space="preserve">2.13593196868896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1098837852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18802762031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09251880645752</t>
+    <t xml:space="preserve">2.10988402366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18802785873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09251856803894</t>
   </si>
   <si>
     <t xml:space="preserve">2.22275829315186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07515358924866</t>
+    <t xml:space="preserve">2.07515335083008</t>
   </si>
   <si>
     <t xml:space="preserve">2.08383584022522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10120153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04042267799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01437497138977</t>
+    <t xml:space="preserve">2.10120129585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0404224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01437473297119</t>
   </si>
   <si>
     <t xml:space="preserve">2.05778813362122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06647086143494</t>
+    <t xml:space="preserve">2.06647062301636</t>
   </si>
   <si>
     <t xml:space="preserve">1.99700963497162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00569248199463</t>
+    <t xml:space="preserve">2.00569200515747</t>
   </si>
   <si>
     <t xml:space="preserve">1.97964406013489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96227872371674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02305746078491</t>
+    <t xml:space="preserve">1.96227896213531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02305722236633</t>
   </si>
   <si>
     <t xml:space="preserve">2.0491054058075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03173995018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93623065948486</t>
+    <t xml:space="preserve">2.03173971176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93623089790344</t>
   </si>
   <si>
     <t xml:space="preserve">1.87545239925385</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">1.89281761646271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82335615158081</t>
+    <t xml:space="preserve">1.8233562707901</t>
   </si>
   <si>
     <t xml:space="preserve">1.81467366218567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77994322776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71916460990906</t>
+    <t xml:space="preserve">1.77994310855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71916472911835</t>
   </si>
   <si>
     <t xml:space="preserve">1.69311678409576</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">1.67575144767761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68443417549133</t>
+    <t xml:space="preserve">1.68443405628204</t>
   </si>
   <si>
     <t xml:space="preserve">1.71048200130463</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">1.69745802879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64536213874817</t>
+    <t xml:space="preserve">1.64536201953888</t>
   </si>
   <si>
     <t xml:space="preserve">1.59760761260986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60628998279572</t>
+    <t xml:space="preserve">1.606290102005</t>
   </si>
   <si>
     <t xml:space="preserve">1.6193140745163</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">1.63667953014374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64970350265503</t>
+    <t xml:space="preserve">1.64970338344574</t>
   </si>
   <si>
     <t xml:space="preserve">1.68009269237518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65838623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70179927349091</t>
+    <t xml:space="preserve">1.65838611125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7017993927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.67141008377075</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">1.51078104972839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54551160335541</t>
+    <t xml:space="preserve">1.54551148414612</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287693977356</t>
@@ -1259,16 +1259,16 @@
     <t xml:space="preserve">1.66272735595703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7278470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76257789134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75389540195465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78862571716309</t>
+    <t xml:space="preserve">1.72784721851349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7625777721405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75389528274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7886255979538</t>
   </si>
   <si>
     <t xml:space="preserve">1.80599093437195</t>
@@ -1277,55 +1277,55 @@
     <t xml:space="preserve">1.77126049995422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74521267414093</t>
+    <t xml:space="preserve">1.74521255493164</t>
   </si>
   <si>
     <t xml:space="preserve">1.83203899860382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79730832576752</t>
+    <t xml:space="preserve">1.79730820655823</t>
   </si>
   <si>
     <t xml:space="preserve">1.84072160720825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86676979064941</t>
+    <t xml:space="preserve">1.86676967144012</t>
   </si>
   <si>
     <t xml:space="preserve">1.91018295288086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359599590302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94491326808929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98832654953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97096121311188</t>
+    <t xml:space="preserve">1.95359623432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94491350650787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98832678794861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97096168994904</t>
   </si>
   <si>
     <t xml:space="preserve">1.91886556148529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92754805088043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85808706283569</t>
+    <t xml:space="preserve">1.92754828929901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85808718204498</t>
   </si>
   <si>
     <t xml:space="preserve">1.84940445423126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88413500785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62365531921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65041899681091</t>
+    <t xml:space="preserve">1.88413488864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62365543842316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6504191160202</t>
   </si>
   <si>
     <t xml:space="preserve">1.61919498443604</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">1.60135245323181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61027371883392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63703727722168</t>
+    <t xml:space="preserve">1.61027383804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63703739643097</t>
   </si>
   <si>
     <t xml:space="preserve">1.65487957000732</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64595854282379</t>
+    <t xml:space="preserve">1.6459584236145</t>
   </si>
   <si>
     <t xml:space="preserve">1.64149785041809</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">1.65934014320374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66826128959656</t>
+    <t xml:space="preserve">1.66826140880585</t>
   </si>
   <si>
     <t xml:space="preserve">1.68610382080078</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">1.58351016044617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57904958724976</t>
+    <t xml:space="preserve">1.57904970645905</t>
   </si>
   <si>
     <t xml:space="preserve">1.552286028862</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">1.59243130683899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56120705604553</t>
+    <t xml:space="preserve">1.56120717525482</t>
   </si>
   <si>
     <t xml:space="preserve">1.53890442848206</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">1.57012832164764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58797085285187</t>
+    <t xml:space="preserve">1.58797073364258</t>
   </si>
   <si>
     <t xml:space="preserve">1.57458901405334</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">1.54782557487488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52552258968353</t>
+    <t xml:space="preserve">1.52552247047424</t>
   </si>
   <si>
     <t xml:space="preserve">1.50768029689789</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">1.42738950252533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51660144329071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48983776569366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34263825416565</t>
+    <t xml:space="preserve">1.51660132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48983764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34263813495636</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709870815277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32479584217072</t>
+    <t xml:space="preserve">1.32479596138</t>
   </si>
   <si>
     <t xml:space="preserve">1.19097805023193</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">1.24450528621674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29803228378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20435976982117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27572917938232</t>
+    <t xml:space="preserve">1.29803240299225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20435965061188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27572929859161</t>
   </si>
   <si>
     <t xml:space="preserve">1.28465068340302</t>
@@ -1472,22 +1472,22 @@
     <t xml:space="preserve">1.30695343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30249297618866</t>
+    <t xml:space="preserve">1.30249309539795</t>
   </si>
   <si>
     <t xml:space="preserve">1.36940169334412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36494123935699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35602009296417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36048066616058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40508651733398</t>
+    <t xml:space="preserve">1.36494112014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35601997375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36048054695129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40508663654327</t>
   </si>
   <si>
     <t xml:space="preserve">1.44969236850739</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">1.44523179531097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43631064891815</t>
+    <t xml:space="preserve">1.43631076812744</t>
   </si>
   <si>
     <t xml:space="preserve">1.41846823692322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46307420730591</t>
+    <t xml:space="preserve">1.4630743265152</t>
   </si>
   <si>
     <t xml:space="preserve">1.39170467853546</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">1.41400766372681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38278353214264</t>
+    <t xml:space="preserve">1.38278341293335</t>
   </si>
   <si>
     <t xml:space="preserve">1.38724398612976</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">1.33817756175995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35155951976776</t>
+    <t xml:space="preserve">1.35155928134918</t>
   </si>
   <si>
     <t xml:space="preserve">1.29357182979584</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">1.33371710777283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3158745765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37386226654053</t>
+    <t xml:space="preserve">1.31587469577789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37386238574982</t>
   </si>
   <si>
     <t xml:space="preserve">1.31141412258148</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">1.28018987178802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4095470905304</t>
+    <t xml:space="preserve">1.40954697132111</t>
   </si>
   <si>
     <t xml:space="preserve">1.39616537094116</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">1.42292881011963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28911113739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27126884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26234769821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24896585941315</t>
+    <t xml:space="preserve">1.28911125659943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2712687253952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26234757900238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24896574020386</t>
   </si>
   <si>
     <t xml:space="preserve">1.46753489971161</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">1.44077122211456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48091650009155</t>
+    <t xml:space="preserve">1.48091661930084</t>
   </si>
   <si>
     <t xml:space="preserve">1.49429833889008</t>
@@ -1613,43 +1613,43 @@
     <t xml:space="preserve">1.72178864479065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76639437675476</t>
+    <t xml:space="preserve">1.76639449596405</t>
   </si>
   <si>
     <t xml:space="preserve">1.73963105678558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81992161273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8734484910965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82884275913239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83776390552521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78423678874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77531552314758</t>
+    <t xml:space="preserve">1.81992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87344861030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8288426399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83776378631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78423690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77531564235687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73517036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085506916046</t>
+    <t xml:space="preserve">1.77085518836975</t>
   </si>
   <si>
     <t xml:space="preserve">1.72624909877777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73070991039276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74855208396912</t>
+    <t xml:space="preserve">1.73070979118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74855220317841</t>
   </si>
   <si>
     <t xml:space="preserve">1.79315805435181</t>
@@ -1661,28 +1661,28 @@
     <t xml:space="preserve">1.74409151077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77977621555328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81100046634674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84668493270874</t>
+    <t xml:space="preserve">1.77977633476257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81100034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84668481349945</t>
   </si>
   <si>
     <t xml:space="preserve">1.86452734470367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80207931995392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75747323036194</t>
+    <t xml:space="preserve">1.80207920074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75747334957123</t>
   </si>
   <si>
     <t xml:space="preserve">2.03402996063232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02510857582092</t>
+    <t xml:space="preserve">2.02510905265808</t>
   </si>
   <si>
     <t xml:space="preserve">1.96266067028046</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">1.9269757270813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050272464752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07863616943359</t>
+    <t xml:space="preserve">1.9805029630661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07863593101501</t>
   </si>
   <si>
     <t xml:space="preserve">2.10539937019348</t>
@@ -1703,16 +1703,16 @@
     <t xml:space="preserve">2.05187249183655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06079387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09647846221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4354829788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46224689483643</t>
+    <t xml:space="preserve">2.06079339981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09647822380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43548321723938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.462247133255</t>
   </si>
   <si>
     <t xml:space="preserve">2.39087724685669</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">2.56037974357605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60498595237732</t>
+    <t xml:space="preserve">2.6049861907959</t>
   </si>
   <si>
     <t xml:space="preserve">2.65005493164062</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">2.64104104042053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74019289016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78526139259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73117899894714</t>
+    <t xml:space="preserve">2.74019265174866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78526163101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73117876052856</t>
   </si>
   <si>
     <t xml:space="preserve">2.90244102478027</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">2.92948222160339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84835815429688</t>
+    <t xml:space="preserve">2.84835839271545</t>
   </si>
   <si>
     <t xml:space="preserve">2.76723408699036</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">2.77624773979187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72216534614563</t>
+    <t xml:space="preserve">2.72216510772705</t>
   </si>
   <si>
     <t xml:space="preserve">2.55991697311401</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">2.53287553787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58695816993713</t>
+    <t xml:space="preserve">2.58695840835571</t>
   </si>
   <si>
     <t xml:space="preserve">2.65906858444214</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.62301349639893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57794427871704</t>
+    <t xml:space="preserve">2.57794451713562</t>
   </si>
   <si>
     <t xml:space="preserve">2.59597206115723</t>
@@ -1808,16 +1808,16 @@
     <t xml:space="preserve">2.51484799385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56893062591553</t>
+    <t xml:space="preserve">2.56893038749695</t>
   </si>
   <si>
     <t xml:space="preserve">2.7942750453949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83033061027527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71315145492554</t>
+    <t xml:space="preserve">2.83033084869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71315121650696</t>
   </si>
   <si>
     <t xml:space="preserve">2.70413756370544</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">2.74920654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80328893661499</t>
+    <t xml:space="preserve">2.80328917503357</t>
   </si>
   <si>
     <t xml:space="preserve">2.86638569831848</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">2.96553754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93849635124207</t>
+    <t xml:space="preserve">2.93849611282349</t>
   </si>
   <si>
     <t xml:space="preserve">2.81230282783508</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">2.54188942909241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47879266738892</t>
+    <t xml:space="preserve">2.4787929058075</t>
   </si>
   <si>
     <t xml:space="preserve">2.63202738761902</t>
@@ -1886,19 +1886,19 @@
     <t xml:space="preserve">2.85737204551697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75822043418884</t>
+    <t xml:space="preserve">2.75822019577026</t>
   </si>
   <si>
     <t xml:space="preserve">2.68611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23542022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19035124778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28048920631409</t>
+    <t xml:space="preserve">2.23542046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19035148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28048944473267</t>
   </si>
   <si>
     <t xml:space="preserve">2.415696144104</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">2.36161351203918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50583410263062</t>
+    <t xml:space="preserve">2.50583434104919</t>
   </si>
   <si>
     <t xml:space="preserve">2.48780655860901</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">2.4427375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37964105606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37062740325928</t>
+    <t xml:space="preserve">2.37964129447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3706271648407</t>
   </si>
   <si>
     <t xml:space="preserve">2.27147555351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26246166229248</t>
+    <t xml:space="preserve">2.26246190071106</t>
   </si>
   <si>
     <t xml:space="preserve">2.28950309753418</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555818557739</t>
+    <t xml:space="preserve">2.32555794715881</t>
   </si>
   <si>
     <t xml:space="preserve">2.29851675033569</t>
@@ -1946,205 +1946,208 @@
     <t xml:space="preserve">2.343585729599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21739268302917</t>
+    <t xml:space="preserve">2.21739292144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20837903022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23598384857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21758079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24518537521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18077397346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16237092018127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19917750358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1715726852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11636304855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08875846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07035541534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01514577865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06115365028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04275059700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05195212364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97833967208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98754107952118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07955694198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09795999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13476610183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10716152191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18997597694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14396786689758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12556481361389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99674272537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9691379070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95073485374451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00594425201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93233156204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91392838954926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90472686290741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9231299161911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94153296947479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88632369041443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86792051792145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84951746463776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89552521705627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8587189912796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87712204456329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111417293549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271111965179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80350959300995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79430794715881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8357150554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82651352882385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84031581878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82191264629364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02434754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31879782676697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3740074634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39241051673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34640264511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29119324684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22678208351135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25438690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30959630012512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28199172019958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26358842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30039477348328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27278995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33720111846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15316939353943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23669123649597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1989414691925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18006634712219</t>
   </si>
   <si>
     <t xml:space="preserve">2.20837879180908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23598384857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21758079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24518537521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18077421188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16237092018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19917750358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17157244682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11636328697205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08875846862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07035517692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01514577865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06115388870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04275059700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05195212364197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97833943367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98754131793976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07955694198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09795999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13476634025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10716152191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18997597694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14396786689758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12556481361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99674272537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96913814544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95073461532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00594425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93233156204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91392838954926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90472686290741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92313015460968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94153308868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88632369041443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86792063713074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84951746463776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89552533626556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8587189912796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87712204456329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111417293549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271111965179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80350959300995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79430794715881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8357150554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82651340961456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84031581878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82191276550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02434754371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31879782676697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3740074634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39241027832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34640264511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29119324684143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22678208351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25438690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3095965385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28199172019958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26358842849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3003945350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27278995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33720088005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15316939353943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23669147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19894123077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18006634712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11400389671326</t>
+    <t xml:space="preserve">2.11400365829468</t>
   </si>
   <si>
     <t xml:space="preserve">2.09512877464294</t>
@@ -2159,25 +2162,25 @@
     <t xml:space="preserve">1.98187851905823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91581594944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94412851333618</t>
+    <t xml:space="preserve">1.91581583023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94412839412689</t>
   </si>
   <si>
     <t xml:space="preserve">1.93469095230103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00075340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03850388526917</t>
+    <t xml:space="preserve">2.00075364112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03850364685059</t>
   </si>
   <si>
     <t xml:space="preserve">2.0101912021637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01962876319885</t>
+    <t xml:space="preserve">2.01962852478027</t>
   </si>
   <si>
     <t xml:space="preserve">2.0573787689209</t>
@@ -2186,19 +2189,19 @@
     <t xml:space="preserve">2.16119122505188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17062902450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22725367546082</t>
+    <t xml:space="preserve">2.17062878608704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22725391387939</t>
   </si>
   <si>
     <t xml:space="preserve">2.24612903594971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26500391960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36881685256958</t>
+    <t xml:space="preserve">2.26500415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.368816614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.34994173049927</t>
@@ -2210,7 +2213,7 @@
     <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18950390815735</t>
+    <t xml:space="preserve">2.18950366973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.21781635284424</t>
@@ -2222,7 +2225,7 @@
     <t xml:space="preserve">1.95356595516205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97244107723236</t>
+    <t xml:space="preserve">1.97244083881378</t>
   </si>
   <si>
     <t xml:space="preserve">1.92525339126587</t>
@@ -2243,7 +2246,7 @@
     <t xml:space="preserve">1.85447204113007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8686283826828</t>
+    <t xml:space="preserve">1.86862826347351</t>
   </si>
   <si>
     <t xml:space="preserve">1.79312813282013</t>
@@ -2252,7 +2255,7 @@
     <t xml:space="preserve">1.82144069671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84503448009491</t>
+    <t xml:space="preserve">1.8450345993042</t>
   </si>
   <si>
     <t xml:space="preserve">1.81672191619873</t>
@@ -2261,16 +2264,16 @@
     <t xml:space="preserve">1.80256569385529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8261593580246</t>
+    <t xml:space="preserve">1.82615947723389</t>
   </si>
   <si>
     <t xml:space="preserve">1.83559703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87334704399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83087837696075</t>
+    <t xml:space="preserve">1.87334716320038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83087825775146</t>
   </si>
   <si>
     <t xml:space="preserve">1.85919082164764</t>
@@ -2288,10 +2291,10 @@
     <t xml:space="preserve">1.75537812709808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74594056606293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76481568813324</t>
+    <t xml:space="preserve">1.74594068527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76481556892395</t>
   </si>
   <si>
     <t xml:space="preserve">1.76009690761566</t>
@@ -2300,10 +2303,10 @@
     <t xml:space="preserve">1.71290934085846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73178446292877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7034717798233</t>
+    <t xml:space="preserve">1.73178434371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70347166061401</t>
   </si>
   <si>
     <t xml:space="preserve">1.67987787723541</t>
@@ -2312,7 +2315,7 @@
     <t xml:space="preserve">1.69875299930573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74122190475464</t>
+    <t xml:space="preserve">1.74122178554535</t>
   </si>
   <si>
     <t xml:space="preserve">1.7270655632019</t>
@@ -2324,7 +2327,7 @@
     <t xml:space="preserve">1.78840935230255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7789717912674</t>
+    <t xml:space="preserve">1.77897191047668</t>
   </si>
   <si>
     <t xml:space="preserve">1.77425312995911</t>
@@ -2339,7 +2342,7 @@
     <t xml:space="preserve">1.96300339698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02906608581543</t>
+    <t xml:space="preserve">2.02906632423401</t>
   </si>
   <si>
     <t xml:space="preserve">2.07625389099121</t>
@@ -51889,7 +51892,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1883" t="s">
-        <v>645</v>
+        <v>710</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51915,7 +51918,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1884" t="s">
-        <v>645</v>
+        <v>710</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51941,7 +51944,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1885" t="s">
-        <v>645</v>
+        <v>710</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51993,7 +51996,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1887" t="s">
-        <v>645</v>
+        <v>710</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52097,7 +52100,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1891" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52123,7 +52126,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1892" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52149,7 +52152,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1893" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52175,7 +52178,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1894" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52201,7 +52204,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1895" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52227,7 +52230,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1896" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52253,7 +52256,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1897" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52279,7 +52282,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1898" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52305,7 +52308,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1899" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52331,7 +52334,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1900" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52357,7 +52360,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1901" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52383,7 +52386,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1902" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52409,7 +52412,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1903" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52435,7 +52438,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1904" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52461,7 +52464,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1905" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52487,7 +52490,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1906" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52513,7 +52516,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1907" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52539,7 +52542,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1908" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52565,7 +52568,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1909" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52591,7 +52594,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1910" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52617,7 +52620,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1911" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52643,7 +52646,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1912" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52669,7 +52672,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1913" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52695,7 +52698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1914" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52721,7 +52724,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1915" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52747,7 +52750,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1916" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52773,7 +52776,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1917" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52799,7 +52802,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1918" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52825,7 +52828,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1919" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52851,7 +52854,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1920" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52877,7 +52880,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1921" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52903,7 +52906,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1922" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52929,7 +52932,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1923" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52955,7 +52958,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1924" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52981,7 +52984,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1925" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53007,7 +53010,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53033,7 +53036,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53059,7 +53062,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1928" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53085,7 +53088,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1929" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53111,7 +53114,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1930" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53137,7 +53140,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1931" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53163,7 +53166,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1932" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53189,7 +53192,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1933" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53241,7 +53244,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1935" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53267,7 +53270,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1936" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53293,7 +53296,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1937" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53319,7 +53322,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1938" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53345,7 +53348,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1939" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53371,7 +53374,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1940" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53423,7 +53426,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1942" t="s">
-        <v>645</v>
+        <v>710</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53449,7 +53452,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1943" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53475,7 +53478,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1944" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53501,7 +53504,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1945" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53527,7 +53530,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1946" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53553,7 +53556,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53579,7 +53582,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1948" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53605,7 +53608,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1949" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53631,7 +53634,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1950" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53709,7 +53712,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1953" t="s">
-        <v>645</v>
+        <v>710</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53787,7 +53790,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1956" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53813,7 +53816,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1957" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53839,7 +53842,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1958" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53891,7 +53894,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1960" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53917,7 +53920,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1961" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53943,7 +53946,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1962" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53969,7 +53972,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1963" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53995,7 +53998,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1964" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54021,7 +54024,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1965" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54047,7 +54050,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1966" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54073,7 +54076,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1967" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54099,7 +54102,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1968" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54125,7 +54128,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1969" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54151,7 +54154,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1970" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54177,7 +54180,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1971" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54203,7 +54206,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1972" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54229,7 +54232,7 @@
         <v>2</v>
       </c>
       <c r="G1973" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54255,7 +54258,7 @@
         <v>2</v>
       </c>
       <c r="G1974" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54281,7 +54284,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1975" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54307,7 +54310,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54359,7 +54362,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1978" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54385,7 +54388,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1979" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54411,7 +54414,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1980" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54437,7 +54440,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1981" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54463,7 +54466,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1982" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54489,7 +54492,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1983" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54515,7 +54518,7 @@
         <v>2</v>
       </c>
       <c r="G1984" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54567,7 +54570,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1986" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54593,7 +54596,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1987" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54619,7 +54622,7 @@
         <v>2</v>
       </c>
       <c r="G1988" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54645,7 +54648,7 @@
         <v>2</v>
       </c>
       <c r="G1989" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54671,7 +54674,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1990" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54697,7 +54700,7 @@
         <v>2</v>
       </c>
       <c r="G1991" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54749,7 +54752,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1993" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54775,7 +54778,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1994" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54801,7 +54804,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1995" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54879,7 +54882,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1998" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54905,7 +54908,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1999" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54931,7 +54934,7 @@
         <v>2</v>
       </c>
       <c r="G2000" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54957,7 +54960,7 @@
         <v>2</v>
       </c>
       <c r="G2001" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54983,7 +54986,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2002" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55009,7 +55012,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2003" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55035,7 +55038,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2004" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55061,7 +55064,7 @@
         <v>2</v>
       </c>
       <c r="G2005" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55087,7 +55090,7 @@
         <v>2</v>
       </c>
       <c r="G2006" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55113,7 +55116,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2007" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55165,7 +55168,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2009" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55191,7 +55194,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2010" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55217,7 +55220,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2011" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55243,7 +55246,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2012" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55269,7 +55272,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2013" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55295,7 +55298,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2014" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55347,7 +55350,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2016" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55373,7 +55376,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2017" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55399,7 +55402,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2018" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55425,7 +55428,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2019" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55451,7 +55454,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2020" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55477,7 +55480,7 @@
         <v>2</v>
       </c>
       <c r="G2021" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55503,7 +55506,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2022" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55529,7 +55532,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2023" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55607,7 +55610,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2026" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55633,7 +55636,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2027" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55659,7 +55662,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2028" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55685,7 +55688,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2029" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55711,7 +55714,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2030" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55737,7 +55740,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2031" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55763,7 +55766,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2032" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55789,7 +55792,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2033" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55815,7 +55818,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2034" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55841,7 +55844,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2035" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55867,7 +55870,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2036" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55893,7 +55896,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2037" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55971,7 +55974,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2040" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56023,7 +56026,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2042" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56101,7 +56104,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2045" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56127,7 +56130,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2046" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56153,7 +56156,7 @@
         <v>1.875</v>
       </c>
       <c r="G2047" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56179,7 +56182,7 @@
         <v>1.875</v>
       </c>
       <c r="G2048" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56205,7 +56208,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2049" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56231,7 +56234,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2050" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56257,7 +56260,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2051" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56283,7 +56286,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2052" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56309,7 +56312,7 @@
         <v>1.875</v>
       </c>
       <c r="G2053" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56335,7 +56338,7 @@
         <v>1.875</v>
       </c>
       <c r="G2054" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56361,7 +56364,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2055" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56387,7 +56390,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2056" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56413,7 +56416,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2057" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56439,7 +56442,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2058" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56465,7 +56468,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2059" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56491,7 +56494,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2060" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56517,7 +56520,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2061" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56543,7 +56546,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2062" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56569,7 +56572,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2063" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56595,7 +56598,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2064" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56621,7 +56624,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2065" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56647,7 +56650,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2066" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56673,7 +56676,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2067" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56699,7 +56702,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2068" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56725,7 +56728,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2069" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56751,7 +56754,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2070" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56777,7 +56780,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56803,7 +56806,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2072" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56829,7 +56832,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2073" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56855,7 +56858,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2074" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56881,7 +56884,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2075" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56907,7 +56910,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2076" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56933,7 +56936,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2077" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56959,7 +56962,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2078" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56985,7 +56988,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2079" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57011,7 +57014,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2080" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57037,7 +57040,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2081" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57063,7 +57066,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2082" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57089,7 +57092,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2083" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57115,7 +57118,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2084" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57141,7 +57144,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2085" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57167,7 +57170,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2086" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57193,7 +57196,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2087" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57219,7 +57222,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2088" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57271,7 +57274,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2090" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57297,7 +57300,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2091" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57323,7 +57326,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2092" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57375,7 +57378,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2094" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57401,7 +57404,7 @@
         <v>2</v>
       </c>
       <c r="G2095" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57427,7 +57430,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2096" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57453,7 +57456,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2097" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57479,7 +57482,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2098" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57505,7 +57508,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2099" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57531,7 +57534,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2100" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57557,7 +57560,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2101" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57583,7 +57586,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57609,7 +57612,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2103" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57635,7 +57638,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2104" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57661,7 +57664,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2105" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57687,7 +57690,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2106" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57713,7 +57716,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2107" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57739,7 +57742,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2108" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57765,7 +57768,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2109" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57791,7 +57794,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2110" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57817,7 +57820,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2111" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57843,7 +57846,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2112" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57869,7 +57872,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2113" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57895,7 +57898,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2114" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57921,7 +57924,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2115" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57947,7 +57950,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2116" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57973,7 +57976,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2117" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57999,7 +58002,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2118" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58025,7 +58028,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2119" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58051,7 +58054,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2120" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58077,7 +58080,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2121" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58103,7 +58106,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2122" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58129,7 +58132,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2123" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58155,7 +58158,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2124" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58181,7 +58184,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2125" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58207,7 +58210,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2126" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58233,7 +58236,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2127" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58259,7 +58262,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2128" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58285,7 +58288,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2129" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58311,7 +58314,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2130" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58337,7 +58340,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2131" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58363,7 +58366,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2132" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58389,7 +58392,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2133" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58415,7 +58418,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2134" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58441,7 +58444,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2135" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58467,7 +58470,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2136" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58493,7 +58496,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2137" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58519,7 +58522,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2138" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58545,7 +58548,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2139" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58571,7 +58574,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2140" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58597,7 +58600,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2141" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58623,7 +58626,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2142" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58649,7 +58652,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2143" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58675,7 +58678,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2144" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58701,7 +58704,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2145" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58727,7 +58730,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2146" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58753,7 +58756,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2147" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58779,7 +58782,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2148" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58805,7 +58808,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2149" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58831,7 +58834,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2150" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58857,7 +58860,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2151" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58883,7 +58886,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2152" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58909,7 +58912,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2153" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58935,7 +58938,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2154" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58961,7 +58964,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2155" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58987,7 +58990,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2156" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59013,7 +59016,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2157" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59039,7 +59042,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2158" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59065,7 +59068,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2159" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59091,7 +59094,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2160" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59117,7 +59120,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2161" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59143,7 +59146,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2162" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59169,7 +59172,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2163" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59195,7 +59198,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2164" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59221,7 +59224,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2165" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59247,7 +59250,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2166" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59273,7 +59276,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2167" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59299,7 +59302,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2168" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59325,7 +59328,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2169" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59351,7 +59354,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2170" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59377,7 +59380,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2171" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59403,7 +59406,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2172" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59429,7 +59432,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2173" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59455,7 +59458,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2174" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59481,7 +59484,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2175" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59507,7 +59510,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2176" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59533,7 +59536,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2177" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59559,7 +59562,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2178" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59585,7 +59588,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2179" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -59611,7 +59614,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2180" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59637,7 +59640,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2181" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59663,7 +59666,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2182" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59689,7 +59692,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2183" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59715,7 +59718,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2184" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59741,7 +59744,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2185" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59767,7 +59770,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2186" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59793,7 +59796,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2187" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59819,7 +59822,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2188" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59845,7 +59848,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59871,7 +59874,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2190" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59897,7 +59900,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2191" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59923,7 +59926,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2192" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59949,7 +59952,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2193" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59975,7 +59978,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2194" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60001,7 +60004,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2195" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60027,7 +60030,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2196" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60053,7 +60056,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2197" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60079,7 +60082,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2198" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60105,7 +60108,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2199" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60131,7 +60134,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2200" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60157,7 +60160,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2201" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60183,7 +60186,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2202" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60209,7 +60212,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2203" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60235,7 +60238,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2204" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60261,7 +60264,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2205" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60287,7 +60290,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2206" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60313,7 +60316,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2207" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60339,7 +60342,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2208" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60365,7 +60368,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2209" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60391,7 +60394,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2210" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60417,7 +60420,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2211" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60443,7 +60446,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2212" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60469,7 +60472,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2213" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60495,7 +60498,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2214" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60521,7 +60524,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60547,7 +60550,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2216" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60573,7 +60576,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2217" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60599,7 +60602,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2218" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60625,7 +60628,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2219" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60651,7 +60654,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2220" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60677,7 +60680,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2221" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60703,7 +60706,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2222" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60729,7 +60732,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2223" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60755,7 +60758,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2224" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60781,7 +60784,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2225" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60807,7 +60810,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60833,7 +60836,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2227" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60859,7 +60862,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2228" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60885,7 +60888,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2229" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60911,7 +60914,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2230" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60937,7 +60940,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2231" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60963,7 +60966,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2232" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60989,7 +60992,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2233" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61015,7 +61018,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2234" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61041,7 +61044,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2235" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61067,7 +61070,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2236" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61093,7 +61096,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2237" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61119,7 +61122,7 @@
         <v>2.25</v>
       </c>
       <c r="G2238" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61145,7 +61148,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2239" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61171,7 +61174,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2240" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61197,7 +61200,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2241" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61223,7 +61226,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2242" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61249,7 +61252,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2243" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61275,7 +61278,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2244" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61301,7 +61304,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61327,7 +61330,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2246" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61353,7 +61356,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2247" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61379,7 +61382,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2248" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61405,7 +61408,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61431,7 +61434,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2250" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61457,7 +61460,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2251" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61483,7 +61486,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2252" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61509,7 +61512,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2253" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61535,7 +61538,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2254" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61561,7 +61564,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2255" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61587,7 +61590,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2256" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61613,7 +61616,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2257" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61639,7 +61642,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2258" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61665,7 +61668,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2259" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61691,7 +61694,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2260" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61717,7 +61720,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2261" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61743,7 +61746,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2262" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61769,7 +61772,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2263" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61795,7 +61798,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2264" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61821,7 +61824,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2265" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61847,7 +61850,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2266" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61873,7 +61876,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2267" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61899,7 +61902,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61925,7 +61928,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2269" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61951,7 +61954,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2270" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61977,7 +61980,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2271" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62003,7 +62006,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2272" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62029,7 +62032,7 @@
         <v>2.25</v>
       </c>
       <c r="G2273" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62055,7 +62058,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2274" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62081,7 +62084,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2275" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62107,7 +62110,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2276" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62133,7 +62136,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2277" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62159,7 +62162,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2278" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62185,7 +62188,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2279" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62211,7 +62214,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2280" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62237,7 +62240,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2281" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62263,7 +62266,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2282" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62289,7 +62292,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2283" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62315,7 +62318,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2284" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62341,7 +62344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2285" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62367,7 +62370,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2286" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62393,7 +62396,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2287" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62419,7 +62422,7 @@
         <v>2</v>
       </c>
       <c r="G2288" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62445,7 +62448,7 @@
         <v>2</v>
       </c>
       <c r="G2289" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62471,7 +62474,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2290" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62497,7 +62500,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2291" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62523,7 +62526,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2292" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62549,7 +62552,7 @@
         <v>2</v>
       </c>
       <c r="G2293" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62575,7 +62578,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2294" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62601,7 +62604,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2295" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62627,7 +62630,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2296" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62653,7 +62656,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2297" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62679,7 +62682,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2298" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62705,7 +62708,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2299" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62731,7 +62734,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2300" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62757,7 +62760,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2301" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62783,7 +62786,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2302" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62809,7 +62812,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2303" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62835,7 +62838,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2304" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62861,7 +62864,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2305" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62887,7 +62890,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2306" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62913,7 +62916,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2307" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62939,7 +62942,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2308" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62965,7 +62968,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2309" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62991,7 +62994,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2310" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63017,7 +63020,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2311" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63043,7 +63046,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2312" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63069,7 +63072,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2313" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63095,7 +63098,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2314" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63121,7 +63124,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2315" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63147,7 +63150,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2316" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63173,7 +63176,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2317" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63199,7 +63202,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2318" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63225,7 +63228,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2319" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63251,7 +63254,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2320" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63277,7 +63280,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2321" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63303,7 +63306,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2322" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63329,7 +63332,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2323" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63355,7 +63358,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2324" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63381,7 +63384,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2325" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63407,7 +63410,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2326" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63433,7 +63436,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2327" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63459,7 +63462,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2328" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63485,7 +63488,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63511,7 +63514,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2330" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63537,7 +63540,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2331" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63563,7 +63566,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63589,7 +63592,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63615,7 +63618,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2334" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63641,7 +63644,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2335" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63667,7 +63670,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2336" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63693,7 +63696,7 @@
         <v>2</v>
       </c>
       <c r="G2337" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63719,7 +63722,7 @@
         <v>2</v>
       </c>
       <c r="G2338" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63745,7 +63748,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2339" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63771,7 +63774,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2340" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63797,7 +63800,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2341" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63823,7 +63826,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2342" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63849,7 +63852,7 @@
         <v>2</v>
       </c>
       <c r="G2343" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63875,7 +63878,7 @@
         <v>2</v>
       </c>
       <c r="G2344" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63901,7 +63904,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2345" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63927,7 +63930,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2346" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63953,7 +63956,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2347" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63979,7 +63982,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2348" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64005,7 +64008,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2349" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64031,7 +64034,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2350" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64057,7 +64060,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2351" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64083,7 +64086,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2352" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64109,7 +64112,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2353" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64135,7 +64138,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2354" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64161,7 +64164,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2355" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64187,7 +64190,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2356" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64213,7 +64216,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2357" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64239,7 +64242,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2358" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64265,7 +64268,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2359" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64291,7 +64294,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2360" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64317,7 +64320,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2361" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64343,7 +64346,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2362" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64369,7 +64372,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2363" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64395,7 +64398,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2364" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64421,7 +64424,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2365" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64447,7 +64450,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2366" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64473,7 +64476,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2367" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64499,7 +64502,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64525,7 +64528,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2369" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64551,7 +64554,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2370" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64577,7 +64580,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2371" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64603,7 +64606,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2372" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64629,7 +64632,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2373" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64655,7 +64658,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2374" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64681,7 +64684,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2375" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64707,7 +64710,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2376" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64733,7 +64736,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2377" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64759,7 +64762,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2378" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64785,7 +64788,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64811,7 +64814,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2380" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64837,7 +64840,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2381" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64863,7 +64866,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2382" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64889,7 +64892,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2383" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64915,7 +64918,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2384" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64941,7 +64944,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2385" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64967,7 +64970,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2386" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64993,7 +64996,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2387" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65019,7 +65022,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2388" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65045,7 +65048,7 @@
         <v>2</v>
       </c>
       <c r="G2389" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65071,7 +65074,7 @@
         <v>2</v>
       </c>
       <c r="G2390" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65097,7 +65100,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2391" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65123,7 +65126,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2392" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65149,7 +65152,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2393" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65175,7 +65178,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65201,7 +65204,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2395" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65227,7 +65230,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2396" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65253,7 +65256,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2397" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65279,7 +65282,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2398" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65305,7 +65308,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2399" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65331,7 +65334,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2400" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65357,7 +65360,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2401" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65383,7 +65386,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2402" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65409,7 +65412,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2403" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65435,7 +65438,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2404" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65461,7 +65464,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65487,7 +65490,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2406" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65513,7 +65516,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2407" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65539,7 +65542,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2408" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65565,7 +65568,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65591,7 +65594,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2410" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65617,7 +65620,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2411" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65643,7 +65646,7 @@
         <v>2</v>
       </c>
       <c r="G2412" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65669,7 +65672,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2413" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65695,7 +65698,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2414" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65721,7 +65724,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2415" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65747,7 +65750,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2416" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65773,7 +65776,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2417" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65799,7 +65802,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2418" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65825,7 +65828,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2419" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65851,7 +65854,7 @@
         <v>2</v>
       </c>
       <c r="G2420" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65877,7 +65880,7 @@
         <v>2</v>
       </c>
       <c r="G2421" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65903,7 +65906,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2422" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65929,7 +65932,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2423" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65955,7 +65958,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2424" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65981,7 +65984,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2425" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66007,7 +66010,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2426" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66033,7 +66036,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2427" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66059,7 +66062,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2428" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66085,7 +66088,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2429" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66111,7 +66114,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66137,7 +66140,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2431" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66163,7 +66166,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2432" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66189,7 +66192,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2433" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66215,7 +66218,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2434" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66241,7 +66244,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2435" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66267,7 +66270,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2436" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66293,7 +66296,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2437" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66319,7 +66322,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2438" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66345,7 +66348,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2439" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66371,7 +66374,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2440" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66397,7 +66400,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2441" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66423,7 +66426,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2442" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66449,7 +66452,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2443" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66475,7 +66478,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2444" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66501,7 +66504,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2445" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66527,7 +66530,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2446" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66553,7 +66556,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2447" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66579,7 +66582,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2448" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66605,7 +66608,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66631,7 +66634,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2450" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66657,7 +66660,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2451" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66683,7 +66686,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2452" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66709,7 +66712,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2453" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66735,7 +66738,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2454" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66761,7 +66764,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2455" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66787,7 +66790,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2456" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66813,7 +66816,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2457" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66839,7 +66842,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2458" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66865,7 +66868,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2459" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66891,7 +66894,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2460" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66917,7 +66920,7 @@
         <v>2.25</v>
       </c>
       <c r="G2461" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66943,7 +66946,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2462" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66969,7 +66972,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2463" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66995,7 +66998,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2464" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67021,7 +67024,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2465" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67047,7 +67050,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2466" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67073,7 +67076,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2467" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67099,7 +67102,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2468" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67125,7 +67128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2469" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67151,7 +67154,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67177,7 +67180,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2471" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67203,7 +67206,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2472" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67229,7 +67232,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2473" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67255,7 +67258,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2474" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67281,7 +67284,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2475" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67307,7 +67310,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2476" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67333,7 +67336,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2477" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67359,7 +67362,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2478" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67385,7 +67388,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2479" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67411,7 +67414,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2480" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67437,7 +67440,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2481" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67463,7 +67466,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2482" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67489,7 +67492,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2483" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67515,7 +67518,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2484" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67541,7 +67544,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2485" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67567,7 +67570,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2486" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67593,7 +67596,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2487" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67619,7 +67622,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2488" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67645,7 +67648,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2489" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67671,7 +67674,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2490" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67697,7 +67700,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2491" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67723,7 +67726,7 @@
         <v>2.25</v>
       </c>
       <c r="G2492" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67749,7 +67752,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2493" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67775,7 +67778,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2494" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67801,7 +67804,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67827,7 +67830,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2496" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67853,7 +67856,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2497" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67879,7 +67882,7 @@
         <v>2.25</v>
       </c>
       <c r="G2498" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67905,7 +67908,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2499" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67931,7 +67934,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2500" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67957,7 +67960,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2501" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67983,7 +67986,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2502" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68009,7 +68012,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2503" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68035,7 +68038,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2504" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68043,27 +68046,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6911111111</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>2144</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>848</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>11339</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>847</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>13946</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>2.15000009536743</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>2.08999991416931</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>2.15000009536743</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>2.09999990463257</v>
       </c>
-      <c r="G2505" t="s">
-        <v>862</v>
-      </c>
-      <c r="H2505" t="s">
+      <c r="G2507" t="s">
+        <v>863</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6866782407</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>6853</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>863</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034153461456</t>
+    <t xml:space="preserve">1.75034165382385</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.74538791179657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69254732131958</t>
+    <t xml:space="preserve">1.69254720211029</t>
   </si>
   <si>
     <t xml:space="preserve">1.70245492458344</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">1.68429100513458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67603480815887</t>
+    <t xml:space="preserve">1.6760345697403</t>
   </si>
   <si>
     <t xml:space="preserve">1.66612696647644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63888144493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61163532733917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59347128868103</t>
+    <t xml:space="preserve">1.63888108730316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61163544654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59347152709961</t>
   </si>
   <si>
     <t xml:space="preserve">1.48613905906677</t>
@@ -77,34 +77,34 @@
     <t xml:space="preserve">1.59264576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59182012081146</t>
+    <t xml:space="preserve">1.59182000160217</t>
   </si>
   <si>
     <t xml:space="preserve">1.58604061603546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172784328461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521497249603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56044602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51255965232849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53980541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56539976596832</t>
+    <t xml:space="preserve">1.60172772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521521091461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56044614315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51255929470062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53980529308319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56539988517761</t>
   </si>
   <si>
     <t xml:space="preserve">1.53567707538605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45311391353607</t>
+    <t xml:space="preserve">1.45311367511749</t>
   </si>
   <si>
     <t xml:space="preserve">1.50595426559448</t>
@@ -116,103 +116,103 @@
     <t xml:space="preserve">1.44238066673279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51833879947662</t>
+    <t xml:space="preserve">1.51833868026733</t>
   </si>
   <si>
     <t xml:space="preserve">1.65126574039459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6347531080246</t>
+    <t xml:space="preserve">1.63475286960602</t>
   </si>
   <si>
     <t xml:space="preserve">1.65621948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64300930500031</t>
+    <t xml:space="preserve">1.64300918579102</t>
   </si>
   <si>
     <t xml:space="preserve">1.63723003864288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64218366146088</t>
+    <t xml:space="preserve">1.64218378067017</t>
   </si>
   <si>
     <t xml:space="preserve">1.63970685005188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66777837276459</t>
+    <t xml:space="preserve">1.6677782535553</t>
   </si>
   <si>
     <t xml:space="preserve">1.60503017902374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59842526912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870234012604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6405326128006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227593898773</t>
+    <t xml:space="preserve">1.5984251499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870245933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053237438202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6322762966156</t>
   </si>
   <si>
     <t xml:space="preserve">1.60255336761475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57283067703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58934330940247</t>
+    <t xml:space="preserve">1.57283055782318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58934319019318</t>
   </si>
   <si>
     <t xml:space="preserve">1.58438944816589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56787693500519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55714356899261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53402590751648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54310774803162</t>
+    <t xml:space="preserve">1.56787705421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5571436882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53402602672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54310786724091</t>
   </si>
   <si>
     <t xml:space="preserve">1.55466663837433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5596204996109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55218994617462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55053842067719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50265169143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696458339691</t>
+    <t xml:space="preserve">1.55962061882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55218958854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55053865909576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50265192985535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4869647026062</t>
   </si>
   <si>
     <t xml:space="preserve">1.48861598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53237450122833</t>
+    <t xml:space="preserve">1.53237438201904</t>
   </si>
   <si>
     <t xml:space="preserve">1.49026727676392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51503622531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779046535492</t>
+    <t xml:space="preserve">1.5150363445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779058456421</t>
   </si>
   <si>
     <t xml:space="preserve">1.47623145580292</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">1.5010005235672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49439525604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48366212844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45971870422363</t>
+    <t xml:space="preserve">1.49439549446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48366236686707</t>
   </si>
   <si>
     <t xml:space="preserve">1.45971882343292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45299983024597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46223855018616</t>
+    <t xml:space="preserve">1.45971894264221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45299994945526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46223843097687</t>
   </si>
   <si>
     <t xml:space="preserve">1.43284261226654</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">1.44040155410767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43620204925537</t>
+    <t xml:space="preserve">1.43620216846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.4429212808609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44880044460297</t>
+    <t xml:space="preserve">1.44880032539368</t>
   </si>
   <si>
     <t xml:space="preserve">1.47819626331329</t>
@@ -275,34 +275,34 @@
     <t xml:space="preserve">1.44460093975067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42360389232635</t>
+    <t xml:space="preserve">1.42360377311707</t>
   </si>
   <si>
     <t xml:space="preserve">1.43032276630402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40260672569275</t>
+    <t xml:space="preserve">1.46139872074127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40260660648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.40848588943481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37825012207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42444384098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41604506969452</t>
+    <t xml:space="preserve">1.37825000286102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42444372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41604471206665</t>
   </si>
   <si>
     <t xml:space="preserve">1.46979749202728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42780339717865</t>
+    <t xml:space="preserve">1.42780315876007</t>
   </si>
   <si>
     <t xml:space="preserve">1.42192399501801</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">1.47567677497864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44796049594879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735631465912</t>
+    <t xml:space="preserve">1.4479603767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735619544983</t>
   </si>
   <si>
     <t xml:space="preserve">1.43368244171143</t>
@@ -323,49 +323,49 @@
     <t xml:space="preserve">1.45803904533386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4521598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48491537570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46391820907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46895742416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48575508594513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45887899398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45635938644409</t>
+    <t xml:space="preserve">1.45215976238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48491525650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46391832828522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46643805503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46895754337311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.485755443573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45887887477875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4563592672348</t>
   </si>
   <si>
     <t xml:space="preserve">1.45719921588898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48827493190765</t>
+    <t xml:space="preserve">1.48827481269836</t>
   </si>
   <si>
     <t xml:space="preserve">1.43956160545349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.473996758461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46727788448334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49835348129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50927197933197</t>
+    <t xml:space="preserve">1.47399687767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46727800369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49835360050201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50927209854126</t>
   </si>
   <si>
     <t xml:space="preserve">1.5033928155899</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">1.4949939250946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48743510246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51011180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49919331073761</t>
+    <t xml:space="preserve">1.48743498325348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51011192798615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4991934299469</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179158687592</t>
@@ -389,40 +389,40 @@
     <t xml:space="preserve">1.45048010349274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44628047943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43872165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50003337860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48071599006653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48155570030212</t>
+    <t xml:space="preserve">1.44628059864044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4387218952179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50003325939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48071575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4815559387207</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095175743103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49583387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5075923204422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49667382240295</t>
+    <t xml:space="preserve">1.49583399295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50759220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49667358398438</t>
   </si>
   <si>
     <t xml:space="preserve">1.47231709957123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49331426620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147727012634</t>
+    <t xml:space="preserve">1.49331414699554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147715091705</t>
   </si>
   <si>
     <t xml:space="preserve">1.50087320804596</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">1.53194892406464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52690958976746</t>
+    <t xml:space="preserve">1.52690947055817</t>
   </si>
   <si>
     <t xml:space="preserve">1.52355003356934</t>
@@ -446,61 +446,61 @@
     <t xml:space="preserve">1.51263153553009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454720020294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54538702964783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55294597148895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52019035816193</t>
+    <t xml:space="preserve">1.54454708099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54538714885712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55294585227966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52019059658051</t>
   </si>
   <si>
     <t xml:space="preserve">1.50843214988708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59578013420105</t>
+    <t xml:space="preserve">1.59578001499176</t>
   </si>
   <si>
     <t xml:space="preserve">1.53446865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56050503253937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53026926517487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53110897541046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55126643180847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55210614204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55378580093384</t>
+    <t xml:space="preserve">1.56050515174866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53026914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53110885620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5512660741806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55210638046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55378592014313</t>
   </si>
   <si>
     <t xml:space="preserve">1.58654153347015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56218469142914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56974351406097</t>
+    <t xml:space="preserve">1.56218481063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56974375247955</t>
   </si>
   <si>
     <t xml:space="preserve">1.57058358192444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60333919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54958629608154</t>
+    <t xml:space="preserve">1.60333895683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54958653450012</t>
   </si>
   <si>
     <t xml:space="preserve">1.55798530578613</t>
@@ -509,37 +509,37 @@
     <t xml:space="preserve">1.57142353057861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56470453739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6108980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61173808574677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60417902469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62517595291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62097656726837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61257767677307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59326028823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58822107315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60753858089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63105523586273</t>
+    <t xml:space="preserve">1.56470441818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61089789867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61173796653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60417890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62517607212067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62097668647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61257791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59326040744781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58822119235992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60753846168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63105547428131</t>
   </si>
   <si>
     <t xml:space="preserve">1.61425757408142</t>
@@ -548,31 +548,31 @@
     <t xml:space="preserve">1.71504378318787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77215540409088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7654367685318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75367832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72512233257294</t>
+    <t xml:space="preserve">1.77215564250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76543664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75367856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72512221336365</t>
   </si>
   <si>
     <t xml:space="preserve">1.74527943134308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72176277637482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70664501190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73856043815613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69992554187775</t>
+    <t xml:space="preserve">1.72176265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70664489269257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73856031894684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69992578029633</t>
   </si>
   <si>
     <t xml:space="preserve">1.67892861366272</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">1.69320678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70496511459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7738356590271</t>
+    <t xml:space="preserve">1.70496499538422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77383553981781</t>
   </si>
   <si>
     <t xml:space="preserve">1.75871777534485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68984735012054</t>
+    <t xml:space="preserve">1.68984723091125</t>
   </si>
   <si>
     <t xml:space="preserve">1.69152688980103</t>
@@ -602,52 +602,52 @@
     <t xml:space="preserve">1.66800999641418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68816721439362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71336376667023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73184132575989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535786151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71000444889069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71672356128693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047598361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031888484955</t>
+    <t xml:space="preserve">1.68816745281219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71336388587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73184144496918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535798072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7100043296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71672344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016154766083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74695932865143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77047610282898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375687122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031900405884</t>
   </si>
   <si>
     <t xml:space="preserve">1.78895354270935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74023997783661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76207733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73352110385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903185367584</t>
+    <t xml:space="preserve">1.74024033546448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76207721233368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73352098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903209209442</t>
   </si>
   <si>
     <t xml:space="preserve">1.78055453300476</t>
@@ -659,19 +659,19 @@
     <t xml:space="preserve">1.86958265304565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86454284191132</t>
+    <t xml:space="preserve">1.8645430803299</t>
   </si>
   <si>
     <t xml:space="preserve">1.84774529933929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78391408920288</t>
+    <t xml:space="preserve">1.78391420841217</t>
   </si>
   <si>
     <t xml:space="preserve">1.90480959415436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98488664627075</t>
+    <t xml:space="preserve">1.98488640785217</t>
   </si>
   <si>
     <t xml:space="preserve">2.34267711639404</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">2.24045157432556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18081951141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36482644081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32223200798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34608483314514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33415818214417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24897003173828</t>
+    <t xml:space="preserve">2.180819272995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36482620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32223224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34608435630798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33415842056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24897027015686</t>
   </si>
   <si>
     <t xml:space="preserve">2.20296835899353</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">2.14163279533386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07007479667664</t>
+    <t xml:space="preserve">2.07007455825806</t>
   </si>
   <si>
     <t xml:space="preserve">2.01896190643311</t>
@@ -716,94 +716,94 @@
     <t xml:space="preserve">1.9593300819397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01044273376465</t>
+    <t xml:space="preserve">2.01044297218323</t>
   </si>
   <si>
     <t xml:space="preserve">2.06496334075928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00192427635193</t>
+    <t xml:space="preserve">2.00192403793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.02407312393188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06155633926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04451847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837105751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303692817688</t>
+    <t xml:space="preserve">2.06155610084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04451823234558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0683708190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303716659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.04111051559448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97977519035339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99340498447418</t>
+    <t xml:space="preserve">1.9797750711441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99340522289276</t>
   </si>
   <si>
     <t xml:space="preserve">1.97636759281158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97125637531281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466421127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95081102848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93888485431671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92525506019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9269585609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94229257106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95762658119202</t>
+    <t xml:space="preserve">1.97125625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9746640920639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95081126689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93888473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92525446414948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92695844173431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94229221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95762646198273</t>
   </si>
   <si>
     <t xml:space="preserve">1.93718099594116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92866194248199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97296035289764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00703549385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01555418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98829400539398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93206965923309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673576831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91332852840424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90821707248688</t>
+    <t xml:space="preserve">1.92866218090057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97296023368835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00703525543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01555442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98829424381256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93206977844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673588752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91332817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90821695327759</t>
   </si>
   <si>
     <t xml:space="preserve">1.93377351760864</t>
@@ -815,31 +815,31 @@
     <t xml:space="preserve">2.13822531700134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2557852268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22341322898865</t>
+    <t xml:space="preserve">2.25578546524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22341346740723</t>
   </si>
   <si>
     <t xml:space="preserve">2.35971474647522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27452635765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41593933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41253137588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36823391914368</t>
+    <t xml:space="preserve">2.27452659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41593885421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41253161430359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3682336807251</t>
   </si>
   <si>
     <t xml:space="preserve">2.30860185623169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31200933456421</t>
+    <t xml:space="preserve">2.31200981140137</t>
   </si>
   <si>
     <t xml:space="preserve">2.31541705131531</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">2.42445802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41423535346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36993741989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39719772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35801148414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30519485473633</t>
+    <t xml:space="preserve">2.41423559188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36993718147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39719796180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35801076889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30519437789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.32052826881409</t>
@@ -878,37 +878,37 @@
     <t xml:space="preserve">2.3477885723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3631227016449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3443808555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32563948631287</t>
+    <t xml:space="preserve">2.36312246322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34438109397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32563996315002</t>
   </si>
   <si>
     <t xml:space="preserve">2.33926963806152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36653017997742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37675261497498</t>
+    <t xml:space="preserve">2.36652994155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3767523765564</t>
   </si>
   <si>
     <t xml:space="preserve">2.38356781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2711193561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25408148765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09392738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15696692466736</t>
+    <t xml:space="preserve">2.27111887931824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25408124923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09392762184143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15696668624878</t>
   </si>
   <si>
     <t xml:space="preserve">2.10585379600525</t>
@@ -917,175 +917,175 @@
     <t xml:space="preserve">2.10415005683899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12800288200378</t>
+    <t xml:space="preserve">2.12800264358521</t>
   </si>
   <si>
     <t xml:space="preserve">2.31712055206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28304529190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30349087715149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29667544364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28815698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21659851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23874759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21489500999451</t>
+    <t xml:space="preserve">2.28304576873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30349040031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29667568206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28815650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21659874916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23874735832214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21489477157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25748944282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24556255340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2319324016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933844566345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26260018348694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22511720657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23363614082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23022866249084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20637583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29156422615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39379024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41934657096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53009152412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57268524169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5471293926239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5812041759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50453495979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47045969963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46194076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38527154922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41082787513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30008292198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45342206954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60676074028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61527943611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6493546962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43638396263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52157258987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53861045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55564761161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48749709129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44490265846252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26600766181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14674425125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671034812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1185667514801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066240310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29221963882446</t>
   </si>
   <si>
     <t xml:space="preserve">2.25748896598816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24556279182434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23193216323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933796882629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26260018348694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22511744499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23363614082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23022866249084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20637559890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29156422615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39379024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41934657096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53009128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5726854801178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54712915420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58120393753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50453472137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47045946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46194100379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3852710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41082787513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30008292198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45342230796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60676074028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61527943611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6493546962738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4363842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52157258987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53861021995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55564761161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48749732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4449028968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26600766181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14674401283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671058654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11856651306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066240310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29221963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25748920440674</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.24880599975586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26617121696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27485418319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34431529045105</t>
+    <t xml:space="preserve">2.26617169380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27485394477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34431505203247</t>
   </si>
   <si>
     <t xml:space="preserve">2.35299801826477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3009021282196</t>
+    <t xml:space="preserve">2.30090260505676</t>
   </si>
   <si>
     <t xml:space="preserve">2.30958485603333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32695007324219</t>
+    <t xml:space="preserve">2.32695031166077</t>
   </si>
   <si>
     <t xml:space="preserve">2.28353714942932</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">2.20539283752441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15329694747925</t>
+    <t xml:space="preserve">2.15329718589783</t>
   </si>
   <si>
     <t xml:space="preserve">2.13593196868896</t>
@@ -1109,85 +1109,85 @@
     <t xml:space="preserve">2.10988402366638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18802738189697</t>
+    <t xml:space="preserve">2.18802785873413</t>
   </si>
   <si>
     <t xml:space="preserve">2.09251856803894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22275853157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07515358924866</t>
+    <t xml:space="preserve">2.22275829315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0751531124115</t>
   </si>
   <si>
     <t xml:space="preserve">2.0838360786438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10120153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04042291641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01437473297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05778813362122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06647062301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700951576233</t>
+    <t xml:space="preserve">2.10120129585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04042267799377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01437449455261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05778789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06647086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700939655304</t>
   </si>
   <si>
     <t xml:space="preserve">2.00569200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964429855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9622790813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02305769920349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04910516738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03173971176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93623077869415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87545228004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.892817735672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82335650920868</t>
+    <t xml:space="preserve">1.97964382171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96227872371674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02305746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0491054058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03173995018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93623065948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87545251846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281761646271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82335638999939</t>
   </si>
   <si>
     <t xml:space="preserve">1.81467366218567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77994322776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71916460990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69311678409576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62799680233002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63233816623688</t>
+    <t xml:space="preserve">1.77994310855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71916449069977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69311690330505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62799692153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63233804702759</t>
   </si>
   <si>
     <t xml:space="preserve">1.67575144767761</t>
@@ -1196,34 +1196,34 @@
     <t xml:space="preserve">1.68443405628204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71048200130463</t>
+    <t xml:space="preserve">1.71048212051392</t>
   </si>
   <si>
     <t xml:space="preserve">1.6887754201889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71482348442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69745790958405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64536225795746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59760749340057</t>
+    <t xml:space="preserve">1.7148232460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69745814800262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64536201953888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59760761260986</t>
   </si>
   <si>
     <t xml:space="preserve">1.60629022121429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6193140745163</t>
+    <t xml:space="preserve">1.61931419372559</t>
   </si>
   <si>
     <t xml:space="preserve">1.61497282981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63667953014374</t>
+    <t xml:space="preserve">1.63667941093445</t>
   </si>
   <si>
     <t xml:space="preserve">1.64970338344574</t>
@@ -1232,46 +1232,46 @@
     <t xml:space="preserve">1.68009269237518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65838599205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7017993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67141008377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6670686006546</t>
+    <t xml:space="preserve">1.65838611125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70179927349091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67140996456146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66706871986389</t>
   </si>
   <si>
     <t xml:space="preserve">1.5715594291687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52814626693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51078104972839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551160335541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56287682056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65404486656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66272747516632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7278470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76257801055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75389528274536</t>
+    <t xml:space="preserve">1.52814638614655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51078116893768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5455117225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56287705898285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6540447473526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66272735595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72784733772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76257789134979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75389516353607</t>
   </si>
   <si>
     <t xml:space="preserve">1.78862571716309</t>
@@ -1280,28 +1280,28 @@
     <t xml:space="preserve">1.80599105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77126049995422</t>
+    <t xml:space="preserve">1.77126038074493</t>
   </si>
   <si>
     <t xml:space="preserve">1.74521267414093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83203887939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79730832576752</t>
+    <t xml:space="preserve">1.83203899860382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79730844497681</t>
   </si>
   <si>
     <t xml:space="preserve">1.84072160720825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86676979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91018283367157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359599590302</t>
+    <t xml:space="preserve">1.86676967144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91018295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9535961151123</t>
   </si>
   <si>
     <t xml:space="preserve">1.94491350650787</t>
@@ -1310,22 +1310,22 @@
     <t xml:space="preserve">1.98832666873932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97096145153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91886556148529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92754805088043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8580869436264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84940433502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413488864899</t>
+    <t xml:space="preserve">1.97096157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91886591911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92754852771759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85808718204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84940445423126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413500785828</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365543842316</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">1.61919498443604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60135245323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61027383804321</t>
+    <t xml:space="preserve">1.6013525724411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61027359962463</t>
   </si>
   <si>
     <t xml:space="preserve">1.63703727722168</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">1.6459584236145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64149785041809</t>
+    <t xml:space="preserve">1.64149808883667</t>
   </si>
   <si>
     <t xml:space="preserve">1.65934026241302</t>
@@ -1364,49 +1364,49 @@
     <t xml:space="preserve">1.66826140880585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68164324760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63257658481598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60581302642822</t>
+    <t xml:space="preserve">1.68610370159149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68164312839508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63257682323456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60581314563751</t>
   </si>
   <si>
     <t xml:space="preserve">1.62811613082886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61473417282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58351004123688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57904970645905</t>
+    <t xml:space="preserve">1.61473429203033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58351016044617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57904958724976</t>
   </si>
   <si>
     <t xml:space="preserve">1.552286028862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54336476325989</t>
+    <t xml:space="preserve">1.54336488246918</t>
   </si>
   <si>
     <t xml:space="preserve">1.59243130683899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56120729446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53890442848206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55674660205841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57012832164764</t>
+    <t xml:space="preserve">1.56120717525482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53890430927277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5567467212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57012844085693</t>
   </si>
   <si>
     <t xml:space="preserve">1.58797073364258</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">1.57458889484406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59689199924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53444373607635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66380071640015</t>
+    <t xml:space="preserve">1.5968918800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53444385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66380095481873</t>
   </si>
   <si>
     <t xml:space="preserve">1.56566786766052</t>
@@ -1430,91 +1430,91 @@
     <t xml:space="preserve">1.54782557487488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52552247047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50768029689789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738950252533</t>
+    <t xml:space="preserve">1.52552258968353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5076801776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738962173462</t>
   </si>
   <si>
     <t xml:space="preserve">1.51660144329071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48983776569366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34263825416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709882736206</t>
+    <t xml:space="preserve">1.48983764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34263813495636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709894657135</t>
   </si>
   <si>
     <t xml:space="preserve">1.32479584217072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19097805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26680815219879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24450528621674</t>
+    <t xml:space="preserve">1.19097816944122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2668080329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24450516700745</t>
   </si>
   <si>
     <t xml:space="preserve">1.29803240299225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20435976982117</t>
+    <t xml:space="preserve">1.20436000823975</t>
   </si>
   <si>
     <t xml:space="preserve">1.27572929859161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28465068340302</t>
+    <t xml:space="preserve">1.28465044498444</t>
   </si>
   <si>
     <t xml:space="preserve">1.30695343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30249297618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36940169334412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36494112014771</t>
+    <t xml:space="preserve">1.30249285697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36940181255341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36494100093842</t>
   </si>
   <si>
     <t xml:space="preserve">1.35601997375488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36048066616058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40508663654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44969236850739</t>
+    <t xml:space="preserve">1.36048054695129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40508651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44969248771667</t>
   </si>
   <si>
     <t xml:space="preserve">1.45415306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44523179531097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43631076812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41846823692322</t>
+    <t xml:space="preserve">1.44523203372955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43631064891815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41846835613251</t>
   </si>
   <si>
     <t xml:space="preserve">1.46307420730591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39170467853546</t>
+    <t xml:space="preserve">1.39170479774475</t>
   </si>
   <si>
     <t xml:space="preserve">1.40062594413757</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">1.41400766372681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38278341293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38724398612976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33817756175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35155928134918</t>
+    <t xml:space="preserve">1.38278353214264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38724410533905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33817780017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35155951976776</t>
   </si>
   <si>
     <t xml:space="preserve">1.29357171058655</t>
@@ -1547,19 +1547,19 @@
     <t xml:space="preserve">1.31587469577789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37386238574982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31141400337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3203352689743</t>
+    <t xml:space="preserve">1.37386226654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31141412258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32033538818359</t>
   </si>
   <si>
     <t xml:space="preserve">1.28018987178802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4095470905304</t>
+    <t xml:space="preserve">1.40954720973969</t>
   </si>
   <si>
     <t xml:space="preserve">1.39616537094116</t>
@@ -1568,64 +1568,64 @@
     <t xml:space="preserve">1.4586136341095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37832295894623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42292881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28911125659943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2712687253952</t>
+    <t xml:space="preserve">1.37832283973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42292892932892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28911113739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27126860618591</t>
   </si>
   <si>
     <t xml:space="preserve">1.26234757900238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24896574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46753489971161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44077122211456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48091661930084</t>
+    <t xml:space="preserve">1.24896562099457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46753466129303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44077134132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48091650009155</t>
   </si>
   <si>
     <t xml:space="preserve">1.49429833889008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5032194852829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52998316287994</t>
+    <t xml:space="preserve">1.50321936607361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52998304367065</t>
   </si>
   <si>
     <t xml:space="preserve">1.49875891208649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51214063167572</t>
+    <t xml:space="preserve">1.51214075088501</t>
   </si>
   <si>
     <t xml:space="preserve">1.48537719249725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52106201648712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72178864479065</t>
+    <t xml:space="preserve">1.52106189727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72178852558136</t>
   </si>
   <si>
     <t xml:space="preserve">1.76639449596405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73963105678558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81992149353027</t>
+    <t xml:space="preserve">1.73963093757629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81992161273956</t>
   </si>
   <si>
     <t xml:space="preserve">1.87344872951508</t>
@@ -1634,19 +1634,19 @@
     <t xml:space="preserve">1.82884275913239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83776378631592</t>
+    <t xml:space="preserve">1.8377640247345</t>
   </si>
   <si>
     <t xml:space="preserve">1.78423678874969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77531552314758</t>
+    <t xml:space="preserve">1.77531564235687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73517036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085518836975</t>
+    <t xml:space="preserve">1.77085506916046</t>
   </si>
   <si>
     <t xml:space="preserve">1.72624909877777</t>
@@ -1658,25 +1658,25 @@
     <t xml:space="preserve">1.74855220317841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79315805435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71732795238495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74409139156342</t>
+    <t xml:space="preserve">1.79315793514252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71732783317566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74409162998199</t>
   </si>
   <si>
     <t xml:space="preserve">1.77977633476257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81100046634674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84668493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86452734470367</t>
+    <t xml:space="preserve">1.81100034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84668517112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86452722549438</t>
   </si>
   <si>
     <t xml:space="preserve">1.80207920074463</t>
@@ -1691,19 +1691,19 @@
     <t xml:space="preserve">2.0251088142395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96266043186188</t>
+    <t xml:space="preserve">1.96266055107117</t>
   </si>
   <si>
     <t xml:space="preserve">1.9269757270813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050272464752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07863616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10539937019348</t>
+    <t xml:space="preserve">1.98050284385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07863569259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1053991317749</t>
   </si>
   <si>
     <t xml:space="preserve">2.05187249183655</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">2.06079339981079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09647846221924</t>
+    <t xml:space="preserve">2.09647822380066</t>
   </si>
   <si>
     <t xml:space="preserve">2.43548321723938</t>
@@ -1727,103 +1727,103 @@
     <t xml:space="preserve">2.56037974357605</t>
   </si>
   <si>
+    <t xml:space="preserve">2.60498571395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65005493164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61399960517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64104104042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74019265174866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78526139259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73117876052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90244102478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1007444858551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99257898330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92948246002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84835839271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76723432540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83934450149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87539958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82131695747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77624773979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72216510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55991673469543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53287553787231</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.60498595237732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65005493164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61399960517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64104104042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74019265174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78526163101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73117876052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90244102478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1007444858551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99257898330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92948222160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84835839271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76723408699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83934426307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87539958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82131671905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77624773979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72216510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55991697311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53287553787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6049861907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58695840835571</t>
+    <t xml:space="preserve">2.58695793151855</t>
   </si>
   <si>
     <t xml:space="preserve">2.65906858444214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67709636688232</t>
+    <t xml:space="preserve">2.67709612846375</t>
   </si>
   <si>
     <t xml:space="preserve">2.52386164665222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62301349639893</t>
+    <t xml:space="preserve">2.6230137348175</t>
   </si>
   <si>
     <t xml:space="preserve">2.57794451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55090308189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51484799385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56893038749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7942750453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83033084869385</t>
+    <t xml:space="preserve">2.59597229957581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5509033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51484775543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56893062591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79427552223206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83033061027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.71315121650696</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">2.80328917503357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86638569831848</t>
+    <t xml:space="preserve">2.86638593673706</t>
   </si>
   <si>
     <t xml:space="preserve">3.0015926361084</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">2.93849611282349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81230282783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54188942909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4787929058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63202738761902</t>
+    <t xml:space="preserve">2.81230306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54188895225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47879266738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63202714920044</t>
   </si>
   <si>
     <t xml:space="preserve">2.91145467758179</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">2.95652365684509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01060652732849</t>
+    <t xml:space="preserve">3.01060628890991</t>
   </si>
   <si>
     <t xml:space="preserve">3.01962018013</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">2.98356509208679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88441324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94751024246216</t>
+    <t xml:space="preserve">2.88441348075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94751000404358</t>
   </si>
   <si>
     <t xml:space="preserve">2.92046856880188</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">2.28048944473267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.415696144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31654453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36161351203918</t>
+    <t xml:space="preserve">2.41569638252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3165442943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36161327362061</t>
   </si>
   <si>
     <t xml:space="preserve">2.50583434104919</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">2.4427375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37964129447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3706271648407</t>
+    <t xml:space="preserve">2.37964105606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37062764167786</t>
   </si>
   <si>
     <t xml:space="preserve">2.27147555351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26246190071106</t>
+    <t xml:space="preserve">2.26246166229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.28950309753418</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555794715881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851675033569</t>
+    <t xml:space="preserve">2.32555842399597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851698875427</t>
   </si>
   <si>
     <t xml:space="preserve">2.343585729599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21739292144775</t>
+    <t xml:space="preserve">2.21739268302917</t>
   </si>
   <si>
     <t xml:space="preserve">2.20837903022766</t>
@@ -68185,7 +68185,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.4483217593</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>100</v>
@@ -68206,6 +68206,32 @@
         <v>857</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.5766203704</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>1150</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>2.13000011444092</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>2.13000011444092</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>2.13000011444092</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>862</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034141540527</t>
+    <t xml:space="preserve">1.75034153461456</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538803100586</t>
+    <t xml:space="preserve">1.74538791179657</t>
   </si>
   <si>
     <t xml:space="preserve">1.69254720211029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70245480537415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6760345697403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66612696647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63888132572174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61163520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59347152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48613917827606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59264588356018</t>
+    <t xml:space="preserve">1.70245492458344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67603468894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66612708568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63888120651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61163532733917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59347128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48613905906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5926456451416</t>
   </si>
   <si>
     <t xml:space="preserve">1.59182000160217</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">1.58604061603546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6017279624939</t>
+    <t xml:space="preserve">1.60172784328461</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521509170532</t>
@@ -95,61 +95,61 @@
     <t xml:space="preserve">1.51255929470062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53980529308319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56539988517761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53567707538605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45311379432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50595438480377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46137022972107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4423805475235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51833879947662</t>
+    <t xml:space="preserve">1.53980541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56540012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53567695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45311403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50595450401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46136999130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44238066673279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51833868026733</t>
   </si>
   <si>
     <t xml:space="preserve">1.65126574039459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63475298881531</t>
+    <t xml:space="preserve">1.6347531080246</t>
   </si>
   <si>
     <t xml:space="preserve">1.65621948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64300942420959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63723003864288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64218354225159</t>
+    <t xml:space="preserve">1.64300930500031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63722991943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64218366146088</t>
   </si>
   <si>
     <t xml:space="preserve">1.63970685005188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66777849197388</t>
+    <t xml:space="preserve">1.66777837276459</t>
   </si>
   <si>
     <t xml:space="preserve">1.60503029823303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59842526912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870245933533</t>
+    <t xml:space="preserve">1.59842538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870234012604</t>
   </si>
   <si>
     <t xml:space="preserve">1.64053249359131</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">1.63227617740631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60255336761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57283043861389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58934307098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58438920974731</t>
+    <t xml:space="preserve">1.60255312919617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57283055782318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58934319019318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58438944816589</t>
   </si>
   <si>
     <t xml:space="preserve">1.5678768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5571436882019</t>
+    <t xml:space="preserve">1.55714380741119</t>
   </si>
   <si>
     <t xml:space="preserve">1.53402578830719</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">1.54310786724091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55466663837433</t>
+    <t xml:space="preserve">1.55466651916504</t>
   </si>
   <si>
     <t xml:space="preserve">1.5596204996109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55218958854675</t>
+    <t xml:space="preserve">1.55218970775604</t>
   </si>
   <si>
     <t xml:space="preserve">1.55053853988647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50265192985535</t>
+    <t xml:space="preserve">1.50265181064606</t>
   </si>
   <si>
     <t xml:space="preserve">1.4869647026062</t>
@@ -206,25 +206,25 @@
     <t xml:space="preserve">1.53237462043762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49026727676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5150363445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779046535492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623133659363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50760555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5010005235672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49439525604248</t>
+    <t xml:space="preserve">1.49026739597321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51503622531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47623157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50760543346405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50100040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49439537525177</t>
   </si>
   <si>
     <t xml:space="preserve">1.48366224765778</t>
@@ -233,13 +233,16 @@
     <t xml:space="preserve">1.45971882343292</t>
   </si>
   <si>
+    <t xml:space="preserve">1.45971870422363</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.45299983024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46223855018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43284261226654</t>
+    <t xml:space="preserve">1.46223866939545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43284249305725</t>
   </si>
   <si>
     <t xml:space="preserve">1.43536233901978</t>
@@ -260,13 +263,13 @@
     <t xml:space="preserve">1.43620204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44292116165161</t>
+    <t xml:space="preserve">1.4429212808609</t>
   </si>
   <si>
     <t xml:space="preserve">1.44880044460297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47819626331329</t>
+    <t xml:space="preserve">1.47819650173187</t>
   </si>
   <si>
     <t xml:space="preserve">1.44460082054138</t>
@@ -275,7 +278,7 @@
     <t xml:space="preserve">1.42360401153564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43032276630402</t>
+    <t xml:space="preserve">1.43032264709473</t>
   </si>
   <si>
     <t xml:space="preserve">1.46139883995056</t>
@@ -284,43 +287,43 @@
     <t xml:space="preserve">1.40260672569275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4084860086441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3782502412796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42444372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41604471206665</t>
+    <t xml:space="preserve">1.40848588943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37825012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42444360256195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41604483127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.46979761123657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42780315876007</t>
+    <t xml:space="preserve">1.42780327796936</t>
   </si>
   <si>
     <t xml:space="preserve">1.42192399501801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47567665576935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44796049594879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735631465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43368244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45803904533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45215976238251</t>
+    <t xml:space="preserve">1.47567677497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44796025753021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43368232250214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45803892612457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4521598815918</t>
   </si>
   <si>
     <t xml:space="preserve">1.48491537570953</t>
@@ -329,34 +332,34 @@
     <t xml:space="preserve">1.46391832828522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46643805503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4689576625824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48575520515442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45887887477875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4563592672348</t>
+    <t xml:space="preserve">1.46643793582916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46895754337311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48575532436371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45887899398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45635914802551</t>
   </si>
   <si>
     <t xml:space="preserve">1.45719909667969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48827481269836</t>
+    <t xml:space="preserve">1.48827493190765</t>
   </si>
   <si>
     <t xml:space="preserve">1.43956160545349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47399687767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46727776527405</t>
+    <t xml:space="preserve">1.473996758461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46727788448334</t>
   </si>
   <si>
     <t xml:space="preserve">1.49835360050201</t>
@@ -365,43 +368,43 @@
     <t xml:space="preserve">1.50927209854126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5033928155899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49499380588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48743486404419</t>
+    <t xml:space="preserve">1.50339269638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4949939250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48743498325348</t>
   </si>
   <si>
     <t xml:space="preserve">1.51011180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49919354915619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179170608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45048022270203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44628059864044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4387218952179</t>
+    <t xml:space="preserve">1.4991934299469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179158687592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45047998428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44628071784973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43872165679932</t>
   </si>
   <si>
     <t xml:space="preserve">1.50003325939178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48071587085724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48155605792999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51095199584961</t>
+    <t xml:space="preserve">1.48071599006653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4815559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51095175743103</t>
   </si>
   <si>
     <t xml:space="preserve">1.49583387374878</t>
@@ -416,49 +419,49 @@
     <t xml:space="preserve">1.47231709957123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49331402778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147727012634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50087320804596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52774930000305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53194892406464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690958976746</t>
+    <t xml:space="preserve">1.49331414699554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147715091705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50087308883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52774941921234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53194904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690947055817</t>
   </si>
   <si>
     <t xml:space="preserve">1.52355015277863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50423288345337</t>
+    <t xml:space="preserve">1.50423276424408</t>
   </si>
   <si>
     <t xml:space="preserve">1.51263153553009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454720020294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54538726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55294597148895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52019035816193</t>
+    <t xml:space="preserve">1.54454708099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54538714885712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55294585227966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52019047737122</t>
   </si>
   <si>
     <t xml:space="preserve">1.50843214988708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59578013420105</t>
+    <t xml:space="preserve">1.59578001499176</t>
   </si>
   <si>
     <t xml:space="preserve">1.53446853160858</t>
@@ -467,13 +470,13 @@
     <t xml:space="preserve">1.56050491333008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53026902675629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53110897541046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5512660741806</t>
+    <t xml:space="preserve">1.53026914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53110909461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55126619338989</t>
   </si>
   <si>
     <t xml:space="preserve">1.55210626125336</t>
@@ -485,7 +488,7 @@
     <t xml:space="preserve">1.58654141426086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56218469142914</t>
+    <t xml:space="preserve">1.56218457221985</t>
   </si>
   <si>
     <t xml:space="preserve">1.56974375247955</t>
@@ -494,34 +497,34 @@
     <t xml:space="preserve">1.57058346271515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60333907604218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54958641529083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55798530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57142353057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56470429897308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6108980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6117377281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60417902469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62517595291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62097680568695</t>
+    <t xml:space="preserve">1.60333895683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54958653450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55798542499542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5714236497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56470441818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61089789867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61173796653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60417890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62517607212067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62097656726837</t>
   </si>
   <si>
     <t xml:space="preserve">1.61257779598236</t>
@@ -530,7 +533,7 @@
     <t xml:space="preserve">1.59326040744781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58822119235992</t>
+    <t xml:space="preserve">1.58822107315063</t>
   </si>
   <si>
     <t xml:space="preserve">1.60753858089447</t>
@@ -539,19 +542,19 @@
     <t xml:space="preserve">1.63105535507202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61425745487213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71504366397858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77215588092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76543664932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75367856025696</t>
+    <t xml:space="preserve">1.61425757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71504378318787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77215564250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76543653011322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75367832183838</t>
   </si>
   <si>
     <t xml:space="preserve">1.72512209415436</t>
@@ -566,34 +569,34 @@
     <t xml:space="preserve">1.70664489269257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73856031894684</t>
+    <t xml:space="preserve">1.73856043815613</t>
   </si>
   <si>
     <t xml:space="preserve">1.69992566108704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67892873287201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6965663433075</t>
+    <t xml:space="preserve">1.67892861366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69656622409821</t>
   </si>
   <si>
     <t xml:space="preserve">1.69320678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70496499538422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77383577823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75871801376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68984711170197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69152700901031</t>
+    <t xml:space="preserve">1.70496511459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77383553981781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75871789455414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68984699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69152688980103</t>
   </si>
   <si>
     <t xml:space="preserve">1.66801011562347</t>
@@ -602,52 +605,52 @@
     <t xml:space="preserve">1.68816733360291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71336400508881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7318412065506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535798072815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71000421047211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71672332286835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016154766083</t>
+    <t xml:space="preserve">1.71336376667023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73184132575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535809993744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71000444889069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71672320365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016166687012</t>
   </si>
   <si>
     <t xml:space="preserve">1.74695932865143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77047610282898</t>
+    <t xml:space="preserve">1.77047634124756</t>
   </si>
   <si>
     <t xml:space="preserve">1.76375699043274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75031888484955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78895366191864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74024021625519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76207733154297</t>
+    <t xml:space="preserve">1.75031900405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78895354270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7402400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76207721233368</t>
   </si>
   <si>
     <t xml:space="preserve">1.73352086544037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79903209209442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78055441379547</t>
+    <t xml:space="preserve">1.799032330513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78055453300476</t>
   </si>
   <si>
     <t xml:space="preserve">1.82254886627197</t>
@@ -656,28 +659,28 @@
     <t xml:space="preserve">1.8695821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86454296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84774553775787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391408920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90480971336365</t>
+    <t xml:space="preserve">1.8645430803299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84774541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391420841217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90480995178223</t>
   </si>
   <si>
     <t xml:space="preserve">1.98488640785217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34267711639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3511962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24045157432556</t>
+    <t xml:space="preserve">2.34267735481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35119581222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2404510974884</t>
   </si>
   <si>
     <t xml:space="preserve">2.180819272995</t>
@@ -689,7 +692,7 @@
     <t xml:space="preserve">2.32223200798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34608459472656</t>
+    <t xml:space="preserve">2.34608435630798</t>
   </si>
   <si>
     <t xml:space="preserve">2.33415842056274</t>
@@ -698,25 +701,25 @@
     <t xml:space="preserve">2.24897027015686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20296883583069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14163303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07007503509521</t>
+    <t xml:space="preserve">2.20296835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14163279533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07007455825806</t>
   </si>
   <si>
     <t xml:space="preserve">2.01896190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95932984352112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01044273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06496334075928</t>
+    <t xml:space="preserve">1.9593300819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01044297218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06496357917786</t>
   </si>
   <si>
     <t xml:space="preserve">2.00192403793335</t>
@@ -725,118 +728,118 @@
     <t xml:space="preserve">2.02407312393188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06155586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04451870918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837105751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303740501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111051559448</t>
+    <t xml:space="preserve">2.06155633926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04451847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0683708190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303716659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04111075401306</t>
   </si>
   <si>
     <t xml:space="preserve">1.9797750711441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99340534210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97636747360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97125613689423</t>
+    <t xml:space="preserve">1.99340498447418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97636783123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97125625610352</t>
   </si>
   <si>
     <t xml:space="preserve">1.9746640920639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95081114768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93888461589813</t>
+    <t xml:space="preserve">1.95081126689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93888473510742</t>
   </si>
   <si>
     <t xml:space="preserve">1.92525470256805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92695868015289</t>
+    <t xml:space="preserve">1.9269585609436</t>
   </si>
   <si>
     <t xml:space="preserve">1.94229233264923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95762670040131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718087673187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866253852844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97296035289764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00703525543213</t>
+    <t xml:space="preserve">1.95762634277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718123435974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866206169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97295999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00703549385071</t>
   </si>
   <si>
     <t xml:space="preserve">2.01555418968201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98829424381256</t>
+    <t xml:space="preserve">1.98829400539398</t>
   </si>
   <si>
     <t xml:space="preserve">1.93206977844238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91673588752747</t>
+    <t xml:space="preserve">1.91673600673676</t>
   </si>
   <si>
     <t xml:space="preserve">1.91332828998566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90821707248688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93377351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94058883190155</t>
+    <t xml:space="preserve">1.90821695327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93377363681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94058895111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.13822507858276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25578498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22341370582581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3597149848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27452683448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41593909263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41253161430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3682336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30860185623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31200909614563</t>
+    <t xml:space="preserve">2.2557852268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22341346740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35971474647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27452635765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41593885421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41253185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36823391914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30860209465027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31200933456421</t>
   </si>
   <si>
     <t xml:space="preserve">2.31541705131531</t>
@@ -845,16 +848,16 @@
     <t xml:space="preserve">2.28986048698425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42445826530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41423559188843</t>
+    <t xml:space="preserve">2.42445802688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41423535346985</t>
   </si>
   <si>
     <t xml:space="preserve">2.36993741989136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39719772338867</t>
+    <t xml:space="preserve">2.39719796180725</t>
   </si>
   <si>
     <t xml:space="preserve">2.35801100730896</t>
@@ -872,10 +875,10 @@
     <t xml:space="preserve">2.31882452964783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34778833389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36312246322632</t>
+    <t xml:space="preserve">2.3477885723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36312222480774</t>
   </si>
   <si>
     <t xml:space="preserve">2.34438109397888</t>
@@ -887,22 +890,22 @@
     <t xml:space="preserve">2.3392698764801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36653017997742</t>
+    <t xml:space="preserve">2.36652994155884</t>
   </si>
   <si>
     <t xml:space="preserve">2.3767523765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38356781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27111887931824</t>
+    <t xml:space="preserve">2.38356757164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27111911773682</t>
   </si>
   <si>
     <t xml:space="preserve">2.25408148765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09392738342285</t>
+    <t xml:space="preserve">2.09392762184143</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696668624878</t>
@@ -911,10 +914,10 @@
     <t xml:space="preserve">2.10585379600525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10415029525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12800288200378</t>
+    <t xml:space="preserve">2.10415005683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12800264358521</t>
   </si>
   <si>
     <t xml:space="preserve">2.31712055206299</t>
@@ -926,19 +929,19 @@
     <t xml:space="preserve">2.30349063873291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29667568206787</t>
+    <t xml:space="preserve">2.29667592048645</t>
   </si>
   <si>
     <t xml:space="preserve">2.28815674781799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21659851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2387478351593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21489453315735</t>
+    <t xml:space="preserve">2.21659874916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23874735832214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21489477157593</t>
   </si>
   <si>
     <t xml:space="preserve">2.25748896598816</t>
@@ -947,100 +950,100 @@
     <t xml:space="preserve">2.24556231498718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23193216323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933820724487</t>
+    <t xml:space="preserve">2.2319324016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933844566345</t>
   </si>
   <si>
     <t xml:space="preserve">2.26259994506836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22511744499207</t>
+    <t xml:space="preserve">2.22511720657349</t>
   </si>
   <si>
     <t xml:space="preserve">2.23363637924194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23022842407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20637583732605</t>
+    <t xml:space="preserve">2.23022866249084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20637607574463</t>
   </si>
   <si>
     <t xml:space="preserve">2.29156422615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39379000663757</t>
+    <t xml:space="preserve">2.39379024505615</t>
   </si>
   <si>
     <t xml:space="preserve">2.41934657096863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53009152412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5726854801178</t>
+    <t xml:space="preserve">2.53009128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57268524169922</t>
   </si>
   <si>
     <t xml:space="preserve">2.54712915420532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58120465278625</t>
+    <t xml:space="preserve">2.58120441436768</t>
   </si>
   <si>
     <t xml:space="preserve">2.50453495979309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47045969963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46194052696228</t>
+    <t xml:space="preserve">2.47045946121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46194076538086</t>
   </si>
   <si>
     <t xml:space="preserve">2.38527131080627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41082763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30008339881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45342230796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60676074028015</t>
+    <t xml:space="preserve">2.41082787513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30008316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45342206954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60676050186157</t>
   </si>
   <si>
     <t xml:space="preserve">2.61527967453003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64935445785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43638396263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52157235145569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53861045837402</t>
+    <t xml:space="preserve">2.64935493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787386894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4363842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52157282829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53861021995544</t>
   </si>
   <si>
     <t xml:space="preserve">2.55564785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48749732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4449028968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26600766181946</t>
+    <t xml:space="preserve">2.48749709129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44490313529968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26600790023804</t>
   </si>
   <si>
     <t xml:space="preserve">2.14674425125122</t>
@@ -1058,9 +1061,6 @@
     <t xml:space="preserve">2.29221963882446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25748872756958</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.24880623817444</t>
   </si>
   <si>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">2.34431552886963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35299801826477</t>
+    <t xml:space="preserve">2.35299825668335</t>
   </si>
   <si>
     <t xml:space="preserve">2.3009021282196</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">2.32695007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28353714942932</t>
+    <t xml:space="preserve">2.28353691101074</t>
   </si>
   <si>
     <t xml:space="preserve">2.21407580375671</t>
@@ -1100,73 +1100,73 @@
     <t xml:space="preserve">2.15329742431641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13593173027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10988402366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18802785873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09251880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22275805473328</t>
+    <t xml:space="preserve">2.13593196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1098837852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18802762031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09251856803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22275829315186</t>
   </si>
   <si>
     <t xml:space="preserve">2.0751531124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0838360786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10120105743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0404224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01437449455261</t>
+    <t xml:space="preserve">2.08383631706238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10120153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04042267799377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01437473297119</t>
   </si>
   <si>
     <t xml:space="preserve">2.05778789520264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06647109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700927734375</t>
+    <t xml:space="preserve">2.06647086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700939655304</t>
   </si>
   <si>
     <t xml:space="preserve">2.00569200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964417934418</t>
+    <t xml:space="preserve">1.97964406013489</t>
   </si>
   <si>
     <t xml:space="preserve">1.96227872371674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02305722236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04910516738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03173995018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93623101711273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87545228004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281785488129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82335638999939</t>
+    <t xml:space="preserve">2.02305746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0491054058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03173971176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93623089790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87545251846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281761646271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82335650920868</t>
   </si>
   <si>
     <t xml:space="preserve">1.81467366218567</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">1.71916460990906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69311678409576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62799680233002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6323379278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67575144767761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68443429470062</t>
+    <t xml:space="preserve">1.69311666488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62799692153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63233804702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67575132846832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68443417549133</t>
   </si>
   <si>
     <t xml:space="preserve">1.71048200130463</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">1.7148232460022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69745802879333</t>
+    <t xml:space="preserve">1.69745814800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.64536213874817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59760773181915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60629022121429</t>
+    <t xml:space="preserve">1.59760761260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60629034042358</t>
   </si>
   <si>
     <t xml:space="preserve">1.61931419372559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61497282981873</t>
+    <t xml:space="preserve">1.61497271060944</t>
   </si>
   <si>
     <t xml:space="preserve">1.63667953014374</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">1.64970338344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68009257316589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65838611125946</t>
+    <t xml:space="preserve">1.68009269237518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65838599205017</t>
   </si>
   <si>
     <t xml:space="preserve">1.70179927349091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67140996456146</t>
+    <t xml:space="preserve">1.67141008377075</t>
   </si>
   <si>
     <t xml:space="preserve">1.66706871986389</t>
@@ -1244,16 +1244,16 @@
     <t xml:space="preserve">1.57155954837799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52814626693726</t>
+    <t xml:space="preserve">1.52814650535583</t>
   </si>
   <si>
     <t xml:space="preserve">1.51078116893768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54551160335541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56287705898285</t>
+    <t xml:space="preserve">1.54551148414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56287693977356</t>
   </si>
   <si>
     <t xml:space="preserve">1.6540447473526</t>
@@ -1265,10 +1265,10 @@
     <t xml:space="preserve">1.72784733772278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7625777721405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75389516353607</t>
+    <t xml:space="preserve">1.76257789134979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75389528274536</t>
   </si>
   <si>
     <t xml:space="preserve">1.78862583637238</t>
@@ -1277,82 +1277,82 @@
     <t xml:space="preserve">1.80599117279053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77126061916351</t>
+    <t xml:space="preserve">1.77126038074493</t>
   </si>
   <si>
     <t xml:space="preserve">1.74521255493164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83203899860382</t>
+    <t xml:space="preserve">1.83203887939453</t>
   </si>
   <si>
     <t xml:space="preserve">1.79730844497681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84072160720825</t>
+    <t xml:space="preserve">1.84072172641754</t>
   </si>
   <si>
     <t xml:space="preserve">1.86676967144012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91018307209015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9535961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94491350650787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98832666873932</t>
+    <t xml:space="preserve">1.91018295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359623432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94491338729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9883269071579</t>
   </si>
   <si>
     <t xml:space="preserve">1.97096157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91886579990387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92754817008972</t>
+    <t xml:space="preserve">1.91886556148529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92754828929901</t>
   </si>
   <si>
     <t xml:space="preserve">1.85808718204498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84940457344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413488864899</t>
+    <t xml:space="preserve">1.84940433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413500785828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62365543842316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6504191160202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61919498443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6013525724411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61027359962463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63703739643097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65487968921661</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6504191160202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61919510364532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6013525724411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61027383804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63703739643097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65487968921661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62365567684174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6459584236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64149796962738</t>
+    <t xml:space="preserve">1.64595866203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64149785041809</t>
   </si>
   <si>
     <t xml:space="preserve">1.65934014320374</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">1.68610382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68164312839508</t>
+    <t xml:space="preserve">1.68164324760437</t>
   </si>
   <si>
     <t xml:space="preserve">1.63257682323456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6058132648468</t>
+    <t xml:space="preserve">1.60581302642822</t>
   </si>
   <si>
     <t xml:space="preserve">1.62811613082886</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">1.61473429203033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58351016044617</t>
+    <t xml:space="preserve">1.58351027965546</t>
   </si>
   <si>
     <t xml:space="preserve">1.57904946804047</t>
@@ -1388,64 +1388,64 @@
     <t xml:space="preserve">1.552286028862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54336500167847</t>
+    <t xml:space="preserve">1.54336488246918</t>
   </si>
   <si>
     <t xml:space="preserve">1.59243142604828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56120729446411</t>
+    <t xml:space="preserve">1.56120717525482</t>
   </si>
   <si>
     <t xml:space="preserve">1.53890430927277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5567467212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57012832164764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58797085285187</t>
+    <t xml:space="preserve">1.55674660205841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57012844085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58797061443329</t>
   </si>
   <si>
     <t xml:space="preserve">1.57458901405334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5968918800354</t>
+    <t xml:space="preserve">1.59689176082611</t>
   </si>
   <si>
     <t xml:space="preserve">1.53444373607635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66380083560944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56566774845123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54782545566559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52552270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50768005847931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738950252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51660120487213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48983764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34263813495636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709870815277</t>
+    <t xml:space="preserve">1.66380095481873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56566786766052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5478253364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52552258968353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50768029689789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51660132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48983776569366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34263825416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709882736206</t>
   </si>
   <si>
     <t xml:space="preserve">1.32479584217072</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">1.19097816944122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2668080329895</t>
+    <t xml:space="preserve">1.26680815219879</t>
   </si>
   <si>
     <t xml:space="preserve">1.24450516700745</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.29803240299225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20436000823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27572917938232</t>
+    <t xml:space="preserve">1.20435988903046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27572929859161</t>
   </si>
   <si>
     <t xml:space="preserve">1.28465056419373</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">1.30249297618866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36940181255341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36494123935699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35601997375488</t>
+    <t xml:space="preserve">1.36940169334412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36494112014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35601985454559</t>
   </si>
   <si>
     <t xml:space="preserve">1.36048066616058</t>
@@ -1493,55 +1493,55 @@
     <t xml:space="preserve">1.40508651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44969248771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4541529417038</t>
+    <t xml:space="preserve">1.44969236850739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45415306091309</t>
   </si>
   <si>
     <t xml:space="preserve">1.44523191452026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43631064891815</t>
+    <t xml:space="preserve">1.43631076812744</t>
   </si>
   <si>
     <t xml:space="preserve">1.41846835613251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46307420730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39170467853546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40062606334686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4140077829361</t>
+    <t xml:space="preserve">1.46307408809662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39170479774475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40062594413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41400766372681</t>
   </si>
   <si>
     <t xml:space="preserve">1.38278353214264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724410533905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33817756175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35155928134918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29357171058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32925641536713</t>
+    <t xml:space="preserve">1.38724398612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33817768096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35155940055847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29357182979584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32925653457642</t>
   </si>
   <si>
     <t xml:space="preserve">1.33371698856354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31587469577789</t>
+    <t xml:space="preserve">1.3158745765686</t>
   </si>
   <si>
     <t xml:space="preserve">1.37386238574982</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">1.28018987178802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4095470905304</t>
+    <t xml:space="preserve">1.40954720973969</t>
   </si>
   <si>
     <t xml:space="preserve">1.39616537094116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45861351490021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37832295894623</t>
+    <t xml:space="preserve">1.4586136341095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37832283973694</t>
   </si>
   <si>
     <t xml:space="preserve">1.42292892932892</t>
@@ -1583,67 +1583,67 @@
     <t xml:space="preserve">1.24896585941315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46753466129303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44077134132385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48091661930084</t>
+    <t xml:space="preserve">1.46753478050232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44077122211456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48091650009155</t>
   </si>
   <si>
     <t xml:space="preserve">1.49429833889008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50321936607361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52998328208923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4987587928772</t>
+    <t xml:space="preserve">1.5032194852829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52998304367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49875891208649</t>
   </si>
   <si>
     <t xml:space="preserve">1.51214075088501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48537707328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52106177806854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72178852558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76639449596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.739630818367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81992161273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87344837188721</t>
+    <t xml:space="preserve">1.48537731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52106189727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72178840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76639437675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73963093757629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8734484910965</t>
   </si>
   <si>
     <t xml:space="preserve">1.82884275913239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83776390552521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78423690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77531576156616</t>
+    <t xml:space="preserve">1.8377640247345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78423678874969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77531564235687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73517036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085506916046</t>
+    <t xml:space="preserve">1.77085518836975</t>
   </si>
   <si>
     <t xml:space="preserve">1.72624909877777</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">1.73070979118347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74855208396912</t>
+    <t xml:space="preserve">1.74855220317841</t>
   </si>
   <si>
     <t xml:space="preserve">1.79315805435181</t>
@@ -1661,16 +1661,16 @@
     <t xml:space="preserve">1.71732795238495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74409151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77977633476257</t>
+    <t xml:space="preserve">1.74409162998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77977645397186</t>
   </si>
   <si>
     <t xml:space="preserve">1.81100046634674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84668493270874</t>
+    <t xml:space="preserve">1.84668517112732</t>
   </si>
   <si>
     <t xml:space="preserve">1.86452734470367</t>
@@ -1679,16 +1679,16 @@
     <t xml:space="preserve">1.80207920074463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75747334957123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0340301990509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0251088142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96266055107117</t>
+    <t xml:space="preserve">1.75747311115265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03402996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02510857582092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96266031265259</t>
   </si>
   <si>
     <t xml:space="preserve">1.92697596549988</t>
@@ -1700,25 +1700,25 @@
     <t xml:space="preserve">2.07863593101501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10539937019348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05187225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06079387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09647846221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43548345565796</t>
+    <t xml:space="preserve">2.1053991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05187249183655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06079339981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09647822380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43548321723938</t>
   </si>
   <si>
     <t xml:space="preserve">2.46224689483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39087748527527</t>
+    <t xml:space="preserve">2.39087724685669</t>
   </si>
   <si>
     <t xml:space="preserve">2.56037974357605</t>
@@ -1736,37 +1736,37 @@
     <t xml:space="preserve">2.64104104042053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74019289016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78526163101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73117876052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90244078636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10074424743652</t>
+    <t xml:space="preserve">2.74019241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78526139259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73117899894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90244102478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1007444858551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99257874488831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92948246002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84835815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76723408699036</t>
+    <t xml:space="preserve">2.92948222160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84835839271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76723384857178</t>
   </si>
   <si>
     <t xml:space="preserve">2.83934450149536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87539958953857</t>
+    <t xml:space="preserve">2.87539982795715</t>
   </si>
   <si>
     <t xml:space="preserve">2.82131695747375</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">2.55991673469543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53287553787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58695793151855</t>
+    <t xml:space="preserve">2.53287529945374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58695816993713</t>
   </si>
   <si>
     <t xml:space="preserve">2.65906858444214</t>
@@ -1793,16 +1793,16 @@
     <t xml:space="preserve">2.67709636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52386140823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62301349639893</t>
+    <t xml:space="preserve">2.5238618850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6230137348175</t>
   </si>
   <si>
     <t xml:space="preserve">2.57794427871704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597182273865</t>
+    <t xml:space="preserve">2.59597206115723</t>
   </si>
   <si>
     <t xml:space="preserve">2.55090308189392</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">2.56893062591553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79427528381348</t>
+    <t xml:space="preserve">2.79427552223206</t>
   </si>
   <si>
     <t xml:space="preserve">2.83033061027527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71315121650696</t>
+    <t xml:space="preserve">2.71315145492554</t>
   </si>
   <si>
     <t xml:space="preserve">2.70413756370544</t>
@@ -1829,22 +1829,22 @@
     <t xml:space="preserve">2.74920654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80328917503357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86638569831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0015926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09173059463501</t>
+    <t xml:space="preserve">2.80328893661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86638593673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00159287452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09173083305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.96553754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93849635124207</t>
+    <t xml:space="preserve">2.93849611282349</t>
   </si>
   <si>
     <t xml:space="preserve">2.81230306625366</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">2.47879266738892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63202738761902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91145491600037</t>
+    <t xml:space="preserve">2.63202714920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91145467758179</t>
   </si>
   <si>
     <t xml:space="preserve">2.9745512008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95652389526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01060652732849</t>
+    <t xml:space="preserve">2.95652341842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01060628890991</t>
   </si>
   <si>
     <t xml:space="preserve">3.01962018013</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">2.94751000404358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92046856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85737180709839</t>
+    <t xml:space="preserve">2.92046880722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85737204551697</t>
   </si>
   <si>
     <t xml:space="preserve">2.75822019577026</t>
@@ -1895,31 +1895,31 @@
     <t xml:space="preserve">2.68611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23542046546936</t>
+    <t xml:space="preserve">2.23542022705078</t>
   </si>
   <si>
     <t xml:space="preserve">2.19035148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28048920631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41569638252258</t>
+    <t xml:space="preserve">2.28048944473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.415696144104</t>
   </si>
   <si>
     <t xml:space="preserve">2.3165442943573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36161351203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50583434104919</t>
+    <t xml:space="preserve">2.36161327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50583410263062</t>
   </si>
   <si>
     <t xml:space="preserve">2.48780655860901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4427375793457</t>
+    <t xml:space="preserve">2.44273734092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.37964105606079</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">2.27147555351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26246166229248</t>
+    <t xml:space="preserve">2.26246190071106</t>
   </si>
   <si>
     <t xml:space="preserve">2.28950309753418</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555818557739</t>
+    <t xml:space="preserve">2.32555842399597</t>
   </si>
   <si>
     <t xml:space="preserve">2.29851698875427</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">2.23598384857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21758079528809</t>
+    <t xml:space="preserve">2.21758055686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.24518537521362</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">2.1715726852417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11636304855347</t>
+    <t xml:space="preserve">2.11636328697205</t>
   </si>
   <si>
     <t xml:space="preserve">2.08875823020935</t>
@@ -1997,16 +1997,16 @@
     <t xml:space="preserve">2.05195212364197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97833967208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98754107952118</t>
+    <t xml:space="preserve">1.97833955287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98754119873047</t>
   </si>
   <si>
     <t xml:space="preserve">2.07955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09796023368835</t>
+    <t xml:space="preserve">2.09795999526978</t>
   </si>
   <si>
     <t xml:space="preserve">2.13476634025574</t>
@@ -2015,28 +2015,28 @@
     <t xml:space="preserve">2.10716152191162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18997573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14396810531616</t>
+    <t xml:space="preserve">2.18997597694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14396786689758</t>
   </si>
   <si>
     <t xml:space="preserve">2.12556457519531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99674272537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96913802623749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95073473453522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00594425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93233156204224</t>
+    <t xml:space="preserve">1.99674260616302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9691379070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95073461532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00594449043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93233144283295</t>
   </si>
   <si>
     <t xml:space="preserve">1.91392827033997</t>
@@ -2045,22 +2045,22 @@
     <t xml:space="preserve">1.90472686290741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92312979698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94153308868408</t>
+    <t xml:space="preserve">1.9231299161911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94153320789337</t>
   </si>
   <si>
     <t xml:space="preserve">1.88632369041443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86792051792145</t>
+    <t xml:space="preserve">1.86792063713074</t>
   </si>
   <si>
     <t xml:space="preserve">1.84951746463776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89552521705627</t>
+    <t xml:space="preserve">1.89552533626556</t>
   </si>
   <si>
     <t xml:space="preserve">1.8587189912796</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">1.83111429214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81271123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80350947380066</t>
+    <t xml:space="preserve">1.8127110004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80350959300995</t>
   </si>
   <si>
     <t xml:space="preserve">1.79430794715881</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">1.82191264629364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02434754371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31879806518555</t>
+    <t xml:space="preserve">2.02434730529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31879782676697</t>
   </si>
   <si>
     <t xml:space="preserve">2.3740074634552</t>
@@ -2117,16 +2117,16 @@
     <t xml:space="preserve">2.25438690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30959630012512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28199172019958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26358819007874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30039477348328</t>
+    <t xml:space="preserve">2.3095965385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28199148178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26358842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3003945350647</t>
   </si>
   <si>
     <t xml:space="preserve">2.27279019355774</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">2.15316939353943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23669123649597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1989414691925</t>
+    <t xml:space="preserve">2.23669147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19894123077393</t>
   </si>
   <si>
     <t xml:space="preserve">2.18006634712219</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">2.20837879180908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11400365829468</t>
+    <t xml:space="preserve">2.11400389671326</t>
   </si>
   <si>
     <t xml:space="preserve">2.09512877464294</t>
@@ -2165,25 +2165,25 @@
     <t xml:space="preserve">1.98187851905823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91581583023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94412839412689</t>
+    <t xml:space="preserve">1.91581594944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94412851333618</t>
   </si>
   <si>
     <t xml:space="preserve">1.93469095230103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00075364112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03850364685059</t>
+    <t xml:space="preserve">2.00075340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03850388526917</t>
   </si>
   <si>
     <t xml:space="preserve">2.0101912021637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01962852478027</t>
+    <t xml:space="preserve">2.01962876319885</t>
   </si>
   <si>
     <t xml:space="preserve">2.0573787689209</t>
@@ -2192,19 +2192,19 @@
     <t xml:space="preserve">2.16119122505188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17062878608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22725391387939</t>
+    <t xml:space="preserve">2.17062902450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22725367546082</t>
   </si>
   <si>
     <t xml:space="preserve">2.24612903594971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26500415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.368816614151</t>
+    <t xml:space="preserve">2.26500391960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36881685256958</t>
   </si>
   <si>
     <t xml:space="preserve">2.34994173049927</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18950366973877</t>
+    <t xml:space="preserve">2.18950390815735</t>
   </si>
   <si>
     <t xml:space="preserve">2.21781635284424</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">1.95356595516205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97244083881378</t>
+    <t xml:space="preserve">1.97244107723236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92525339126587</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">1.85447204113007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86862826347351</t>
+    <t xml:space="preserve">1.8686283826828</t>
   </si>
   <si>
     <t xml:space="preserve">1.79312813282013</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.82144069671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8450345993042</t>
+    <t xml:space="preserve">1.84503448009491</t>
   </si>
   <si>
     <t xml:space="preserve">1.81672191619873</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">1.80256569385529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82615947723389</t>
+    <t xml:space="preserve">1.8261593580246</t>
   </si>
   <si>
     <t xml:space="preserve">1.83559703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87334716320038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83087825775146</t>
+    <t xml:space="preserve">1.87334704399109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83087837696075</t>
   </si>
   <si>
     <t xml:space="preserve">1.85919082164764</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">1.75537812709808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74594068527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76481556892395</t>
+    <t xml:space="preserve">1.74594056606293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76481568813324</t>
   </si>
   <si>
     <t xml:space="preserve">1.76009690761566</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">1.71290934085846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73178434371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70347166061401</t>
+    <t xml:space="preserve">1.73178446292877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7034717798233</t>
   </si>
   <si>
     <t xml:space="preserve">1.67987787723541</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">1.69875299930573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74122178554535</t>
+    <t xml:space="preserve">1.74122190475464</t>
   </si>
   <si>
     <t xml:space="preserve">1.7270655632019</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">1.78840935230255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77897191047668</t>
+    <t xml:space="preserve">1.7789717912674</t>
   </si>
   <si>
     <t xml:space="preserve">1.77425312995911</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">1.96300339698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02906632423401</t>
+    <t xml:space="preserve">2.02906608581543</t>
   </si>
   <si>
     <t xml:space="preserve">2.07625389099121</t>
@@ -5540,7 +5540,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H100" t="s">
         <v>9</v>
@@ -5566,7 +5566,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G101" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H101" t="s">
         <v>9</v>
@@ -5592,7 +5592,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G102" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H102" t="s">
         <v>9</v>
@@ -5618,7 +5618,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G103" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H103" t="s">
         <v>9</v>
@@ -5644,7 +5644,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G104" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H104" t="s">
         <v>9</v>
@@ -5670,7 +5670,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G105" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H105" t="s">
         <v>9</v>
@@ -5696,7 +5696,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G106" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H106" t="s">
         <v>9</v>
@@ -5722,7 +5722,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G107" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H107" t="s">
         <v>9</v>
@@ -5748,7 +5748,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H108" t="s">
         <v>9</v>
@@ -5774,7 +5774,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G109" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s">
         <v>9</v>
@@ -5800,7 +5800,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G110" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H110" t="s">
         <v>9</v>
@@ -5826,7 +5826,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G111" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H111" t="s">
         <v>9</v>
@@ -5852,7 +5852,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G112" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H112" t="s">
         <v>9</v>
@@ -5878,7 +5878,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G113" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H113" t="s">
         <v>9</v>
@@ -5904,7 +5904,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G114" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H114" t="s">
         <v>9</v>
@@ -5930,7 +5930,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G115" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H115" t="s">
         <v>9</v>
@@ -5956,7 +5956,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G116" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H116" t="s">
         <v>9</v>
@@ -5982,7 +5982,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G117" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H117" t="s">
         <v>9</v>
@@ -6008,7 +6008,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G118" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H118" t="s">
         <v>9</v>
@@ -6034,7 +6034,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G119" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -6060,7 +6060,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G120" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -6086,7 +6086,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G121" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -6112,7 +6112,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G122" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -6138,7 +6138,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G123" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -6164,7 +6164,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G124" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -6190,7 +6190,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G125" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -6216,7 +6216,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G126" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -6242,7 +6242,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G127" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -6268,7 +6268,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G128" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -6294,7 +6294,7 @@
         <v>1.75</v>
       </c>
       <c r="G129" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -6320,7 +6320,7 @@
         <v>1.75</v>
       </c>
       <c r="G130" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -6346,7 +6346,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G131" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -6372,7 +6372,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G132" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -6398,7 +6398,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G133" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -6424,7 +6424,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G134" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -6450,7 +6450,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G135" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -6476,7 +6476,7 @@
         <v>1.75</v>
       </c>
       <c r="G136" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6502,7 +6502,7 @@
         <v>1.75</v>
       </c>
       <c r="G137" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6528,7 +6528,7 @@
         <v>1.75</v>
       </c>
       <c r="G138" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6554,7 +6554,7 @@
         <v>1.75</v>
       </c>
       <c r="G139" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6580,7 +6580,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G140" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6606,7 +6606,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G141" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6632,7 +6632,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G142" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -6658,7 +6658,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G143" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6684,7 +6684,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G144" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6710,7 +6710,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G145" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6736,7 +6736,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G146" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6762,7 +6762,7 @@
         <v>1.75</v>
       </c>
       <c r="G147" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6788,7 +6788,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G148" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6814,7 +6814,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G149" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6840,7 +6840,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G150" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6866,7 +6866,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G151" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6892,7 +6892,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G152" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6918,7 +6918,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G153" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6944,7 +6944,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G154" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6970,7 +6970,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G155" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6996,7 +6996,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G156" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -7022,7 +7022,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G157" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -7048,7 +7048,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G158" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -7074,7 +7074,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G159" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -7100,7 +7100,7 @@
         <v>1.75</v>
       </c>
       <c r="G160" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -7126,7 +7126,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G161" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -7152,7 +7152,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G162" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -7178,7 +7178,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G163" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -7204,7 +7204,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G164" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -7230,7 +7230,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G165" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7256,7 +7256,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G166" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7282,7 +7282,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G167" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7308,7 +7308,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G168" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7334,7 +7334,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G169" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7360,7 +7360,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G170" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7386,7 +7386,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G171" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7412,7 +7412,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G172" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7438,7 +7438,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G173" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7464,7 +7464,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G174" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7490,7 +7490,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G175" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7516,7 +7516,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G176" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7542,7 +7542,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G177" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7568,7 +7568,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G178" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7594,7 +7594,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G179" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7620,7 +7620,7 @@
         <v>1.75</v>
       </c>
       <c r="G180" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7646,7 +7646,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G181" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7672,7 +7672,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G182" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7698,7 +7698,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7724,7 +7724,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G184" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7750,7 +7750,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G185" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7776,7 +7776,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G186" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7802,7 +7802,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G187" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7828,7 +7828,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G188" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7854,7 +7854,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7880,7 +7880,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G190" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7906,7 +7906,7 @@
         <v>1.75</v>
       </c>
       <c r="G191" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7932,7 +7932,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G192" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7958,7 +7958,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G193" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7984,7 +7984,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G194" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -8010,7 +8010,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G195" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8036,7 +8036,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G196" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8062,7 +8062,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G197" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8088,7 +8088,7 @@
         <v>1.75</v>
       </c>
       <c r="G198" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8114,7 +8114,7 @@
         <v>1.75</v>
       </c>
       <c r="G199" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8140,7 +8140,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G200" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8166,7 +8166,7 @@
         <v>1.75</v>
       </c>
       <c r="G201" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8192,7 +8192,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G202" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8218,7 +8218,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G203" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8244,7 +8244,7 @@
         <v>1.75</v>
       </c>
       <c r="G204" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8270,7 +8270,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G205" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8296,7 +8296,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G206" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8322,7 +8322,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G207" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8348,7 +8348,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G208" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8374,7 +8374,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G209" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8400,7 +8400,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G210" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8426,7 +8426,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G211" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8452,7 +8452,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G212" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8478,7 +8478,7 @@
         <v>1.75</v>
       </c>
       <c r="G213" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8504,7 +8504,7 @@
         <v>1.75</v>
       </c>
       <c r="G214" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8530,7 +8530,7 @@
         <v>1.75</v>
       </c>
       <c r="G215" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8556,7 +8556,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G216" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8582,7 +8582,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G217" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8608,7 +8608,7 @@
         <v>1.75</v>
       </c>
       <c r="G218" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8634,7 +8634,7 @@
         <v>1.75</v>
       </c>
       <c r="G219" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8660,7 +8660,7 @@
         <v>1.75</v>
       </c>
       <c r="G220" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8686,7 +8686,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G221" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8712,7 +8712,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G222" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8738,7 +8738,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G223" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8764,7 +8764,7 @@
         <v>1.75</v>
       </c>
       <c r="G224" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8790,7 +8790,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G225" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8816,7 +8816,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G226" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8842,7 +8842,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G227" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8868,7 +8868,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G228" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8894,7 +8894,7 @@
         <v>1.75</v>
       </c>
       <c r="G229" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8920,7 +8920,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G230" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8946,7 +8946,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G231" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8972,7 +8972,7 @@
         <v>1.75</v>
       </c>
       <c r="G232" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8998,7 +8998,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G233" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9024,7 +9024,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G234" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9050,7 +9050,7 @@
         <v>1.75</v>
       </c>
       <c r="G235" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9076,7 +9076,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G236" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9102,7 +9102,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G237" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9128,7 +9128,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G238" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9154,7 +9154,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G239" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9180,7 +9180,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G240" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9206,7 +9206,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G241" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9232,7 +9232,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G242" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9258,7 +9258,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G243" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9284,7 +9284,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G244" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9310,7 +9310,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G245" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9336,7 +9336,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G246" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9362,7 +9362,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G247" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9388,7 +9388,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G248" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9414,7 +9414,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G249" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9440,7 +9440,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G250" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9466,7 +9466,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G251" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9492,7 +9492,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G252" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9518,7 +9518,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G253" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9544,7 +9544,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G254" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9570,7 +9570,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G255" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9596,7 +9596,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G256" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9622,7 +9622,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G257" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9648,7 +9648,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G258" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9674,7 +9674,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G259" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9700,7 +9700,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G260" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9726,7 +9726,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G261" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9752,7 +9752,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G262" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9778,7 +9778,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9804,7 +9804,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G264" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9830,7 +9830,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G265" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9856,7 +9856,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G266" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9882,7 +9882,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G267" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9908,7 +9908,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G268" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9934,7 +9934,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G269" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9960,7 +9960,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G270" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9986,7 +9986,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G271" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10012,7 +10012,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G272" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10038,7 +10038,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G273" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10064,7 +10064,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G274" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10090,7 +10090,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G275" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10116,7 +10116,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G276" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10142,7 +10142,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G277" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10168,7 +10168,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G278" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10194,7 +10194,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G279" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10220,7 +10220,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G280" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10246,7 +10246,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G281" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10272,7 +10272,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G282" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10298,7 +10298,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G283" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10324,7 +10324,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G284" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10350,7 +10350,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G285" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10376,7 +10376,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G286" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10402,7 +10402,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G287" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10428,7 +10428,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G288" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10454,7 +10454,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G289" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10480,7 +10480,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G290" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10506,7 +10506,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G291" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10532,7 +10532,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G292" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10558,7 +10558,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G293" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10584,7 +10584,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G294" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10610,7 +10610,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G295" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10636,7 +10636,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G296" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10662,7 +10662,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G297" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10688,7 +10688,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G298" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10714,7 +10714,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G299" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10740,7 +10740,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G300" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10766,7 +10766,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G301" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10792,7 +10792,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G302" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10818,7 +10818,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G303" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10844,7 +10844,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G304" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10870,7 +10870,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G305" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10896,7 +10896,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G306" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10922,7 +10922,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G307" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10948,7 +10948,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10974,7 +10974,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G309" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11000,7 +11000,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G310" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11026,7 +11026,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G311" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11052,7 +11052,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G312" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11078,7 +11078,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G313" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11104,7 +11104,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G314" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11130,7 +11130,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G315" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11156,7 +11156,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11182,7 +11182,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G317" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11208,7 +11208,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G318" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11234,7 +11234,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G319" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11260,7 +11260,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G320" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11286,7 +11286,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G321" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11312,7 +11312,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G322" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11338,7 +11338,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G323" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11364,7 +11364,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G324" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11390,7 +11390,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G325" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11416,7 +11416,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G326" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11442,7 +11442,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G327" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11468,7 +11468,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G328" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11494,7 +11494,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G329" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11520,7 +11520,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G330" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11546,7 +11546,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G331" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11572,7 +11572,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G332" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11598,7 +11598,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G333" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11624,7 +11624,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G334" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11650,7 +11650,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G335" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11676,7 +11676,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G336" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11702,7 +11702,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G337" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11728,7 +11728,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G338" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11754,7 +11754,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G339" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11780,7 +11780,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G340" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11806,7 +11806,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G341" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11832,7 +11832,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G342" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11858,7 +11858,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G343" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11884,7 +11884,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G344" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11910,7 +11910,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G345" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11936,7 +11936,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11962,7 +11962,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G347" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11988,7 +11988,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G348" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12014,7 +12014,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G349" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12040,7 +12040,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G350" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12066,7 +12066,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G351" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12092,7 +12092,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G352" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12118,7 +12118,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G353" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12144,7 +12144,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G354" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12170,7 +12170,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G355" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12196,7 +12196,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G356" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12222,7 +12222,7 @@
         <v>2.75</v>
       </c>
       <c r="G357" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12248,7 +12248,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G358" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12274,7 +12274,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G359" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12300,7 +12300,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G360" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12326,7 +12326,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G361" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12352,7 +12352,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G362" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12378,7 +12378,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G363" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12404,7 +12404,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G364" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12430,7 +12430,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G365" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12456,7 +12456,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G366" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12482,7 +12482,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G367" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12508,7 +12508,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G368" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12534,7 +12534,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G369" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12560,7 +12560,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G370" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12586,7 +12586,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G371" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12612,7 +12612,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G372" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12638,7 +12638,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G373" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12664,7 +12664,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G374" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12690,7 +12690,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G375" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12716,7 +12716,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G376" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12742,7 +12742,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G377" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12768,7 +12768,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G378" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12794,7 +12794,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G379" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12820,7 +12820,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G380" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12846,7 +12846,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G381" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12872,7 +12872,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G382" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12898,7 +12898,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G383" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12924,7 +12924,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G384" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12950,7 +12950,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G385" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12976,7 +12976,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G386" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13002,7 +13002,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G387" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13028,7 +13028,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G388" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13054,7 +13054,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G389" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13080,7 +13080,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G390" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13106,7 +13106,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G391" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13132,7 +13132,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G392" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13158,7 +13158,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G393" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13184,7 +13184,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G394" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13210,7 +13210,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G395" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13236,7 +13236,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G396" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13262,7 +13262,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G397" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13288,7 +13288,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G398" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13314,7 +13314,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13340,7 +13340,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13366,7 +13366,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G401" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13392,7 +13392,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G402" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13418,7 +13418,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G403" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13444,7 +13444,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G404" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13470,7 +13470,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G405" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13496,7 +13496,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G406" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13522,7 +13522,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G407" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13548,7 +13548,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G408" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13574,7 +13574,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G409" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13600,7 +13600,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G410" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13626,7 +13626,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G411" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13652,7 +13652,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G412" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13678,7 +13678,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G413" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13704,7 +13704,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G414" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13730,7 +13730,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G415" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13756,7 +13756,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G416" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13782,7 +13782,7 @@
         <v>2.25</v>
       </c>
       <c r="G417" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13808,7 +13808,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G418" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13834,7 +13834,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G419" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13860,7 +13860,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G420" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13886,7 +13886,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G421" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13912,7 +13912,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G422" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13938,7 +13938,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13964,7 +13964,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G424" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13990,7 +13990,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G425" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14016,7 +14016,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G426" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14042,7 +14042,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G427" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14068,7 +14068,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14094,7 +14094,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G429" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14120,7 +14120,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G430" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14146,7 +14146,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G431" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14172,7 +14172,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G432" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14198,7 +14198,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G433" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14224,7 +14224,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G434" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14250,7 +14250,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G435" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14276,7 +14276,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G436" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14302,7 +14302,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G437" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14328,7 +14328,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G438" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14354,7 +14354,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14380,7 +14380,7 @@
         <v>2.75</v>
       </c>
       <c r="G440" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14406,7 +14406,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G441" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14432,7 +14432,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G442" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14458,7 +14458,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G443" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14484,7 +14484,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G444" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14510,7 +14510,7 @@
         <v>2.75</v>
       </c>
       <c r="G445" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14536,7 +14536,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G446" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14562,7 +14562,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G447" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14588,7 +14588,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G448" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14614,7 +14614,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G449" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14640,7 +14640,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G450" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14666,7 +14666,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G451" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14692,7 +14692,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G452" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14718,7 +14718,7 @@
         <v>2.75</v>
       </c>
       <c r="G453" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14744,7 +14744,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G454" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14770,7 +14770,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G455" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14796,7 +14796,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G456" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14822,7 +14822,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G457" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14848,7 +14848,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G458" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14874,7 +14874,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G459" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14900,7 +14900,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G460" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14926,7 +14926,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G461" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14952,7 +14952,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G462" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14978,7 +14978,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G463" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15004,7 +15004,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15030,7 +15030,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G465" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15056,7 +15056,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G466" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15082,7 +15082,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G467" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15108,7 +15108,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G468" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15134,7 +15134,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G469" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15160,7 +15160,7 @@
         <v>2.75</v>
       </c>
       <c r="G470" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15186,7 +15186,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G471" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15212,7 +15212,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G472" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15238,7 +15238,7 @@
         <v>2.75</v>
       </c>
       <c r="G473" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15264,7 +15264,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G474" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15290,7 +15290,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G475" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15316,7 +15316,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G476" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15342,7 +15342,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G477" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15368,7 +15368,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G478" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15394,7 +15394,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G479" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15420,7 +15420,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G480" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15446,7 +15446,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G481" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15472,7 +15472,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G482" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15498,7 +15498,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G483" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15524,7 +15524,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G484" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15550,7 +15550,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G485" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15576,7 +15576,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G486" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15602,7 +15602,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G487" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15628,7 +15628,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G488" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15654,7 +15654,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G489" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15680,7 +15680,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G490" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15706,7 +15706,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G491" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15732,7 +15732,7 @@
         <v>2.75</v>
       </c>
       <c r="G492" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15758,7 +15758,7 @@
         <v>2.75</v>
       </c>
       <c r="G493" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15784,7 +15784,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G494" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15810,7 +15810,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G495" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15836,7 +15836,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G496" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15862,7 +15862,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G497" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15888,7 +15888,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G498" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15914,7 +15914,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G499" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15940,7 +15940,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G500" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15966,7 +15966,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G501" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15992,7 +15992,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G502" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16018,7 +16018,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G503" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16044,7 +16044,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G504" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16070,7 +16070,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G505" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16096,7 +16096,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G506" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16122,7 +16122,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G507" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16148,7 +16148,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G508" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16174,7 +16174,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G509" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16200,7 +16200,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G510" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16226,7 +16226,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G511" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16252,7 +16252,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G512" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16278,7 +16278,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G513" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16304,7 +16304,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G514" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16330,7 +16330,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G515" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16356,7 +16356,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G516" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16382,7 +16382,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G517" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16408,7 +16408,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16434,7 +16434,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16460,7 +16460,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16486,7 +16486,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G521" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16512,7 +16512,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G522" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16538,7 +16538,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16564,7 +16564,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G524" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16590,7 +16590,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G525" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16616,7 +16616,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G526" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16642,7 +16642,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G527" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16668,7 +16668,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G528" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16694,7 +16694,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G529" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16720,7 +16720,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G530" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16746,7 +16746,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G531" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16772,7 +16772,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G532" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16798,7 +16798,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G533" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16824,7 +16824,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G534" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16850,7 +16850,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G535" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16876,7 +16876,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G536" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16902,7 +16902,7 @@
         <v>2.75</v>
       </c>
       <c r="G537" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16928,7 +16928,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G538" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16954,7 +16954,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G539" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16980,7 +16980,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G540" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17006,7 +17006,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G541" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17032,7 +17032,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G542" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17058,7 +17058,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G543" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17084,7 +17084,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17110,7 +17110,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G545" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17136,7 +17136,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G546" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17162,7 +17162,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G547" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17188,7 +17188,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G548" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17214,7 +17214,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G549" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17240,7 +17240,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G550" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17266,7 +17266,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G551" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17292,7 +17292,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G552" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17318,7 +17318,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G553" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17344,7 +17344,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17370,7 +17370,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17396,7 +17396,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G556" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17422,7 +17422,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G557" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17448,7 +17448,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G558" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17474,7 +17474,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G559" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17500,7 +17500,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G560" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17526,7 +17526,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17552,7 +17552,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17578,7 +17578,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G563" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17604,7 +17604,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G564" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17630,7 +17630,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G565" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17656,7 +17656,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G566" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17682,7 +17682,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G567" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17708,7 +17708,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G568" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17734,7 +17734,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G569" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17760,7 +17760,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G570" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17786,7 +17786,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G571" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17812,7 +17812,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17838,7 +17838,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G573" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17864,7 +17864,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G574" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17890,7 +17890,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G575" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17916,7 +17916,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G576" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17942,7 +17942,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G577" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17968,7 +17968,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G578" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17994,7 +17994,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G579" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18020,7 +18020,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18046,7 +18046,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18072,7 +18072,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G582" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18098,7 +18098,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G583" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18124,7 +18124,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G584" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18150,7 +18150,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G585" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18176,7 +18176,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G586" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18202,7 +18202,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G587" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18228,7 +18228,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G588" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18254,7 +18254,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G589" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18280,7 +18280,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G590" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18306,7 +18306,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G591" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18332,7 +18332,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G592" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18358,7 +18358,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G593" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18384,7 +18384,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G594" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18410,7 +18410,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G595" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18436,7 +18436,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G596" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18462,7 +18462,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G597" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18488,7 +18488,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G598" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18514,7 +18514,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G599" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18540,7 +18540,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G600" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18566,7 +18566,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G601" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18592,7 +18592,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G602" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18618,7 +18618,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18644,7 +18644,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G604" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18670,7 +18670,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G605" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18696,7 +18696,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G606" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18722,7 +18722,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G607" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18748,7 +18748,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G608" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18774,7 +18774,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G609" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18800,7 +18800,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G610" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18826,7 +18826,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18852,7 +18852,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G612" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18878,7 +18878,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G613" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18904,7 +18904,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G614" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18930,7 +18930,7 @@
         <v>2.5</v>
       </c>
       <c r="G615" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18956,7 +18956,7 @@
         <v>2.5</v>
       </c>
       <c r="G616" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18982,7 +18982,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G617" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19008,7 +19008,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G618" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19060,7 +19060,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G620" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19502,7 +19502,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19528,7 +19528,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19658,7 +19658,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G643" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19762,7 +19762,7 @@
         <v>2.5</v>
       </c>
       <c r="G647" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19840,7 +19840,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G650" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19866,7 +19866,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G651" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19892,7 +19892,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G652" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19944,7 +19944,7 @@
         <v>2.5</v>
       </c>
       <c r="G654" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20074,7 +20074,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20204,7 +20204,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G664" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -68390,7 +68390,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6566782407</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>2122</v>
@@ -68411,6 +68411,32 @@
         <v>860</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6397916667</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>848</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034141540527</t>
+    <t xml:space="preserve">1.75034165382385</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
@@ -50,67 +50,67 @@
     <t xml:space="preserve">1.69254732131958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70245504379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68429100513458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6760345697403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66612696647644</t>
+    <t xml:space="preserve">1.70245516300201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67603468894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66612708568573</t>
   </si>
   <si>
     <t xml:space="preserve">1.63888120651245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61163532733917</t>
+    <t xml:space="preserve">1.61163544654846</t>
   </si>
   <si>
     <t xml:space="preserve">1.59347140789032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48613882064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59264576435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59182024002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58604061603546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172784328461</t>
+    <t xml:space="preserve">1.48613917827606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59264588356018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59182012081146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58604073524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172772407532</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521509170532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56044614315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51255941390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53980529308319</t>
+    <t xml:space="preserve">1.56044602394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51255929470062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53980541229248</t>
   </si>
   <si>
     <t xml:space="preserve">1.56539988517761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53567731380463</t>
+    <t xml:space="preserve">1.53567695617676</t>
   </si>
   <si>
     <t xml:space="preserve">1.45311379432678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50595426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46137011051178</t>
+    <t xml:space="preserve">1.50595438480377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46137022972107</t>
   </si>
   <si>
     <t xml:space="preserve">1.44238066673279</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">1.51833868026733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65126574039459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6347531080246</t>
+    <t xml:space="preserve">1.65126585960388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63475286960602</t>
   </si>
   <si>
     <t xml:space="preserve">1.65621960163116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64300942420959</t>
+    <t xml:space="preserve">1.64300930500031</t>
   </si>
   <si>
     <t xml:space="preserve">1.6372298002243</t>
@@ -137,82 +137,82 @@
     <t xml:space="preserve">1.64218366146088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63970685005188</t>
+    <t xml:space="preserve">1.63970673084259</t>
   </si>
   <si>
     <t xml:space="preserve">1.66777837276459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60503029823303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5984251499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870257854462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053249359131</t>
+    <t xml:space="preserve">1.60503041744232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59842503070831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870245933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053237438202</t>
   </si>
   <si>
     <t xml:space="preserve">1.63227617740631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60255324840546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57283043861389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58934307098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58438944816589</t>
+    <t xml:space="preserve">1.60255336761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57283055782318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58934319019318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58438956737518</t>
   </si>
   <si>
     <t xml:space="preserve">1.56787693500519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55714344978333</t>
+    <t xml:space="preserve">1.55714356899261</t>
   </si>
   <si>
     <t xml:space="preserve">1.53402578830719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54310762882233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962061882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55219006538391</t>
+    <t xml:space="preserve">1.54310774803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466663837433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962038040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55218982696533</t>
   </si>
   <si>
     <t xml:space="preserve">1.55053842067719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50265169143677</t>
+    <t xml:space="preserve">1.50265192985535</t>
   </si>
   <si>
     <t xml:space="preserve">1.4869647026062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48861598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237462043762</t>
+    <t xml:space="preserve">1.48861610889435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237450122833</t>
   </si>
   <si>
     <t xml:space="preserve">1.49026739597321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5150363445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779046535492</t>
+    <t xml:space="preserve">1.51503622531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779058456421</t>
   </si>
   <si>
     <t xml:space="preserve">1.47623145580292</t>
@@ -221,19 +221,19 @@
     <t xml:space="preserve">1.50760555267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50100064277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49439513683319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48366224765778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45971882343292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45299983024597</t>
+    <t xml:space="preserve">1.5010005235672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49439537525177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48366236686707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45971894264221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45299971103668</t>
   </si>
   <si>
     <t xml:space="preserve">1.46223855018616</t>
@@ -245,22 +245,22 @@
     <t xml:space="preserve">1.43536221981049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43200266361237</t>
+    <t xml:space="preserve">1.43200290203094</t>
   </si>
   <si>
     <t xml:space="preserve">1.4261234998703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41100537776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44040167331696</t>
+    <t xml:space="preserve">1.41100561618805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44040143489838</t>
   </si>
   <si>
     <t xml:space="preserve">1.43620216846466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44292140007019</t>
+    <t xml:space="preserve">1.4429212808609</t>
   </si>
   <si>
     <t xml:space="preserve">1.44880032539368</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">1.44460093975067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42360401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4303230047226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46139872074127</t>
+    <t xml:space="preserve">1.42360389232635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43032288551331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46139860153198</t>
   </si>
   <si>
     <t xml:space="preserve">1.40260672569275</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">1.37825012207031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42444360256195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41604495048523</t>
+    <t xml:space="preserve">1.42444372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41604471206665</t>
   </si>
   <si>
     <t xml:space="preserve">1.46979749202728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42780339717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192411422729</t>
+    <t xml:space="preserve">1.42780315876007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192399501801</t>
   </si>
   <si>
     <t xml:space="preserve">1.47567665576935</t>
@@ -311,34 +311,34 @@
     <t xml:space="preserve">1.44796049594879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47735619544983</t>
+    <t xml:space="preserve">1.47735631465912</t>
   </si>
   <si>
     <t xml:space="preserve">1.43368244171143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45803904533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4521598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48491525650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46391832828522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46643805503845</t>
+    <t xml:space="preserve">1.45803892612457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45216000080109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48491537570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46391820907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46643793582916</t>
   </si>
   <si>
     <t xml:space="preserve">1.46895754337311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.485755443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45887887477875</t>
+    <t xml:space="preserve">1.48575532436371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45887899398804</t>
   </si>
   <si>
     <t xml:space="preserve">1.4563592672348</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">1.45719921588898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48827493190765</t>
+    <t xml:space="preserve">1.48827481269836</t>
   </si>
   <si>
     <t xml:space="preserve">1.43956160545349</t>
@@ -356,94 +356,94 @@
     <t xml:space="preserve">1.47399687767029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727776527405</t>
+    <t xml:space="preserve">1.46727788448334</t>
   </si>
   <si>
     <t xml:space="preserve">1.49835360050201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50927209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50339293479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49499404430389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48743498325348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51011192798615</t>
+    <t xml:space="preserve">1.50927221775055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50339269638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4949939250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48743510246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51011168956757</t>
   </si>
   <si>
     <t xml:space="preserve">1.4991934299469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179146766663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45048022270203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44628071784973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43872165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5000331401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48071610927582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48155605792999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51095175743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49583387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50759208202362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49667358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47231709957123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49331426620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147703170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50087320804596</t>
+    <t xml:space="preserve">1.51179170608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45048010349274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44628059864044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4387218952179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50003325939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48071599006653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48155581951141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51095187664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49583399295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50759196281433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49667370319366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47231721878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49331438541412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147750854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50087308883667</t>
   </si>
   <si>
     <t xml:space="preserve">1.52774941921234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53194880485535</t>
+    <t xml:space="preserve">1.53194892406464</t>
   </si>
   <si>
     <t xml:space="preserve">1.52690958976746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52355015277863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50423276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51263165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54454696178436</t>
+    <t xml:space="preserve">1.52354991436005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50423264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51263153553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54454708099365</t>
   </si>
   <si>
     <t xml:space="preserve">1.54538702964783</t>
@@ -452,52 +452,52 @@
     <t xml:space="preserve">1.55294609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52019023895264</t>
+    <t xml:space="preserve">1.52019047737122</t>
   </si>
   <si>
     <t xml:space="preserve">1.50843214988708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59578025341034</t>
+    <t xml:space="preserve">1.59578001499176</t>
   </si>
   <si>
     <t xml:space="preserve">1.53446853160858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56050503253937</t>
+    <t xml:space="preserve">1.56050491333008</t>
   </si>
   <si>
     <t xml:space="preserve">1.53026914596558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53110897541046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55126619338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55210626125336</t>
+    <t xml:space="preserve">1.53110885620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55126631259918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55210614204407</t>
   </si>
   <si>
     <t xml:space="preserve">1.55378592014313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58654153347015</t>
+    <t xml:space="preserve">1.58654129505157</t>
   </si>
   <si>
     <t xml:space="preserve">1.56218469142914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56974363327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57058370113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60333931446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54958653450012</t>
+    <t xml:space="preserve">1.56974375247955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57058358192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60333907604218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54958641529083</t>
   </si>
   <si>
     <t xml:space="preserve">1.55798542499542</t>
@@ -506,82 +506,82 @@
     <t xml:space="preserve">1.57142353057861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56470453739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61089789867401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61173784732819</t>
+    <t xml:space="preserve">1.56470429897308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61089777946472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61173808574677</t>
   </si>
   <si>
     <t xml:space="preserve">1.60417890548706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62517595291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62097668647766</t>
+    <t xml:space="preserve">1.62517607212067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62097656726837</t>
   </si>
   <si>
     <t xml:space="preserve">1.61257779598236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59326028823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58822131156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60753858089447</t>
+    <t xml:space="preserve">1.59326040744781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58822119235992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60753846168518</t>
   </si>
   <si>
     <t xml:space="preserve">1.63105523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61425757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71504366397858</t>
+    <t xml:space="preserve">1.61425745487213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71504390239716</t>
   </si>
   <si>
     <t xml:space="preserve">1.77215564250946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76543664932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75367832183838</t>
+    <t xml:space="preserve">1.7654367685318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75367844104767</t>
   </si>
   <si>
     <t xml:space="preserve">1.72512221336365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74527966976166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72176277637482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70664489269257</t>
+    <t xml:space="preserve">1.74527955055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72176265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70664477348328</t>
   </si>
   <si>
     <t xml:space="preserve">1.73856055736542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69992554187775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67892861366272</t>
+    <t xml:space="preserve">1.69992578029633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67892873287201</t>
   </si>
   <si>
     <t xml:space="preserve">1.69656622409821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69320666790009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70496499538422</t>
+    <t xml:space="preserve">1.6932065486908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70496511459351</t>
   </si>
   <si>
     <t xml:space="preserve">1.77383553981781</t>
@@ -593,49 +593,49 @@
     <t xml:space="preserve">1.68984723091125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69152677059174</t>
+    <t xml:space="preserve">1.69152688980103</t>
   </si>
   <si>
     <t xml:space="preserve">1.66800999641418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68816733360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71336388587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73184144496918</t>
+    <t xml:space="preserve">1.68816745281219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71336376667023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73184156417847</t>
   </si>
   <si>
     <t xml:space="preserve">1.75535798072815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71000444889069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71672320365906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016142845154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74695909023285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047610282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375699043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031900405884</t>
+    <t xml:space="preserve">1.7100043296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71672332286835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016154766083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74695920944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77047598361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375687122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031888484955</t>
   </si>
   <si>
     <t xml:space="preserve">1.78895366191864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7402400970459</t>
+    <t xml:space="preserve">1.74024021625519</t>
   </si>
   <si>
     <t xml:space="preserve">1.76207733154297</t>
@@ -647,55 +647,55 @@
     <t xml:space="preserve">1.79903221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78055441379547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254898548126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86958241462708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86454319953918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84774541854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391420841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90480971336365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98488640785217</t>
+    <t xml:space="preserve">1.78055465221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254886627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86958229541779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8645430803299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84774553775787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391444683075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90480995178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98488664627075</t>
   </si>
   <si>
     <t xml:space="preserve">2.34267711639404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35119605064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24045133590698</t>
+    <t xml:space="preserve">2.35119581222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2404510974884</t>
   </si>
   <si>
     <t xml:space="preserve">2.180819272995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36482620239258</t>
+    <t xml:space="preserve">2.364825963974</t>
   </si>
   <si>
     <t xml:space="preserve">2.32223200798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34608483314514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33415842056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24897027015686</t>
+    <t xml:space="preserve">2.34608459472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33415818214417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24897003173828</t>
   </si>
   <si>
     <t xml:space="preserve">2.20296859741211</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">2.07007479667664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01896166801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95932996273041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01044273376465</t>
+    <t xml:space="preserve">2.01896190643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95932984352112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01044321060181</t>
   </si>
   <si>
     <t xml:space="preserve">2.06496357917786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00192403793335</t>
+    <t xml:space="preserve">2.00192356109619</t>
   </si>
   <si>
     <t xml:space="preserve">2.02407312393188</t>
@@ -728,82 +728,82 @@
     <t xml:space="preserve">2.06155610084534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04451823234558</t>
+    <t xml:space="preserve">2.04451847076416</t>
   </si>
   <si>
     <t xml:space="preserve">2.0683708190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303716659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111099243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9797750711441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99340510368347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97636759281158</t>
+    <t xml:space="preserve">2.05303740501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04111051559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97977530956268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99340522289276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97636783123016</t>
   </si>
   <si>
     <t xml:space="preserve">1.97125625610352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97466397285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95081102848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93888485431671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92525482177734</t>
+    <t xml:space="preserve">1.97466385364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95081126689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93888509273529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92525494098663</t>
   </si>
   <si>
     <t xml:space="preserve">1.92695832252502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94229257106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95762622356415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718123435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866218090057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97296011447906</t>
+    <t xml:space="preserve">1.94229233264923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95762658119202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718099594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866206169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97296047210693</t>
   </si>
   <si>
     <t xml:space="preserve">2.00703549385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01555418968201</t>
+    <t xml:space="preserve">2.01555395126343</t>
   </si>
   <si>
     <t xml:space="preserve">1.98829400539398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93206965923309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673576831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91332864761353</t>
+    <t xml:space="preserve">1.93206977844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673612594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91332840919495</t>
   </si>
   <si>
     <t xml:space="preserve">1.90821695327759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93377351760864</t>
+    <t xml:space="preserve">1.93377327919006</t>
   </si>
   <si>
     <t xml:space="preserve">1.94058859348297</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">2.13822531700134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2557852268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22341370582581</t>
+    <t xml:space="preserve">2.25578498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22341346740723</t>
   </si>
   <si>
     <t xml:space="preserve">2.3597149848938</t>
@@ -824,37 +824,37 @@
     <t xml:space="preserve">2.27452659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41593885421753</t>
+    <t xml:space="preserve">2.41593909263611</t>
   </si>
   <si>
     <t xml:space="preserve">2.41253185272217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36823344230652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30860185623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31200957298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31541705131531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28986024856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42445778846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41423535346985</t>
+    <t xml:space="preserve">2.3682336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30860161781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31200981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31541681289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28986048698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42445826530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41423511505127</t>
   </si>
   <si>
     <t xml:space="preserve">2.36993765830994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39719748497009</t>
+    <t xml:space="preserve">2.39719796180725</t>
   </si>
   <si>
     <t xml:space="preserve">2.35801100730896</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">2.30519437789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32052826881409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32904672622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31882405281067</t>
+    <t xml:space="preserve">2.32052803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32904696464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31882452964783</t>
   </si>
   <si>
     <t xml:space="preserve">2.34778833389282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36312246322632</t>
+    <t xml:space="preserve">2.36312222480774</t>
   </si>
   <si>
     <t xml:space="preserve">2.34438109397888</t>
@@ -884,22 +884,22 @@
     <t xml:space="preserve">2.32563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33926963806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36652970314026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37675261497498</t>
+    <t xml:space="preserve">2.3392698764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36653017997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3767523765564</t>
   </si>
   <si>
     <t xml:space="preserve">2.38356781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27111864089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25408148765564</t>
+    <t xml:space="preserve">2.27111911773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25408101081848</t>
   </si>
   <si>
     <t xml:space="preserve">2.09392738342285</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">2.15696692466736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10585355758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10415029525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12800312042236</t>
+    <t xml:space="preserve">2.10585379600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10415053367615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12800240516663</t>
   </si>
   <si>
     <t xml:space="preserve">2.31712079048157</t>
@@ -923,103 +923,103 @@
     <t xml:space="preserve">2.28304553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30349063873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29667592048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28815698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21659851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2387478351593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21489477157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25748896598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24556231498718</t>
+    <t xml:space="preserve">2.30349087715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29667568206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28815674781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21659874916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23874759674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21489453315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25748920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24556255340576</t>
   </si>
   <si>
     <t xml:space="preserve">2.23193264007568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18933844566345</t>
+    <t xml:space="preserve">2.18933820724487</t>
   </si>
   <si>
     <t xml:space="preserve">2.26260018348694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22511720657349</t>
+    <t xml:space="preserve">2.22511744499207</t>
   </si>
   <si>
     <t xml:space="preserve">2.23363614082336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23022866249084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20637583732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29156398773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39379000663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41934680938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53009176254272</t>
+    <t xml:space="preserve">2.23022890090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20637607574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29156422615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39379024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41934633255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53009152412415</t>
   </si>
   <si>
     <t xml:space="preserve">2.5726854801178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54712891578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58120441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50453519821167</t>
+    <t xml:space="preserve">2.5471293926239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58120393753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50453495979309</t>
   </si>
   <si>
     <t xml:space="preserve">2.47045969963074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46194100379944</t>
+    <t xml:space="preserve">2.46194076538086</t>
   </si>
   <si>
     <t xml:space="preserve">2.38527131080627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41082763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30008292198181</t>
+    <t xml:space="preserve">2.41082811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30008339881897</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342206954956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60676097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61527967453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64935517311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787363052368</t>
+    <t xml:space="preserve">2.60676074028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61527943611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64935493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787386894226</t>
   </si>
   <si>
     <t xml:space="preserve">2.43638443946838</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">2.53861021995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55564761161804</t>
+    <t xml:space="preserve">2.55564785003662</t>
   </si>
   <si>
     <t xml:space="preserve">2.48749709129333</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">2.4449028968811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26600766181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1467444896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671010971069</t>
+    <t xml:space="preserve">2.26600813865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14674401283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671034812927</t>
   </si>
   <si>
     <t xml:space="preserve">2.1185667514801</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">2.25748872756958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24880599975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2661714553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2748544216156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34431552886963</t>
+    <t xml:space="preserve">2.24880623817444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26617121696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27485418319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34431576728821</t>
   </si>
   <si>
     <t xml:space="preserve">2.35299801826477</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">2.32695007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2835373878479</t>
+    <t xml:space="preserve">2.28353691101074</t>
   </si>
   <si>
     <t xml:space="preserve">2.21407580375671</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">2.15329718589783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13593149185181</t>
+    <t xml:space="preserve">2.13593173027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.10988402366638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18802785873413</t>
+    <t xml:space="preserve">2.18802762031555</t>
   </si>
   <si>
     <t xml:space="preserve">2.0925190448761</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.22275829315186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07515358924866</t>
+    <t xml:space="preserve">2.0751531124115</t>
   </si>
   <si>
     <t xml:space="preserve">2.0838360786438</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">2.10120129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0404224395752</t>
+    <t xml:space="preserve">2.04042220115662</t>
   </si>
   <si>
     <t xml:space="preserve">2.01437473297119</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">2.06647038459778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99700927734375</t>
+    <t xml:space="preserve">1.99700939655304</t>
   </si>
   <si>
     <t xml:space="preserve">2.00569200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964429855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96227884292603</t>
+    <t xml:space="preserve">1.97964406013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96227896213531</t>
   </si>
   <si>
     <t xml:space="preserve">2.02305769920349</t>
@@ -1157,13 +1157,13 @@
     <t xml:space="preserve">2.03173995018005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93623089790344</t>
+    <t xml:space="preserve">1.93623077869415</t>
   </si>
   <si>
     <t xml:space="preserve">1.87545228004456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89281761646271</t>
+    <t xml:space="preserve">1.892817735672</t>
   </si>
   <si>
     <t xml:space="preserve">1.82335650920868</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">1.81467366218567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77994310855865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71916472911835</t>
+    <t xml:space="preserve">1.77994322776794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71916460990906</t>
   </si>
   <si>
     <t xml:space="preserve">1.69311678409576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62799668312073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63233816623688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67575120925903</t>
+    <t xml:space="preserve">1.62799680233002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63233804702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67575132846832</t>
   </si>
   <si>
     <t xml:space="preserve">1.68443405628204</t>
@@ -1202,34 +1202,34 @@
     <t xml:space="preserve">1.71482336521149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69745814800262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64536213874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59760773181915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60629022121429</t>
+    <t xml:space="preserve">1.69745802879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64536201953888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59760749340057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60629034042358</t>
   </si>
   <si>
     <t xml:space="preserve">1.61931419372559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61497294902802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63667929172516</t>
+    <t xml:space="preserve">1.61497282981873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63667941093445</t>
   </si>
   <si>
     <t xml:space="preserve">1.64970338344574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68009281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65838599205017</t>
+    <t xml:space="preserve">1.68009269237518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65838611125946</t>
   </si>
   <si>
     <t xml:space="preserve">1.70179927349091</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">1.67140996456146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6670686006546</t>
+    <t xml:space="preserve">1.66706871986389</t>
   </si>
   <si>
     <t xml:space="preserve">1.57155954837799</t>
@@ -1247,31 +1247,31 @@
     <t xml:space="preserve">1.52814626693726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5107809305191</t>
+    <t xml:space="preserve">1.51078104972839</t>
   </si>
   <si>
     <t xml:space="preserve">1.54551160335541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56287693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6540447473526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66272747516632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72784745693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7625777721405</t>
+    <t xml:space="preserve">1.56287705898285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65404486656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66272735595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72784733772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76257789134979</t>
   </si>
   <si>
     <t xml:space="preserve">1.75389528274536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78862583637238</t>
+    <t xml:space="preserve">1.78862571716309</t>
   </si>
   <si>
     <t xml:space="preserve">1.80599093437195</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">1.83203899860382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79730844497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84072172641754</t>
+    <t xml:space="preserve">1.7973085641861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84072160720825</t>
   </si>
   <si>
     <t xml:space="preserve">1.86676979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91018307209015</t>
+    <t xml:space="preserve">1.91018295288086</t>
   </si>
   <si>
     <t xml:space="preserve">1.95359635353088</t>
@@ -1304,40 +1304,40 @@
     <t xml:space="preserve">1.94491338729858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98832654953003</t>
+    <t xml:space="preserve">1.9883269071579</t>
   </si>
   <si>
     <t xml:space="preserve">1.97096109390259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91886579990387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9275484085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85808706283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84940457344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413512706757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62365543842316</t>
+    <t xml:space="preserve">1.91886568069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92754828929901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85808718204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84940445423126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413500785828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
     <t xml:space="preserve">1.6504191160202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61919498443604</t>
+    <t xml:space="preserve">1.61919486522675</t>
   </si>
   <si>
     <t xml:space="preserve">1.60135245323181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61027371883392</t>
+    <t xml:space="preserve">1.61027359962463</t>
   </si>
   <si>
     <t xml:space="preserve">1.63703715801239</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">1.65487957000732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62365555763245</t>
+    <t xml:space="preserve">1.62365567684174</t>
   </si>
   <si>
     <t xml:space="preserve">1.6459584236145</t>
@@ -1373,16 +1373,16 @@
     <t xml:space="preserve">1.60581314563751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62811625003815</t>
+    <t xml:space="preserve">1.62811613082886</t>
   </si>
   <si>
     <t xml:space="preserve">1.61473429203033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58351016044617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57904970645905</t>
+    <t xml:space="preserve">1.58351027965546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57904958724976</t>
   </si>
   <si>
     <t xml:space="preserve">1.55228590965271</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">1.54336488246918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59243142604828</t>
+    <t xml:space="preserve">1.59243154525757</t>
   </si>
   <si>
     <t xml:space="preserve">1.56120717525482</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">1.5567467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57012844085693</t>
+    <t xml:space="preserve">1.57012832164764</t>
   </si>
   <si>
     <t xml:space="preserve">1.58797073364258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57458901405334</t>
+    <t xml:space="preserve">1.57458913326263</t>
   </si>
   <si>
     <t xml:space="preserve">1.5968918800354</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">1.66380083560944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56566774845123</t>
+    <t xml:space="preserve">1.56566786766052</t>
   </si>
   <si>
     <t xml:space="preserve">1.54782545566559</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">1.5076801776886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42738950252533</t>
+    <t xml:space="preserve">1.42738962173462</t>
   </si>
   <si>
     <t xml:space="preserve">1.51660132408142</t>
@@ -1460,16 +1460,16 @@
     <t xml:space="preserve">1.24450516700745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29803228378296</t>
+    <t xml:space="preserve">1.29803240299225</t>
   </si>
   <si>
     <t xml:space="preserve">1.20435988903046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2757294178009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28465056419373</t>
+    <t xml:space="preserve">1.27572929859161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28465044498444</t>
   </si>
   <si>
     <t xml:space="preserve">1.30695354938507</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">1.30249297618866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36940181255341</t>
+    <t xml:space="preserve">1.36940169334412</t>
   </si>
   <si>
     <t xml:space="preserve">1.36494112014771</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.35601997375488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36048066616058</t>
+    <t xml:space="preserve">1.36048054695129</t>
   </si>
   <si>
     <t xml:space="preserve">1.40508651733398</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">1.45415306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44523179531097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43631052970886</t>
+    <t xml:space="preserve">1.44523191452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43631064891815</t>
   </si>
   <si>
     <t xml:space="preserve">1.41846835613251</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">1.29357171058655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32925629615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33371710777283</t>
+    <t xml:space="preserve">1.32925641536713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33371698856354</t>
   </si>
   <si>
     <t xml:space="preserve">1.31587469577789</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">1.3203352689743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28018975257874</t>
+    <t xml:space="preserve">1.28018987178802</t>
   </si>
   <si>
     <t xml:space="preserve">1.40954720973969</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">1.37832283973694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42292892932892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28911113739014</t>
+    <t xml:space="preserve">1.42292881011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28911125659943</t>
   </si>
   <si>
     <t xml:space="preserve">1.2712687253952</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">1.44077134132385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48091650009155</t>
+    <t xml:space="preserve">1.48091638088226</t>
   </si>
   <si>
     <t xml:space="preserve">1.49429833889008</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">1.52106201648712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72178840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76639449596405</t>
+    <t xml:space="preserve">1.72178852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76639437675476</t>
   </si>
   <si>
     <t xml:space="preserve">1.73963093757629</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">1.81992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87344872951508</t>
+    <t xml:space="preserve">1.87344861030579</t>
   </si>
   <si>
     <t xml:space="preserve">1.82884275913239</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">1.78423678874969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77531576156616</t>
+    <t xml:space="preserve">1.77531564235687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73517036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72624921798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73070967197418</t>
+    <t xml:space="preserve">1.77085506916046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72624909877777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73070979118347</t>
   </si>
   <si>
     <t xml:space="preserve">1.74855208396912</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">1.79315805435181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71732795238495</t>
+    <t xml:space="preserve">1.71732783317566</t>
   </si>
   <si>
     <t xml:space="preserve">1.74409162998199</t>
@@ -1670,16 +1670,16 @@
     <t xml:space="preserve">1.81100034713745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84668505191803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86452734470367</t>
+    <t xml:space="preserve">1.84668517112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86452722549438</t>
   </si>
   <si>
     <t xml:space="preserve">1.80207920074463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75747346878052</t>
+    <t xml:space="preserve">1.75747334957123</t>
   </si>
   <si>
     <t xml:space="preserve">2.0340301990509</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">2.02510857582092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96266067028046</t>
+    <t xml:space="preserve">1.96266055107117</t>
   </si>
   <si>
     <t xml:space="preserve">1.92697584629059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9805029630661</t>
+    <t xml:space="preserve">1.98050284385681</t>
   </si>
   <si>
     <t xml:space="preserve">2.07863616943359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10539960861206</t>
+    <t xml:space="preserve">2.10539937019348</t>
   </si>
   <si>
     <t xml:space="preserve">2.05187225341797</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">2.06079339981079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09647798538208</t>
+    <t xml:space="preserve">2.09647822380066</t>
   </si>
   <si>
     <t xml:space="preserve">2.43548321723938</t>
@@ -1718,10 +1718,10 @@
     <t xml:space="preserve">2.46224689483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39087724685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56037950515747</t>
+    <t xml:space="preserve">2.39087748527527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56037974357605</t>
   </si>
   <si>
     <t xml:space="preserve">2.60498595237732</t>
@@ -68523,7 +68523,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.5598726852</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>2897</v>
@@ -68544,6 +68544,32 @@
         <v>855</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.5309143519</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>850</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034165382385</t>
+    <t xml:space="preserve">1.75034153461456</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">1.74538791179657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69254744052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245516300201</t>
+    <t xml:space="preserve">1.69254732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245504379272</t>
   </si>
   <si>
     <t xml:space="preserve">1.68429112434387</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">1.67603468894958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66612708568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63888108730316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61163532733917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59347152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48613905906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59264576435089</t>
+    <t xml:space="preserve">1.66612696647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63888120651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61163544654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59347128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48613917827606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59264600276947</t>
   </si>
   <si>
     <t xml:space="preserve">1.59182024002075</t>
@@ -83,55 +83,55 @@
     <t xml:space="preserve">1.58604073524475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172784328461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521521091461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56044602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51255917549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53980541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56539976596832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53567707538605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45311391353607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50595438480377</t>
+    <t xml:space="preserve">1.60172772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521497249603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56044614315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5125595331192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53980529308319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56539988517761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53567719459534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45311379432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50595450401306</t>
   </si>
   <si>
     <t xml:space="preserve">1.46137011051178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44238066673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51833868026733</t>
+    <t xml:space="preserve">1.4423805475235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51833891868591</t>
   </si>
   <si>
     <t xml:space="preserve">1.6512656211853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63475298881531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65621948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64300918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63723003864288</t>
+    <t xml:space="preserve">1.6347531080246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65621960163116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64300942420959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63722991943359</t>
   </si>
   <si>
     <t xml:space="preserve">1.64218378067017</t>
@@ -146,43 +146,43 @@
     <t xml:space="preserve">1.60503041744232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5984251499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870245933533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053237438202</t>
+    <t xml:space="preserve">1.59842526912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870234012604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053249359131</t>
   </si>
   <si>
     <t xml:space="preserve">1.63227617740631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60255348682404</t>
+    <t xml:space="preserve">1.60255312919617</t>
   </si>
   <si>
     <t xml:space="preserve">1.57283043861389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58934330940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58438968658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5678768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5571436882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53402590751648</t>
+    <t xml:space="preserve">1.58934307098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58438944816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56787669658661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55714356899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53402578830719</t>
   </si>
   <si>
     <t xml:space="preserve">1.54310786724091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55466663837433</t>
+    <t xml:space="preserve">1.55466675758362</t>
   </si>
   <si>
     <t xml:space="preserve">1.55962061882019</t>
@@ -194,49 +194,49 @@
     <t xml:space="preserve">1.55053853988647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50265192985535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4869647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861610889435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237450122833</t>
+    <t xml:space="preserve">1.50265169143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696482181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237438201904</t>
   </si>
   <si>
     <t xml:space="preserve">1.49026715755463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5150363445282</t>
+    <t xml:space="preserve">1.51503622531891</t>
   </si>
   <si>
     <t xml:space="preserve">1.48779046535492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47623133659363</t>
+    <t xml:space="preserve">1.47623145580292</t>
   </si>
   <si>
     <t xml:space="preserve">1.50760555267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50100040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49439561367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48366212844849</t>
+    <t xml:space="preserve">1.5010005235672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49439525604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48366224765778</t>
   </si>
   <si>
     <t xml:space="preserve">1.45971882343292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45299983024597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46223843097687</t>
+    <t xml:space="preserve">1.45299971103668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46223866939545</t>
   </si>
   <si>
     <t xml:space="preserve">1.43284261226654</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">1.43536221981049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43200278282166</t>
+    <t xml:space="preserve">1.43200254440308</t>
   </si>
   <si>
     <t xml:space="preserve">1.42612338066101</t>
@@ -254,43 +254,43 @@
     <t xml:space="preserve">1.41100561618805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44040167331696</t>
+    <t xml:space="preserve">1.44040155410767</t>
   </si>
   <si>
     <t xml:space="preserve">1.43620204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4429212808609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44880032539368</t>
+    <t xml:space="preserve">1.44292104244232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44880044460297</t>
   </si>
   <si>
     <t xml:space="preserve">1.47819638252258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44460082054138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42360389232635</t>
+    <t xml:space="preserve">1.44460093975067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42360401153564</t>
   </si>
   <si>
     <t xml:space="preserve">1.43032276630402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40260672569275</t>
+    <t xml:space="preserve">1.46139848232269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40260660648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.4084860086441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37825000286102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42444384098053</t>
+    <t xml:space="preserve">1.3782502412796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42444348335266</t>
   </si>
   <si>
     <t xml:space="preserve">1.41604495048523</t>
@@ -299,31 +299,31 @@
     <t xml:space="preserve">1.46979749202728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42780327796936</t>
+    <t xml:space="preserve">1.42780339717865</t>
   </si>
   <si>
     <t xml:space="preserve">1.42192399501801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47567665576935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44796049594879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735619544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43368244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45803892612457</t>
+    <t xml:space="preserve">1.47567653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4479603767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735631465912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43368232250214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45803916454315</t>
   </si>
   <si>
     <t xml:space="preserve">1.4521598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48491525650024</t>
+    <t xml:space="preserve">1.48491537570953</t>
   </si>
   <si>
     <t xml:space="preserve">1.46391832828522</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">1.46643793582916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46895742416382</t>
+    <t xml:space="preserve">1.4689576625824</t>
   </si>
   <si>
     <t xml:space="preserve">1.485755443573</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">1.45887887477875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45635938644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45719933509827</t>
+    <t xml:space="preserve">1.4563592672348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45719921588898</t>
   </si>
   <si>
     <t xml:space="preserve">1.48827493190765</t>
@@ -359,34 +359,34 @@
     <t xml:space="preserve">1.46727788448334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49835348129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50927209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5033928155899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49499404430389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48743498325348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51011204719543</t>
+    <t xml:space="preserve">1.49835360050201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50927197933197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50339269638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49499416351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48743510246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51011180877686</t>
   </si>
   <si>
     <t xml:space="preserve">1.49919331073761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179158687592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45047998428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44628071784973</t>
+    <t xml:space="preserve">1.51179170608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45048022270203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44628083705902</t>
   </si>
   <si>
     <t xml:space="preserve">1.43872177600861</t>
@@ -404,22 +404,22 @@
     <t xml:space="preserve">1.51095175743103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49583399295807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50759220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49667358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47231698036194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49331438541412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147727012634</t>
+    <t xml:space="preserve">1.49583375453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5075923204422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49667394161224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47231709957123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49331426620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147715091705</t>
   </si>
   <si>
     <t xml:space="preserve">1.50087320804596</t>
@@ -428,28 +428,28 @@
     <t xml:space="preserve">1.52774953842163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53194904327393</t>
+    <t xml:space="preserve">1.53194892406464</t>
   </si>
   <si>
     <t xml:space="preserve">1.52690947055817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52355003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50423276424408</t>
+    <t xml:space="preserve">1.52354991436005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50423264503479</t>
   </si>
   <si>
     <t xml:space="preserve">1.51263153553009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54454720020294</t>
+    <t xml:space="preserve">1.54454731941223</t>
   </si>
   <si>
     <t xml:space="preserve">1.54538702964783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55294585227966</t>
+    <t xml:space="preserve">1.55294597148895</t>
   </si>
   <si>
     <t xml:space="preserve">1.52019059658051</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">1.50843214988708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59578001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53446865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56050503253937</t>
+    <t xml:space="preserve">1.59578025341034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53446853160858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56050491333008</t>
   </si>
   <si>
     <t xml:space="preserve">1.53026914596558</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">1.55126619338989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55210614204407</t>
+    <t xml:space="preserve">1.55210626125336</t>
   </si>
   <si>
     <t xml:space="preserve">1.55378580093384</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">1.56974363327026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57058370113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60333907604218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54958665370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55798518657684</t>
+    <t xml:space="preserve">1.57058358192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54958653450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55798530578613</t>
   </si>
   <si>
     <t xml:space="preserve">1.57142353057861</t>
@@ -509,55 +509,55 @@
     <t xml:space="preserve">1.56470441818237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61089813709259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61173796653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60417902469635</t>
+    <t xml:space="preserve">1.6108980178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61173808574677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60417890548706</t>
   </si>
   <si>
     <t xml:space="preserve">1.62517607212067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62097656726837</t>
+    <t xml:space="preserve">1.62097644805908</t>
   </si>
   <si>
     <t xml:space="preserve">1.61257779598236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59326028823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58822119235992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60753834247589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63105535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61425745487213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71504390239716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77215564250946</t>
+    <t xml:space="preserve">1.59326040744781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58822107315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60753846168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63105523586273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61425769329071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71504354476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77215576171875</t>
   </si>
   <si>
     <t xml:space="preserve">1.76543664932251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75367832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72512221336365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74527955055237</t>
+    <t xml:space="preserve">1.75367856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72512209415436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74527966976166</t>
   </si>
   <si>
     <t xml:space="preserve">1.72176277637482</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">1.70664477348328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73856043815613</t>
+    <t xml:space="preserve">1.73856031894684</t>
   </si>
   <si>
     <t xml:space="preserve">1.69992566108704</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">1.67892849445343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69656622409821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69320666790009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70496511459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77383553981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75871777534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68984735012054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69152677059174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66800999641418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68816733360291</t>
+    <t xml:space="preserve">1.69656610488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69320678710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70496499538422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77383542060852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75871753692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68984711170197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69152688980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66801011562347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68816745281219</t>
   </si>
   <si>
     <t xml:space="preserve">1.71336388587952</t>
@@ -608,28 +608,28 @@
     <t xml:space="preserve">1.73184144496918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75535798072815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7100043296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71672308444977</t>
+    <t xml:space="preserve">1.75535809993744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71000444889069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71672332286835</t>
   </si>
   <si>
     <t xml:space="preserve">1.73016154766083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74695909023285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047610282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031912326813</t>
+    <t xml:space="preserve">1.74695932865143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77047598361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375687122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031876564026</t>
   </si>
   <si>
     <t xml:space="preserve">1.78895354270935</t>
@@ -638,127 +638,127 @@
     <t xml:space="preserve">1.74024021625519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76207721233368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73352110385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903209209442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78055477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254886627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8695821762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8645430803299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84774529933929</t>
+    <t xml:space="preserve">1.76207733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73352122306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903197288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78055465221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254874706268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86958277225494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86454319953918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84774553775787</t>
   </si>
   <si>
     <t xml:space="preserve">1.78391432762146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90480947494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98488616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34267711639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35119605064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24045157432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.180819272995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36482620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32223200798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34608459472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33415818214417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24897003173828</t>
+    <t xml:space="preserve">1.90480983257294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98488640785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34267735481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3511962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24045133590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18081951141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.364825963974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3222324848175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34608483314514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33415842056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24897027015686</t>
   </si>
   <si>
     <t xml:space="preserve">2.20296835899353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14163279533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07007455825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01896190643311</t>
+    <t xml:space="preserve">2.14163303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07007503509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01896166801453</t>
   </si>
   <si>
     <t xml:space="preserve">1.9593300819397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01044273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06496334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00192379951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02407336235046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06155610084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04451823234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0683708190918</t>
+    <t xml:space="preserve">2.01044297218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06496357917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00192427635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02407312393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06155633926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04451870918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837105751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.05303740501404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04111051559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9797750711441</t>
+    <t xml:space="preserve">2.04111099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97977495193481</t>
   </si>
   <si>
     <t xml:space="preserve">1.99340546131134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97636735439301</t>
+    <t xml:space="preserve">1.97636771202087</t>
   </si>
   <si>
     <t xml:space="preserve">1.97125649452209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9746640920639</t>
+    <t xml:space="preserve">1.97466433048248</t>
   </si>
   <si>
     <t xml:space="preserve">1.95081126689911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93888473510742</t>
+    <t xml:space="preserve">1.93888509273529</t>
   </si>
   <si>
     <t xml:space="preserve">1.92525470256805</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">1.92695844173431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94229221343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95762622356415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718123435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866218090057</t>
+    <t xml:space="preserve">1.94229257106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95762634277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718087673187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866206169128</t>
   </si>
   <si>
     <t xml:space="preserve">1.97296023368835</t>
@@ -788,55 +788,55 @@
     <t xml:space="preserve">2.01555418968201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98829424381256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93206989765167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673588752747</t>
+    <t xml:space="preserve">1.98829412460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93207001686096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673600673676</t>
   </si>
   <si>
     <t xml:space="preserve">1.91332840919495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90821695327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93377327919006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94058871269226</t>
+    <t xml:space="preserve">1.90821707248688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93377339839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94058859348297</t>
   </si>
   <si>
     <t xml:space="preserve">2.13822531700134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2557852268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22341346740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35971450805664</t>
+    <t xml:space="preserve">2.25578498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22341322898865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35971474647522</t>
   </si>
   <si>
     <t xml:space="preserve">2.27452659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41593885421753</t>
+    <t xml:space="preserve">2.41593909263611</t>
   </si>
   <si>
     <t xml:space="preserve">2.41253161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36823391914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30860185623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31200933456421</t>
+    <t xml:space="preserve">2.3682336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30860161781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31200957298279</t>
   </si>
   <si>
     <t xml:space="preserve">2.31541705131531</t>
@@ -845,49 +845,49 @@
     <t xml:space="preserve">2.28986072540283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42445826530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41423535346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36993741989136</t>
+    <t xml:space="preserve">2.42445802688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41423559188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36993765830994</t>
   </si>
   <si>
     <t xml:space="preserve">2.39719772338867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35801100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30519437789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32052826881409</t>
+    <t xml:space="preserve">2.35801148414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30519461631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32052803039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.32904720306396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31882452964783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3477885723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36312222480774</t>
+    <t xml:space="preserve">2.31882429122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34778833389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36312246322632</t>
   </si>
   <si>
     <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32563996315002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33926963806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36652994155884</t>
+    <t xml:space="preserve">2.32563948631287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3392698764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.366530418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.37675261497498</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">2.27111911773682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25408101081848</t>
+    <t xml:space="preserve">2.25408148765564</t>
   </si>
   <si>
     <t xml:space="preserve">2.09392738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15696668624878</t>
+    <t xml:space="preserve">2.15696692466736</t>
   </si>
   <si>
     <t xml:space="preserve">2.10585379600525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10415029525757</t>
+    <t xml:space="preserve">2.10414981842041</t>
   </si>
   <si>
     <t xml:space="preserve">2.12800264358521</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">2.30349040031433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29667592048645</t>
+    <t xml:space="preserve">2.29667568206787</t>
   </si>
   <si>
     <t xml:space="preserve">2.28815698623657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21659874916077</t>
+    <t xml:space="preserve">2.21659851074219</t>
   </si>
   <si>
     <t xml:space="preserve">2.23874735832214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21489477157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25748920440674</t>
+    <t xml:space="preserve">2.21489453315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25748896598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.24556255340576</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">2.2319324016571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18933844566345</t>
+    <t xml:space="preserve">2.18933820724487</t>
   </si>
   <si>
     <t xml:space="preserve">2.26260018348694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22511720657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23363614082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23022890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20637583732605</t>
+    <t xml:space="preserve">2.22511744499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23363637924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23022842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20637607574463</t>
   </si>
   <si>
     <t xml:space="preserve">2.29156422615051</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">2.53009128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57268524169922</t>
+    <t xml:space="preserve">2.5726854801178</t>
   </si>
   <si>
     <t xml:space="preserve">2.54712915420532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58120441436768</t>
+    <t xml:space="preserve">2.5812041759491</t>
   </si>
   <si>
     <t xml:space="preserve">2.50453495979309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47045969963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46194100379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38527131080627</t>
+    <t xml:space="preserve">2.47045993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46194076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38527154922485</t>
   </si>
   <si>
     <t xml:space="preserve">2.41082787513733</t>
@@ -1007,40 +1007,40 @@
     <t xml:space="preserve">2.30008316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45342230796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60676050186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61527943611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64935493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787386894226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4363842010498</t>
+    <t xml:space="preserve">2.45342206954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60676074028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61527967453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6493546962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43638443946838</t>
   </si>
   <si>
     <t xml:space="preserve">2.52157258987427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53861045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55564785003662</t>
+    <t xml:space="preserve">2.53861021995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55564761161804</t>
   </si>
   <si>
     <t xml:space="preserve">2.48749732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4449028968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26600766181946</t>
+    <t xml:space="preserve">2.44490313529968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26600790023804</t>
   </si>
   <si>
     <t xml:space="preserve">2.14674401283264</t>
@@ -1049,46 +1049,46 @@
     <t xml:space="preserve">2.19671034812927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1185667514801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066240310669</t>
+    <t xml:space="preserve">2.11856651306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066216468811</t>
   </si>
   <si>
     <t xml:space="preserve">2.29221963882446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25748896598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24880599975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26617169380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27485370635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34431529045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35299801826477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30090236663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30958461761475</t>
+    <t xml:space="preserve">2.25748872756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24880623817444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26617121696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27485418319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34431552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35299777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3009021282196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30958485603333</t>
   </si>
   <si>
     <t xml:space="preserve">2.32695031166077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28353714942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21407556533813</t>
+    <t xml:space="preserve">2.28353691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21407532691956</t>
   </si>
   <si>
     <t xml:space="preserve">2.17934489250183</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">2.20539283752441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15329742431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13593196868896</t>
+    <t xml:space="preserve">2.15329694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13593173027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.10988402366638</t>
@@ -1109,25 +1109,25 @@
     <t xml:space="preserve">2.18802762031555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09251856803894</t>
+    <t xml:space="preserve">2.09251880645752</t>
   </si>
   <si>
     <t xml:space="preserve">2.22275829315186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0751531124115</t>
+    <t xml:space="preserve">2.07515358924866</t>
   </si>
   <si>
     <t xml:space="preserve">2.08383631706238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10120129585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0404224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01437425613403</t>
+    <t xml:space="preserve">2.10120153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04042267799377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01437473297119</t>
   </si>
   <si>
     <t xml:space="preserve">2.05778789520264</t>
@@ -1136,49 +1136,49 @@
     <t xml:space="preserve">2.06647086143494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99700939655304</t>
+    <t xml:space="preserve">1.99700951576233</t>
   </si>
   <si>
     <t xml:space="preserve">2.00569200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964406013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96227872371674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02305746078491</t>
+    <t xml:space="preserve">1.97964429855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96227884292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02305722236633</t>
   </si>
   <si>
     <t xml:space="preserve">2.0491054058075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03173995018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93623089790344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87545228004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281785488129</t>
+    <t xml:space="preserve">2.03174018859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93623101711273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87545216083527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281761646271</t>
   </si>
   <si>
     <t xml:space="preserve">1.82335638999939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81467366218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77994322776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71916449069977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69311690330505</t>
+    <t xml:space="preserve">1.81467378139496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77994310855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71916460990906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69311678409576</t>
   </si>
   <si>
     <t xml:space="preserve">1.62799680233002</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">1.67575132846832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68443417549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71048212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68877530097961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7148232460022</t>
+    <t xml:space="preserve">1.68443405628204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71048200130463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68877553939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71482348442078</t>
   </si>
   <si>
     <t xml:space="preserve">1.69745802879333</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">1.64536201953888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59760761260986</t>
+    <t xml:space="preserve">1.59760749340057</t>
   </si>
   <si>
     <t xml:space="preserve">1.60629022121429</t>
@@ -1217,22 +1217,22 @@
     <t xml:space="preserve">1.61931419372559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61497282981873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63667953014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64970338344574</t>
+    <t xml:space="preserve">1.61497294902802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63667941093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64970326423645</t>
   </si>
   <si>
     <t xml:space="preserve">1.68009269237518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65838611125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70179927349091</t>
+    <t xml:space="preserve">1.65838599205017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7017993927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.67140996456146</t>
@@ -1244,16 +1244,16 @@
     <t xml:space="preserve">1.5715594291687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52814638614655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51078128814697</t>
+    <t xml:space="preserve">1.52814626693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5107809305191</t>
   </si>
   <si>
     <t xml:space="preserve">1.54551160335541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56287705898285</t>
+    <t xml:space="preserve">1.56287682056427</t>
   </si>
   <si>
     <t xml:space="preserve">1.6540447473526</t>
@@ -1262,61 +1262,61 @@
     <t xml:space="preserve">1.66272735595703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72784745693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7625777721405</t>
+    <t xml:space="preserve">1.72784733772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76257789134979</t>
   </si>
   <si>
     <t xml:space="preserve">1.75389516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78862571716309</t>
+    <t xml:space="preserve">1.78862583637238</t>
   </si>
   <si>
     <t xml:space="preserve">1.80599105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77126049995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74521255493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83203899860382</t>
+    <t xml:space="preserve">1.77126038074493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74521243572235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83203887939453</t>
   </si>
   <si>
     <t xml:space="preserve">1.79730844497681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84072172641754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86676967144012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91018295288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9535961151123</t>
+    <t xml:space="preserve">1.84072160720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86676955223083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91018283367157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359623432159</t>
   </si>
   <si>
     <t xml:space="preserve">1.94491350650787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98832666873932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97096157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91886568069458</t>
+    <t xml:space="preserve">1.98832678794861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97096133232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.918865442276</t>
   </si>
   <si>
     <t xml:space="preserve">1.92754828929901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85808718204498</t>
+    <t xml:space="preserve">1.85808682441711</t>
   </si>
   <si>
     <t xml:space="preserve">1.84940445423126</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.88413500785828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62365543842316</t>
+    <t xml:space="preserve">1.62365531921387</t>
   </si>
   <si>
     <t xml:space="preserve">1.6504191160202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61919498443604</t>
+    <t xml:space="preserve">1.61919486522675</t>
   </si>
   <si>
     <t xml:space="preserve">1.6013525724411</t>
@@ -1340,76 +1340,76 @@
     <t xml:space="preserve">1.61027371883392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63703727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65487968921661</t>
+    <t xml:space="preserve">1.63703739643097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65487957000732</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64595854282379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64149808883667</t>
+    <t xml:space="preserve">1.6459584236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64149785041809</t>
   </si>
   <si>
     <t xml:space="preserve">1.65934026241302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66826140880585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68610370159149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68164312839508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63257682323456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60581314563751</t>
+    <t xml:space="preserve">1.66826128959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68610394001007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68164324760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63257670402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60581302642822</t>
   </si>
   <si>
     <t xml:space="preserve">1.62811613082886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61473429203033</t>
+    <t xml:space="preserve">1.61473417282104</t>
   </si>
   <si>
     <t xml:space="preserve">1.58351016044617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57904946804047</t>
+    <t xml:space="preserve">1.57904958724976</t>
   </si>
   <si>
     <t xml:space="preserve">1.552286028862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54336500167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59243130683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56120717525482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53890442848206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5567467212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57012832164764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58797073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57458889484406</t>
+    <t xml:space="preserve">1.54336476325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5924311876297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56120729446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53890430927277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55674660205841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57012844085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58797085285187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57458901405334</t>
   </si>
   <si>
     <t xml:space="preserve">1.5968918800354</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">1.66380095481873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56566786766052</t>
+    <t xml:space="preserve">1.56566774845123</t>
   </si>
   <si>
     <t xml:space="preserve">1.54782557487488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52552270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5076801776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738950252533</t>
+    <t xml:space="preserve">1.52552258968353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50768029689789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738938331604</t>
   </si>
   <si>
     <t xml:space="preserve">1.51660132408142</t>
@@ -1451,28 +1451,28 @@
     <t xml:space="preserve">1.32479584217072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19097816944122</t>
+    <t xml:space="preserve">1.19097805023193</t>
   </si>
   <si>
     <t xml:space="preserve">1.2668080329895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24450516700745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29803240299225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20436000823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27572929859161</t>
+    <t xml:space="preserve">1.24450528621674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29803228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20435988903046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2757294178009</t>
   </si>
   <si>
     <t xml:space="preserve">1.28465056419373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30695354938507</t>
+    <t xml:space="preserve">1.30695366859436</t>
   </si>
   <si>
     <t xml:space="preserve">1.30249297618866</t>
@@ -1484,31 +1484,31 @@
     <t xml:space="preserve">1.36494112014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35601985454559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36048066616058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40508639812469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44969248771667</t>
+    <t xml:space="preserve">1.35602009296417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36048054695129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40508651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44969236850739</t>
   </si>
   <si>
     <t xml:space="preserve">1.45415306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44523203372955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43631064891815</t>
+    <t xml:space="preserve">1.44523179531097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43631052970886</t>
   </si>
   <si>
     <t xml:space="preserve">1.41846835613251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46307408809662</t>
+    <t xml:space="preserve">1.46307420730591</t>
   </si>
   <si>
     <t xml:space="preserve">1.39170467853546</t>
@@ -1517,28 +1517,28 @@
     <t xml:space="preserve">1.40062594413757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4140077829361</t>
+    <t xml:space="preserve">1.41400754451752</t>
   </si>
   <si>
     <t xml:space="preserve">1.38278353214264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724410533905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33817768096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35155940055847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29357171058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32925653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33371698856354</t>
+    <t xml:space="preserve">1.38724398612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33817756175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35155928134918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29357182979584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32925641536713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33371710777283</t>
   </si>
   <si>
     <t xml:space="preserve">1.31587469577789</t>
@@ -1547,22 +1547,22 @@
     <t xml:space="preserve">1.37386226654053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31141412258148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32033538818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28018987178802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4095470905304</t>
+    <t xml:space="preserve">1.31141400337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3203352689743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28018999099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40954720973969</t>
   </si>
   <si>
     <t xml:space="preserve">1.39616537094116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4586136341095</t>
+    <t xml:space="preserve">1.45861375331879</t>
   </si>
   <si>
     <t xml:space="preserve">1.37832295894623</t>
@@ -1574,43 +1574,43 @@
     <t xml:space="preserve">1.28911113739014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27126860618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26234745979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24896574020386</t>
+    <t xml:space="preserve">1.2712687253952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26234757900238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24896585941315</t>
   </si>
   <si>
     <t xml:space="preserve">1.46753466129303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44077134132385</t>
+    <t xml:space="preserve">1.44077110290527</t>
   </si>
   <si>
     <t xml:space="preserve">1.48091650009155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49429833889008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50321936607361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52998316287994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4987587928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51214063167572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48537719249725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52106177806854</t>
+    <t xml:space="preserve">1.49429845809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5032194852829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52998304367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49875891208649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51214075088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48537731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52106201648712</t>
   </si>
   <si>
     <t xml:space="preserve">1.72178852558136</t>
@@ -1622,28 +1622,28 @@
     <t xml:space="preserve">1.73963093757629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81992161273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8734484910965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82884275913239</t>
+    <t xml:space="preserve">1.81992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87344861030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8288426399231</t>
   </si>
   <si>
     <t xml:space="preserve">1.83776390552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423678874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77531576156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73517036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77085518836975</t>
+    <t xml:space="preserve">1.78423690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77531564235687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73517048358917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77085494995117</t>
   </si>
   <si>
     <t xml:space="preserve">1.72624909877777</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">1.73070979118347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74855208396912</t>
+    <t xml:space="preserve">1.74855220317841</t>
   </si>
   <si>
     <t xml:space="preserve">1.79315793514252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71732783317566</t>
+    <t xml:space="preserve">1.71732795238495</t>
   </si>
   <si>
     <t xml:space="preserve">1.74409151077271</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">1.84668505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86452722549438</t>
+    <t xml:space="preserve">1.86452746391296</t>
   </si>
   <si>
     <t xml:space="preserve">1.80207908153534</t>
@@ -1688,25 +1688,25 @@
     <t xml:space="preserve">2.0251088142395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96266055107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92697596549988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98050284385681</t>
+    <t xml:space="preserve">1.96266043186188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9269757270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9805029630661</t>
   </si>
   <si>
     <t xml:space="preserve">2.07863569259644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1053991317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05187249183655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06079339981079</t>
+    <t xml:space="preserve">2.10539937019348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05187225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06079363822937</t>
   </si>
   <si>
     <t xml:space="preserve">2.09647822380066</t>
@@ -1715,52 +1715,52 @@
     <t xml:space="preserve">2.43548321723938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46224689483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39087748527527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56037974357605</t>
+    <t xml:space="preserve">2.462247133255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39087724685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56037998199463</t>
   </si>
   <si>
     <t xml:space="preserve">2.60498595237732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65005493164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61399960517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64104104042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74019265174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78526139259338</t>
+    <t xml:space="preserve">2.65005469322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61399984359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64104127883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74019289016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78526163101196</t>
   </si>
   <si>
     <t xml:space="preserve">2.73117876052856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90244102478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1007444858551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99257898330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92948246002197</t>
+    <t xml:space="preserve">2.90244078636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10074472427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99257874488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92948222160339</t>
   </si>
   <si>
     <t xml:space="preserve">2.84835839271545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76723432540894</t>
+    <t xml:space="preserve">2.76723408699036</t>
   </si>
   <si>
     <t xml:space="preserve">2.83934450149536</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">2.53287553787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58695793151855</t>
+    <t xml:space="preserve">2.58695840835571</t>
   </si>
   <si>
     <t xml:space="preserve">2.65906858444214</t>
@@ -1793,22 +1793,22 @@
     <t xml:space="preserve">2.67709612846375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52386164665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6230137348175</t>
+    <t xml:space="preserve">2.5238618850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62301349639893</t>
   </si>
   <si>
     <t xml:space="preserve">2.57794451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597229957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5509033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51484775543213</t>
+    <t xml:space="preserve">2.59597206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55090308189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51484799385071</t>
   </si>
   <si>
     <t xml:space="preserve">2.56893062591553</t>
@@ -1823,46 +1823,46 @@
     <t xml:space="preserve">2.71315121650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70413756370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74920654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80328917503357</t>
+    <t xml:space="preserve">2.70413732528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74920630455017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80328893661499</t>
   </si>
   <si>
     <t xml:space="preserve">2.86638593673706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0015926361084</t>
+    <t xml:space="preserve">3.00159287452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.09173059463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96553754806519</t>
+    <t xml:space="preserve">2.96553730964661</t>
   </si>
   <si>
     <t xml:space="preserve">2.93849611282349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81230306625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54188895225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47879266738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63202714920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91145467758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9745512008667</t>
+    <t xml:space="preserve">2.81230282783508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54188942909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4787929058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63202738761902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91145443916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97455143928528</t>
   </si>
   <si>
     <t xml:space="preserve">2.95652365684509</t>
@@ -1871,22 +1871,22 @@
     <t xml:space="preserve">3.01060628890991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01962018013</t>
+    <t xml:space="preserve">3.01962041854858</t>
   </si>
   <si>
     <t xml:space="preserve">2.98356509208679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88441348075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94751000404358</t>
+    <t xml:space="preserve">2.88441324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94751024246216</t>
   </si>
   <si>
     <t xml:space="preserve">2.92046856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85737204551697</t>
+    <t xml:space="preserve">2.85737180709839</t>
   </si>
   <si>
     <t xml:space="preserve">2.75822019577026</t>
@@ -1904,34 +1904,34 @@
     <t xml:space="preserve">2.28048944473267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41569638252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3165442943573</t>
+    <t xml:space="preserve">2.415696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31654453277588</t>
   </si>
   <si>
     <t xml:space="preserve">2.36161327362061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50583434104919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48780655860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4427375793457</t>
+    <t xml:space="preserve">2.50583410263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48780679702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44273734092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.37964105606079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37062764167786</t>
+    <t xml:space="preserve">2.37062740325928</t>
   </si>
   <si>
     <t xml:space="preserve">2.27147555351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26246166229248</t>
+    <t xml:space="preserve">2.26246190071106</t>
   </si>
   <si>
     <t xml:space="preserve">2.28950309753418</t>
@@ -1940,16 +1940,16 @@
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555842399597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851698875427</t>
+    <t xml:space="preserve">2.32555818557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851675033569</t>
   </si>
   <si>
     <t xml:space="preserve">2.343585729599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21739268302917</t>
+    <t xml:space="preserve">2.21739292144775</t>
   </si>
   <si>
     <t xml:space="preserve">2.20837903022766</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">2.23598384857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21758079528809</t>
+    <t xml:space="preserve">2.21758055686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.24518537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18077397346497</t>
+    <t xml:space="preserve">2.18077421188354</t>
   </si>
   <si>
     <t xml:space="preserve">2.16237092018127</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">2.1715726852417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11636304855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08875846862793</t>
+    <t xml:space="preserve">2.11636328697205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08875823020935</t>
   </si>
   <si>
     <t xml:space="preserve">2.07035541534424</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">2.05195212364197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97833967208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98754107952118</t>
+    <t xml:space="preserve">1.97833955287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98754119873047</t>
   </si>
   <si>
     <t xml:space="preserve">2.07955694198608</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">2.09795999526978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13476610183716</t>
+    <t xml:space="preserve">2.13476634025574</t>
   </si>
   <si>
     <t xml:space="preserve">2.10716152191162</t>
@@ -2021,25 +2021,25 @@
     <t xml:space="preserve">2.14396786689758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12556481361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99674272537231</t>
+    <t xml:space="preserve">2.12556457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99674260616302</t>
   </si>
   <si>
     <t xml:space="preserve">1.9691379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95073485374451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00594425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93233156204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91392838954926</t>
+    <t xml:space="preserve">1.95073461532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00594449043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93233144283295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91392827033997</t>
   </si>
   <si>
     <t xml:space="preserve">1.90472686290741</t>
@@ -2048,19 +2048,19 @@
     <t xml:space="preserve">1.9231299161911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94153296947479</t>
+    <t xml:space="preserve">1.94153320789337</t>
   </si>
   <si>
     <t xml:space="preserve">1.88632369041443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86792051792145</t>
+    <t xml:space="preserve">1.86792063713074</t>
   </si>
   <si>
     <t xml:space="preserve">1.84951746463776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89552521705627</t>
+    <t xml:space="preserve">1.89552533626556</t>
   </si>
   <si>
     <t xml:space="preserve">1.8587189912796</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">1.87712204456329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83111417293549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271111965179</t>
+    <t xml:space="preserve">1.83111429214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8127110004425</t>
   </si>
   <si>
     <t xml:space="preserve">1.80350959300995</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">1.8357150554657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82651352882385</t>
+    <t xml:space="preserve">1.82651340961456</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031581878662</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">1.82191264629364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02434754371643</t>
+    <t xml:space="preserve">2.02434730529785</t>
   </si>
   <si>
     <t xml:space="preserve">2.31879782676697</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">2.25438690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30959630012512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28199172019958</t>
+    <t xml:space="preserve">2.3095965385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28199148178101</t>
   </si>
   <si>
     <t xml:space="preserve">2.26358842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30039477348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27278995513916</t>
+    <t xml:space="preserve">2.3003945350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27279019355774</t>
   </si>
   <si>
     <t xml:space="preserve">2.33720111846924</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">2.15316939353943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23669123649597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1989414691925</t>
+    <t xml:space="preserve">2.23669147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19894123077393</t>
   </si>
   <si>
     <t xml:space="preserve">2.18006634712219</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">2.20837879180908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11400365829468</t>
+    <t xml:space="preserve">2.11400389671326</t>
   </si>
   <si>
     <t xml:space="preserve">2.09512877464294</t>
@@ -2165,25 +2165,25 @@
     <t xml:space="preserve">1.98187851905823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91581583023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94412839412689</t>
+    <t xml:space="preserve">1.91581594944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94412851333618</t>
   </si>
   <si>
     <t xml:space="preserve">1.93469095230103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00075364112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03850364685059</t>
+    <t xml:space="preserve">2.00075340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03850388526917</t>
   </si>
   <si>
     <t xml:space="preserve">2.0101912021637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01962852478027</t>
+    <t xml:space="preserve">2.01962876319885</t>
   </si>
   <si>
     <t xml:space="preserve">2.0573787689209</t>
@@ -2192,19 +2192,19 @@
     <t xml:space="preserve">2.16119122505188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17062878608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22725391387939</t>
+    <t xml:space="preserve">2.17062902450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22725367546082</t>
   </si>
   <si>
     <t xml:space="preserve">2.24612903594971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26500415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.368816614151</t>
+    <t xml:space="preserve">2.26500391960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36881685256958</t>
   </si>
   <si>
     <t xml:space="preserve">2.34994173049927</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18950366973877</t>
+    <t xml:space="preserve">2.18950390815735</t>
   </si>
   <si>
     <t xml:space="preserve">2.21781635284424</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">1.95356595516205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97244083881378</t>
+    <t xml:space="preserve">1.97244107723236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92525339126587</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">1.85447204113007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86862826347351</t>
+    <t xml:space="preserve">1.8686283826828</t>
   </si>
   <si>
     <t xml:space="preserve">1.79312813282013</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.82144069671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8450345993042</t>
+    <t xml:space="preserve">1.84503448009491</t>
   </si>
   <si>
     <t xml:space="preserve">1.81672191619873</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">1.80256569385529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82615947723389</t>
+    <t xml:space="preserve">1.8261593580246</t>
   </si>
   <si>
     <t xml:space="preserve">1.83559703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87334716320038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83087825775146</t>
+    <t xml:space="preserve">1.87334704399109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83087837696075</t>
   </si>
   <si>
     <t xml:space="preserve">1.85919082164764</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">1.75537812709808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74594068527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76481556892395</t>
+    <t xml:space="preserve">1.74594056606293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76481568813324</t>
   </si>
   <si>
     <t xml:space="preserve">1.76009690761566</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">1.71290934085846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73178434371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70347166061401</t>
+    <t xml:space="preserve">1.73178446292877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7034717798233</t>
   </si>
   <si>
     <t xml:space="preserve">1.67987787723541</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">1.69875299930573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74122178554535</t>
+    <t xml:space="preserve">1.74122190475464</t>
   </si>
   <si>
     <t xml:space="preserve">1.7270655632019</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">1.78840935230255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77897191047668</t>
+    <t xml:space="preserve">1.7789717912674</t>
   </si>
   <si>
     <t xml:space="preserve">1.77425312995911</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">1.96300339698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02906632423401</t>
+    <t xml:space="preserve">2.02906608581543</t>
   </si>
   <si>
     <t xml:space="preserve">2.07625389099121</t>
@@ -68653,7 +68653,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.4978356481</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>11914</v>
@@ -68674,6 +68674,32 @@
         <v>855</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.4704976852</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>848</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034165382385</t>
+    <t xml:space="preserve">1.75034141540527</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538791179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69254744052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245516300201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67603468894958</t>
+    <t xml:space="preserve">1.74538803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69254732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245504379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.684290766716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6760345697403</t>
   </si>
   <si>
     <t xml:space="preserve">1.66612696647644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63888108730316</t>
+    <t xml:space="preserve">1.63888120651245</t>
   </si>
   <si>
     <t xml:space="preserve">1.61163532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59347128868103</t>
+    <t xml:space="preserve">1.59347140789032</t>
   </si>
   <si>
     <t xml:space="preserve">1.48613905906677</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">1.59264588356018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59182012081146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58604073524475</t>
+    <t xml:space="preserve">1.59182024002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58604049682617</t>
   </si>
   <si>
     <t xml:space="preserve">1.60172784328461</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">1.58521509170532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56044614315033</t>
+    <t xml:space="preserve">1.56044626235962</t>
   </si>
   <si>
     <t xml:space="preserve">1.51255929470062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53980529308319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56539988517761</t>
+    <t xml:space="preserve">1.5398051738739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5654000043869</t>
   </si>
   <si>
     <t xml:space="preserve">1.53567719459534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45311379432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50595426559448</t>
+    <t xml:space="preserve">1.45311367511749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50595414638519</t>
   </si>
   <si>
     <t xml:space="preserve">1.46137022972107</t>
@@ -116,55 +116,55 @@
     <t xml:space="preserve">1.44238066673279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51833868026733</t>
+    <t xml:space="preserve">1.51833891868591</t>
   </si>
   <si>
     <t xml:space="preserve">1.65126574039459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63475322723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65621972084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64300942420959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63723015785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64218378067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63970673084259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66777837276459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60503017902374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59842526912689</t>
+    <t xml:space="preserve">1.6347531080246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65621948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64300918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63723003864288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64218389987946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63970685005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6677782535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60503029823303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5984251499176</t>
   </si>
   <si>
     <t xml:space="preserve">1.56870245933533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64053249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227593898773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60255336761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57283055782318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58934330940247</t>
+    <t xml:space="preserve">1.64053237438202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6322762966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60255348682404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57283043861389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58934319019318</t>
   </si>
   <si>
     <t xml:space="preserve">1.58438956737518</t>
@@ -182,37 +182,37 @@
     <t xml:space="preserve">1.54310786724091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55466651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5596204996109</t>
+    <t xml:space="preserve">1.55466663837433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962061882019</t>
   </si>
   <si>
     <t xml:space="preserve">1.55218982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55053842067719</t>
+    <t xml:space="preserve">1.55053853988647</t>
   </si>
   <si>
     <t xml:space="preserve">1.50265169143677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4869647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861598968506</t>
+    <t xml:space="preserve">1.48696458339691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861622810364</t>
   </si>
   <si>
     <t xml:space="preserve">1.53237462043762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49026715755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51503622531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779058456421</t>
+    <t xml:space="preserve">1.49026739597321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5150363445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779034614563</t>
   </si>
   <si>
     <t xml:space="preserve">1.47623157501221</t>
@@ -221,40 +221,40 @@
     <t xml:space="preserve">1.50760567188263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50100064277649</t>
+    <t xml:space="preserve">1.5010005235672</t>
   </si>
   <si>
     <t xml:space="preserve">1.49439537525177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48366212844849</t>
+    <t xml:space="preserve">1.48366224765778</t>
   </si>
   <si>
     <t xml:space="preserve">1.45971870422363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45299971103668</t>
+    <t xml:space="preserve">1.45299983024597</t>
   </si>
   <si>
     <t xml:space="preserve">1.46223866939545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43284249305725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43536233901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43200278282166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42612361907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41100561618805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44040143489838</t>
+    <t xml:space="preserve">1.43284261226654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43536221981049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43200266361237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4261234998703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41100549697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44040155410767</t>
   </si>
   <si>
     <t xml:space="preserve">1.43620204925537</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">1.44880044460297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47819626331329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460105895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42360389232635</t>
+    <t xml:space="preserve">1.478196144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460093975067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42360401153564</t>
   </si>
   <si>
     <t xml:space="preserve">1.43032276630402</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">1.46139860153198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40260672569275</t>
+    <t xml:space="preserve">1.40260660648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.40848588943481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37825000286102</t>
+    <t xml:space="preserve">1.3782502412796</t>
   </si>
   <si>
     <t xml:space="preserve">1.42444372177124</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">1.41604483127594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46979749202728</t>
+    <t xml:space="preserve">1.46979761123657</t>
   </si>
   <si>
     <t xml:space="preserve">1.42780327796936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42192399501801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47567677497864</t>
+    <t xml:space="preserve">1.42192423343658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47567665576935</t>
   </si>
   <si>
     <t xml:space="preserve">1.44796049594879</t>
@@ -314,22 +314,22 @@
     <t xml:space="preserve">1.47735643386841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43368256092072</t>
+    <t xml:space="preserve">1.43368232250214</t>
   </si>
   <si>
     <t xml:space="preserve">1.45803904533386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45216000080109</t>
+    <t xml:space="preserve">1.4521598815918</t>
   </si>
   <si>
     <t xml:space="preserve">1.48491537570953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46391820907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46643793582916</t>
+    <t xml:space="preserve">1.46391832828522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46643817424774</t>
   </si>
   <si>
     <t xml:space="preserve">1.46895742416382</t>
@@ -338,19 +338,19 @@
     <t xml:space="preserve">1.48575532436371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45887887477875</t>
+    <t xml:space="preserve">1.45887899398804</t>
   </si>
   <si>
     <t xml:space="preserve">1.4563592672348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45719933509827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48827493190765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43956172466278</t>
+    <t xml:space="preserve">1.45719921588898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48827481269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43956160545349</t>
   </si>
   <si>
     <t xml:space="preserve">1.47399699687958</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">1.49835360050201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50927197933197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50339269638062</t>
+    <t xml:space="preserve">1.50927209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5033928155899</t>
   </si>
   <si>
     <t xml:space="preserve">1.4949939250946</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">1.48743498325348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51011192798615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4991934299469</t>
+    <t xml:space="preserve">1.51011180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49919354915619</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179158687592</t>
@@ -386,46 +386,46 @@
     <t xml:space="preserve">1.45048010349274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44628071784973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43872177600861</t>
+    <t xml:space="preserve">1.44628059864044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4387218952179</t>
   </si>
   <si>
     <t xml:space="preserve">1.50003325939178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48071587085724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48155581951141</t>
+    <t xml:space="preserve">1.48071610927582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4815559387207</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095187664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49583375453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5075923204422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49667382240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47231709957123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49331414699554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147715091705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50087332725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52774941921234</t>
+    <t xml:space="preserve">1.49583399295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50759208202362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49667358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47231721878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49331426620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147703170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50087320804596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52774953842163</t>
   </si>
   <si>
     <t xml:space="preserve">1.53194892406464</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">1.52690958976746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52355015277863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50423276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51263153553009</t>
+    <t xml:space="preserve">1.52355003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50423264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51263165473938</t>
   </si>
   <si>
     <t xml:space="preserve">1.54454708099365</t>
@@ -449,25 +449,25 @@
     <t xml:space="preserve">1.54538714885712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55294609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52019035816193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5084320306778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59578013420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53446853160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56050515174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53026926517487</t>
+    <t xml:space="preserve">1.55294597148895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52019047737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50843214988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59578001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53446865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56050503253937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53026914596558</t>
   </si>
   <si>
     <t xml:space="preserve">1.53110885620117</t>
@@ -479,31 +479,31 @@
     <t xml:space="preserve">1.55210614204407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55378580093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58654153347015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56218457221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56974375247955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57058358192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60333895683289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54958641529083</t>
+    <t xml:space="preserve">1.55378592014313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58654141426086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56218469142914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56974363327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57058370113373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54958653450012</t>
   </si>
   <si>
     <t xml:space="preserve">1.55798542499542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57142341136932</t>
+    <t xml:space="preserve">1.57142353057861</t>
   </si>
   <si>
     <t xml:space="preserve">1.56470441818237</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">1.61089789867401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61173796653748</t>
+    <t xml:space="preserve">1.61173784732819</t>
   </si>
   <si>
     <t xml:space="preserve">1.60417890548706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62517607212067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62097656726837</t>
+    <t xml:space="preserve">1.62517583370209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62097680568695</t>
   </si>
   <si>
     <t xml:space="preserve">1.61257767677307</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">1.58822119235992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60753846168518</t>
+    <t xml:space="preserve">1.60753858089447</t>
   </si>
   <si>
     <t xml:space="preserve">1.63105535507202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61425769329071</t>
+    <t xml:space="preserve">1.61425757408142</t>
   </si>
   <si>
     <t xml:space="preserve">1.71504354476929</t>
@@ -548,22 +548,22 @@
     <t xml:space="preserve">1.77215564250946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76543688774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75367844104767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72512209415436</t>
+    <t xml:space="preserve">1.76543664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75367832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72512221336365</t>
   </si>
   <si>
     <t xml:space="preserve">1.74527966976166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72176289558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70664477348328</t>
+    <t xml:space="preserve">1.72176277637482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70664501190186</t>
   </si>
   <si>
     <t xml:space="preserve">1.73856043815613</t>
@@ -572,28 +572,28 @@
     <t xml:space="preserve">1.69992554187775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67892837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69656610488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69320678710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70496487617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77383553981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75871753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68984723091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69152688980103</t>
+    <t xml:space="preserve">1.67892873287201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69656622409821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69320666790009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70496511459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7738356590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75871777534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68984735012054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69152677059174</t>
   </si>
   <si>
     <t xml:space="preserve">1.66801011562347</t>
@@ -602,40 +602,40 @@
     <t xml:space="preserve">1.68816733360291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71336388587952</t>
+    <t xml:space="preserve">1.71336376667023</t>
   </si>
   <si>
     <t xml:space="preserve">1.73184144496918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75535798072815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7100043296814</t>
+    <t xml:space="preserve">1.75535809993744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71000444889069</t>
   </si>
   <si>
     <t xml:space="preserve">1.71672344207764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73016154766083</t>
+    <t xml:space="preserve">1.73016166687012</t>
   </si>
   <si>
     <t xml:space="preserve">1.74695920944214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7704758644104</t>
+    <t xml:space="preserve">1.77047610282898</t>
   </si>
   <si>
     <t xml:space="preserve">1.76375699043274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75031888484955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78895378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74024021625519</t>
+    <t xml:space="preserve">1.75031876564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78895354270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7402400970459</t>
   </si>
   <si>
     <t xml:space="preserve">1.76207721233368</t>
@@ -644,34 +644,34 @@
     <t xml:space="preserve">1.73352098464966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79903197288513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78055465221405</t>
+    <t xml:space="preserve">1.79903221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78055453300476</t>
   </si>
   <si>
     <t xml:space="preserve">1.82254886627197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86958265304565</t>
+    <t xml:space="preserve">1.86958229541779</t>
   </si>
   <si>
     <t xml:space="preserve">1.8645430803299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84774529933929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391420841217</t>
+    <t xml:space="preserve">1.84774565696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391432762146</t>
   </si>
   <si>
     <t xml:space="preserve">1.90480959415436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98488616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34267687797546</t>
+    <t xml:space="preserve">1.98488640785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34267711639404</t>
   </si>
   <si>
     <t xml:space="preserve">2.35119605064392</t>
@@ -692,31 +692,31 @@
     <t xml:space="preserve">2.34608459472656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33415818214417</t>
+    <t xml:space="preserve">2.33415842056274</t>
   </si>
   <si>
     <t xml:space="preserve">2.24897003173828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20296835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14163303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07007479667664</t>
+    <t xml:space="preserve">2.20296859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14163279533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07007503509521</t>
   </si>
   <si>
     <t xml:space="preserve">2.01896190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95933032035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01044297218323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06496357917786</t>
+    <t xml:space="preserve">1.95932996273041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01044273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06496334075928</t>
   </si>
   <si>
     <t xml:space="preserve">2.00192403793335</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">2.02407336235046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06155610084534</t>
+    <t xml:space="preserve">2.06155633926392</t>
   </si>
   <si>
     <t xml:space="preserve">2.04451823234558</t>
@@ -734,52 +734,52 @@
     <t xml:space="preserve">2.0683708190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303692817688</t>
+    <t xml:space="preserve">2.05303716659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.04111051559448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97977495193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99340522289276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97636759281158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97125637531281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466397285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95081126689911</t>
+    <t xml:space="preserve">1.9797750711441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99340534210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97636783123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97125649452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97466373443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95081102848053</t>
   </si>
   <si>
     <t xml:space="preserve">1.93888485431671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92525470256805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9269585609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94229257106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95762610435486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718123435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866218090057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97296035289764</t>
+    <t xml:space="preserve">1.92525458335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92695832252502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94229233264923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95762598514557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718099594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866241931915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97295987606049</t>
   </si>
   <si>
     <t xml:space="preserve">2.00703549385071</t>
@@ -788,31 +788,31 @@
     <t xml:space="preserve">2.01555418968201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98829448223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9320695400238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673588752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91332828998566</t>
+    <t xml:space="preserve">1.98829400539398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93206989765167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673576831818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91332852840424</t>
   </si>
   <si>
     <t xml:space="preserve">1.90821719169617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93377363681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94058871269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822531700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25578498840332</t>
+    <t xml:space="preserve">1.93377351760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94058883190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822555541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25578546524048</t>
   </si>
   <si>
     <t xml:space="preserve">2.22341370582581</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">2.3597149848938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27452659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41593909263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41253161430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36823391914368</t>
+    <t xml:space="preserve">2.27452683448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41593933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41253185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3682336807251</t>
   </si>
   <si>
     <t xml:space="preserve">2.30860185623169</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">2.31541681289673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28986024856567</t>
+    <t xml:space="preserve">2.28986048698425</t>
   </si>
   <si>
     <t xml:space="preserve">2.42445778846741</t>
@@ -851,34 +851,34 @@
     <t xml:space="preserve">2.41423535346985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36993718147278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39719724655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35801100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30519461631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32052850723267</t>
+    <t xml:space="preserve">2.36993765830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39719772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35801076889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30519437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32052803039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.32904720306396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31882452964783</t>
+    <t xml:space="preserve">2.31882429122925</t>
   </si>
   <si>
     <t xml:space="preserve">2.3477885723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36312222480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3443808555603</t>
+    <t xml:space="preserve">2.36312246322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
     <t xml:space="preserve">2.32563972473145</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">2.33926963806152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36652994155884</t>
+    <t xml:space="preserve">2.36652970314026</t>
   </si>
   <si>
     <t xml:space="preserve">2.37675285339355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38356781005859</t>
+    <t xml:space="preserve">2.38356757164001</t>
   </si>
   <si>
     <t xml:space="preserve">2.27111887931824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25408101081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09392714500427</t>
+    <t xml:space="preserve">2.25408124923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09392738342285</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696692466736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10585379600525</t>
+    <t xml:space="preserve">2.10585355758667</t>
   </si>
   <si>
     <t xml:space="preserve">2.10414981842041</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">2.12800264358521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31712079048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28304553031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30349063873291</t>
+    <t xml:space="preserve">2.31712126731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28304529190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30349040031433</t>
   </si>
   <si>
     <t xml:space="preserve">2.29667568206787</t>
@@ -932,37 +932,37 @@
     <t xml:space="preserve">2.28815674781799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21659827232361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23874735832214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21489500999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25748920440674</t>
+    <t xml:space="preserve">2.21659851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2387478351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21489453315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25748896598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.24556255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2319324016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933796882629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26260042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22511744499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23363614082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23022890090942</t>
+    <t xml:space="preserve">2.23193264007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933820724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26260018348694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22511720657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23363590240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23022866249084</t>
   </si>
   <si>
     <t xml:space="preserve">2.20637583732605</t>
@@ -971,52 +971,52 @@
     <t xml:space="preserve">2.29156446456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39379024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41934680938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53009176254272</t>
+    <t xml:space="preserve">2.39379000663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41934657096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53009152412415</t>
   </si>
   <si>
     <t xml:space="preserve">2.5726854801178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54712915420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58120441436768</t>
+    <t xml:space="preserve">2.54712891578674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5812041759491</t>
   </si>
   <si>
     <t xml:space="preserve">2.50453495979309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47045946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46194076538086</t>
+    <t xml:space="preserve">2.47045993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46194052696228</t>
   </si>
   <si>
     <t xml:space="preserve">2.38527131080627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41082787513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30008316040039</t>
+    <t xml:space="preserve">2.41082763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30008292198181</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342206954956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60676074028015</t>
+    <t xml:space="preserve">2.60676097869873</t>
   </si>
   <si>
     <t xml:space="preserve">2.61527967453003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64935517311096</t>
+    <t xml:space="preserve">2.64935493469238</t>
   </si>
   <si>
     <t xml:space="preserve">2.65787363052368</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">2.43638443946838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52157258987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53861021995544</t>
+    <t xml:space="preserve">2.52157282829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53861045837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.55564785003662</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">2.26600790023804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14674401283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671034812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11856651306152</t>
+    <t xml:space="preserve">2.14674425125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671010971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1185667514801</t>
   </si>
   <si>
     <t xml:space="preserve">2.17066216468811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29221940040588</t>
+    <t xml:space="preserve">2.29221963882446</t>
   </si>
   <si>
     <t xml:space="preserve">2.25748872756958</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">2.2661714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27485418319702</t>
+    <t xml:space="preserve">2.2748544216156</t>
   </si>
   <si>
     <t xml:space="preserve">2.34431552886963</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">2.35299801826477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30090260505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30958485603333</t>
+    <t xml:space="preserve">2.30090236663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3095850944519</t>
   </si>
   <si>
     <t xml:space="preserve">2.32695007324219</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">2.17934513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20539283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15329694747925</t>
+    <t xml:space="preserve">2.20539307594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15329718589783</t>
   </si>
   <si>
     <t xml:space="preserve">2.13593173027039</t>
@@ -1112,76 +1112,76 @@
     <t xml:space="preserve">2.09251880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22275853157043</t>
+    <t xml:space="preserve">2.22275829315186</t>
   </si>
   <si>
     <t xml:space="preserve">2.07515358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08383560180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10120129585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04042267799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01437473297119</t>
+    <t xml:space="preserve">2.08383584022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10120153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0404224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01437497138977</t>
   </si>
   <si>
     <t xml:space="preserve">2.05778813362122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06647038459778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700975418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00569200515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964429855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96227860450745</t>
+    <t xml:space="preserve">2.06647062301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00569224357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964406013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96227884292603</t>
   </si>
   <si>
     <t xml:space="preserve">2.02305722236633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04910492897034</t>
+    <t xml:space="preserve">2.04910516738892</t>
   </si>
   <si>
     <t xml:space="preserve">2.03173995018005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93623113632202</t>
+    <t xml:space="preserve">1.93623089790344</t>
   </si>
   <si>
     <t xml:space="preserve">1.87545251846313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89281785488129</t>
+    <t xml:space="preserve">1.89281761646271</t>
   </si>
   <si>
     <t xml:space="preserve">1.82335650920868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81467378139496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77994334697723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71916460990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69311666488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62799692153931</t>
+    <t xml:space="preserve">1.81467390060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77994322776794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71916472911835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69311678409576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62799680233002</t>
   </si>
   <si>
     <t xml:space="preserve">1.63233804702759</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">1.6887754201889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71482336521149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69745802879333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64536213874817</t>
+    <t xml:space="preserve">1.71482348442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69745790958405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64536201953888</t>
   </si>
   <si>
     <t xml:space="preserve">1.59760761260986</t>
@@ -1214,25 +1214,25 @@
     <t xml:space="preserve">1.60629022121429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61931431293488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61497282981873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63667941093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64970338344574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68009257316589</t>
+    <t xml:space="preserve">1.61931419372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61497294902802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63667929172516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64970350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68009269237518</t>
   </si>
   <si>
     <t xml:space="preserve">1.65838611125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7017993927002</t>
+    <t xml:space="preserve">1.70179951190948</t>
   </si>
   <si>
     <t xml:space="preserve">1.67140996456146</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">1.6670686006546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5715594291687</t>
+    <t xml:space="preserve">1.57155954837799</t>
   </si>
   <si>
     <t xml:space="preserve">1.52814626693726</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">1.66272723674774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72784721851349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76257801055908</t>
+    <t xml:space="preserve">1.72784733772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76257789134979</t>
   </si>
   <si>
     <t xml:space="preserve">1.75389528274536</t>
@@ -1277,16 +1277,16 @@
     <t xml:space="preserve">1.80599105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77126061916351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74521267414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83203899860382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7973085641861</t>
+    <t xml:space="preserve">1.77126038074493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74521255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83203911781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79730844497681</t>
   </si>
   <si>
     <t xml:space="preserve">1.84072160720825</t>
@@ -1298,34 +1298,34 @@
     <t xml:space="preserve">1.91018319129944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359599590302</t>
+    <t xml:space="preserve">1.95359623432159</t>
   </si>
   <si>
     <t xml:space="preserve">1.94491362571716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98832643032074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97096145153046</t>
+    <t xml:space="preserve">1.98832654953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97096157073975</t>
   </si>
   <si>
     <t xml:space="preserve">1.91886568069458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92754817008972</t>
+    <t xml:space="preserve">1.9275484085083</t>
   </si>
   <si>
     <t xml:space="preserve">1.85808718204498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84940457344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62365543842316</t>
+    <t xml:space="preserve">1.84940445423126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413500785828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
     <t xml:space="preserve">1.6504191160202</t>
@@ -1346,9 +1346,6 @@
     <t xml:space="preserve">1.65487968921661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62365555763245</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.64595854282379</t>
   </si>
   <si>
@@ -1358,7 +1355,7 @@
     <t xml:space="preserve">1.65934026241302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66826140880585</t>
+    <t xml:space="preserve">1.66826152801514</t>
   </si>
   <si>
     <t xml:space="preserve">1.68610382080078</t>
@@ -1367,7 +1364,7 @@
     <t xml:space="preserve">1.68164312839508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63257682323456</t>
+    <t xml:space="preserve">1.63257670402527</t>
   </si>
   <si>
     <t xml:space="preserve">1.60581314563751</t>
@@ -1376,7 +1373,7 @@
     <t xml:space="preserve">1.62811613082886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61473417282104</t>
+    <t xml:space="preserve">1.61473429203033</t>
   </si>
   <si>
     <t xml:space="preserve">1.58351016044617</t>
@@ -1403,13 +1400,13 @@
     <t xml:space="preserve">1.55674660205841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57012832164764</t>
+    <t xml:space="preserve">1.57012844085693</t>
   </si>
   <si>
     <t xml:space="preserve">1.58797073364258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57458913326263</t>
+    <t xml:space="preserve">1.57458901405334</t>
   </si>
   <si>
     <t xml:space="preserve">1.5968918800354</t>
@@ -1418,7 +1415,7 @@
     <t xml:space="preserve">1.53444373607635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66380095481873</t>
+    <t xml:space="preserve">1.66380083560944</t>
   </si>
   <si>
     <t xml:space="preserve">1.56566786766052</t>
@@ -1430,7 +1427,7 @@
     <t xml:space="preserve">1.52552247047424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5076801776886</t>
+    <t xml:space="preserve">1.50768005847931</t>
   </si>
   <si>
     <t xml:space="preserve">1.42738950252533</t>
@@ -1445,28 +1442,28 @@
     <t xml:space="preserve">1.34263813495636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34709882736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32479584217072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19097816944122</t>
+    <t xml:space="preserve">1.34709894657135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32479596138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19097828865051</t>
   </si>
   <si>
     <t xml:space="preserve">1.26680815219879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24450528621674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29803240299225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20435988903046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27572929859161</t>
+    <t xml:space="preserve">1.24450540542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29803228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20435976982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2757294178009</t>
   </si>
   <si>
     <t xml:space="preserve">1.28465056419373</t>
@@ -1475,7 +1472,7 @@
     <t xml:space="preserve">1.30695343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30249285697937</t>
+    <t xml:space="preserve">1.30249297618866</t>
   </si>
   <si>
     <t xml:space="preserve">1.36940181255341</t>
@@ -1484,7 +1481,7 @@
     <t xml:space="preserve">1.36494112014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35601997375488</t>
+    <t xml:space="preserve">1.35602009296417</t>
   </si>
   <si>
     <t xml:space="preserve">1.36048054695129</t>
@@ -1493,19 +1490,19 @@
     <t xml:space="preserve">1.40508651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44969248771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45415306091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44523191452026</t>
+    <t xml:space="preserve">1.44969236850739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45415318012238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44523179531097</t>
   </si>
   <si>
     <t xml:space="preserve">1.43631076812744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4184684753418</t>
+    <t xml:space="preserve">1.41846835613251</t>
   </si>
   <si>
     <t xml:space="preserve">1.46307420730591</t>
@@ -1514,28 +1511,28 @@
     <t xml:space="preserve">1.39170479774475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40062594413757</t>
+    <t xml:space="preserve">1.40062606334686</t>
   </si>
   <si>
     <t xml:space="preserve">1.41400766372681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38278353214264</t>
+    <t xml:space="preserve">1.38278341293335</t>
   </si>
   <si>
     <t xml:space="preserve">1.38724410533905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33817780017853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35155940055847</t>
+    <t xml:space="preserve">1.33817768096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35155928134918</t>
   </si>
   <si>
     <t xml:space="preserve">1.29357182979584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32925653457642</t>
+    <t xml:space="preserve">1.32925641536713</t>
   </si>
   <si>
     <t xml:space="preserve">1.33371698856354</t>
@@ -1544,13 +1541,13 @@
     <t xml:space="preserve">1.3158745765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37386226654053</t>
+    <t xml:space="preserve">1.37386238574982</t>
   </si>
   <si>
     <t xml:space="preserve">1.31141412258148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32033538818359</t>
+    <t xml:space="preserve">1.3203352689743</t>
   </si>
   <si>
     <t xml:space="preserve">1.28018987178802</t>
@@ -1559,10 +1556,10 @@
     <t xml:space="preserve">1.40954720973969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39616537094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45861351490021</t>
+    <t xml:space="preserve">1.39616525173187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4586136341095</t>
   </si>
   <si>
     <t xml:space="preserve">1.37832295894623</t>
@@ -1571,7 +1568,7 @@
     <t xml:space="preserve">1.42292892932892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28911113739014</t>
+    <t xml:space="preserve">1.28911101818085</t>
   </si>
   <si>
     <t xml:space="preserve">1.27126860618591</t>
@@ -1580,7 +1577,7 @@
     <t xml:space="preserve">1.26234745979309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24896585941315</t>
+    <t xml:space="preserve">1.24896574020386</t>
   </si>
   <si>
     <t xml:space="preserve">1.46753478050232</t>
@@ -1589,10 +1586,10 @@
     <t xml:space="preserve">1.44077122211456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48091650009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49429833889008</t>
+    <t xml:space="preserve">1.48091661930084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49429821968079</t>
   </si>
   <si>
     <t xml:space="preserve">1.5032194852829</t>
@@ -1604,7 +1601,7 @@
     <t xml:space="preserve">1.4987587928772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51214075088501</t>
+    <t xml:space="preserve">1.5121408700943</t>
   </si>
   <si>
     <t xml:space="preserve">1.48537719249725</t>
@@ -1622,7 +1619,7 @@
     <t xml:space="preserve">1.73963093757629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81992161273956</t>
+    <t xml:space="preserve">1.81992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">1.87344872951508</t>
@@ -1634,7 +1631,7 @@
     <t xml:space="preserve">1.8377640247345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423678874969</t>
+    <t xml:space="preserve">1.78423690795898</t>
   </si>
   <si>
     <t xml:space="preserve">1.77531564235687</t>
@@ -1643,37 +1640,37 @@
     <t xml:space="preserve">1.73517036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085506916046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72624897956848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73070991039276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74855220317841</t>
+    <t xml:space="preserve">1.77085494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72624909877777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73070979118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7485523223877</t>
   </si>
   <si>
     <t xml:space="preserve">1.79315805435181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71732783317566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74409151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77977621555328</t>
+    <t xml:space="preserve">1.71732795238495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74409139156342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77977633476257</t>
   </si>
   <si>
     <t xml:space="preserve">1.81100046634674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84668517112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86452746391296</t>
+    <t xml:space="preserve">1.84668505191803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86452758312225</t>
   </si>
   <si>
     <t xml:space="preserve">1.80207920074463</t>
@@ -1682,37 +1679,37 @@
     <t xml:space="preserve">1.75747334957123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0340301990509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0251088142395</t>
+    <t xml:space="preserve">2.03402996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02510905265808</t>
   </si>
   <si>
     <t xml:space="preserve">1.96266078948975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92697596549988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98050284385681</t>
+    <t xml:space="preserve">1.92697608470917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9805029630661</t>
   </si>
   <si>
     <t xml:space="preserve">2.07863569259644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1053991317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05187273025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06079339981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09647822380066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43548321723938</t>
+    <t xml:space="preserve">2.10539937019348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05187225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06079363822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09647798538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43548345565796</t>
   </si>
   <si>
     <t xml:space="preserve">2.46224689483643</t>
@@ -1724,76 +1721,79 @@
     <t xml:space="preserve">2.56037974357605</t>
   </si>
   <si>
+    <t xml:space="preserve">2.60498595237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65005493164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61399984359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64104080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74019289016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78526163101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73117876052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90244126319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1007444858551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99257898330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92948222160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84835839271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76723408699036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83934450149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87539958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82131671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77624797821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72216534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55991697311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53287553787231</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.60498571395874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65005493164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61399984359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64104080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74019265174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78526139259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73117876052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90244126319885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1007444858551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99257898330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92948246002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84835839271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76723432540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83934450149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87539958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82131695747375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77624797821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72216510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55991673469543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53287553787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58695793151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65906858444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67709612846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5238618850708</t>
+    <t xml:space="preserve">2.58695816993713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65906834602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67709636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52386164665222</t>
   </si>
   <si>
     <t xml:space="preserve">2.62301349639893</t>
@@ -1802,31 +1802,31 @@
     <t xml:space="preserve">2.57794451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597229957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55090308189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51484799385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56893062591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79427552223206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83033061027527</t>
+    <t xml:space="preserve">2.59597206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55090284347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51484823226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56893038749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79427528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83033084869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.71315121650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70413780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74920654296875</t>
+    <t xml:space="preserve">2.70413756370544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74920630455017</t>
   </si>
   <si>
     <t xml:space="preserve">2.80328917503357</t>
@@ -1838,40 +1838,40 @@
     <t xml:space="preserve">3.0015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09173083305359</t>
+    <t xml:space="preserve">3.09173059463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.96553754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93849611282349</t>
+    <t xml:space="preserve">2.93849635124207</t>
   </si>
   <si>
     <t xml:space="preserve">2.81230306625366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54188895225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4787929058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63202714920044</t>
+    <t xml:space="preserve">2.54188919067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47879266738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63202738761902</t>
   </si>
   <si>
     <t xml:space="preserve">2.91145467758179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9745512008667</t>
+    <t xml:space="preserve">2.97455096244812</t>
   </si>
   <si>
     <t xml:space="preserve">2.95652365684509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01060605049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01962018013</t>
+    <t xml:space="preserve">3.01060628890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01961994171143</t>
   </si>
   <si>
     <t xml:space="preserve">2.98356485366821</t>
@@ -1901,16 +1901,16 @@
     <t xml:space="preserve">2.19035148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28048944473267</t>
+    <t xml:space="preserve">2.28048920631409</t>
   </si>
   <si>
     <t xml:space="preserve">2.415696144104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3165442943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36161327362061</t>
+    <t xml:space="preserve">2.31654453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36161351203918</t>
   </si>
   <si>
     <t xml:space="preserve">2.50583410263062</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">2.37964105606079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37062764167786</t>
+    <t xml:space="preserve">2.37062740325928</t>
   </si>
   <si>
     <t xml:space="preserve">2.27147555351257</t>
@@ -1934,19 +1934,19 @@
     <t xml:space="preserve">2.26246190071106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2895028591156</t>
+    <t xml:space="preserve">2.28950309753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555842399597</t>
+    <t xml:space="preserve">2.32555818557739</t>
   </si>
   <si>
     <t xml:space="preserve">2.29851698875427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34358549118042</t>
+    <t xml:space="preserve">2.343585729599</t>
   </si>
   <si>
     <t xml:space="preserve">2.21739268302917</t>
@@ -25618,7 +25618,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G872" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25670,7 +25670,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G874" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25696,7 +25696,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G875" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25748,7 +25748,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G877" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25774,7 +25774,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G878" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25800,7 +25800,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G879" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25826,7 +25826,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G880" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25852,7 +25852,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G881" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25878,7 +25878,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G882" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25956,7 +25956,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G885" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25982,7 +25982,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G886" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26008,7 +26008,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G887" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26034,7 +26034,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G888" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26086,7 +26086,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G890" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26112,7 +26112,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G891" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26138,7 +26138,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G892" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26190,7 +26190,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G894" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26216,7 +26216,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G895" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26242,7 +26242,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G896" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26268,7 +26268,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26294,7 +26294,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G898" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26320,7 +26320,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G899" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26372,7 +26372,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G901" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26398,7 +26398,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G902" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26424,7 +26424,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G903" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26450,7 +26450,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G904" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26502,7 +26502,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G906" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26528,7 +26528,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G907" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26554,7 +26554,7 @@
         <v>1.75</v>
       </c>
       <c r="G908" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26580,7 +26580,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G909" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26606,7 +26606,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G910" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26632,7 +26632,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G911" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26658,7 +26658,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G912" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26684,7 +26684,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G913" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26710,7 +26710,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G914" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26736,7 +26736,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G915" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26762,7 +26762,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G916" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26788,7 +26788,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G917" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26814,7 +26814,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G918" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26840,7 +26840,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G919" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26866,7 +26866,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G920" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26892,7 +26892,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G921" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26918,7 +26918,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G922" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26970,7 +26970,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G924" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26996,7 +26996,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G925" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27022,7 +27022,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G926" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27100,7 +27100,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G929" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27126,7 +27126,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G930" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27152,7 +27152,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G931" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27178,7 +27178,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G932" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27230,7 +27230,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G934" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27256,7 +27256,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27282,7 +27282,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G936" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27308,7 +27308,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G937" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27334,7 +27334,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G938" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27360,7 +27360,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G939" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27386,7 +27386,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G940" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27412,7 +27412,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G941" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27438,7 +27438,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G942" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27464,7 +27464,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G943" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27516,7 +27516,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G945" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27542,7 +27542,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27568,7 +27568,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G947" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27594,7 +27594,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27620,7 +27620,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27646,7 +27646,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G950" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27672,7 +27672,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G951" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27698,7 +27698,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G952" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27724,7 +27724,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G953" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27750,7 +27750,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G954" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27776,7 +27776,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G955" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27802,7 +27802,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G956" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27828,7 +27828,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G957" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27854,7 +27854,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G958" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27880,7 +27880,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27906,7 +27906,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G960" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27932,7 +27932,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G961" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27958,7 +27958,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G962" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27984,7 +27984,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G963" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28062,7 +28062,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G966" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28088,7 +28088,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G967" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28114,7 +28114,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G968" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28166,7 +28166,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G970" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28218,7 +28218,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G972" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28244,7 +28244,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G973" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28270,7 +28270,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G974" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28296,7 +28296,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G975" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28348,7 +28348,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G977" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28374,7 +28374,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G978" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28400,7 +28400,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G979" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28426,7 +28426,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G980" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28530,7 +28530,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G984" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28556,7 +28556,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G985" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28582,7 +28582,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G986" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28608,7 +28608,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G987" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28634,7 +28634,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28660,7 +28660,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G989" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28686,7 +28686,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G990" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28712,7 +28712,7 @@
         <v>1.75</v>
       </c>
       <c r="G991" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28738,7 +28738,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G992" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28764,7 +28764,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G993" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28790,7 +28790,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G994" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28894,7 +28894,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G998" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28920,7 +28920,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G999" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28998,7 +28998,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1002" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29050,7 +29050,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1004" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29076,7 +29076,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1005" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29128,7 +29128,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1007" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29154,7 +29154,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29206,7 +29206,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1010" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29232,7 +29232,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1011" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29258,7 +29258,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1012" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29284,7 +29284,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1013" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29310,7 +29310,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1014" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29336,7 +29336,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1015" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29362,7 +29362,7 @@
         <v>1.75</v>
       </c>
       <c r="G1016" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29388,7 +29388,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1017" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29414,7 +29414,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1018" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29466,7 +29466,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1020" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29492,7 +29492,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1021" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29518,7 +29518,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1022" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29544,7 +29544,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1023" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29570,7 +29570,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1024" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29596,7 +29596,7 @@
         <v>1.75</v>
       </c>
       <c r="G1025" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29622,7 +29622,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1026" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29648,7 +29648,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1027" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29674,7 +29674,7 @@
         <v>1.75</v>
       </c>
       <c r="G1028" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29700,7 +29700,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1029" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29726,7 +29726,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1030" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29752,7 +29752,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1031" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29778,7 +29778,7 @@
         <v>1.75</v>
       </c>
       <c r="G1032" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29804,7 +29804,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1033" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29830,7 +29830,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1034" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29856,7 +29856,7 @@
         <v>1.75</v>
       </c>
       <c r="G1035" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29882,7 +29882,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29908,7 +29908,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1037" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29934,7 +29934,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1038" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29960,7 +29960,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1039" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29986,7 +29986,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1040" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30012,7 +30012,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1041" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30038,7 +30038,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1042" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30064,7 +30064,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1043" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30090,7 +30090,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1044" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30116,7 +30116,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1045" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30142,7 +30142,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1046" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30168,7 +30168,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1047" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30194,7 +30194,7 @@
         <v>1.75</v>
       </c>
       <c r="G1048" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30220,7 +30220,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1049" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30246,7 +30246,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1050" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30272,7 +30272,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1051" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30298,7 +30298,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30324,7 +30324,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1053" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30350,7 +30350,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1054" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30376,7 +30376,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1055" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30402,7 +30402,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1056" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30428,7 +30428,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30454,7 +30454,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1058" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30480,7 +30480,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1059" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30506,7 +30506,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1060" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30532,7 +30532,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30558,7 +30558,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1062" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30584,7 +30584,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1063" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30610,7 +30610,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1064" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30636,7 +30636,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1065" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30662,7 +30662,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1066" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30688,7 +30688,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30714,7 +30714,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30740,7 +30740,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1069" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30766,7 +30766,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1070" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30792,7 +30792,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1071" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30818,7 +30818,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1072" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30844,7 +30844,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1073" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30870,7 +30870,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1074" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30896,7 +30896,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1075" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30922,7 +30922,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1076" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30948,7 +30948,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1077" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30974,7 +30974,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1078" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31000,7 +31000,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1079" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31026,7 +31026,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1080" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31052,7 +31052,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1081" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31078,7 +31078,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1082" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31104,7 +31104,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1083" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31130,7 +31130,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1084" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31156,7 +31156,7 @@
         <v>1.625</v>
       </c>
       <c r="G1085" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31182,7 +31182,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1086" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31208,7 +31208,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1087" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31234,7 +31234,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1088" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31260,7 +31260,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1089" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31286,7 +31286,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1090" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31312,7 +31312,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1091" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31338,7 +31338,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1092" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31364,7 +31364,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1093" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31390,7 +31390,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1094" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31416,7 +31416,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1095" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31442,7 +31442,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1096" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31468,7 +31468,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1097" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31494,7 +31494,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31520,7 +31520,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1099" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31546,7 +31546,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1100" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31572,7 +31572,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1101" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31598,7 +31598,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1102" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31624,7 +31624,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1103" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31650,7 +31650,7 @@
         <v>1.5</v>
       </c>
       <c r="G1104" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31676,7 +31676,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1105" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31702,7 +31702,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1106" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31728,7 +31728,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1107" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31754,7 +31754,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1108" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31780,7 +31780,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1109" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31806,7 +31806,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1110" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31832,7 +31832,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1111" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31858,7 +31858,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1112" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31884,7 +31884,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1113" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31910,7 +31910,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1114" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31936,7 +31936,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1115" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31962,7 +31962,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1116" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31988,7 +31988,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1117" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32014,7 +32014,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1118" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32040,7 +32040,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1119" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32066,7 +32066,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1120" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32092,7 +32092,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1121" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32118,7 +32118,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1122" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32144,7 +32144,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1123" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32170,7 +32170,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1124" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32196,7 +32196,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1125" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32222,7 +32222,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1126" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32248,7 +32248,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1127" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32274,7 +32274,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1128" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32300,7 +32300,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1129" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32326,7 +32326,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1130" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32352,7 +32352,7 @@
         <v>1.5</v>
       </c>
       <c r="G1131" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32378,7 +32378,7 @@
         <v>1.5</v>
       </c>
       <c r="G1132" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32404,7 +32404,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1133" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32430,7 +32430,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1134" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32456,7 +32456,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1135" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32482,7 +32482,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1136" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32508,7 +32508,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1137" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32534,7 +32534,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1138" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32560,7 +32560,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1139" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32586,7 +32586,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1140" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32612,7 +32612,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1141" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32638,7 +32638,7 @@
         <v>1.5</v>
       </c>
       <c r="G1142" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32664,7 +32664,7 @@
         <v>1.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32690,7 +32690,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1144" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32716,7 +32716,7 @@
         <v>1.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32742,7 +32742,7 @@
         <v>1.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32768,7 +32768,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1147" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32794,7 +32794,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32820,7 +32820,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1149" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32846,7 +32846,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1150" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32872,7 +32872,7 @@
         <v>1.5</v>
       </c>
       <c r="G1151" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32898,7 +32898,7 @@
         <v>1.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32924,7 +32924,7 @@
         <v>1.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32950,7 +32950,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1154" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32976,7 +32976,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33002,7 +33002,7 @@
         <v>1.5</v>
       </c>
       <c r="G1156" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33028,7 +33028,7 @@
         <v>1.5</v>
       </c>
       <c r="G1157" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33054,7 +33054,7 @@
         <v>1.5</v>
       </c>
       <c r="G1158" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33080,7 +33080,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1159" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33106,7 +33106,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1160" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33132,7 +33132,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1161" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33158,7 +33158,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33184,7 +33184,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1163" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33210,7 +33210,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1164" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33236,7 +33236,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1165" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33262,7 +33262,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33288,7 +33288,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1167" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33314,7 +33314,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33340,7 +33340,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1169" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33366,7 +33366,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1170" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33392,7 +33392,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33418,7 +33418,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1172" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33444,7 +33444,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1173" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33470,7 +33470,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1174" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33496,7 +33496,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1175" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33522,7 +33522,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1176" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33548,7 +33548,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1177" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33574,7 +33574,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33600,7 +33600,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1179" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33626,7 +33626,7 @@
         <v>1.5</v>
       </c>
       <c r="G1180" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33652,7 +33652,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1181" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33678,7 +33678,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1182" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33704,7 +33704,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1183" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33730,7 +33730,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1184" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33756,7 +33756,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33782,7 +33782,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1186" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33808,7 +33808,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1187" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33834,7 +33834,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1188" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33860,7 +33860,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1189" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33886,7 +33886,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1190" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33912,7 +33912,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1191" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33938,7 +33938,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1192" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33964,7 +33964,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1193" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33990,7 +33990,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1194" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34016,7 +34016,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1195" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34042,7 +34042,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1196" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34068,7 +34068,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1197" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34094,7 +34094,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1198" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34120,7 +34120,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1199" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34146,7 +34146,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1200" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34172,7 +34172,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1201" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34198,7 +34198,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1202" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34224,7 +34224,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1203" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34250,7 +34250,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34276,7 +34276,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34302,7 +34302,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34328,7 +34328,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34354,7 +34354,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34380,7 +34380,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34406,7 +34406,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34432,7 +34432,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34458,7 +34458,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34484,7 +34484,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1213" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34510,7 +34510,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1214" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34536,7 +34536,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1215" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34562,7 +34562,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34588,7 +34588,7 @@
         <v>1.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34614,7 +34614,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1218" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34640,7 +34640,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1219" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34666,7 +34666,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1220" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34692,7 +34692,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1221" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34718,7 +34718,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1222" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34744,7 +34744,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1223" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34770,7 +34770,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34796,7 +34796,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1225" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34822,7 +34822,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1226" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34848,7 +34848,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1227" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34874,7 +34874,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1228" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34900,7 +34900,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1229" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34926,7 +34926,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1230" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34952,7 +34952,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1231" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34978,7 +34978,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35004,7 +35004,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1233" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35030,7 +35030,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1234" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35056,7 +35056,7 @@
         <v>1.5</v>
       </c>
       <c r="G1235" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35082,7 +35082,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1236" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35108,7 +35108,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35134,7 +35134,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35160,7 +35160,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1239" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35186,7 +35186,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35212,7 +35212,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35238,7 +35238,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1242" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35264,7 +35264,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35290,7 +35290,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1244" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35316,7 +35316,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35342,7 +35342,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1246" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35368,7 +35368,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1247" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35394,7 +35394,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35420,7 +35420,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1249" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35446,7 +35446,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1250" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35472,7 +35472,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1251" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35498,7 +35498,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35524,7 +35524,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35550,7 +35550,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1254" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35576,7 +35576,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1255" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35602,7 +35602,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1256" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35628,7 +35628,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1257" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35654,7 +35654,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1258" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35680,7 +35680,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1259" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35706,7 +35706,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1260" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35732,7 +35732,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1261" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35758,7 +35758,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1262" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35784,7 +35784,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1263" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35810,7 +35810,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1264" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35836,7 +35836,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1265" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35862,7 +35862,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1266" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35888,7 +35888,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35914,7 +35914,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35940,7 +35940,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1269" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35966,7 +35966,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35992,7 +35992,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1271" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36018,7 +36018,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1272" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36044,7 +36044,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1273" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36070,7 +36070,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1274" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36096,7 +36096,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1275" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36122,7 +36122,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36148,7 +36148,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1277" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36174,7 +36174,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36200,7 +36200,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1279" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36226,7 +36226,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1280" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36252,7 +36252,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1281" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36278,7 +36278,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1282" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36304,7 +36304,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1283" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36330,7 +36330,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1284" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36356,7 +36356,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1285" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36382,7 +36382,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1286" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36408,7 +36408,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1287" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36434,7 +36434,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36460,7 +36460,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1289" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36486,7 +36486,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1290" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36512,7 +36512,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1291" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36538,7 +36538,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1292" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36564,7 +36564,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1293" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36590,7 +36590,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1294" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36616,7 +36616,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1295" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36642,7 +36642,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1296" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36668,7 +36668,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1297" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36694,7 +36694,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1298" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36720,7 +36720,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1299" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36772,7 +36772,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1301" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36798,7 +36798,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1302" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36824,7 +36824,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1303" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36850,7 +36850,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1304" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36876,7 +36876,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1305" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36902,7 +36902,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1306" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36928,7 +36928,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1307" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36954,7 +36954,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1308" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36980,7 +36980,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1309" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37006,7 +37006,7 @@
         <v>2</v>
       </c>
       <c r="G1310" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37032,7 +37032,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37058,7 +37058,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1312" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37084,7 +37084,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1313" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -37110,7 +37110,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1314" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37136,7 +37136,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1315" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37162,7 +37162,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1316" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37188,7 +37188,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1317" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37214,7 +37214,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1318" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37240,7 +37240,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37266,7 +37266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37292,7 +37292,7 @@
         <v>2</v>
       </c>
       <c r="G1321" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37318,7 +37318,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1322" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37344,7 +37344,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1323" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37370,7 +37370,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1324" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37396,7 +37396,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1325" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37422,7 +37422,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1326" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37448,7 +37448,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1327" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37474,7 +37474,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1328" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37500,7 +37500,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1329" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37526,7 +37526,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1330" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37552,7 +37552,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1331" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37578,7 +37578,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1332" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37604,7 +37604,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1333" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37630,7 +37630,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1334" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37656,7 +37656,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37682,7 +37682,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1336" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37708,7 +37708,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1337" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37734,7 +37734,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1338" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37760,7 +37760,7 @@
         <v>2</v>
       </c>
       <c r="G1339" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37786,7 +37786,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1340" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37812,7 +37812,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1341" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37838,7 +37838,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1342" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37864,7 +37864,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1343" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37890,7 +37890,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37916,7 +37916,7 @@
         <v>2</v>
       </c>
       <c r="G1345" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37942,7 +37942,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1346" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37968,7 +37968,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37994,7 +37994,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38020,7 +38020,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -38046,7 +38046,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1350" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -38072,7 +38072,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1351" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -38098,7 +38098,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1352" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -38124,7 +38124,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1353" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -38150,7 +38150,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1354" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -38176,7 +38176,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1355" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -38202,7 +38202,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1356" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -38228,7 +38228,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1357" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38254,7 +38254,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1358" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38280,7 +38280,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1359" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38306,7 +38306,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1360" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38332,7 +38332,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1361" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38358,7 +38358,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1362" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38384,7 +38384,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1363" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38410,7 +38410,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1364" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38436,7 +38436,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1365" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38462,7 +38462,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1366" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38488,7 +38488,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38514,7 +38514,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38540,7 +38540,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1369" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38566,7 +38566,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1370" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38592,7 +38592,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1371" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38618,7 +38618,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38644,7 +38644,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1373" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38670,7 +38670,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1374" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38696,7 +38696,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1375" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38722,7 +38722,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1376" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38748,7 +38748,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1377" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38774,7 +38774,7 @@
         <v>3.25</v>
       </c>
       <c r="G1378" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38800,7 +38800,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1379" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38826,7 +38826,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1380" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38852,7 +38852,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1381" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38878,7 +38878,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38904,7 +38904,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38930,7 +38930,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1384" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38956,7 +38956,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1385" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38982,7 +38982,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1386" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -39008,7 +39008,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1387" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -39034,7 +39034,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1388" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -39060,7 +39060,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1389" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39086,7 +39086,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1390" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -39190,7 +39190,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1394" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -39216,7 +39216,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1395" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39294,7 +39294,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1398" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39320,7 +39320,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1399" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39346,7 +39346,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1400" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39372,7 +39372,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39476,7 +39476,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1405" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39788,7 +39788,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1417" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39814,7 +39814,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1418" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39892,7 +39892,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1421" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39918,7 +39918,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1422" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39970,7 +39970,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1424" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39996,7 +39996,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1425" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -40048,7 +40048,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1427" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -40074,7 +40074,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1428" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -40152,7 +40152,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1431" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -40204,7 +40204,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1433" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -40230,7 +40230,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1434" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40308,7 +40308,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1437" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40334,7 +40334,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40386,7 +40386,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40412,7 +40412,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1441" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40438,7 +40438,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1442" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40464,7 +40464,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1443" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40490,7 +40490,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1444" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40516,7 +40516,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1445" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40542,7 +40542,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1446" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40750,7 +40750,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1454" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40828,7 +40828,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40854,7 +40854,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1458" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40880,7 +40880,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1459" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41218,7 +41218,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1472" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41244,7 +41244,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41296,7 +41296,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1475" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41348,7 +41348,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1477" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41400,7 +41400,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1479" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41660,7 +41660,7 @@
         <v>3.25</v>
       </c>
       <c r="G1489" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41686,7 +41686,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1490" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41894,7 +41894,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41972,7 +41972,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1501" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -42076,7 +42076,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1505" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -42102,7 +42102,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -42180,7 +42180,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -42206,7 +42206,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1510" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -42232,7 +42232,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1511" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42258,7 +42258,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1512" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42284,7 +42284,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1513" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42310,7 +42310,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1514" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42336,7 +42336,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1515" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42388,7 +42388,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42466,7 +42466,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1520" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42492,7 +42492,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42544,7 +42544,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1523" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42570,7 +42570,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42596,7 +42596,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42648,7 +42648,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1527" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42752,7 +42752,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1531" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42856,7 +42856,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1535" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42934,7 +42934,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1538" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42960,7 +42960,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1539" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42986,7 +42986,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1540" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43038,7 +43038,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1542" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43116,7 +43116,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1545" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -43142,7 +43142,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1546" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -43376,7 +43376,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1555" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43402,7 +43402,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1556" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43454,7 +43454,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1558" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43480,7 +43480,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1559" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43558,7 +43558,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1562" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43688,7 +43688,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43714,7 +43714,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1568" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44000,7 +44000,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -44286,7 +44286,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1590" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44338,7 +44338,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -69072,13 +69072,13 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.6833449074</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
-        <v>6312</v>
+        <v>13879</v>
       </c>
       <c r="C2544" t="n">
-        <v>2.05999994277954</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="D2544" t="n">
         <v>2.05999994277954</v>
@@ -69087,12 +69087,38 @@
         <v>2.05999994277954</v>
       </c>
       <c r="F2544" t="n">
-        <v>2.11999988555908</v>
+        <v>2.10999989509583</v>
       </c>
       <c r="G2544" t="s">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.6732291667</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>32563</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>2.19000005722046</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>853</v>
+      </c>
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034141540527</t>
+    <t xml:space="preserve">1.75034153461456</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538791179657</t>
+    <t xml:space="preserve">1.74538803100586</t>
   </si>
   <si>
     <t xml:space="preserve">1.69254732131958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70245504379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67603480815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66612684726715</t>
+    <t xml:space="preserve">1.70245480537415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68429100513458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6760345697403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66612708568573</t>
   </si>
   <si>
     <t xml:space="preserve">1.63888120651245</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">1.61163532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59347152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48613905906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59264588356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59181988239288</t>
+    <t xml:space="preserve">1.59347140789032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48613917827606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59182000160217</t>
   </si>
   <si>
     <t xml:space="preserve">1.58604061603546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521509170532</t>
+    <t xml:space="preserve">1.6017279624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521521091461</t>
   </si>
   <si>
     <t xml:space="preserve">1.56044602394104</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">1.53980529308319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5654000043869</t>
+    <t xml:space="preserve">1.56539988517761</t>
   </si>
   <si>
     <t xml:space="preserve">1.53567707538605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45311367511749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50595450401306</t>
+    <t xml:space="preserve">1.45311403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50595438480377</t>
   </si>
   <si>
     <t xml:space="preserve">1.46137011051178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44238066673279</t>
+    <t xml:space="preserve">1.4423805475235</t>
   </si>
   <si>
     <t xml:space="preserve">1.51833879947662</t>
@@ -122,46 +122,46 @@
     <t xml:space="preserve">1.65126574039459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6347531080246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65621972084045</t>
+    <t xml:space="preserve">1.63475298881531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65621960163116</t>
   </si>
   <si>
     <t xml:space="preserve">1.64300942420959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6372298002243</t>
+    <t xml:space="preserve">1.63722991943359</t>
   </si>
   <si>
     <t xml:space="preserve">1.64218378067017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63970685005188</t>
+    <t xml:space="preserve">1.63970673084259</t>
   </si>
   <si>
     <t xml:space="preserve">1.66777837276459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60503017902374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59842526912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870234012604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053237438202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227605819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60255348682404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57283055782318</t>
+    <t xml:space="preserve">1.60503029823303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5984251499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870245933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6322762966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60255336761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57283043861389</t>
   </si>
   <si>
     <t xml:space="preserve">1.58934319019318</t>
@@ -170,76 +170,76 @@
     <t xml:space="preserve">1.58438944816589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56787693500519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5571436882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53402578830719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54310774803162</t>
+    <t xml:space="preserve">1.5678768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55714380741119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53402602672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54310786724091</t>
   </si>
   <si>
     <t xml:space="preserve">1.55466663837433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5596204996109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55218982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55053842067719</t>
+    <t xml:space="preserve">1.55962038040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55218970775604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55053853988647</t>
   </si>
   <si>
     <t xml:space="preserve">1.50265192985535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48696458339691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237450122833</t>
+    <t xml:space="preserve">1.4869647026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861587047577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237438201904</t>
   </si>
   <si>
     <t xml:space="preserve">1.49026715755463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51503610610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779058456421</t>
+    <t xml:space="preserve">1.5150363445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779034614563</t>
   </si>
   <si>
     <t xml:space="preserve">1.47623145580292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50760543346405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5010005235672</t>
+    <t xml:space="preserve">1.50760555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50100064277649</t>
   </si>
   <si>
     <t xml:space="preserve">1.49439537525177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48366224765778</t>
+    <t xml:space="preserve">1.48366212844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45971882343292</t>
   </si>
   <si>
     <t xml:space="preserve">1.45971894264221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45971882343292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45299971103668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46223855018616</t>
+    <t xml:space="preserve">1.45299983024597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46223866939545</t>
   </si>
   <si>
     <t xml:space="preserve">1.43284261226654</t>
@@ -248,28 +248,28 @@
     <t xml:space="preserve">1.43536221981049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43200266361237</t>
+    <t xml:space="preserve">1.43200278282166</t>
   </si>
   <si>
     <t xml:space="preserve">1.4261234998703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41100537776947</t>
+    <t xml:space="preserve">1.41100561618805</t>
   </si>
   <si>
     <t xml:space="preserve">1.44040167331696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43620216846466</t>
+    <t xml:space="preserve">1.43620204925537</t>
   </si>
   <si>
     <t xml:space="preserve">1.4429212808609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44880044460297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47819626331329</t>
+    <t xml:space="preserve">1.44880032539368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47819650173187</t>
   </si>
   <si>
     <t xml:space="preserve">1.44460105895996</t>
@@ -278,76 +278,76 @@
     <t xml:space="preserve">1.42360389232635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43032288551331</t>
+    <t xml:space="preserve">1.43032276630402</t>
   </si>
   <si>
     <t xml:space="preserve">1.46139872074127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40260672569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40848588943481</t>
+    <t xml:space="preserve">1.40260660648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40848577022552</t>
   </si>
   <si>
     <t xml:space="preserve">1.37825000286102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42444372177124</t>
+    <t xml:space="preserve">1.42444384098053</t>
   </si>
   <si>
     <t xml:space="preserve">1.41604483127594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46979737281799</t>
+    <t xml:space="preserve">1.46979749202728</t>
   </si>
   <si>
     <t xml:space="preserve">1.42780327796936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42192399501801</t>
+    <t xml:space="preserve">1.42192387580872</t>
   </si>
   <si>
     <t xml:space="preserve">1.47567665576935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44796061515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735631465912</t>
+    <t xml:space="preserve">1.4479603767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735643386841</t>
   </si>
   <si>
     <t xml:space="preserve">1.43368244171143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45803904533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4521598815918</t>
+    <t xml:space="preserve">1.45803916454315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45215976238251</t>
   </si>
   <si>
     <t xml:space="preserve">1.48491537570953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46391820907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46643793582916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46895754337311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.485755443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45887899398804</t>
+    <t xml:space="preserve">1.46391832828522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46643781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4689576625824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48575520515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45887887477875</t>
   </si>
   <si>
     <t xml:space="preserve">1.4563592672348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45719921588898</t>
+    <t xml:space="preserve">1.45719909667969</t>
   </si>
   <si>
     <t xml:space="preserve">1.48827481269836</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">1.473996758461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727788448334</t>
+    <t xml:space="preserve">1.46727776527405</t>
   </si>
   <si>
     <t xml:space="preserve">1.49835360050201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50927209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50339293479919</t>
+    <t xml:space="preserve">1.50927197933197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5033928155899</t>
   </si>
   <si>
     <t xml:space="preserve">1.4949939250946</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">1.49919331073761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179146766663</t>
+    <t xml:space="preserve">1.51179170608521</t>
   </si>
   <si>
     <t xml:space="preserve">1.45048010349274</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">1.48071599006653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48155581951141</t>
+    <t xml:space="preserve">1.4815559387207</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095187664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49583399295807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5075923204422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49667358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47231721878052</t>
+    <t xml:space="preserve">1.49583387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50759220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49667382240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47231709957123</t>
   </si>
   <si>
     <t xml:space="preserve">1.49331426620483</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">1.50087308883667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52774941921234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53194904327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690958976746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52354991436005</t>
+    <t xml:space="preserve">1.52774930000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53194892406464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690970897675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355003356934</t>
   </si>
   <si>
     <t xml:space="preserve">1.50423276424408</t>
@@ -449,10 +449,10 @@
     <t xml:space="preserve">1.54454720020294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54538726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55294609069824</t>
+    <t xml:space="preserve">1.54538714885712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55294585227966</t>
   </si>
   <si>
     <t xml:space="preserve">1.52019047737122</t>
@@ -461,67 +461,67 @@
     <t xml:space="preserve">1.50843214988708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59577989578247</t>
+    <t xml:space="preserve">1.59578013420105</t>
   </si>
   <si>
     <t xml:space="preserve">1.53446853160858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56050479412079</t>
+    <t xml:space="preserve">1.56050515174866</t>
   </si>
   <si>
     <t xml:space="preserve">1.53026914596558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53110909461975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55126631259918</t>
+    <t xml:space="preserve">1.53110897541046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55126619338989</t>
   </si>
   <si>
     <t xml:space="preserve">1.55210614204407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55378580093384</t>
+    <t xml:space="preserve">1.55378592014313</t>
   </si>
   <si>
     <t xml:space="preserve">1.58654129505157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56218481063843</t>
+    <t xml:space="preserve">1.56218469142914</t>
   </si>
   <si>
     <t xml:space="preserve">1.56974375247955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57058370113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60333907604218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54958665370941</t>
+    <t xml:space="preserve">1.57058346271515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60333931446075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54958641529083</t>
   </si>
   <si>
     <t xml:space="preserve">1.55798518657684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57142341136932</t>
+    <t xml:space="preserve">1.57142329216003</t>
   </si>
   <si>
     <t xml:space="preserve">1.56470429897308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6108980178833</t>
+    <t xml:space="preserve">1.61089789867401</t>
   </si>
   <si>
     <t xml:space="preserve">1.61173796653748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60417902469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62517595291138</t>
+    <t xml:space="preserve">1.60417890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62517583370209</t>
   </si>
   <si>
     <t xml:space="preserve">1.62097668647766</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">1.61257791519165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5932605266571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58822119235992</t>
+    <t xml:space="preserve">1.59326028823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58822107315063</t>
   </si>
   <si>
     <t xml:space="preserve">1.60753846168518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63105535507202</t>
+    <t xml:space="preserve">1.63105523586273</t>
   </si>
   <si>
     <t xml:space="preserve">1.61425757408142</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">1.77215564250946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7654367685318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75367832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72512233257294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74527931213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72176253795624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70664489269257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73856031894684</t>
+    <t xml:space="preserve">1.76543653011322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75367844104767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72512209415436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74527966976166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72176277637482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70664501190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73856019973755</t>
   </si>
   <si>
     <t xml:space="preserve">1.69992578029633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67892861366272</t>
+    <t xml:space="preserve">1.67892873287201</t>
   </si>
   <si>
     <t xml:space="preserve">1.69656622409821</t>
@@ -584,34 +584,34 @@
     <t xml:space="preserve">1.69320666790009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7049652338028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77383553981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75871777534485</t>
+    <t xml:space="preserve">1.70496499538422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77383577823639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75871789455414</t>
   </si>
   <si>
     <t xml:space="preserve">1.68984723091125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69152665138245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66801023483276</t>
+    <t xml:space="preserve">1.69152677059174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66800999641418</t>
   </si>
   <si>
     <t xml:space="preserve">1.68816745281219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71336400508881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73184132575989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535809993744</t>
+    <t xml:space="preserve">1.71336388587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7318412065506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535798072815</t>
   </si>
   <si>
     <t xml:space="preserve">1.7100043296814</t>
@@ -620,22 +620,22 @@
     <t xml:space="preserve">1.71672332286835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73016154766083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74695944786072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047610282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031888484955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78895378112793</t>
+    <t xml:space="preserve">1.73016142845154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74695932865143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77047598361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375687122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031876564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78895354270935</t>
   </si>
   <si>
     <t xml:space="preserve">1.74024021625519</t>
@@ -644,34 +644,34 @@
     <t xml:space="preserve">1.76207733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73352110385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903185367584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78055441379547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254886627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86958265304565</t>
+    <t xml:space="preserve">1.73352098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903209209442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78055453300476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254874706268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86958229541779</t>
   </si>
   <si>
     <t xml:space="preserve">1.86454296112061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84774529933929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391420841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90480971336365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98488640785217</t>
+    <t xml:space="preserve">1.84774541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391408920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90480959415436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98488652706146</t>
   </si>
   <si>
     <t xml:space="preserve">2.34267735481262</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">2.35119581222534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24045133590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18081951141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36482620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32223200798035</t>
+    <t xml:space="preserve">2.24045157432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.180819272995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.364825963974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32223224639893</t>
   </si>
   <si>
     <t xml:space="preserve">2.34608459472656</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">2.33415842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24897003173828</t>
+    <t xml:space="preserve">2.24897027015686</t>
   </si>
   <si>
     <t xml:space="preserve">2.20296835899353</t>
@@ -707,22 +707,22 @@
     <t xml:space="preserve">2.14163279533386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07007503509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01896190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95932984352112</t>
+    <t xml:space="preserve">2.07007479667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01896166801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95932996273041</t>
   </si>
   <si>
     <t xml:space="preserve">2.01044273376465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00192403793335</t>
+    <t xml:space="preserve">2.0649631023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00192427635193</t>
   </si>
   <si>
     <t xml:space="preserve">2.02407312393188</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">2.06155610084534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04451823234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0683708190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303740501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111075401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9797750711441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99340522289276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97636735439301</t>
+    <t xml:space="preserve">2.04451847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837129592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303692817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0411102771759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97977519035339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99340498447418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97636723518372</t>
   </si>
   <si>
     <t xml:space="preserve">1.97125649452209</t>
@@ -758,64 +758,64 @@
     <t xml:space="preserve">1.9746640920639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95081114768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93888473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92525470256805</t>
+    <t xml:space="preserve">1.95081126689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.938884973526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92525446414948</t>
   </si>
   <si>
     <t xml:space="preserve">1.9269585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94229257106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95762646198273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718075752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866206169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97295999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00703549385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01555418968201</t>
+    <t xml:space="preserve">1.94229221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95762634277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718087673187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97296011447906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00703525543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01555442810059</t>
   </si>
   <si>
     <t xml:space="preserve">1.98829400539398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93206977844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673576831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91332852840424</t>
+    <t xml:space="preserve">1.93206965923309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673624515533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91332840919495</t>
   </si>
   <si>
     <t xml:space="preserve">1.90821695327759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93377375602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94058871269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822531700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25578546524048</t>
+    <t xml:space="preserve">1.93377351760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94058883190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25578498840332</t>
   </si>
   <si>
     <t xml:space="preserve">2.22341346740723</t>
@@ -824,46 +824,46 @@
     <t xml:space="preserve">2.35971474647522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27452659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41593885421753</t>
+    <t xml:space="preserve">2.27452683448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41593933105469</t>
   </si>
   <si>
     <t xml:space="preserve">2.41253185272217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3682336807251</t>
+    <t xml:space="preserve">2.36823391914368</t>
   </si>
   <si>
     <t xml:space="preserve">2.30860185623169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31200957298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31541705131531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28986024856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42445778846741</t>
+    <t xml:space="preserve">2.31200933456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31541681289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28986048698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42445802688599</t>
   </si>
   <si>
     <t xml:space="preserve">2.41423535346985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36993718147278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39719748497009</t>
+    <t xml:space="preserve">2.36993741989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39719772338867</t>
   </si>
   <si>
     <t xml:space="preserve">2.35801100730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30519461631775</t>
+    <t xml:space="preserve">2.30519437789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.32052803039551</t>
@@ -875,55 +875,55 @@
     <t xml:space="preserve">2.31882452964783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34778833389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36312222480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3443808555603</t>
+    <t xml:space="preserve">2.3477885723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3631227016449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
     <t xml:space="preserve">2.32563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33926963806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36653017997742</t>
+    <t xml:space="preserve">2.3392698764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36652994155884</t>
   </si>
   <si>
     <t xml:space="preserve">2.3767523765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38356781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27111911773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25408124923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09392762184143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15696668624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10585379600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10415005683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12800288200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31712079048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28304553031921</t>
+    <t xml:space="preserve">2.38356757164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27111864089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25408148765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09392714500427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15696716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10585355758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10414981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12800240516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31712055206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28304529190063</t>
   </si>
   <si>
     <t xml:space="preserve">2.30349063873291</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">2.29667568206787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28815698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21659851074219</t>
+    <t xml:space="preserve">2.28815674781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21659874916077</t>
   </si>
   <si>
     <t xml:space="preserve">2.23874759674072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21489477157593</t>
+    <t xml:space="preserve">2.21489453315735</t>
   </si>
   <si>
     <t xml:space="preserve">2.25748944282532</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">2.18933844566345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26259994506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22511720657349</t>
+    <t xml:space="preserve">2.26260018348694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22511768341064</t>
   </si>
   <si>
     <t xml:space="preserve">2.23363637924194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23022890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20637607574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29156446456909</t>
+    <t xml:space="preserve">2.23022866249084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20637583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29156422615051</t>
   </si>
   <si>
     <t xml:space="preserve">2.39379000663757</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">2.41934657096863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53009104728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57268524169922</t>
+    <t xml:space="preserve">2.53009152412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5726854801178</t>
   </si>
   <si>
     <t xml:space="preserve">2.54712891578674</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">2.47045969963074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46194076538086</t>
+    <t xml:space="preserve">2.46194052696228</t>
   </si>
   <si>
     <t xml:space="preserve">2.38527131080627</t>
@@ -1007,28 +1007,28 @@
     <t xml:space="preserve">2.41082787513733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30008316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45342206954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60676074028015</t>
+    <t xml:space="preserve">2.30008292198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45342183113098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60676050186157</t>
   </si>
   <si>
     <t xml:space="preserve">2.61527943611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64935493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4363842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52157258987427</t>
+    <t xml:space="preserve">2.6493546962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43638396263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52157235145569</t>
   </si>
   <si>
     <t xml:space="preserve">2.53861021995544</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">2.44490265846252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26600790023804</t>
+    <t xml:space="preserve">2.26600766181946</t>
   </si>
   <si>
     <t xml:space="preserve">2.14674425125122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19671082496643</t>
+    <t xml:space="preserve">2.19671034812927</t>
   </si>
   <si>
     <t xml:space="preserve">2.1185667514801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17066240310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29221963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25748872756958</t>
+    <t xml:space="preserve">2.17066216468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29221940040588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25748896598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.24880623817444</t>
@@ -1073,49 +1073,49 @@
     <t xml:space="preserve">2.27485394477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34431552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35299825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30090260505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30958485603333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32695031166077</t>
+    <t xml:space="preserve">2.34431529045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35299801826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30090236663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30958461761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32695007324219</t>
   </si>
   <si>
     <t xml:space="preserve">2.28353714942932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21407580375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17934489250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20539307594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15329694747925</t>
+    <t xml:space="preserve">2.21407556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17934465408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20539283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15329742431641</t>
   </si>
   <si>
     <t xml:space="preserve">2.13593196868896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10988426208496</t>
+    <t xml:space="preserve">2.1098837852478</t>
   </si>
   <si>
     <t xml:space="preserve">2.18802762031555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09251880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22275853157043</t>
+    <t xml:space="preserve">2.09251832962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22275829315186</t>
   </si>
   <si>
     <t xml:space="preserve">2.07515335083008</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">2.0838360786438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10120105743408</t>
+    <t xml:space="preserve">2.10120129585266</t>
   </si>
   <si>
     <t xml:space="preserve">2.04042267799377</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">2.01437449455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05778789520264</t>
+    <t xml:space="preserve">2.05778813362122</t>
   </si>
   <si>
     <t xml:space="preserve">2.06647086143494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99700927734375</t>
+    <t xml:space="preserve">1.99700939655304</t>
   </si>
   <si>
     <t xml:space="preserve">2.00569200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964429855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96227872371674</t>
+    <t xml:space="preserve">1.97964406013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96227860450745</t>
   </si>
   <si>
     <t xml:space="preserve">2.02305746078491</t>
@@ -1157,31 +1157,31 @@
     <t xml:space="preserve">2.04910516738892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03173995018005</t>
+    <t xml:space="preserve">2.03173971176147</t>
   </si>
   <si>
     <t xml:space="preserve">1.93623089790344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87545251846313</t>
+    <t xml:space="preserve">1.87545228004456</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281785488129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82335638999939</t>
+    <t xml:space="preserve">1.82335650920868</t>
   </si>
   <si>
     <t xml:space="preserve">1.81467366218567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77994322776794</t>
+    <t xml:space="preserve">1.77994310855865</t>
   </si>
   <si>
     <t xml:space="preserve">1.71916460990906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69311666488647</t>
+    <t xml:space="preserve">1.69311678409576</t>
   </si>
   <si>
     <t xml:space="preserve">1.62799680233002</t>
@@ -1190,52 +1190,52 @@
     <t xml:space="preserve">1.63233804702759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67575132846832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68443405628204</t>
+    <t xml:space="preserve">1.67575120925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68443417549133</t>
   </si>
   <si>
     <t xml:space="preserve">1.71048212051392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6887754201889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71482348442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69745802879333</t>
+    <t xml:space="preserve">1.68877530097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7148232460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69745790958405</t>
   </si>
   <si>
     <t xml:space="preserve">1.64536201953888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59760773181915</t>
+    <t xml:space="preserve">1.59760749340057</t>
   </si>
   <si>
     <t xml:space="preserve">1.60629022121429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61931419372559</t>
+    <t xml:space="preserve">1.61931431293488</t>
   </si>
   <si>
     <t xml:space="preserve">1.61497271060944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63667953014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64970338344574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68009269237518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65838599205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70179927349091</t>
+    <t xml:space="preserve">1.63667941093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64970350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68009257316589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65838611125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70179951190948</t>
   </si>
   <si>
     <t xml:space="preserve">1.67141008377075</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">1.66706871986389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5715594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52814614772797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51078104972839</t>
+    <t xml:space="preserve">1.57155954837799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52814626693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51078116893768</t>
   </si>
   <si>
     <t xml:space="preserve">1.54551160335541</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">1.66272747516632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72784733772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76257789134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75389528274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78862571716309</t>
+    <t xml:space="preserve">1.72784721851349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7625777721405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75389516353607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78862583637238</t>
   </si>
   <si>
     <t xml:space="preserve">1.80599117279053</t>
@@ -1283,79 +1283,82 @@
     <t xml:space="preserve">1.77126049995422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74521243572235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83203887939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79730844497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84072148799896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86676979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91018283367157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9535961151123</t>
+    <t xml:space="preserve">1.74521255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83203899860382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79730832576752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84072160720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86676967144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91018307209015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359647274017</t>
   </si>
   <si>
     <t xml:space="preserve">1.94491338729858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98832666873932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97096157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.918865442276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92754805088043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85808730125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84940457344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413512706757</t>
+    <t xml:space="preserve">1.98832678794861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97096145153046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91886556148529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9275484085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8580869436264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84940445423126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413488864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62365543842316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6504191160202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61919510364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6013525724411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61027371883392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63703727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6548798084259</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6504191160202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61919498443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6013525724411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61027359962463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63703727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65487968921661</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.64595866203308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64149808883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65934014320374</t>
+    <t xml:space="preserve">1.64149796962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65934026241302</t>
   </si>
   <si>
     <t xml:space="preserve">1.66826140880585</t>
@@ -1364,13 +1367,13 @@
     <t xml:space="preserve">1.68610382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68164324760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63257670402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60581302642822</t>
+    <t xml:space="preserve">1.68164312839508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63257658481598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60581314563751</t>
   </si>
   <si>
     <t xml:space="preserve">1.62811613082886</t>
@@ -1382,16 +1385,16 @@
     <t xml:space="preserve">1.58351027965546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57904946804047</t>
+    <t xml:space="preserve">1.57904958724976</t>
   </si>
   <si>
     <t xml:space="preserve">1.552286028862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54336488246918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59243142604828</t>
+    <t xml:space="preserve">1.54336500167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59243130683899</t>
   </si>
   <si>
     <t xml:space="preserve">1.56120717525482</t>
@@ -1400,10 +1403,10 @@
     <t xml:space="preserve">1.53890430927277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5567467212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57012820243835</t>
+    <t xml:space="preserve">1.55674660205841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57012832164764</t>
   </si>
   <si>
     <t xml:space="preserve">1.58797073364258</t>
@@ -1412,10 +1415,10 @@
     <t xml:space="preserve">1.57458901405334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59689199924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53444373607635</t>
+    <t xml:space="preserve">1.5968918800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53444385528564</t>
   </si>
   <si>
     <t xml:space="preserve">1.66380095481873</t>
@@ -1433,22 +1436,22 @@
     <t xml:space="preserve">1.50768029689789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42738962173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51660144329071</t>
+    <t xml:space="preserve">1.42738950252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51660132408142</t>
   </si>
   <si>
     <t xml:space="preserve">1.48983776569366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34263813495636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709882736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32479572296143</t>
+    <t xml:space="preserve">1.34263825416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709870815277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32479584217072</t>
   </si>
   <si>
     <t xml:space="preserve">1.19097816944122</t>
@@ -1457,7 +1460,7 @@
     <t xml:space="preserve">1.26680815219879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24450516700745</t>
+    <t xml:space="preserve">1.24450528621674</t>
   </si>
   <si>
     <t xml:space="preserve">1.29803240299225</t>
@@ -1472,7 +1475,7 @@
     <t xml:space="preserve">1.28465056419373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30695354938507</t>
+    <t xml:space="preserve">1.30695366859436</t>
   </si>
   <si>
     <t xml:space="preserve">1.30249297618866</t>
@@ -1484,10 +1487,10 @@
     <t xml:space="preserve">1.36494112014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35601997375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36048054695129</t>
+    <t xml:space="preserve">1.35602009296417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36048066616058</t>
   </si>
   <si>
     <t xml:space="preserve">1.40508639812469</t>
@@ -1496,13 +1499,13 @@
     <t xml:space="preserve">1.44969236850739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4541529417038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44523191452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43631076812744</t>
+    <t xml:space="preserve">1.45415306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44523179531097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43631064891815</t>
   </si>
   <si>
     <t xml:space="preserve">1.4184684753418</t>
@@ -1517,13 +1520,13 @@
     <t xml:space="preserve">1.40062594413757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41400766372681</t>
+    <t xml:space="preserve">1.4140077829361</t>
   </si>
   <si>
     <t xml:space="preserve">1.38278353214264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724410533905</t>
+    <t xml:space="preserve">1.38724398612976</t>
   </si>
   <si>
     <t xml:space="preserve">1.33817768096924</t>
@@ -1532,34 +1535,34 @@
     <t xml:space="preserve">1.35155940055847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29357171058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32925653457642</t>
+    <t xml:space="preserve">1.29357159137726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32925641536713</t>
   </si>
   <si>
     <t xml:space="preserve">1.33371698856354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3158745765686</t>
+    <t xml:space="preserve">1.31587469577789</t>
   </si>
   <si>
     <t xml:space="preserve">1.37386238574982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31141424179077</t>
+    <t xml:space="preserve">1.31141412258148</t>
   </si>
   <si>
     <t xml:space="preserve">1.3203352689743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28018975257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4095470905304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39616549015045</t>
+    <t xml:space="preserve">1.28018987178802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40954697132111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39616537094116</t>
   </si>
   <si>
     <t xml:space="preserve">1.45861351490021</t>
@@ -1577,10 +1580,10 @@
     <t xml:space="preserve">1.2712687253952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26234757900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24896585941315</t>
+    <t xml:space="preserve">1.26234769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24896574020386</t>
   </si>
   <si>
     <t xml:space="preserve">1.46753478050232</t>
@@ -1598,7 +1601,7 @@
     <t xml:space="preserve">1.50321936607361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52998316287994</t>
+    <t xml:space="preserve">1.52998328208923</t>
   </si>
   <si>
     <t xml:space="preserve">1.49875891208649</t>
@@ -1610,13 +1613,13 @@
     <t xml:space="preserve">1.48537719249725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52106189727783</t>
+    <t xml:space="preserve">1.52106177806854</t>
   </si>
   <si>
     <t xml:space="preserve">1.72178852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76639449596405</t>
+    <t xml:space="preserve">1.76639461517334</t>
   </si>
   <si>
     <t xml:space="preserve">1.73963093757629</t>
@@ -1634,22 +1637,22 @@
     <t xml:space="preserve">1.83776390552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423678874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77531564235687</t>
+    <t xml:space="preserve">1.78423690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77531576156616</t>
   </si>
   <si>
     <t xml:space="preserve">1.73517036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085518836975</t>
+    <t xml:space="preserve">1.77085506916046</t>
   </si>
   <si>
     <t xml:space="preserve">1.72624909877777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73070979118347</t>
+    <t xml:space="preserve">1.73070991039276</t>
   </si>
   <si>
     <t xml:space="preserve">1.74855208396912</t>
@@ -1661,10 +1664,10 @@
     <t xml:space="preserve">1.71732795238495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74409151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77977633476257</t>
+    <t xml:space="preserve">1.74409139156342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77977621555328</t>
   </si>
   <si>
     <t xml:space="preserve">1.81100046634674</t>
@@ -1673,7 +1676,7 @@
     <t xml:space="preserve">1.84668517112732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86452734470367</t>
+    <t xml:space="preserve">1.86452746391296</t>
   </si>
   <si>
     <t xml:space="preserve">1.80207920074463</t>
@@ -1682,19 +1685,19 @@
     <t xml:space="preserve">1.75747334957123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0340301990509</t>
+    <t xml:space="preserve">2.03402996063232</t>
   </si>
   <si>
     <t xml:space="preserve">2.0251088142395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96266031265259</t>
+    <t xml:space="preserve">1.96266067028046</t>
   </si>
   <si>
     <t xml:space="preserve">1.92697596549988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050260543823</t>
+    <t xml:space="preserve">1.98050272464752</t>
   </si>
   <si>
     <t xml:space="preserve">2.07863593101501</t>
@@ -1703,13 +1706,13 @@
     <t xml:space="preserve">2.1053991317749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05187225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06079339981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09647822380066</t>
+    <t xml:space="preserve">2.05187249183655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06079363822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09647798538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.43548321723938</t>
@@ -1718,16 +1721,16 @@
     <t xml:space="preserve">2.46224665641785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39087748527527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56037950515747</t>
+    <t xml:space="preserve">2.39087772369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56037974357605</t>
   </si>
   <si>
     <t xml:space="preserve">2.60498595237732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65005493164062</t>
+    <t xml:space="preserve">2.65005469322205</t>
   </si>
   <si>
     <t xml:space="preserve">2.61399960517883</t>
@@ -1736,34 +1739,34 @@
     <t xml:space="preserve">2.64104080200195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74019265174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78526139259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73117899894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90244126319885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1007444858551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99257898330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92948246002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84835839271545</t>
+    <t xml:space="preserve">2.74019289016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78526163101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73117876052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90244102478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10074472427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99257874488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92948222160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84835815429688</t>
   </si>
   <si>
     <t xml:space="preserve">2.76723408699036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83934450149536</t>
+    <t xml:space="preserve">2.83934473991394</t>
   </si>
   <si>
     <t xml:space="preserve">2.87539958953857</t>
@@ -1772,7 +1775,7 @@
     <t xml:space="preserve">2.82131695747375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77624797821045</t>
+    <t xml:space="preserve">2.77624773979187</t>
   </si>
   <si>
     <t xml:space="preserve">2.72216510772705</t>
@@ -1787,34 +1790,34 @@
     <t xml:space="preserve">2.58695816993713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65906858444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67709636688232</t>
+    <t xml:space="preserve">2.65906882286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67709612846375</t>
   </si>
   <si>
     <t xml:space="preserve">2.5238618850708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6230137348175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57794451713562</t>
+    <t xml:space="preserve">2.62301349639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5779447555542</t>
   </si>
   <si>
     <t xml:space="preserve">2.59597206115723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55090308189392</t>
+    <t xml:space="preserve">2.5509033203125</t>
   </si>
   <si>
     <t xml:space="preserve">2.51484799385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56893062591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79427552223206</t>
+    <t xml:space="preserve">2.56893038749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79427528381348</t>
   </si>
   <si>
     <t xml:space="preserve">2.83033061027527</t>
@@ -1832,22 +1835,22 @@
     <t xml:space="preserve">2.80328917503357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86638593673706</t>
+    <t xml:space="preserve">2.86638617515564</t>
   </si>
   <si>
     <t xml:space="preserve">3.0015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09173083305359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96553754806519</t>
+    <t xml:space="preserve">3.09173059463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96553730964661</t>
   </si>
   <si>
     <t xml:space="preserve">2.93849611282349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81230282783508</t>
+    <t xml:space="preserve">2.81230306625366</t>
   </si>
   <si>
     <t xml:space="preserve">2.54188919067383</t>
@@ -1856,7 +1859,7 @@
     <t xml:space="preserve">2.47879266738892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63202714920044</t>
+    <t xml:space="preserve">2.63202738761902</t>
   </si>
   <si>
     <t xml:space="preserve">2.91145467758179</t>
@@ -1865,7 +1868,7 @@
     <t xml:space="preserve">2.9745512008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95652341842651</t>
+    <t xml:space="preserve">2.95652365684509</t>
   </si>
   <si>
     <t xml:space="preserve">3.01060628890991</t>
@@ -1874,10 +1877,10 @@
     <t xml:space="preserve">3.01962018013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98356485366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88441348075867</t>
+    <t xml:space="preserve">2.98356509208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88441324234009</t>
   </si>
   <si>
     <t xml:space="preserve">2.94751000404358</t>
@@ -1886,7 +1889,7 @@
     <t xml:space="preserve">2.92046856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85737180709839</t>
+    <t xml:space="preserve">2.85737204551697</t>
   </si>
   <si>
     <t xml:space="preserve">2.75822019577026</t>
@@ -1901,13 +1904,13 @@
     <t xml:space="preserve">2.19035148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28048944473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.415696144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3165442943573</t>
+    <t xml:space="preserve">2.28048920631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41569590568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31654453277588</t>
   </si>
   <si>
     <t xml:space="preserve">2.36161327362061</t>
@@ -1922,7 +1925,7 @@
     <t xml:space="preserve">2.44273734092712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37964105606079</t>
+    <t xml:space="preserve">2.37964129447937</t>
   </si>
   <si>
     <t xml:space="preserve">2.37062740325928</t>
@@ -1931,28 +1934,28 @@
     <t xml:space="preserve">2.27147555351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26246190071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2895028591156</t>
+    <t xml:space="preserve">2.26246213912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28950309753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555842399597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.343585729599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21739268302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20837903022766</t>
+    <t xml:space="preserve">2.32555818557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851698875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34358596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21739292144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20837879180908</t>
   </si>
   <si>
     <t xml:space="preserve">2.23598384857178</t>
@@ -1965,9 +1968,6 @@
   </si>
   <si>
     <t xml:space="preserve">2.18077421188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20837879180908</t>
   </si>
   <si>
     <t xml:space="preserve">2.16237092018127</t>
@@ -25618,7 +25618,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G872" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25670,7 +25670,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G874" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25696,7 +25696,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G875" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25748,7 +25748,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G877" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25774,7 +25774,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G878" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25800,7 +25800,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G879" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25826,7 +25826,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G880" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25852,7 +25852,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G881" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25878,7 +25878,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G882" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25956,7 +25956,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G885" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25982,7 +25982,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G886" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26008,7 +26008,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G887" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26034,7 +26034,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G888" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26086,7 +26086,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G890" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26112,7 +26112,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G891" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26138,7 +26138,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G892" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26190,7 +26190,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G894" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26216,7 +26216,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G895" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26242,7 +26242,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G896" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26268,7 +26268,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26294,7 +26294,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G898" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26320,7 +26320,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G899" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26372,7 +26372,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G901" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26398,7 +26398,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G902" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26424,7 +26424,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G903" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26450,7 +26450,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G904" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26502,7 +26502,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G906" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26528,7 +26528,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G907" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26554,7 +26554,7 @@
         <v>1.75</v>
       </c>
       <c r="G908" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26580,7 +26580,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G909" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26606,7 +26606,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G910" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26632,7 +26632,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G911" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26658,7 +26658,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G912" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26684,7 +26684,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G913" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26710,7 +26710,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G914" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26736,7 +26736,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G915" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26762,7 +26762,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G916" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26788,7 +26788,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G917" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26814,7 +26814,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G918" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26840,7 +26840,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G919" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26866,7 +26866,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G920" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26892,7 +26892,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G921" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26918,7 +26918,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G922" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26970,7 +26970,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G924" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26996,7 +26996,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G925" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27022,7 +27022,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G926" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27100,7 +27100,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G929" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27126,7 +27126,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G930" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27152,7 +27152,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G931" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27178,7 +27178,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G932" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27230,7 +27230,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G934" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27256,7 +27256,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27282,7 +27282,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G936" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27308,7 +27308,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G937" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27334,7 +27334,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G938" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27360,7 +27360,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G939" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27386,7 +27386,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G940" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27412,7 +27412,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G941" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27438,7 +27438,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G942" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27464,7 +27464,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G943" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27516,7 +27516,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G945" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27542,7 +27542,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27568,7 +27568,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G947" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27594,7 +27594,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27620,7 +27620,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27646,7 +27646,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G950" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27672,7 +27672,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G951" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27698,7 +27698,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G952" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27724,7 +27724,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G953" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27750,7 +27750,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G954" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27776,7 +27776,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G955" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27802,7 +27802,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G956" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27828,7 +27828,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G957" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27854,7 +27854,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G958" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27880,7 +27880,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27906,7 +27906,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G960" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27932,7 +27932,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G961" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27958,7 +27958,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G962" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27984,7 +27984,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G963" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28062,7 +28062,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G966" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28088,7 +28088,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G967" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28114,7 +28114,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G968" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28166,7 +28166,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G970" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28218,7 +28218,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G972" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28244,7 +28244,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G973" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28270,7 +28270,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G974" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28296,7 +28296,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G975" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28348,7 +28348,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G977" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28374,7 +28374,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G978" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28400,7 +28400,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G979" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28426,7 +28426,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G980" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28530,7 +28530,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G984" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28556,7 +28556,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G985" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28582,7 +28582,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G986" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28608,7 +28608,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G987" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28634,7 +28634,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28660,7 +28660,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G989" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28686,7 +28686,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G990" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28712,7 +28712,7 @@
         <v>1.75</v>
       </c>
       <c r="G991" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28738,7 +28738,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G992" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28764,7 +28764,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G993" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28790,7 +28790,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G994" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28894,7 +28894,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G998" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28920,7 +28920,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G999" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28998,7 +28998,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1002" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29050,7 +29050,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1004" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29076,7 +29076,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1005" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29128,7 +29128,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1007" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29154,7 +29154,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29206,7 +29206,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1010" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29232,7 +29232,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1011" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29258,7 +29258,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1012" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29284,7 +29284,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1013" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29310,7 +29310,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1014" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29336,7 +29336,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1015" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29362,7 +29362,7 @@
         <v>1.75</v>
       </c>
       <c r="G1016" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29388,7 +29388,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1017" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29414,7 +29414,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1018" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29466,7 +29466,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1020" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29492,7 +29492,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1021" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29518,7 +29518,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1022" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29544,7 +29544,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1023" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29570,7 +29570,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1024" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29596,7 +29596,7 @@
         <v>1.75</v>
       </c>
       <c r="G1025" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29622,7 +29622,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1026" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29648,7 +29648,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1027" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29674,7 +29674,7 @@
         <v>1.75</v>
       </c>
       <c r="G1028" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29700,7 +29700,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1029" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29726,7 +29726,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1030" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29752,7 +29752,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1031" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29778,7 +29778,7 @@
         <v>1.75</v>
       </c>
       <c r="G1032" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29804,7 +29804,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1033" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29830,7 +29830,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1034" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29856,7 +29856,7 @@
         <v>1.75</v>
       </c>
       <c r="G1035" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29882,7 +29882,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29908,7 +29908,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1037" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29934,7 +29934,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1038" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29960,7 +29960,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1039" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29986,7 +29986,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1040" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30012,7 +30012,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1041" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30038,7 +30038,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1042" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30064,7 +30064,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1043" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30090,7 +30090,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1044" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30116,7 +30116,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1045" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30142,7 +30142,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1046" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30168,7 +30168,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1047" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30194,7 +30194,7 @@
         <v>1.75</v>
       </c>
       <c r="G1048" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30220,7 +30220,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1049" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30246,7 +30246,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1050" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30272,7 +30272,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1051" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30298,7 +30298,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30324,7 +30324,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1053" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30350,7 +30350,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1054" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30376,7 +30376,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1055" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30402,7 +30402,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1056" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30428,7 +30428,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30454,7 +30454,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1058" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30480,7 +30480,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1059" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30506,7 +30506,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1060" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30532,7 +30532,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30558,7 +30558,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1062" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30584,7 +30584,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1063" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30610,7 +30610,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1064" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30636,7 +30636,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1065" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30662,7 +30662,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1066" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30688,7 +30688,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30714,7 +30714,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30740,7 +30740,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1069" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30766,7 +30766,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1070" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30792,7 +30792,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1071" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30818,7 +30818,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1072" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30844,7 +30844,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1073" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30870,7 +30870,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1074" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30896,7 +30896,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1075" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30922,7 +30922,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1076" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30948,7 +30948,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1077" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30974,7 +30974,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1078" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31000,7 +31000,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1079" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31026,7 +31026,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1080" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31052,7 +31052,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1081" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31078,7 +31078,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1082" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31104,7 +31104,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1083" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31130,7 +31130,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1084" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31156,7 +31156,7 @@
         <v>1.625</v>
       </c>
       <c r="G1085" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31182,7 +31182,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1086" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31208,7 +31208,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1087" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31234,7 +31234,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1088" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31260,7 +31260,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1089" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31286,7 +31286,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1090" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31312,7 +31312,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1091" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31338,7 +31338,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1092" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31364,7 +31364,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1093" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31390,7 +31390,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1094" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31416,7 +31416,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1095" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31442,7 +31442,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1096" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31468,7 +31468,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1097" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31494,7 +31494,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31520,7 +31520,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1099" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31546,7 +31546,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1100" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31572,7 +31572,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1101" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31598,7 +31598,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1102" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31624,7 +31624,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1103" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31650,7 +31650,7 @@
         <v>1.5</v>
       </c>
       <c r="G1104" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31676,7 +31676,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1105" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31702,7 +31702,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1106" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31728,7 +31728,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1107" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31754,7 +31754,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1108" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31780,7 +31780,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1109" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31806,7 +31806,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1110" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31832,7 +31832,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1111" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31858,7 +31858,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1112" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31884,7 +31884,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1113" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31910,7 +31910,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1114" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31936,7 +31936,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1115" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31962,7 +31962,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1116" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31988,7 +31988,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1117" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32014,7 +32014,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1118" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32040,7 +32040,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1119" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32066,7 +32066,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1120" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32092,7 +32092,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1121" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32118,7 +32118,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1122" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32144,7 +32144,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1123" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32170,7 +32170,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1124" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32196,7 +32196,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1125" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32222,7 +32222,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1126" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32248,7 +32248,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1127" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32274,7 +32274,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1128" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32300,7 +32300,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1129" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32326,7 +32326,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1130" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32352,7 +32352,7 @@
         <v>1.5</v>
       </c>
       <c r="G1131" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32378,7 +32378,7 @@
         <v>1.5</v>
       </c>
       <c r="G1132" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32404,7 +32404,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1133" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32430,7 +32430,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1134" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32456,7 +32456,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1135" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32482,7 +32482,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1136" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32508,7 +32508,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1137" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32534,7 +32534,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1138" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32560,7 +32560,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1139" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32586,7 +32586,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1140" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32612,7 +32612,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1141" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32638,7 +32638,7 @@
         <v>1.5</v>
       </c>
       <c r="G1142" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32664,7 +32664,7 @@
         <v>1.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32690,7 +32690,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1144" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32716,7 +32716,7 @@
         <v>1.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32742,7 +32742,7 @@
         <v>1.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32768,7 +32768,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1147" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32794,7 +32794,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32820,7 +32820,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1149" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32846,7 +32846,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1150" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32872,7 +32872,7 @@
         <v>1.5</v>
       </c>
       <c r="G1151" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32898,7 +32898,7 @@
         <v>1.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32924,7 +32924,7 @@
         <v>1.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32950,7 +32950,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1154" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32976,7 +32976,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33002,7 +33002,7 @@
         <v>1.5</v>
       </c>
       <c r="G1156" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33028,7 +33028,7 @@
         <v>1.5</v>
       </c>
       <c r="G1157" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33054,7 +33054,7 @@
         <v>1.5</v>
       </c>
       <c r="G1158" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33080,7 +33080,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1159" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33106,7 +33106,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1160" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33132,7 +33132,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1161" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33158,7 +33158,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33184,7 +33184,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1163" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33210,7 +33210,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1164" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33236,7 +33236,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1165" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33262,7 +33262,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33288,7 +33288,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1167" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33314,7 +33314,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33340,7 +33340,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1169" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33366,7 +33366,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1170" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33392,7 +33392,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33418,7 +33418,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1172" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33444,7 +33444,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1173" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33470,7 +33470,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1174" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33496,7 +33496,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1175" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33522,7 +33522,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1176" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33548,7 +33548,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1177" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33574,7 +33574,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33600,7 +33600,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1179" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33626,7 +33626,7 @@
         <v>1.5</v>
       </c>
       <c r="G1180" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33652,7 +33652,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1181" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33678,7 +33678,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1182" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33704,7 +33704,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1183" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33730,7 +33730,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1184" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33756,7 +33756,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33782,7 +33782,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1186" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33808,7 +33808,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1187" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33834,7 +33834,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1188" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33860,7 +33860,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1189" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33886,7 +33886,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1190" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33912,7 +33912,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1191" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33938,7 +33938,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1192" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33964,7 +33964,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1193" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33990,7 +33990,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1194" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34016,7 +34016,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1195" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34042,7 +34042,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1196" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34068,7 +34068,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1197" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34094,7 +34094,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1198" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34120,7 +34120,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1199" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34146,7 +34146,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1200" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34172,7 +34172,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1201" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34198,7 +34198,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1202" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34224,7 +34224,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1203" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34250,7 +34250,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34276,7 +34276,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34302,7 +34302,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34328,7 +34328,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1207" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34354,7 +34354,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1208" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34380,7 +34380,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34406,7 +34406,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1210" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34432,7 +34432,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34458,7 +34458,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34484,7 +34484,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1213" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34510,7 +34510,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1214" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34536,7 +34536,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1215" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34562,7 +34562,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34588,7 +34588,7 @@
         <v>1.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34614,7 +34614,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1218" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34640,7 +34640,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1219" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34666,7 +34666,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1220" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34692,7 +34692,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1221" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34718,7 +34718,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1222" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34744,7 +34744,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1223" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34770,7 +34770,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34796,7 +34796,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1225" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34822,7 +34822,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1226" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34848,7 +34848,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1227" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34874,7 +34874,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1228" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34900,7 +34900,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1229" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34926,7 +34926,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1230" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34952,7 +34952,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1231" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34978,7 +34978,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35004,7 +35004,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1233" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35030,7 +35030,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1234" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35056,7 +35056,7 @@
         <v>1.5</v>
       </c>
       <c r="G1235" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35082,7 +35082,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1236" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35108,7 +35108,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35134,7 +35134,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35160,7 +35160,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1239" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35186,7 +35186,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35212,7 +35212,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35238,7 +35238,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1242" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35264,7 +35264,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35290,7 +35290,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1244" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35316,7 +35316,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35342,7 +35342,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1246" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35368,7 +35368,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1247" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35394,7 +35394,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35420,7 +35420,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1249" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35446,7 +35446,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1250" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35472,7 +35472,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1251" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35498,7 +35498,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35524,7 +35524,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35550,7 +35550,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1254" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35576,7 +35576,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1255" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35602,7 +35602,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1256" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35628,7 +35628,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1257" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35654,7 +35654,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1258" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35680,7 +35680,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1259" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35706,7 +35706,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1260" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35732,7 +35732,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1261" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35758,7 +35758,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1262" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35784,7 +35784,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1263" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35810,7 +35810,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1264" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35836,7 +35836,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1265" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35862,7 +35862,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1266" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35888,7 +35888,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35914,7 +35914,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35940,7 +35940,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1269" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35966,7 +35966,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35992,7 +35992,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1271" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36018,7 +36018,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1272" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36044,7 +36044,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1273" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36070,7 +36070,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1274" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36096,7 +36096,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1275" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36122,7 +36122,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36148,7 +36148,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1277" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36174,7 +36174,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36200,7 +36200,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1279" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36226,7 +36226,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1280" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36252,7 +36252,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1281" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36278,7 +36278,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1282" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36304,7 +36304,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1283" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36330,7 +36330,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1284" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36356,7 +36356,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1285" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36382,7 +36382,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1286" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36408,7 +36408,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1287" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36434,7 +36434,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36460,7 +36460,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1289" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36486,7 +36486,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1290" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36512,7 +36512,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1291" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36538,7 +36538,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1292" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36564,7 +36564,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1293" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36590,7 +36590,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1294" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36616,7 +36616,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1295" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36642,7 +36642,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1296" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36668,7 +36668,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1297" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36694,7 +36694,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1298" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36720,7 +36720,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1299" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36772,7 +36772,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1301" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36798,7 +36798,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1302" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36824,7 +36824,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1303" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36850,7 +36850,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1304" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36876,7 +36876,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1305" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36902,7 +36902,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1306" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36928,7 +36928,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1307" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36954,7 +36954,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1308" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36980,7 +36980,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1309" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37006,7 +37006,7 @@
         <v>2</v>
       </c>
       <c r="G1310" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37032,7 +37032,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37058,7 +37058,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1312" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37084,7 +37084,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1313" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -37110,7 +37110,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1314" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37136,7 +37136,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1315" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37162,7 +37162,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1316" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37188,7 +37188,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1317" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37214,7 +37214,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1318" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37240,7 +37240,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37266,7 +37266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37292,7 +37292,7 @@
         <v>2</v>
       </c>
       <c r="G1321" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37318,7 +37318,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1322" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37344,7 +37344,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1323" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37370,7 +37370,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1324" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37396,7 +37396,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1325" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37422,7 +37422,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1326" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37448,7 +37448,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1327" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37474,7 +37474,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1328" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37500,7 +37500,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1329" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37526,7 +37526,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1330" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37552,7 +37552,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1331" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37578,7 +37578,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1332" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37604,7 +37604,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1333" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37630,7 +37630,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1334" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37656,7 +37656,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37682,7 +37682,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1336" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37708,7 +37708,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1337" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37734,7 +37734,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1338" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37760,7 +37760,7 @@
         <v>2</v>
       </c>
       <c r="G1339" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37786,7 +37786,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1340" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37812,7 +37812,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1341" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37838,7 +37838,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1342" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37864,7 +37864,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1343" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37890,7 +37890,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37916,7 +37916,7 @@
         <v>2</v>
       </c>
       <c r="G1345" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37942,7 +37942,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1346" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37968,7 +37968,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37994,7 +37994,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38020,7 +38020,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -38046,7 +38046,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1350" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -38072,7 +38072,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1351" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -38098,7 +38098,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1352" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -38124,7 +38124,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1353" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -38150,7 +38150,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1354" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -38176,7 +38176,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1355" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -38202,7 +38202,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1356" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -38228,7 +38228,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1357" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38254,7 +38254,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1358" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38280,7 +38280,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1359" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38306,7 +38306,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1360" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38332,7 +38332,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1361" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38358,7 +38358,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1362" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38384,7 +38384,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1363" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38410,7 +38410,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1364" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38436,7 +38436,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1365" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38462,7 +38462,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1366" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38488,7 +38488,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38514,7 +38514,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38540,7 +38540,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1369" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38566,7 +38566,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1370" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38592,7 +38592,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1371" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38618,7 +38618,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38644,7 +38644,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1373" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38670,7 +38670,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1374" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38696,7 +38696,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1375" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38722,7 +38722,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1376" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38748,7 +38748,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1377" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38774,7 +38774,7 @@
         <v>3.25</v>
       </c>
       <c r="G1378" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38800,7 +38800,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1379" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38826,7 +38826,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1380" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38852,7 +38852,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1381" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38878,7 +38878,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38904,7 +38904,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38930,7 +38930,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1384" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38956,7 +38956,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1385" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38982,7 +38982,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1386" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -39008,7 +39008,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1387" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -39034,7 +39034,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1388" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -39060,7 +39060,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1389" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39086,7 +39086,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1390" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -39112,7 +39112,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1391" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -39138,7 +39138,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1392" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -39164,7 +39164,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1393" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -39190,7 +39190,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1394" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -39216,7 +39216,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1395" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39242,7 +39242,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1396" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39268,7 +39268,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1397" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -39294,7 +39294,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1398" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39320,7 +39320,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1399" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39346,7 +39346,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1400" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39372,7 +39372,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39398,7 +39398,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1402" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39424,7 +39424,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1403" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39450,7 +39450,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1404" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39476,7 +39476,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1405" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39502,7 +39502,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1406" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39528,7 +39528,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1407" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39554,7 +39554,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1408" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39580,7 +39580,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1409" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39606,7 +39606,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1410" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39632,7 +39632,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1411" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39658,7 +39658,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1412" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39684,7 +39684,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1413" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39710,7 +39710,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1414" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39736,7 +39736,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1415" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39762,7 +39762,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1416" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39788,7 +39788,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1417" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39814,7 +39814,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1418" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39840,7 +39840,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1419" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39866,7 +39866,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1420" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39892,7 +39892,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1421" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39918,7 +39918,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1422" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39944,7 +39944,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1423" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39970,7 +39970,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1424" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39996,7 +39996,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1425" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -40022,7 +40022,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1426" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -40048,7 +40048,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1427" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -40074,7 +40074,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1428" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -40100,7 +40100,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1429" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -40126,7 +40126,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1430" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -40152,7 +40152,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1431" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -40178,7 +40178,7 @@
         <v>3</v>
       </c>
       <c r="G1432" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -40204,7 +40204,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1433" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -40230,7 +40230,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1434" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40256,7 +40256,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1435" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -40282,7 +40282,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1436" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40308,7 +40308,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1437" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40334,7 +40334,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40360,7 +40360,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1439" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40386,7 +40386,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40412,7 +40412,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1441" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40438,7 +40438,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1442" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40464,7 +40464,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1443" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40490,7 +40490,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1444" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40516,7 +40516,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1445" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40542,7 +40542,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1446" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40568,7 +40568,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1447" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40594,7 +40594,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1448" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40620,7 +40620,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1449" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40646,7 +40646,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1450" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40672,7 +40672,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1451" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40698,7 +40698,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1452" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40724,7 +40724,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1453" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40750,7 +40750,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1454" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40776,7 +40776,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1455" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40802,7 +40802,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1456" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40828,7 +40828,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40854,7 +40854,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1458" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40880,7 +40880,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1459" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40906,7 +40906,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1460" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40932,7 +40932,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1461" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40958,7 +40958,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1462" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40984,7 +40984,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1463" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -41010,7 +41010,7 @@
         <v>2.75</v>
       </c>
       <c r="G1464" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -41036,7 +41036,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1465" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -41062,7 +41062,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1466" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -41088,7 +41088,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -41114,7 +41114,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1468" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -41140,7 +41140,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1469" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -41166,7 +41166,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1470" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -41192,7 +41192,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -41218,7 +41218,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1472" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41244,7 +41244,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41270,7 +41270,7 @@
         <v>3</v>
       </c>
       <c r="G1474" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -41296,7 +41296,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1475" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41322,7 +41322,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1476" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41348,7 +41348,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1477" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41374,7 +41374,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1478" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41400,7 +41400,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1479" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41426,7 +41426,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1480" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41452,7 +41452,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1481" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41478,7 +41478,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1482" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41504,7 +41504,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1483" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41530,7 +41530,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1484" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41556,7 +41556,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1485" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41582,7 +41582,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1486" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41608,7 +41608,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1487" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41634,7 +41634,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1488" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41660,7 +41660,7 @@
         <v>3.25</v>
       </c>
       <c r="G1489" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41686,7 +41686,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1490" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41712,7 +41712,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1491" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41738,7 +41738,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1492" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41764,7 +41764,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1493" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41790,7 +41790,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1494" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41816,7 +41816,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1495" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41842,7 +41842,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1496" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41868,7 +41868,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1497" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41894,7 +41894,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41920,7 +41920,7 @@
         <v>3</v>
       </c>
       <c r="G1499" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41946,7 +41946,7 @@
         <v>3</v>
       </c>
       <c r="G1500" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41972,7 +41972,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1501" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41998,7 +41998,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1502" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -42024,7 +42024,7 @@
         <v>3</v>
       </c>
       <c r="G1503" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -42050,7 +42050,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1504" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -42076,7 +42076,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1505" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -42102,7 +42102,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -42128,7 +42128,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1507" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -42154,7 +42154,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1508" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -42180,7 +42180,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -42206,7 +42206,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1510" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -42232,7 +42232,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1511" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42258,7 +42258,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1512" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42284,7 +42284,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1513" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42310,7 +42310,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1514" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42336,7 +42336,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1515" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42362,7 +42362,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1516" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42388,7 +42388,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42414,7 +42414,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1518" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42440,7 +42440,7 @@
         <v>3</v>
       </c>
       <c r="G1519" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42466,7 +42466,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1520" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42492,7 +42492,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42518,7 +42518,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1522" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42544,7 +42544,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1523" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42570,7 +42570,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42596,7 +42596,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42622,7 +42622,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1526" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42648,7 +42648,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1527" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42674,7 +42674,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1528" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42700,7 +42700,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1529" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42726,7 +42726,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1530" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42752,7 +42752,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1531" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42778,7 +42778,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1532" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42804,7 +42804,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1533" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42830,7 +42830,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1534" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42856,7 +42856,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1535" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42882,7 +42882,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1536" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42908,7 +42908,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1537" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42934,7 +42934,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1538" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42960,7 +42960,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1539" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42986,7 +42986,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1540" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43012,7 +43012,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1541" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -43038,7 +43038,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1542" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43064,7 +43064,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1543" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -43090,7 +43090,7 @@
         <v>3</v>
       </c>
       <c r="G1544" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -43116,7 +43116,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1545" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -43142,7 +43142,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1546" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -43168,7 +43168,7 @@
         <v>3</v>
       </c>
       <c r="G1547" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -43194,7 +43194,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1548" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -43220,7 +43220,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1549" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -43246,7 +43246,7 @@
         <v>3</v>
       </c>
       <c r="G1550" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43272,7 +43272,7 @@
         <v>3</v>
       </c>
       <c r="G1551" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43298,7 +43298,7 @@
         <v>3</v>
       </c>
       <c r="G1552" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43324,7 +43324,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1553" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43350,7 +43350,7 @@
         <v>3</v>
       </c>
       <c r="G1554" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43376,7 +43376,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1555" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43402,7 +43402,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1556" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43428,7 +43428,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1557" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43454,7 +43454,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1558" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43480,7 +43480,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1559" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43506,7 +43506,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1560" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43532,7 +43532,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1561" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43558,7 +43558,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1562" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43584,7 +43584,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1563" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43610,7 +43610,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1564" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43636,7 +43636,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1565" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43662,7 +43662,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43688,7 +43688,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43714,7 +43714,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1568" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43740,7 +43740,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1569" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43766,7 +43766,7 @@
         <v>2.75</v>
       </c>
       <c r="G1570" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43792,7 +43792,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1571" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43818,7 +43818,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1572" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43844,7 +43844,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1573" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43870,7 +43870,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1574" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43896,7 +43896,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1575" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43922,7 +43922,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1576" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43948,7 +43948,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1577" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43974,7 +43974,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1578" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -44000,7 +44000,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -44026,7 +44026,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1580" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44052,7 +44052,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1581" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -44078,7 +44078,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1582" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -44104,7 +44104,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1583" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -44130,7 +44130,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1584" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -44156,7 +44156,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1585" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -44182,7 +44182,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1586" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -44208,7 +44208,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1587" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -44234,7 +44234,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1588" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44260,7 +44260,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1589" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44286,7 +44286,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1590" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44312,7 +44312,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1591" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44338,7 +44338,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44364,7 +44364,7 @@
         <v>2.75</v>
       </c>
       <c r="G1593" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44390,7 +44390,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1594" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44416,7 +44416,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1595" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44442,7 +44442,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1596" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44468,7 +44468,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44494,7 +44494,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44520,7 +44520,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1599" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44546,7 +44546,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1600" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44572,7 +44572,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1601" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44598,7 +44598,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1602" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44624,7 +44624,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1603" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44650,7 +44650,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1604" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44676,7 +44676,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1605" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44702,7 +44702,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1606" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44728,7 +44728,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1607" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44754,7 +44754,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1608" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44780,7 +44780,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1609" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44806,7 +44806,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1610" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44832,7 +44832,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1611" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44858,7 +44858,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1612" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44884,7 +44884,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1613" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44910,7 +44910,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1614" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44936,7 +44936,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1615" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44962,7 +44962,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44988,7 +44988,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1617" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -45014,7 +45014,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1618" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -45040,7 +45040,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1619" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -45066,7 +45066,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1620" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -45092,7 +45092,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1621" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -45118,7 +45118,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1622" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -45144,7 +45144,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1623" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -45170,7 +45170,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1624" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -45196,7 +45196,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1625" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -45222,7 +45222,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1626" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45248,7 +45248,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1627" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45274,7 +45274,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1628" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45300,7 +45300,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1629" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45326,7 +45326,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1630" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45352,7 +45352,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1631" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45378,7 +45378,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1632" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45430,7 +45430,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1634" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45456,7 +45456,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1635" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45482,7 +45482,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1636" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46158,7 +46158,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1662" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -49668,7 +49668,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1797" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49850,7 +49850,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1804" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49876,7 +49876,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1805" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49928,7 +49928,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50110,7 +50110,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1814" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -50318,7 +50318,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1822" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50370,7 +50370,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1824" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50578,7 +50578,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1832" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50786,7 +50786,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1840" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50812,7 +50812,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1841" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50864,7 +50864,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1843" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50942,7 +50942,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1846" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50968,7 +50968,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1847" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51280,7 +51280,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1859" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51332,7 +51332,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1861" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51358,7 +51358,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1862" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51384,7 +51384,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1863" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51436,7 +51436,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1865" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51514,7 +51514,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1868" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51566,7 +51566,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1870" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51592,7 +51592,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1871" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51722,7 +51722,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1876" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51800,7 +51800,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1879" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51904,7 +51904,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1883" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51930,7 +51930,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1884" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51956,7 +51956,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1885" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52008,7 +52008,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1887" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53438,7 +53438,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1942" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53724,7 +53724,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1953" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -69566,7 +69566,7 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.6873726852</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>5568</v>
@@ -69587,6 +69587,32 @@
         <v>851</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6872106481</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>6639</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>2.19000005722046</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>2.19000005722046</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>850</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034165382385</t>
+    <t xml:space="preserve">1.75034141540527</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
@@ -65,40 +65,40 @@
     <t xml:space="preserve">1.63888120651245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61163532733917</t>
+    <t xml:space="preserve">1.61163544654846</t>
   </si>
   <si>
     <t xml:space="preserve">1.59347128868103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48613917827606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59264576435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59182000160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58604073524475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172784328461</t>
+    <t xml:space="preserve">1.48613893985748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59182035923004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58604061603546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172760486603</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521509170532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56044614315033</t>
+    <t xml:space="preserve">1.56044602394104</t>
   </si>
   <si>
     <t xml:space="preserve">1.51255941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53980529308319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56539988517761</t>
+    <t xml:space="preserve">1.5398051738739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5654000043869</t>
   </si>
   <si>
     <t xml:space="preserve">1.53567707538605</t>
@@ -107,34 +107,34 @@
     <t xml:space="preserve">1.45311379432678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50595426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46136999130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44238066673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51833891868591</t>
+    <t xml:space="preserve">1.50595438480377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46137011051178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4423805475235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51833879947662</t>
   </si>
   <si>
     <t xml:space="preserve">1.65126574039459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63475298881531</t>
+    <t xml:space="preserve">1.6347531080246</t>
   </si>
   <si>
     <t xml:space="preserve">1.65621948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64300918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6372298002243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64218366146088</t>
+    <t xml:space="preserve">1.64300930500031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63722991943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64218389987946</t>
   </si>
   <si>
     <t xml:space="preserve">1.63970685005188</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">1.60503029823303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59842526912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870245933533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053237438202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6322762966156</t>
+    <t xml:space="preserve">1.5984251499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870234012604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227605819702</t>
   </si>
   <si>
     <t xml:space="preserve">1.60255324840546</t>
@@ -164,43 +164,43 @@
     <t xml:space="preserve">1.57283055782318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58934330940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58438944816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5678768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55714356899261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53402602672577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54310774803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466675758362</t>
+    <t xml:space="preserve">1.58934307098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58438956737518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56787669658661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55714344978333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53402578830719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54310762882233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466687679291</t>
   </si>
   <si>
     <t xml:space="preserve">1.5596204996109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55218994617462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55053842067719</t>
+    <t xml:space="preserve">1.55218982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55053853988647</t>
   </si>
   <si>
     <t xml:space="preserve">1.50265181064606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4869647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861598968506</t>
+    <t xml:space="preserve">1.48696482181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861610889435</t>
   </si>
   <si>
     <t xml:space="preserve">1.53237438201904</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.49026727676392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51503622531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779046535492</t>
+    <t xml:space="preserve">1.5150363445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779034614563</t>
   </si>
   <si>
     <t xml:space="preserve">1.47623157501221</t>
@@ -224,13 +224,10 @@
     <t xml:space="preserve">1.5010005235672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49439537525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48366224765778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45971882343292</t>
+    <t xml:space="preserve">1.49439549446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48366236686707</t>
   </si>
   <si>
     <t xml:space="preserve">1.45971894264221</t>
@@ -239,58 +236,58 @@
     <t xml:space="preserve">1.45299971103668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46223855018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43284261226654</t>
+    <t xml:space="preserve">1.46223866939545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43284249305725</t>
   </si>
   <si>
     <t xml:space="preserve">1.43536221981049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43200266361237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42612338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41100573539734</t>
+    <t xml:space="preserve">1.43200278282166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4261234998703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41100549697876</t>
   </si>
   <si>
     <t xml:space="preserve">1.44040155410767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43620193004608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44292104244232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44880044460297</t>
+    <t xml:space="preserve">1.43620216846466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4429212808609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44880056381226</t>
   </si>
   <si>
     <t xml:space="preserve">1.47819626331329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44460093975067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42360377311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4303230047226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46139860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40260672569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40848588943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37825012207031</t>
+    <t xml:space="preserve">1.44460082054138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42360389232635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43032276630402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46139872074127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40260660648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4084860086441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3782502412796</t>
   </si>
   <si>
     <t xml:space="preserve">1.42444360256195</t>
@@ -302,25 +299,25 @@
     <t xml:space="preserve">1.46979749202728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42780327796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192399501801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47567689418793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4479603767395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735643386841</t>
+    <t xml:space="preserve">1.42780315876007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192387580872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47567665576935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44796049594879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735631465912</t>
   </si>
   <si>
     <t xml:space="preserve">1.43368232250214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45803904533386</t>
+    <t xml:space="preserve">1.45803916454315</t>
   </si>
   <si>
     <t xml:space="preserve">1.45215976238251</t>
@@ -329,46 +326,46 @@
     <t xml:space="preserve">1.48491537570953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46391832828522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46643793582916</t>
+    <t xml:space="preserve">1.46391820907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46643805503845</t>
   </si>
   <si>
     <t xml:space="preserve">1.46895742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48575520515442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45887899398804</t>
+    <t xml:space="preserve">1.485755443573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45887887477875</t>
   </si>
   <si>
     <t xml:space="preserve">1.45635938644409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45719921588898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48827493190765</t>
+    <t xml:space="preserve">1.45719909667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48827481269836</t>
   </si>
   <si>
     <t xml:space="preserve">1.43956160545349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47399687767029</t>
+    <t xml:space="preserve">1.473996758461</t>
   </si>
   <si>
     <t xml:space="preserve">1.46727788448334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49835348129272</t>
+    <t xml:space="preserve">1.49835360050201</t>
   </si>
   <si>
     <t xml:space="preserve">1.50927209854126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50339269638062</t>
+    <t xml:space="preserve">1.5033928155899</t>
   </si>
   <si>
     <t xml:space="preserve">1.4949939250946</t>
@@ -377,49 +374,49 @@
     <t xml:space="preserve">1.48743510246277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51011192798615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4991934299469</t>
+    <t xml:space="preserve">1.51011180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49919354915619</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179170608521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45048022270203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44628095626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4387218952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50003337860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48071587085724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48155581951141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51095175743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49583387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5075923204422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49667382240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47231698036194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49331426620483</t>
+    <t xml:space="preserve">1.45047998428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44628059864044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43872177600861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50003325939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48071610927582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4815559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51095187664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49583399295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50759196281433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49667370319366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47231721878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49331414699554</t>
   </si>
   <si>
     <t xml:space="preserve">1.47147727012634</t>
@@ -428,7 +425,7 @@
     <t xml:space="preserve">1.50087308883667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52774965763092</t>
+    <t xml:space="preserve">1.52774941921234</t>
   </si>
   <si>
     <t xml:space="preserve">1.53194880485535</t>
@@ -440,19 +437,19 @@
     <t xml:space="preserve">1.52355015277863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50423288345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51263153553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54454731941223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54538691043854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55294609069824</t>
+    <t xml:space="preserve">1.50423264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5126314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54454708099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54538726806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55294597148895</t>
   </si>
   <si>
     <t xml:space="preserve">1.52019047737122</t>
@@ -461,34 +458,34 @@
     <t xml:space="preserve">1.50843226909637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59578013420105</t>
+    <t xml:space="preserve">1.59578001499176</t>
   </si>
   <si>
     <t xml:space="preserve">1.53446865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56050515174866</t>
+    <t xml:space="preserve">1.56050503253937</t>
   </si>
   <si>
     <t xml:space="preserve">1.53026914596558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53110909461975</t>
+    <t xml:space="preserve">1.53110885620117</t>
   </si>
   <si>
     <t xml:space="preserve">1.55126619338989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55210626125336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55378580093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58654141426086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56218469142914</t>
+    <t xml:space="preserve">1.55210614204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55378603935242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58654129505157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56218481063843</t>
   </si>
   <si>
     <t xml:space="preserve">1.56974363327026</t>
@@ -497,7 +494,7 @@
     <t xml:space="preserve">1.57058346271515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60333895683289</t>
+    <t xml:space="preserve">1.60333931446075</t>
   </si>
   <si>
     <t xml:space="preserve">1.54958641529083</t>
@@ -509,16 +506,16 @@
     <t xml:space="preserve">1.57142353057861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56470441818237</t>
+    <t xml:space="preserve">1.56470453739166</t>
   </si>
   <si>
     <t xml:space="preserve">1.61089777946472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61173796653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60417890548706</t>
+    <t xml:space="preserve">1.61173808574677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60417866706848</t>
   </si>
   <si>
     <t xml:space="preserve">1.62517607212067</t>
@@ -527,40 +524,40 @@
     <t xml:space="preserve">1.62097656726837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61257779598236</t>
+    <t xml:space="preserve">1.61257767677307</t>
   </si>
   <si>
     <t xml:space="preserve">1.59326040744781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58822107315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60753846168518</t>
+    <t xml:space="preserve">1.58822119235992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60753834247589</t>
   </si>
   <si>
     <t xml:space="preserve">1.63105523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61425757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71504390239716</t>
+    <t xml:space="preserve">1.61425745487213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71504378318787</t>
   </si>
   <si>
     <t xml:space="preserve">1.77215576171875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76543688774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75367844104767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72512221336365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74527943134308</t>
+    <t xml:space="preserve">1.76543664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75367832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72512233257294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74527978897095</t>
   </si>
   <si>
     <t xml:space="preserve">1.72176277637482</t>
@@ -572,49 +569,49 @@
     <t xml:space="preserve">1.73856043815613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69992542266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67892861366272</t>
+    <t xml:space="preserve">1.69992566108704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67892849445343</t>
   </si>
   <si>
     <t xml:space="preserve">1.69656610488892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69320678710938</t>
+    <t xml:space="preserve">1.6932065486908</t>
   </si>
   <si>
     <t xml:space="preserve">1.70496511459351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7738356590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75871777534485</t>
+    <t xml:space="preserve">1.77383542060852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75871765613556</t>
   </si>
   <si>
     <t xml:space="preserve">1.68984723091125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69152688980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66801011562347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68816733360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71336376667023</t>
+    <t xml:space="preserve">1.69152700901031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66801023483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68816745281219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71336388587952</t>
   </si>
   <si>
     <t xml:space="preserve">1.73184144496918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75535821914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71000456809998</t>
+    <t xml:space="preserve">1.75535798072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7100043296814</t>
   </si>
   <si>
     <t xml:space="preserve">1.71672332286835</t>
@@ -623,16 +620,16 @@
     <t xml:space="preserve">1.73016154766083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74695920944214</t>
+    <t xml:space="preserve">1.74695909023285</t>
   </si>
   <si>
     <t xml:space="preserve">1.7704758644104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76375687122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031900405884</t>
+    <t xml:space="preserve">1.76375699043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031888484955</t>
   </si>
   <si>
     <t xml:space="preserve">1.78895366191864</t>
@@ -641,7 +638,7 @@
     <t xml:space="preserve">1.7402400970459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76207721233368</t>
+    <t xml:space="preserve">1.76207733154297</t>
   </si>
   <si>
     <t xml:space="preserve">1.73352098464966</t>
@@ -650,16 +647,16 @@
     <t xml:space="preserve">1.79903221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78055465221405</t>
+    <t xml:space="preserve">1.78055453300476</t>
   </si>
   <si>
     <t xml:space="preserve">1.82254886627197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86958253383636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86454296112061</t>
+    <t xml:space="preserve">1.86958229541779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8645430803299</t>
   </si>
   <si>
     <t xml:space="preserve">1.84774541854858</t>
@@ -668,28 +665,28 @@
     <t xml:space="preserve">1.78391420841217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90480983257294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98488640785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34267735481262</t>
+    <t xml:space="preserve">1.90480995178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98488688468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34267711639404</t>
   </si>
   <si>
     <t xml:space="preserve">2.3511962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24045133590698</t>
+    <t xml:space="preserve">2.24045157432556</t>
   </si>
   <si>
     <t xml:space="preserve">2.180819272995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36482644081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32223224639893</t>
+    <t xml:space="preserve">2.36482620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32223200798035</t>
   </si>
   <si>
     <t xml:space="preserve">2.34608459472656</t>
@@ -707,58 +704,58 @@
     <t xml:space="preserve">2.14163279533386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07007479667664</t>
+    <t xml:space="preserve">2.07007503509521</t>
   </si>
   <si>
     <t xml:space="preserve">2.01896166801453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95933032035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01044321060181</t>
+    <t xml:space="preserve">1.95932996273041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01044297218323</t>
   </si>
   <si>
     <t xml:space="preserve">2.06496357917786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00192427635193</t>
+    <t xml:space="preserve">2.00192379951477</t>
   </si>
   <si>
     <t xml:space="preserve">2.02407312393188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06155633926392</t>
+    <t xml:space="preserve">2.06155610084534</t>
   </si>
   <si>
     <t xml:space="preserve">2.04451847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06837105751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303716659546</t>
+    <t xml:space="preserve">2.0683708190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303740501404</t>
   </si>
   <si>
     <t xml:space="preserve">2.04111075401306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97977483272552</t>
+    <t xml:space="preserve">1.97977530956268</t>
   </si>
   <si>
     <t xml:space="preserve">1.99340534210205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97636771202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97125637531281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466421127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95081114768982</t>
+    <t xml:space="preserve">1.97636783123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97125613689423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97466373443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95081126689911</t>
   </si>
   <si>
     <t xml:space="preserve">1.938884973526</t>
@@ -767,31 +764,31 @@
     <t xml:space="preserve">1.92525470256805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9269585609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94229245185852</t>
+    <t xml:space="preserve">1.92695832252502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94229257106781</t>
   </si>
   <si>
     <t xml:space="preserve">1.95762646198273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93718111515045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866206169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97296011447906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00703525543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01555395126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98829400539398</t>
+    <t xml:space="preserve">1.93718099594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97296035289764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00703549385071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01555442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98829424381256</t>
   </si>
   <si>
     <t xml:space="preserve">1.93206977844238</t>
@@ -803,19 +800,19 @@
     <t xml:space="preserve">1.91332840919495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9082168340683</t>
+    <t xml:space="preserve">1.90821695327759</t>
   </si>
   <si>
     <t xml:space="preserve">1.93377351760864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94058859348297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822531700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25578498840332</t>
+    <t xml:space="preserve">1.94058847427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822555541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25578474998474</t>
   </si>
   <si>
     <t xml:space="preserve">2.22341370582581</t>
@@ -830,13 +827,13 @@
     <t xml:space="preserve">2.41593909263611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41253161430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3682336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30860185623169</t>
+    <t xml:space="preserve">2.41253185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36823391914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30860161781311</t>
   </si>
   <si>
     <t xml:space="preserve">2.31200957298279</t>
@@ -851,16 +848,16 @@
     <t xml:space="preserve">2.42445802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41423511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36993741989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39719772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35801124572754</t>
+    <t xml:space="preserve">2.41423535346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36993765830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39719748497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35801100730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.30519437789917</t>
@@ -869,13 +866,13 @@
     <t xml:space="preserve">2.32052803039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32904696464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31882429122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3477885723114</t>
+    <t xml:space="preserve">2.32904672622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31882452964783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34778833389282</t>
   </si>
   <si>
     <t xml:space="preserve">2.36312246322632</t>
@@ -884,13 +881,13 @@
     <t xml:space="preserve">2.3443808555603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32563948631287</t>
+    <t xml:space="preserve">2.32563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">2.3392698764801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36653017997742</t>
+    <t xml:space="preserve">2.36652970314026</t>
   </si>
   <si>
     <t xml:space="preserve">2.3767523765564</t>
@@ -899,7 +896,7 @@
     <t xml:space="preserve">2.38356757164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27111887931824</t>
+    <t xml:space="preserve">2.27111911773682</t>
   </si>
   <si>
     <t xml:space="preserve">2.25408124923706</t>
@@ -908,16 +905,16 @@
     <t xml:space="preserve">2.09392738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15696668624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10585355758667</t>
+    <t xml:space="preserve">2.15696716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10585379600525</t>
   </si>
   <si>
     <t xml:space="preserve">2.10415029525757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12800288200378</t>
+    <t xml:space="preserve">2.12800264358521</t>
   </si>
   <si>
     <t xml:space="preserve">2.31712079048157</t>
@@ -926,16 +923,16 @@
     <t xml:space="preserve">2.28304553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30349040031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29667544364929</t>
+    <t xml:space="preserve">2.30349087715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29667568206787</t>
   </si>
   <si>
     <t xml:space="preserve">2.28815674781799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21659851074219</t>
+    <t xml:space="preserve">2.21659827232361</t>
   </si>
   <si>
     <t xml:space="preserve">2.23874759674072</t>
@@ -944,172 +941,175 @@
     <t xml:space="preserve">2.21489477157593</t>
   </si>
   <si>
+    <t xml:space="preserve">2.25748920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24556255340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23193264007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933820724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26260018348694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22511720657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23363614082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23022890090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20637583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29156422615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39379000663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41934657096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53009152412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5726854801178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54712891578674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5812041759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50453519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47045969963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46194076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3852710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41082787513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30008292198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45342183113098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60676074028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61527943611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64935493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787386894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43638467788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52157235145569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53860998153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55564761161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48749732971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44490313529968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26600790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14674425125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671010971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1185667514801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066240310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29221963882446</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.25748896598816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24556279182434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23193216323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933820724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26260018348694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22511744499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23363614082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23022866249084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20637607574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29156446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39379000663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41934680938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53009152412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57268524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5471293926239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58120441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50453472137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47045969963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46194076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38527131080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41082763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30008316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45342183113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60676074028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61527967453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6493546962738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43638443946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52157258987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53861045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55564785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48749732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44490313529968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26600766181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14674401283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671058654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1185667514801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066240310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29221963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24880647659302</t>
+    <t xml:space="preserve">2.24880623817444</t>
   </si>
   <si>
     <t xml:space="preserve">2.2661714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27485418319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34431529045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35299777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3009021282196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30958485603333</t>
+    <t xml:space="preserve">2.2748544216156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34431552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35299801826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30090236663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3095850944519</t>
   </si>
   <si>
     <t xml:space="preserve">2.32695007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28353691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21407532691956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17934513092041</t>
+    <t xml:space="preserve">2.28353714942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21407556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17934489250183</t>
   </si>
   <si>
     <t xml:space="preserve">2.20539283752441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15329694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13593220710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10988402366638</t>
+    <t xml:space="preserve">2.15329718589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13593149185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10988426208496</t>
   </si>
   <si>
     <t xml:space="preserve">2.18802785873413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09251856803894</t>
+    <t xml:space="preserve">2.09251880645752</t>
   </si>
   <si>
     <t xml:space="preserve">2.22275805473328</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">2.07515335083008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08383584022522</t>
+    <t xml:space="preserve">2.0838360786438</t>
   </si>
   <si>
     <t xml:space="preserve">2.10120129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04042267799377</t>
+    <t xml:space="preserve">2.0404224395752</t>
   </si>
   <si>
     <t xml:space="preserve">2.01437473297119</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">2.05778789520264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06647086143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700975418091</t>
+    <t xml:space="preserve">2.06647062301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700927734375</t>
   </si>
   <si>
     <t xml:space="preserve">2.00569200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964441776276</t>
+    <t xml:space="preserve">1.97964429855347</t>
   </si>
   <si>
     <t xml:space="preserve">1.96227872371674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02305722236633</t>
+    <t xml:space="preserve">2.02305769920349</t>
   </si>
   <si>
     <t xml:space="preserve">2.0491054058075</t>
@@ -1157,25 +1157,25 @@
     <t xml:space="preserve">2.03173995018005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93623077869415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87545239925385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.892817735672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8233562707901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81467378139496</t>
+    <t xml:space="preserve">1.93623089790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87545228004456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281761646271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82335650920868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81467366218567</t>
   </si>
   <si>
     <t xml:space="preserve">1.77994310855865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71916449069977</t>
+    <t xml:space="preserve">1.71916472911835</t>
   </si>
   <si>
     <t xml:space="preserve">1.69311678409576</t>
@@ -1187,31 +1187,31 @@
     <t xml:space="preserve">1.63233816623688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67575144767761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68443417549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71048200130463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6887754201889</t>
+    <t xml:space="preserve">1.67575120925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68443393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71048223972321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68877553939819</t>
   </si>
   <si>
     <t xml:space="preserve">1.71482336521149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69745802879333</t>
+    <t xml:space="preserve">1.69745814800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.64536213874817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59760749340057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60629022121429</t>
+    <t xml:space="preserve">1.59760773181915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60629034042358</t>
   </si>
   <si>
     <t xml:space="preserve">1.61931419372559</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">1.61497282981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63667953014374</t>
+    <t xml:space="preserve">1.63667941093445</t>
   </si>
   <si>
     <t xml:space="preserve">1.64970338344574</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">1.7017993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67141008377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66706883907318</t>
+    <t xml:space="preserve">1.67140996456146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6670686006546</t>
   </si>
   <si>
     <t xml:space="preserve">1.57155954837799</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">1.52814626693726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51078104972839</t>
+    <t xml:space="preserve">1.5107809305191</t>
   </si>
   <si>
     <t xml:space="preserve">1.54551160335541</t>
@@ -1259,91 +1259,91 @@
     <t xml:space="preserve">1.6540447473526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66272735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72784721851349</t>
+    <t xml:space="preserve">1.66272747516632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72784733772278</t>
   </si>
   <si>
     <t xml:space="preserve">1.76257789134979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75389516353607</t>
+    <t xml:space="preserve">1.75389528274536</t>
   </si>
   <si>
     <t xml:space="preserve">1.78862571716309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80599117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77126038074493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74521267414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83203887939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79730832576752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84072160720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86676967144012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91018295288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9535961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94491326808929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9883269071579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97096157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91886556148529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92754817008972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8580869436264</t>
+    <t xml:space="preserve">1.80599093437195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77126049995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74521255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83203911781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79730844497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84072172641754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86676979064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91018307209015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359623432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94491350650787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98832678794861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97096133232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91886568069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92754828929901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85808706283569</t>
   </si>
   <si>
     <t xml:space="preserve">1.84940457344055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88413500785828</t>
+    <t xml:space="preserve">1.88413512706757</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365543842316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65041899681091</t>
+    <t xml:space="preserve">1.6504191160202</t>
   </si>
   <si>
     <t xml:space="preserve">1.61919498443604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6013525724411</t>
+    <t xml:space="preserve">1.60135245323181</t>
   </si>
   <si>
     <t xml:space="preserve">1.61027371883392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63703739643097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65487968921661</t>
+    <t xml:space="preserve">1.63703715801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65487957000732</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365555763245</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">1.6459584236145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64149785041809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65934014320374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66826128959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68610394001007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68164324760437</t>
+    <t xml:space="preserve">1.64149808883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65934026241302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66826140880585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68610382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68164312839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.63257682323456</t>
@@ -1373,34 +1373,34 @@
     <t xml:space="preserve">1.60581314563751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62811613082886</t>
+    <t xml:space="preserve">1.62811625003815</t>
   </si>
   <si>
     <t xml:space="preserve">1.61473429203033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58351027965546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57904958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.552286028862</t>
+    <t xml:space="preserve">1.58351016044617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57904970645905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55228590965271</t>
   </si>
   <si>
     <t xml:space="preserve">1.54336488246918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59243130683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56120729446411</t>
+    <t xml:space="preserve">1.59243142604828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56120717525482</t>
   </si>
   <si>
     <t xml:space="preserve">1.53890430927277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55674660205841</t>
+    <t xml:space="preserve">1.5567467212677</t>
   </si>
   <si>
     <t xml:space="preserve">1.57012844085693</t>
@@ -1427,49 +1427,49 @@
     <t xml:space="preserve">1.54782545566559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52552247047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50768029689789</t>
+    <t xml:space="preserve">1.52552258968353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5076801776886</t>
   </si>
   <si>
     <t xml:space="preserve">1.42738950252533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51660144329071</t>
+    <t xml:space="preserve">1.51660132408142</t>
   </si>
   <si>
     <t xml:space="preserve">1.48983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34263825416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709870815277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32479584217072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19097805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26680815219879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24450528621674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29803240299225</t>
+    <t xml:space="preserve">1.34263813495636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709882736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32479596138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19097816944122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2668080329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24450516700745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29803228378296</t>
   </si>
   <si>
     <t xml:space="preserve">1.20435988903046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27572929859161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28465044498444</t>
+    <t xml:space="preserve">1.2757294178009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28465056419373</t>
   </si>
   <si>
     <t xml:space="preserve">1.30695354938507</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">1.30249297618866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36940169334412</t>
+    <t xml:space="preserve">1.36940181255341</t>
   </si>
   <si>
     <t xml:space="preserve">1.36494112014771</t>
@@ -1487,73 +1487,73 @@
     <t xml:space="preserve">1.35601997375488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36048054695129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40508663654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44969236850739</t>
+    <t xml:space="preserve">1.36048066616058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40508651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44969248771667</t>
   </si>
   <si>
     <t xml:space="preserve">1.45415306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44523191452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43631064891815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41846823692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46307408809662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39170467853546</t>
+    <t xml:space="preserve">1.44523179531097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43631052970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41846835613251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46307420730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39170479774475</t>
   </si>
   <si>
     <t xml:space="preserve">1.40062594413757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41400766372681</t>
+    <t xml:space="preserve">1.41400754451752</t>
   </si>
   <si>
     <t xml:space="preserve">1.38278353214264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724398612976</t>
+    <t xml:space="preserve">1.38724410533905</t>
   </si>
   <si>
     <t xml:space="preserve">1.33817768096924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35155940055847</t>
+    <t xml:space="preserve">1.35155928134918</t>
   </si>
   <si>
     <t xml:space="preserve">1.29357171058655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32925653457642</t>
+    <t xml:space="preserve">1.32925629615784</t>
   </si>
   <si>
     <t xml:space="preserve">1.33371710777283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3158745765686</t>
+    <t xml:space="preserve">1.31587469577789</t>
   </si>
   <si>
     <t xml:space="preserve">1.37386238574982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31141400337219</t>
+    <t xml:space="preserve">1.31141412258148</t>
   </si>
   <si>
     <t xml:space="preserve">1.3203352689743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28018987178802</t>
+    <t xml:space="preserve">1.28018975257874</t>
   </si>
   <si>
     <t xml:space="preserve">1.40954720973969</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">1.4586136341095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37832295894623</t>
+    <t xml:space="preserve">1.37832283973694</t>
   </si>
   <si>
     <t xml:space="preserve">1.42292892932892</t>
@@ -1577,28 +1577,28 @@
     <t xml:space="preserve">1.2712687253952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26234745979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24896585941315</t>
+    <t xml:space="preserve">1.26234757900238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24896574020386</t>
   </si>
   <si>
     <t xml:space="preserve">1.46753478050232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44077122211456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48091661930084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49429821968079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5032194852829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52998316287994</t>
+    <t xml:space="preserve">1.44077134132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48091650009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49429833889008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50321936607361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52998304367065</t>
   </si>
   <si>
     <t xml:space="preserve">1.49875891208649</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">1.48537719249725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52106189727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72178852558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76639437675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73963105678558</t>
+    <t xml:space="preserve">1.52106201648712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72178840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76639449596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73963093757629</t>
   </si>
   <si>
     <t xml:space="preserve">1.81992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8734484910965</t>
+    <t xml:space="preserve">1.87344872951508</t>
   </si>
   <si>
     <t xml:space="preserve">1.82884275913239</t>
@@ -1634,25 +1634,25 @@
     <t xml:space="preserve">1.83776390552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77531564235687</t>
+    <t xml:space="preserve">1.78423678874969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77531576156616</t>
   </si>
   <si>
     <t xml:space="preserve">1.73517036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085506916046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72624909877777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73070979118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74855220317841</t>
+    <t xml:space="preserve">1.77085494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72624921798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73070967197418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74855208396912</t>
   </si>
   <si>
     <t xml:space="preserve">1.79315805435181</t>
@@ -1661,85 +1661,85 @@
     <t xml:space="preserve">1.71732795238495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74409151077271</t>
+    <t xml:space="preserve">1.74409162998199</t>
   </si>
   <si>
     <t xml:space="preserve">1.77977633476257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81100046634674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84668493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86452746391296</t>
+    <t xml:space="preserve">1.81100034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84668505191803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86452734470367</t>
   </si>
   <si>
     <t xml:space="preserve">1.80207920074463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75747334957123</t>
+    <t xml:space="preserve">1.75747346878052</t>
   </si>
   <si>
     <t xml:space="preserve">2.0340301990509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0251088142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96266055107117</t>
+    <t xml:space="preserve">2.02510857582092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96266067028046</t>
   </si>
   <si>
     <t xml:space="preserve">1.92697584629059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050284385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07863593101501</t>
+    <t xml:space="preserve">1.9805029630661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07863616943359</t>
   </si>
   <si>
     <t xml:space="preserve">2.10539960861206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05187273025513</t>
+    <t xml:space="preserve">2.05187225341797</t>
   </si>
   <si>
     <t xml:space="preserve">2.06079339981079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09647846221924</t>
+    <t xml:space="preserve">2.09647798538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.43548321723938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.462247133255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39087748527527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56037974357605</t>
+    <t xml:space="preserve">2.46224689483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39087724685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56037950515747</t>
   </si>
   <si>
     <t xml:space="preserve">2.60498595237732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65005469322205</t>
+    <t xml:space="preserve">2.65005493164062</t>
   </si>
   <si>
     <t xml:space="preserve">2.61399960517883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64104127883911</t>
+    <t xml:space="preserve">2.64104104042053</t>
   </si>
   <si>
     <t xml:space="preserve">2.74019265174866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78526163101196</t>
+    <t xml:space="preserve">2.78526139259338</t>
   </si>
   <si>
     <t xml:space="preserve">2.73117876052856</t>
@@ -1751,16 +1751,16 @@
     <t xml:space="preserve">3.1007444858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99257898330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92948222160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84835815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76723384857178</t>
+    <t xml:space="preserve">2.99257874488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92948246002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84835839271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76723408699036</t>
   </si>
   <si>
     <t xml:space="preserve">2.83934450149536</t>
@@ -1772,19 +1772,19 @@
     <t xml:space="preserve">2.82131695747375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77624773979187</t>
+    <t xml:space="preserve">2.77624797821045</t>
   </si>
   <si>
     <t xml:space="preserve">2.72216510772705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55991697311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53287577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58695816993713</t>
+    <t xml:space="preserve">2.55991673469543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53287553787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58695793151855</t>
   </si>
   <si>
     <t xml:space="preserve">2.65906858444214</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">2.67709636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5238618850708</t>
+    <t xml:space="preserve">2.52386164665222</t>
   </si>
   <si>
     <t xml:space="preserve">2.62301349639893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57794427871704</t>
+    <t xml:space="preserve">2.57794451713562</t>
   </si>
   <si>
     <t xml:space="preserve">2.59597206115723</t>
@@ -1808,16 +1808,16 @@
     <t xml:space="preserve">2.55090308189392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51484799385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56893086433411</t>
+    <t xml:space="preserve">2.51484775543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56893062591553</t>
   </si>
   <si>
     <t xml:space="preserve">2.79427552223206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83033084869385</t>
+    <t xml:space="preserve">2.83033061027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.71315121650696</t>
@@ -1826,46 +1826,46 @@
     <t xml:space="preserve">2.70413756370544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74920630455017</t>
+    <t xml:space="preserve">2.74920654296875</t>
   </si>
   <si>
     <t xml:space="preserve">2.80328917503357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86638569831848</t>
+    <t xml:space="preserve">2.86638593673706</t>
   </si>
   <si>
     <t xml:space="preserve">3.0015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09173083305359</t>
+    <t xml:space="preserve">3.09173059463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.96553754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93849635124207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81230282783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54188942909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4787929058075</t>
+    <t xml:space="preserve">2.93849611282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81230306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54188919067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47879266738892</t>
   </si>
   <si>
     <t xml:space="preserve">2.63202738761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91145467758179</t>
+    <t xml:space="preserve">2.91145491600037</t>
   </si>
   <si>
     <t xml:space="preserve">2.9745512008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95652389526367</t>
+    <t xml:space="preserve">2.95652365684509</t>
   </si>
   <si>
     <t xml:space="preserve">3.01060628890991</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">2.98356509208679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88441324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94751024246216</t>
+    <t xml:space="preserve">2.88441348075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94751000404358</t>
   </si>
   <si>
     <t xml:space="preserve">2.92046856880188</t>
@@ -1892,46 +1892,46 @@
     <t xml:space="preserve">2.75822019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68611025810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23542022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19035124778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28048944473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41569638252258</t>
+    <t xml:space="preserve">2.68610978126526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23542046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19035148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28048920631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.415696144104</t>
   </si>
   <si>
     <t xml:space="preserve">2.3165442943573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36161327362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50583410263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48780679702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44273734092712</t>
+    <t xml:space="preserve">2.36161351203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50583434104919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48780655860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4427375793457</t>
   </si>
   <si>
     <t xml:space="preserve">2.37964105606079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37062740325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27147555351257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26246190071106</t>
+    <t xml:space="preserve">2.37062764167786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27147579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26246166229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.28950309753418</t>
@@ -1940,16 +1940,16 @@
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555818557739</t>
+    <t xml:space="preserve">2.32555842399597</t>
   </si>
   <si>
     <t xml:space="preserve">2.29851698875427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34358549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21739292144775</t>
+    <t xml:space="preserve">2.343585729599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2173924446106</t>
   </si>
   <si>
     <t xml:space="preserve">2.20837903022766</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">2.23598384857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21758055686951</t>
+    <t xml:space="preserve">2.21758079528809</t>
   </si>
   <si>
     <t xml:space="preserve">2.24518537521362</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">2.18077421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16237115859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19917774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17157244682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11636328697205</t>
+    <t xml:space="preserve">2.16237092018127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19917750358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1715726852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11636304855347</t>
   </si>
   <si>
     <t xml:space="preserve">2.08875823020935</t>
@@ -1997,16 +1997,16 @@
     <t xml:space="preserve">2.05195212364197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97833943367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98754131793976</t>
+    <t xml:space="preserve">1.97833967208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98754107952118</t>
   </si>
   <si>
     <t xml:space="preserve">2.07955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09795999526978</t>
+    <t xml:space="preserve">2.09796023368835</t>
   </si>
   <si>
     <t xml:space="preserve">2.13476634025574</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">2.18997573852539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14396786689758</t>
+    <t xml:space="preserve">2.14396810531616</t>
   </si>
   <si>
     <t xml:space="preserve">2.12556457519531</t>
@@ -2036,31 +2036,31 @@
     <t xml:space="preserve">2.00594425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93233144283295</t>
+    <t xml:space="preserve">1.93233156204224</t>
   </si>
   <si>
     <t xml:space="preserve">1.91392827033997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90472674369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9231299161911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94153320789337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88632357120514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86792063713074</t>
+    <t xml:space="preserve">1.90472686290741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92312979698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94153308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88632369041443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86792051792145</t>
   </si>
   <si>
     <t xml:space="preserve">1.84951746463776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89552533626556</t>
+    <t xml:space="preserve">1.89552521705627</t>
   </si>
   <si>
     <t xml:space="preserve">1.8587189912796</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">1.83111429214478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81271111965179</t>
+    <t xml:space="preserve">1.81271123886108</t>
   </si>
   <si>
     <t xml:space="preserve">1.80350947380066</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">1.8357150554657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82651352882385</t>
+    <t xml:space="preserve">1.82651340961456</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031581878662</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">2.39241051673889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3464024066925</t>
+    <t xml:space="preserve">2.34640264511108</t>
   </si>
   <si>
     <t xml:space="preserve">2.29119324684143</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">2.28199172019958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26358842849731</t>
+    <t xml:space="preserve">2.26358819007874</t>
   </si>
   <si>
     <t xml:space="preserve">2.30039477348328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27278995513916</t>
+    <t xml:space="preserve">2.27279019355774</t>
   </si>
   <si>
     <t xml:space="preserve">2.33720111846924</t>
@@ -5549,7 +5549,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G100" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H100" t="s">
         <v>9</v>
@@ -5575,7 +5575,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G101" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H101" t="s">
         <v>9</v>
@@ -5601,7 +5601,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G102" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H102" t="s">
         <v>9</v>
@@ -5627,7 +5627,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G103" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H103" t="s">
         <v>9</v>
@@ -5653,7 +5653,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G104" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H104" t="s">
         <v>9</v>
@@ -5679,7 +5679,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G105" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H105" t="s">
         <v>9</v>
@@ -5705,7 +5705,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G106" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H106" t="s">
         <v>9</v>
@@ -5731,7 +5731,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G107" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H107" t="s">
         <v>9</v>
@@ -5757,7 +5757,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G108" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H108" t="s">
         <v>9</v>
@@ -5783,7 +5783,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G109" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H109" t="s">
         <v>9</v>
@@ -5809,7 +5809,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G110" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s">
         <v>9</v>
@@ -5835,7 +5835,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G111" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H111" t="s">
         <v>9</v>
@@ -5861,7 +5861,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G112" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H112" t="s">
         <v>9</v>
@@ -5887,7 +5887,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G113" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s">
         <v>9</v>
@@ -5913,7 +5913,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G114" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H114" t="s">
         <v>9</v>
@@ -5939,7 +5939,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G115" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H115" t="s">
         <v>9</v>
@@ -5965,7 +5965,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G116" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H116" t="s">
         <v>9</v>
@@ -5991,7 +5991,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G117" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H117" t="s">
         <v>9</v>
@@ -6017,7 +6017,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G118" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H118" t="s">
         <v>9</v>
@@ -6043,7 +6043,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G119" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -6069,7 +6069,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G120" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -6095,7 +6095,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G121" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -6121,7 +6121,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G122" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -6147,7 +6147,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G123" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -6173,7 +6173,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G124" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -6199,7 +6199,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G125" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -6225,7 +6225,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G126" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -6251,7 +6251,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G127" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -6277,7 +6277,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G128" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -6303,7 +6303,7 @@
         <v>1.75</v>
       </c>
       <c r="G129" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -6329,7 +6329,7 @@
         <v>1.75</v>
       </c>
       <c r="G130" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -6355,7 +6355,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G131" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -6381,7 +6381,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G132" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -6407,7 +6407,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G133" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -6433,7 +6433,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G134" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -6459,7 +6459,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G135" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -6485,7 +6485,7 @@
         <v>1.75</v>
       </c>
       <c r="G136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6511,7 +6511,7 @@
         <v>1.75</v>
       </c>
       <c r="G137" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6537,7 +6537,7 @@
         <v>1.75</v>
       </c>
       <c r="G138" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6563,7 +6563,7 @@
         <v>1.75</v>
       </c>
       <c r="G139" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6589,7 +6589,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G140" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6615,7 +6615,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G141" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6641,7 +6641,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G142" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -6667,7 +6667,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G143" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6693,7 +6693,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G144" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6719,7 +6719,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G145" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6745,7 +6745,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G146" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6771,7 +6771,7 @@
         <v>1.75</v>
       </c>
       <c r="G147" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6797,7 +6797,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G148" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6823,7 +6823,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G149" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6849,7 +6849,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G150" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6875,7 +6875,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G151" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6901,7 +6901,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G152" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6927,7 +6927,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G153" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6953,7 +6953,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G154" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6979,7 +6979,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G155" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -7005,7 +7005,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G156" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -7031,7 +7031,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G157" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -7057,7 +7057,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -7083,7 +7083,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G159" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -7109,7 +7109,7 @@
         <v>1.75</v>
       </c>
       <c r="G160" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -7135,7 +7135,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G161" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -7161,7 +7161,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G162" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -7187,7 +7187,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G163" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -7213,7 +7213,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G164" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -7239,7 +7239,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G165" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7265,7 +7265,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G166" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7291,7 +7291,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G167" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7317,7 +7317,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G168" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7343,7 +7343,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G169" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7369,7 +7369,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G170" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7395,7 +7395,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G171" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7421,7 +7421,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G172" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7447,7 +7447,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G173" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7473,7 +7473,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G174" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7499,7 +7499,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G175" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7525,7 +7525,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G176" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7551,7 +7551,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G177" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7577,7 +7577,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G178" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7603,7 +7603,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G179" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7629,7 +7629,7 @@
         <v>1.75</v>
       </c>
       <c r="G180" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7655,7 +7655,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G181" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7681,7 +7681,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G182" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7707,7 +7707,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7733,7 +7733,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G184" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7759,7 +7759,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G185" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7785,7 +7785,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G186" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7811,7 +7811,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G187" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7837,7 +7837,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G188" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7863,7 +7863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7889,7 +7889,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G190" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7915,7 +7915,7 @@
         <v>1.75</v>
       </c>
       <c r="G191" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7941,7 +7941,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G192" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7967,7 +7967,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G193" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7993,7 +7993,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G194" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -8019,7 +8019,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G195" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8045,7 +8045,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G196" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8071,7 +8071,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G197" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8097,7 +8097,7 @@
         <v>1.75</v>
       </c>
       <c r="G198" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8123,7 +8123,7 @@
         <v>1.75</v>
       </c>
       <c r="G199" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8149,7 +8149,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G200" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8175,7 +8175,7 @@
         <v>1.75</v>
       </c>
       <c r="G201" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8201,7 +8201,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G202" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8227,7 +8227,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G203" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8253,7 +8253,7 @@
         <v>1.75</v>
       </c>
       <c r="G204" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8279,7 +8279,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G205" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8305,7 +8305,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G206" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8331,7 +8331,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G207" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8357,7 +8357,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G208" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8383,7 +8383,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G209" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8409,7 +8409,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G210" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8435,7 +8435,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G211" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8461,7 +8461,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G212" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8487,7 +8487,7 @@
         <v>1.75</v>
       </c>
       <c r="G213" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8513,7 +8513,7 @@
         <v>1.75</v>
       </c>
       <c r="G214" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8539,7 +8539,7 @@
         <v>1.75</v>
       </c>
       <c r="G215" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8565,7 +8565,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G216" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8591,7 +8591,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G217" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8617,7 +8617,7 @@
         <v>1.75</v>
       </c>
       <c r="G218" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8643,7 +8643,7 @@
         <v>1.75</v>
       </c>
       <c r="G219" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8669,7 +8669,7 @@
         <v>1.75</v>
       </c>
       <c r="G220" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8695,7 +8695,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G221" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8721,7 +8721,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G222" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8747,7 +8747,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G223" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8773,7 +8773,7 @@
         <v>1.75</v>
       </c>
       <c r="G224" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8799,7 +8799,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G225" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8825,7 +8825,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G226" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8851,7 +8851,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G227" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8877,7 +8877,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G228" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8903,7 +8903,7 @@
         <v>1.75</v>
       </c>
       <c r="G229" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8929,7 +8929,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G230" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8955,7 +8955,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G231" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8981,7 +8981,7 @@
         <v>1.75</v>
       </c>
       <c r="G232" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -9007,7 +9007,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9033,7 +9033,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G234" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9059,7 +9059,7 @@
         <v>1.75</v>
       </c>
       <c r="G235" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9085,7 +9085,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G236" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9111,7 +9111,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G237" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9137,7 +9137,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G238" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9163,7 +9163,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G239" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9189,7 +9189,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G240" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9215,7 +9215,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G241" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9241,7 +9241,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G242" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9267,7 +9267,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G243" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9293,7 +9293,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G244" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9319,7 +9319,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G245" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9345,7 +9345,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G246" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9371,7 +9371,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G247" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9397,7 +9397,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G248" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9423,7 +9423,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G249" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9449,7 +9449,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G250" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9475,7 +9475,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G251" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9501,7 +9501,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G252" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9527,7 +9527,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G253" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9553,7 +9553,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G254" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9579,7 +9579,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G255" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9605,7 +9605,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G256" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9631,7 +9631,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G257" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9657,7 +9657,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G258" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9683,7 +9683,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G259" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9709,7 +9709,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G260" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9735,7 +9735,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G261" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9761,7 +9761,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G262" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9787,7 +9787,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9813,7 +9813,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G264" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9839,7 +9839,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G265" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9865,7 +9865,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G266" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9891,7 +9891,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G267" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9917,7 +9917,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G268" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9943,7 +9943,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G269" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9969,7 +9969,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G270" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9995,7 +9995,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G271" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10021,7 +10021,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G272" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10047,7 +10047,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G273" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10073,7 +10073,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G274" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10099,7 +10099,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G275" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10125,7 +10125,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G276" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10151,7 +10151,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G277" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10177,7 +10177,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G278" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10203,7 +10203,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G279" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10229,7 +10229,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G280" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10255,7 +10255,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G281" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10281,7 +10281,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G282" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10307,7 +10307,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G283" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10333,7 +10333,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G284" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10359,7 +10359,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G285" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10385,7 +10385,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G286" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10411,7 +10411,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G287" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10437,7 +10437,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G288" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10463,7 +10463,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G289" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10489,7 +10489,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G290" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10515,7 +10515,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G291" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10541,7 +10541,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G292" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10567,7 +10567,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G293" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10593,7 +10593,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G294" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10619,7 +10619,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G295" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10645,7 +10645,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G296" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10671,7 +10671,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G297" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10697,7 +10697,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G298" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10723,7 +10723,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G299" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10749,7 +10749,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G300" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10775,7 +10775,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G301" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10801,7 +10801,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G302" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10827,7 +10827,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G303" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10853,7 +10853,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G304" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10879,7 +10879,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G305" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10905,7 +10905,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G306" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10931,7 +10931,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G307" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10957,7 +10957,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10983,7 +10983,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G309" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11009,7 +11009,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G310" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11035,7 +11035,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G311" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11061,7 +11061,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G312" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11087,7 +11087,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G313" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11113,7 +11113,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G314" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11139,7 +11139,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G315" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11165,7 +11165,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11191,7 +11191,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G317" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11217,7 +11217,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G318" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11243,7 +11243,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G319" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11269,7 +11269,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G320" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11295,7 +11295,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G321" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11321,7 +11321,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G322" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11347,7 +11347,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G323" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11373,7 +11373,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G324" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11399,7 +11399,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G325" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11425,7 +11425,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G326" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11451,7 +11451,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G327" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11477,7 +11477,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G328" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11503,7 +11503,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G329" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11529,7 +11529,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G330" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11555,7 +11555,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G331" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11581,7 +11581,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G332" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11607,7 +11607,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G333" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11633,7 +11633,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G334" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11659,7 +11659,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G335" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11685,7 +11685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G336" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11711,7 +11711,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G337" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11737,7 +11737,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G338" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11763,7 +11763,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G339" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11789,7 +11789,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G340" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11815,7 +11815,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G341" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11841,7 +11841,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G342" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11867,7 +11867,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G343" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11893,7 +11893,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G344" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11919,7 +11919,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G345" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11945,7 +11945,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11971,7 +11971,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G347" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11997,7 +11997,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G348" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12023,7 +12023,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G349" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12049,7 +12049,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G350" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12075,7 +12075,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G351" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12101,7 +12101,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G352" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12127,7 +12127,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G353" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12153,7 +12153,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G354" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12179,7 +12179,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G355" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12205,7 +12205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G356" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12231,7 +12231,7 @@
         <v>2.75</v>
       </c>
       <c r="G357" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12257,7 +12257,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G358" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12283,7 +12283,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G359" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12309,7 +12309,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G360" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12335,7 +12335,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G361" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12361,7 +12361,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G362" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12387,7 +12387,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G363" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12413,7 +12413,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G364" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12439,7 +12439,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G365" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12465,7 +12465,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G366" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12491,7 +12491,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G367" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12517,7 +12517,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G368" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12543,7 +12543,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G369" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12569,7 +12569,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G370" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12595,7 +12595,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G371" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12621,7 +12621,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G372" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12647,7 +12647,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G373" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12673,7 +12673,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G374" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12699,7 +12699,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G375" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12725,7 +12725,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G376" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12751,7 +12751,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G377" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12777,7 +12777,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G378" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12803,7 +12803,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G379" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12829,7 +12829,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G380" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12855,7 +12855,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G381" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12881,7 +12881,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G382" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12907,7 +12907,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G383" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12933,7 +12933,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G384" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12959,7 +12959,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G385" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12985,7 +12985,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G386" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13011,7 +13011,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G387" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13037,7 +13037,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G388" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13063,7 +13063,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G389" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13089,7 +13089,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G390" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13115,7 +13115,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G391" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13141,7 +13141,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G392" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13167,7 +13167,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G393" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13193,7 +13193,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G394" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13219,7 +13219,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G395" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13245,7 +13245,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G396" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13271,7 +13271,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G397" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13297,7 +13297,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G398" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13323,7 +13323,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13349,7 +13349,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13375,7 +13375,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G401" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13401,7 +13401,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G402" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13427,7 +13427,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G403" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13453,7 +13453,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G404" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13479,7 +13479,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G405" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13505,7 +13505,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G406" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13531,7 +13531,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G407" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13557,7 +13557,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G408" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13583,7 +13583,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G409" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13609,7 +13609,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G410" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13635,7 +13635,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G411" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13661,7 +13661,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G412" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13687,7 +13687,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G413" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13713,7 +13713,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G414" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13739,7 +13739,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G415" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13765,7 +13765,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G416" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13791,7 +13791,7 @@
         <v>2.25</v>
       </c>
       <c r="G417" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13817,7 +13817,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G418" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13843,7 +13843,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G419" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13869,7 +13869,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G420" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13895,7 +13895,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G421" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13921,7 +13921,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G422" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13947,7 +13947,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13973,7 +13973,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G424" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13999,7 +13999,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G425" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14025,7 +14025,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G426" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14051,7 +14051,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G427" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14077,7 +14077,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14103,7 +14103,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G429" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14129,7 +14129,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G430" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14155,7 +14155,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G431" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14181,7 +14181,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G432" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14207,7 +14207,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G433" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14233,7 +14233,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G434" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14259,7 +14259,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G435" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14285,7 +14285,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G436" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14311,7 +14311,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G437" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14337,7 +14337,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G438" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14363,7 +14363,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14389,7 +14389,7 @@
         <v>2.75</v>
       </c>
       <c r="G440" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14415,7 +14415,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G441" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14441,7 +14441,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G442" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14467,7 +14467,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G443" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14493,7 +14493,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G444" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14519,7 +14519,7 @@
         <v>2.75</v>
       </c>
       <c r="G445" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14545,7 +14545,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G446" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14571,7 +14571,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G447" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14597,7 +14597,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G448" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14623,7 +14623,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G449" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14649,7 +14649,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G450" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14675,7 +14675,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G451" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14701,7 +14701,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G452" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14727,7 +14727,7 @@
         <v>2.75</v>
       </c>
       <c r="G453" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14753,7 +14753,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G454" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14779,7 +14779,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G455" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14805,7 +14805,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G456" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14831,7 +14831,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G457" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14857,7 +14857,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G458" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14883,7 +14883,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G459" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14909,7 +14909,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G460" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14935,7 +14935,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G461" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14961,7 +14961,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G462" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14987,7 +14987,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G463" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15013,7 +15013,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15039,7 +15039,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G465" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15065,7 +15065,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G466" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15091,7 +15091,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G467" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15117,7 +15117,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G468" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15143,7 +15143,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G469" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15169,7 +15169,7 @@
         <v>2.75</v>
       </c>
       <c r="G470" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15195,7 +15195,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G471" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15221,7 +15221,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G472" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15247,7 +15247,7 @@
         <v>2.75</v>
       </c>
       <c r="G473" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15273,7 +15273,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G474" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15299,7 +15299,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G475" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15325,7 +15325,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G476" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15351,7 +15351,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G477" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15377,7 +15377,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G478" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15403,7 +15403,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G479" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15429,7 +15429,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G480" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15455,7 +15455,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G481" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15481,7 +15481,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G482" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15507,7 +15507,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G483" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15533,7 +15533,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G484" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15559,7 +15559,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G485" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15585,7 +15585,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G486" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15611,7 +15611,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G487" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15637,7 +15637,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G488" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15663,7 +15663,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G489" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15689,7 +15689,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G490" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15715,7 +15715,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G491" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15741,7 +15741,7 @@
         <v>2.75</v>
       </c>
       <c r="G492" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15767,7 +15767,7 @@
         <v>2.75</v>
       </c>
       <c r="G493" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15793,7 +15793,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G494" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15819,7 +15819,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G495" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15845,7 +15845,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G496" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15871,7 +15871,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G497" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15897,7 +15897,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G498" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15923,7 +15923,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G499" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15949,7 +15949,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G500" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15975,7 +15975,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G501" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16001,7 +16001,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G502" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16027,7 +16027,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G503" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16053,7 +16053,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G504" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16079,7 +16079,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G505" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16105,7 +16105,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G506" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16131,7 +16131,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G507" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16157,7 +16157,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G508" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16183,7 +16183,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G509" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16209,7 +16209,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G510" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16235,7 +16235,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G511" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16261,7 +16261,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G512" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16287,7 +16287,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G513" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16313,7 +16313,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G514" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16339,7 +16339,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G515" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16365,7 +16365,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G516" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16391,7 +16391,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G517" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16417,7 +16417,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16443,7 +16443,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16469,7 +16469,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16495,7 +16495,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G521" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16521,7 +16521,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G522" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16547,7 +16547,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16573,7 +16573,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G524" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16599,7 +16599,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G525" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16625,7 +16625,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G526" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16651,7 +16651,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G527" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16677,7 +16677,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G528" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16703,7 +16703,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G529" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16729,7 +16729,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G530" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16755,7 +16755,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G531" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16781,7 +16781,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G532" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16807,7 +16807,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G533" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16833,7 +16833,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G534" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16859,7 +16859,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G535" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16885,7 +16885,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G536" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16911,7 +16911,7 @@
         <v>2.75</v>
       </c>
       <c r="G537" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16937,7 +16937,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G538" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16963,7 +16963,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G539" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16989,7 +16989,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G540" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17015,7 +17015,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G541" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17041,7 +17041,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G542" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17067,7 +17067,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G543" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17093,7 +17093,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17119,7 +17119,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G545" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17145,7 +17145,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G546" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17171,7 +17171,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G547" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17197,7 +17197,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G548" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17223,7 +17223,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G549" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17249,7 +17249,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G550" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17275,7 +17275,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G551" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17301,7 +17301,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G552" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17327,7 +17327,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G553" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17353,7 +17353,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17379,7 +17379,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17405,7 +17405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G556" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17431,7 +17431,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G557" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17457,7 +17457,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G558" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17483,7 +17483,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G559" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17509,7 +17509,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G560" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17535,7 +17535,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17561,7 +17561,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17587,7 +17587,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G563" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17613,7 +17613,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G564" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17639,7 +17639,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G565" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17665,7 +17665,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G566" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17691,7 +17691,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G567" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17717,7 +17717,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G568" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17743,7 +17743,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G569" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17769,7 +17769,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G570" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17795,7 +17795,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G571" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17821,7 +17821,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17847,7 +17847,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G573" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17873,7 +17873,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G574" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17899,7 +17899,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G575" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17925,7 +17925,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G576" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17951,7 +17951,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G577" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17977,7 +17977,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G578" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18003,7 +18003,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G579" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18029,7 +18029,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18055,7 +18055,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18081,7 +18081,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G582" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18107,7 +18107,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G583" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18133,7 +18133,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G584" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18159,7 +18159,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G585" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18185,7 +18185,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G586" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18211,7 +18211,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G587" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18237,7 +18237,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G588" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18263,7 +18263,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G589" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18289,7 +18289,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G590" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18315,7 +18315,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G591" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18341,7 +18341,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G592" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18367,7 +18367,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G593" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18393,7 +18393,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G594" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18419,7 +18419,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G595" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18445,7 +18445,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G596" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18471,7 +18471,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G597" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18497,7 +18497,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G598" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18523,7 +18523,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G599" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18549,7 +18549,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G600" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18575,7 +18575,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G601" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18601,7 +18601,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G602" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18627,7 +18627,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18653,7 +18653,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G604" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18679,7 +18679,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G605" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18705,7 +18705,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G606" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18731,7 +18731,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G607" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18757,7 +18757,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G608" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18783,7 +18783,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G609" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18809,7 +18809,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G610" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18835,7 +18835,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18861,7 +18861,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G612" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18887,7 +18887,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G613" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18913,7 +18913,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G614" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18939,7 +18939,7 @@
         <v>2.5</v>
       </c>
       <c r="G615" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18965,7 +18965,7 @@
         <v>2.5</v>
       </c>
       <c r="G616" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18991,7 +18991,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G617" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19017,7 +19017,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G618" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19069,7 +19069,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G620" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19511,7 +19511,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19537,7 +19537,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19667,7 +19667,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G643" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19771,7 +19771,7 @@
         <v>2.5</v>
       </c>
       <c r="G647" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19849,7 +19849,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G650" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19875,7 +19875,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G651" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19901,7 +19901,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G652" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19953,7 +19953,7 @@
         <v>2.5</v>
       </c>
       <c r="G654" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20083,7 +20083,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20213,7 +20213,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G664" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -70337,9 +70337,11 @@
       <c r="E2592" t="n">
         <v>2</v>
       </c>
-      <c r="F2592"/>
+      <c r="F2592" t="n">
+        <v>1.96000003814697</v>
+      </c>
       <c r="G2592" t="s">
-        <v>868</v>
+        <v>829</v>
       </c>
       <c r="H2592" t="s">
         <v>9</v>
@@ -70347,27 +70349,51 @@
     </row>
     <row r="2593">
       <c r="A2593" s="1" t="n">
-        <v>46094.6910648148</v>
+        <v>46097.3333333333</v>
       </c>
       <c r="B2593" t="n">
-        <v>6778</v>
+        <v>4619</v>
       </c>
       <c r="C2593" t="n">
-        <v>2.00999999046326</v>
+        <v>1.9650000333786</v>
       </c>
       <c r="D2593" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E2593" t="n">
         <v>1.95500004291534</v>
       </c>
-      <c r="E2593" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2593" t="n">
+      <c r="F2593"/>
+      <c r="G2593" t="s">
+        <v>868</v>
+      </c>
+      <c r="H2593" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" s="1" t="n">
+        <v>46097.685474537</v>
+      </c>
+      <c r="B2594" t="n">
+        <v>4619</v>
+      </c>
+      <c r="C2594" t="n">
+        <v>1.9650000333786</v>
+      </c>
+      <c r="D2594" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E2594" t="n">
+        <v>1.95500004291534</v>
+      </c>
+      <c r="F2594" t="n">
         <v>1.96000003814697</v>
       </c>
-      <c r="G2593" t="s">
+      <c r="G2594" t="s">
         <v>829</v>
       </c>
-      <c r="H2593" t="s">
+      <c r="H2594" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034141540527</t>
+    <t xml:space="preserve">1.75034165382385</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538779258728</t>
+    <t xml:space="preserve">1.74538791179657</t>
   </si>
   <si>
     <t xml:space="preserve">1.69254732131958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70245504379272</t>
+    <t xml:space="preserve">1.70245492458344</t>
   </si>
   <si>
     <t xml:space="preserve">1.68429088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6760345697403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66612708568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63888120651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61163520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59347128868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48613917827606</t>
+    <t xml:space="preserve">1.67603445053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66612720489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63888108730316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61163544654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59347152709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48613905906677</t>
   </si>
   <si>
     <t xml:space="preserve">1.59264576435089</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">1.59182000160217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58604073524475</t>
+    <t xml:space="preserve">1.58604085445404</t>
   </si>
   <si>
     <t xml:space="preserve">1.60172784328461</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">1.58521509170532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56044602394104</t>
+    <t xml:space="preserve">1.56044614315033</t>
   </si>
   <si>
     <t xml:space="preserve">1.51255929470062</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">1.53567719459534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45311367511749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50595426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46136999130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44238066673279</t>
+    <t xml:space="preserve">1.45311391353607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50595438480377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46137011051178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4423805475235</t>
   </si>
   <si>
     <t xml:space="preserve">1.51833879947662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65126574039459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63475322723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65621960163116</t>
+    <t xml:space="preserve">1.6512656211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6347531080246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65621948242188</t>
   </si>
   <si>
     <t xml:space="preserve">1.64300942420959</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">1.63723003864288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64218366146088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63970685005188</t>
+    <t xml:space="preserve">1.64218378067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63970673084259</t>
   </si>
   <si>
     <t xml:space="preserve">1.66777837276459</t>
@@ -146,19 +146,19 @@
     <t xml:space="preserve">1.60503029823303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5984251499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870245933533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053225517273</t>
+    <t xml:space="preserve">1.59842538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870234012604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6405326128006</t>
   </si>
   <si>
     <t xml:space="preserve">1.63227605819702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60255312919617</t>
+    <t xml:space="preserve">1.60255336761475</t>
   </si>
   <si>
     <t xml:space="preserve">1.57283055782318</t>
@@ -167,31 +167,31 @@
     <t xml:space="preserve">1.58934319019318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58438944816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56787669658661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55714392662048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53402590751648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54310774803162</t>
+    <t xml:space="preserve">1.5843893289566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56787693500519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5571436882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53402578830719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54310786724091</t>
   </si>
   <si>
     <t xml:space="preserve">1.55466663837433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55962038040161</t>
+    <t xml:space="preserve">1.55962061882019</t>
   </si>
   <si>
     <t xml:space="preserve">1.55218970775604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55053853988647</t>
+    <t xml:space="preserve">1.55053865909576</t>
   </si>
   <si>
     <t xml:space="preserve">1.50265181064606</t>
@@ -203,142 +203,142 @@
     <t xml:space="preserve">1.48861598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53237450122833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49026727676392</t>
+    <t xml:space="preserve">1.53237438201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49026715755463</t>
   </si>
   <si>
     <t xml:space="preserve">1.5150363445282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48779058456421</t>
+    <t xml:space="preserve">1.48779046535492</t>
   </si>
   <si>
     <t xml:space="preserve">1.47623157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50760555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5010005235672</t>
+    <t xml:space="preserve">1.50760543346405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50100040435791</t>
   </si>
   <si>
     <t xml:space="preserve">1.49439537525177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48366212844849</t>
+    <t xml:space="preserve">1.48366224765778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45971870422363</t>
   </si>
   <si>
     <t xml:space="preserve">1.45971894264221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45971882343292</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.45299983024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46223843097687</t>
+    <t xml:space="preserve">1.46223855018616</t>
   </si>
   <si>
     <t xml:space="preserve">1.43284249305725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43536221981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43200266361237</t>
+    <t xml:space="preserve">1.43536233901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43200254440308</t>
   </si>
   <si>
     <t xml:space="preserve">1.4261234998703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41100549697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44040155410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43620228767395</t>
+    <t xml:space="preserve">1.41100561618805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44040143489838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43620204925537</t>
   </si>
   <si>
     <t xml:space="preserve">1.4429212808609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44880044460297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.478196144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460105895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42360389232635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43032276630402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46139860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40260684490204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4084860086441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3782502412796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42444384098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41604506969452</t>
+    <t xml:space="preserve">1.44880032539368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47819638252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460093975067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42360401153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43032288551331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46139872074127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40260660648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40848588943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37825012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42444360256195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41604483127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.46979749202728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42780303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192399501801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47567665576935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44796025753021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735631465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43368232250214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45803892612457</t>
+    <t xml:space="preserve">1.42780327796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192387580872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47567677497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4479603767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43368244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45803904533386</t>
   </si>
   <si>
     <t xml:space="preserve">1.4521598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48491549491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46391832828522</t>
+    <t xml:space="preserve">1.48491525650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46391820907593</t>
   </si>
   <si>
     <t xml:space="preserve">1.46643805503845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46895754337311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48575520515442</t>
+    <t xml:space="preserve">1.4689576625824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48575532436371</t>
   </si>
   <si>
     <t xml:space="preserve">1.45887899398804</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">1.45635914802551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45719921588898</t>
+    <t xml:space="preserve">1.45719909667969</t>
   </si>
   <si>
     <t xml:space="preserve">1.48827481269836</t>
@@ -359,31 +359,31 @@
     <t xml:space="preserve">1.47399687767029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727788448334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49835348129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50927197933197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50339293479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49499404430389</t>
+    <t xml:space="preserve">1.46727776527405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49835360050201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50927209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5033928155899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49499380588531</t>
   </si>
   <si>
     <t xml:space="preserve">1.48743498325348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51011180877686</t>
+    <t xml:space="preserve">1.51011168956757</t>
   </si>
   <si>
     <t xml:space="preserve">1.4991934299469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179170608521</t>
+    <t xml:space="preserve">1.51179158687592</t>
   </si>
   <si>
     <t xml:space="preserve">1.45048010349274</t>
@@ -392,25 +392,25 @@
     <t xml:space="preserve">1.44628083705902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43872177600861</t>
+    <t xml:space="preserve">1.4387218952179</t>
   </si>
   <si>
     <t xml:space="preserve">1.50003337860107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48071599006653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4815559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51095175743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49583399295807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50759208202362</t>
+    <t xml:space="preserve">1.48071587085724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48155581951141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51095187664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49583375453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50759220123291</t>
   </si>
   <si>
     <t xml:space="preserve">1.49667382240295</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">1.47231709957123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49331438541412</t>
+    <t xml:space="preserve">1.49331414699554</t>
   </si>
   <si>
     <t xml:space="preserve">1.47147715091705</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">1.52774953842163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53194880485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690958976746</t>
+    <t xml:space="preserve">1.53194904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690947055817</t>
   </si>
   <si>
     <t xml:space="preserve">1.52355015277863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50423264503479</t>
+    <t xml:space="preserve">1.50423288345337</t>
   </si>
   <si>
     <t xml:space="preserve">1.51263153553009</t>
@@ -455,127 +455,127 @@
     <t xml:space="preserve">1.55294597148895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52019047737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5084320306778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59578013420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53446865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56050503253937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53026914596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53110909461975</t>
+    <t xml:space="preserve">1.52019035816193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50843214988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59578001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53446853160858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56050491333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53026902675629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53110897541046</t>
   </si>
   <si>
     <t xml:space="preserve">1.5512660741806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55210614204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55378592014313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58654129505157</t>
+    <t xml:space="preserve">1.55210638046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55378580093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58654153347015</t>
   </si>
   <si>
     <t xml:space="preserve">1.56218481063843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56974363327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57058370113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60333919525146</t>
+    <t xml:space="preserve">1.56974375247955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57058346271515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60333907604218</t>
   </si>
   <si>
     <t xml:space="preserve">1.54958653450012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55798542499542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57142341136932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56470429897308</t>
+    <t xml:space="preserve">1.55798518657684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57142353057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56470441818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.6108980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61173796653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60417902469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62517595291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62097656726837</t>
+    <t xml:space="preserve">1.61173784732819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60417890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62517607212067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62097668647766</t>
   </si>
   <si>
     <t xml:space="preserve">1.61257779598236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59326040744781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58822107315063</t>
+    <t xml:space="preserve">1.5932605266571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58822119235992</t>
   </si>
   <si>
     <t xml:space="preserve">1.60753858089447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63105511665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61425769329071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71504366397858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77215576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7654367685318</t>
+    <t xml:space="preserve">1.63105523586273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61425757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71504390239716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77215564250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76543664932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.75367856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72512233257294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74527955055237</t>
+    <t xml:space="preserve">1.72512221336365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74527931213379</t>
   </si>
   <si>
     <t xml:space="preserve">1.72176277637482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70664477348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73856043815613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69992566108704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67892849445343</t>
+    <t xml:space="preserve">1.70664489269257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73856031894684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69992554187775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67892873287201</t>
   </si>
   <si>
     <t xml:space="preserve">1.69656622409821</t>
@@ -590,16 +590,16 @@
     <t xml:space="preserve">1.77383553981781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75871777534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68984711170197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69152688980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66801011562347</t>
+    <t xml:space="preserve">1.75871789455414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68984699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69152677059174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66800999641418</t>
   </si>
   <si>
     <t xml:space="preserve">1.68816733360291</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">1.73184144496918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75535809993744</t>
+    <t xml:space="preserve">1.75535798072815</t>
   </si>
   <si>
     <t xml:space="preserve">1.7100043296814</t>
@@ -620,37 +620,37 @@
     <t xml:space="preserve">1.71672332286835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73016166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74695909023285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7704758644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375687122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031900405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78895366191864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74024021625519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76207733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73352086544037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903209209442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78055441379547</t>
+    <t xml:space="preserve">1.73016154766083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74695944786072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77047634124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375699043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031888484955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78895342350006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7402400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76207709312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73352098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78055465221405</t>
   </si>
   <si>
     <t xml:space="preserve">1.82254874706268</t>
@@ -659,166 +659,166 @@
     <t xml:space="preserve">1.86958241462708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86454296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84774529933929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391420841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90480995178223</t>
+    <t xml:space="preserve">1.86454319953918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84774565696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391432762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90480959415436</t>
   </si>
   <si>
     <t xml:space="preserve">1.98488640785217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34267735481262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35119581222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24045157432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18081951141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36482644081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32223224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34608459472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33415842056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24897050857544</t>
+    <t xml:space="preserve">2.34267711639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3511962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24045133590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.180819272995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36482620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32223200798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34608483314514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33415865898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24897027015686</t>
   </si>
   <si>
     <t xml:space="preserve">2.20296859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14163279533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07007503509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01896190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9593300819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01044273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06496357917786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00192427635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02407336235046</t>
+    <t xml:space="preserve">2.14163303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07007479667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01896166801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95932984352112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01044297218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06496381759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00192451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02407312393188</t>
   </si>
   <si>
     <t xml:space="preserve">2.06155610084534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04451847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837105751038</t>
+    <t xml:space="preserve">2.04451870918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0683708190918</t>
   </si>
   <si>
     <t xml:space="preserve">2.05303716659546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04111075401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97977519035339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99340522289276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97636771202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97125601768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466385364532</t>
+    <t xml:space="preserve">2.04111051559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97977483272552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99340510368347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97636747360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97125613689423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9746640920639</t>
   </si>
   <si>
     <t xml:space="preserve">1.95081114768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93888473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92525482177734</t>
+    <t xml:space="preserve">1.93888461589813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92525470256805</t>
   </si>
   <si>
     <t xml:space="preserve">1.92695868015289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94229245185852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95762634277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718075752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866230010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97295999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00703549385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01555418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98829412460327</t>
+    <t xml:space="preserve">1.94229209423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95762646198273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718111515045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866206169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97296011447906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00703525543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01555442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98829400539398</t>
   </si>
   <si>
     <t xml:space="preserve">1.93206977844238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91673588752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91332817077637</t>
+    <t xml:space="preserve">1.91673612594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91332828998566</t>
   </si>
   <si>
     <t xml:space="preserve">1.90821707248688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93377339839935</t>
+    <t xml:space="preserve">1.93377351760864</t>
   </si>
   <si>
     <t xml:space="preserve">1.94058883190155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13822555541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25578474998474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22341346740723</t>
+    <t xml:space="preserve">2.13822507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25578498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22341394424438</t>
   </si>
   <si>
     <t xml:space="preserve">2.3597149848938</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">2.27452659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41593885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41253185272217</t>
+    <t xml:space="preserve">2.41593909263611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41253161430359</t>
   </si>
   <si>
     <t xml:space="preserve">2.3682336807251</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">2.30860185623169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31200909614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31541657447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28986072540283</t>
+    <t xml:space="preserve">2.31200933456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31541705131531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28986048698425</t>
   </si>
   <si>
     <t xml:space="preserve">2.42445802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41423559188843</t>
+    <t xml:space="preserve">2.41423535346985</t>
   </si>
   <si>
     <t xml:space="preserve">2.36993741989136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39719748497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35801100730896</t>
+    <t xml:space="preserve">2.39719772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35801076889038</t>
   </si>
   <si>
     <t xml:space="preserve">2.30519461631775</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">2.32052826881409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32904720306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31882429122925</t>
+    <t xml:space="preserve">2.32904696464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31882452964783</t>
   </si>
   <si>
     <t xml:space="preserve">2.3477885723114</t>
@@ -884,10 +884,10 @@
     <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32563972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33926963806152</t>
+    <t xml:space="preserve">2.32563996315002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3392698764801</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653017997742</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">2.3767523765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38356781005859</t>
+    <t xml:space="preserve">2.38356757164001</t>
   </si>
   <si>
     <t xml:space="preserve">2.27111887931824</t>
@@ -905,13 +905,13 @@
     <t xml:space="preserve">2.25408124923706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09392738342285</t>
+    <t xml:space="preserve">2.09392762184143</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696692466736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10585379600525</t>
+    <t xml:space="preserve">2.10585355758667</t>
   </si>
   <si>
     <t xml:space="preserve">2.10415005683899</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">2.31712079048157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28304529190063</t>
+    <t xml:space="preserve">2.28304576873779</t>
   </si>
   <si>
     <t xml:space="preserve">2.30349040031433</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">2.29667568206787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28815698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21659851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23874735832214</t>
+    <t xml:space="preserve">2.28815650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21659874916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23874759674072</t>
   </si>
   <si>
     <t xml:space="preserve">2.21489453315735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25748896598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24556279182434</t>
+    <t xml:space="preserve">2.25748920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24556231498718</t>
   </si>
   <si>
     <t xml:space="preserve">2.23193216323853</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">2.26260018348694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22511744499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23363637924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23022890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20637631416321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29156422615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39379000663757</t>
+    <t xml:space="preserve">2.22511696815491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23363661766052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23022842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20637607574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29156446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39378976821899</t>
   </si>
   <si>
     <t xml:space="preserve">2.41934657096863</t>
@@ -983,82 +983,82 @@
     <t xml:space="preserve">2.53009152412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57268571853638</t>
+    <t xml:space="preserve">2.5726854801178</t>
   </si>
   <si>
     <t xml:space="preserve">2.54712915420532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58120441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50453495979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47045993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46194076538086</t>
+    <t xml:space="preserve">2.58120465278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50453519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47045946121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46194052696228</t>
   </si>
   <si>
     <t xml:space="preserve">2.38527131080627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41082811355591</t>
+    <t xml:space="preserve">2.41082787513733</t>
   </si>
   <si>
     <t xml:space="preserve">2.30008316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45342206954956</t>
+    <t xml:space="preserve">2.45342230796814</t>
   </si>
   <si>
     <t xml:space="preserve">2.60676097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61527943611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64935493469238</t>
+    <t xml:space="preserve">2.61527967453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6493546962738</t>
   </si>
   <si>
     <t xml:space="preserve">2.65787363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4363842010498</t>
+    <t xml:space="preserve">2.43638396263123</t>
   </si>
   <si>
     <t xml:space="preserve">2.52157258987427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53861021995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55564761161804</t>
+    <t xml:space="preserve">2.53861045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55564785003662</t>
   </si>
   <si>
     <t xml:space="preserve">2.48749732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4449028968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26600790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14674425125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671034812927</t>
+    <t xml:space="preserve">2.44490313529968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26600766181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14674401283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671010971069</t>
   </si>
   <si>
     <t xml:space="preserve">2.1185667514801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17066240310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29221987724304</t>
+    <t xml:space="preserve">2.17066264152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29221963882446</t>
   </si>
   <si>
     <t xml:space="preserve">2.25748872756958</t>
@@ -1067,55 +1067,55 @@
     <t xml:space="preserve">2.24880647659302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2661714553833</t>
+    <t xml:space="preserve">2.26617169380188</t>
   </si>
   <si>
     <t xml:space="preserve">2.27485394477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34431552886963</t>
+    <t xml:space="preserve">2.34431529045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.35299801826477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3009021282196</t>
+    <t xml:space="preserve">2.30090236663818</t>
   </si>
   <si>
     <t xml:space="preserve">2.30958485603333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32695007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28353714942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21407556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17934513092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20539283752441</t>
+    <t xml:space="preserve">2.32695031166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28353691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21407580375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17934489250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20539307594299</t>
   </si>
   <si>
     <t xml:space="preserve">2.15329718589783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13593173027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10988402366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18802785873413</t>
+    <t xml:space="preserve">2.13593220710754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1098837852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18802762031555</t>
   </si>
   <si>
     <t xml:space="preserve">2.09251856803894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22275829315186</t>
+    <t xml:space="preserve">2.22275805473328</t>
   </si>
   <si>
     <t xml:space="preserve">2.07515335083008</t>
@@ -1127,40 +1127,40 @@
     <t xml:space="preserve">2.10120129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04042267799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01437473297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05778813362122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06647062301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700951576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00569200515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964417934418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96227896213531</t>
+    <t xml:space="preserve">2.04042291641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01437449455261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05778765678406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06647086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00569224357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9796439409256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96227872371674</t>
   </si>
   <si>
     <t xml:space="preserve">2.02305722236633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04910516738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03173995018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93623101711273</t>
+    <t xml:space="preserve">2.0491054058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03173971176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93623089790344</t>
   </si>
   <si>
     <t xml:space="preserve">1.87545251846313</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">1.82335638999939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81467378139496</t>
+    <t xml:space="preserve">1.81467354297638</t>
   </si>
   <si>
     <t xml:space="preserve">1.77994310855865</t>
@@ -1181,31 +1181,31 @@
     <t xml:space="preserve">1.71916472911835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69311678409576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62799680233002</t>
+    <t xml:space="preserve">1.69311666488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62799668312073</t>
   </si>
   <si>
     <t xml:space="preserve">1.63233804702759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67575132846832</t>
+    <t xml:space="preserve">1.67575144767761</t>
   </si>
   <si>
     <t xml:space="preserve">1.68443417549133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71048188209534</t>
+    <t xml:space="preserve">1.71048200130463</t>
   </si>
   <si>
     <t xml:space="preserve">1.6887754201889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71482336521149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69745802879333</t>
+    <t xml:space="preserve">1.7148232460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69745814800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.64536213874817</t>
@@ -1220,22 +1220,22 @@
     <t xml:space="preserve">1.61931419372559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61497282981873</t>
+    <t xml:space="preserve">1.61497294902802</t>
   </si>
   <si>
     <t xml:space="preserve">1.63667953014374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64970350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68009257316589</t>
+    <t xml:space="preserve">1.64970326423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68009269237518</t>
   </si>
   <si>
     <t xml:space="preserve">1.65838611125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70179927349091</t>
+    <t xml:space="preserve">1.7017993927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.67140996456146</t>
@@ -1247,61 +1247,61 @@
     <t xml:space="preserve">1.57155954837799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52814626693726</t>
+    <t xml:space="preserve">1.52814638614655</t>
   </si>
   <si>
     <t xml:space="preserve">1.51078104972839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54551160335541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56287693977356</t>
+    <t xml:space="preserve">1.54551148414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56287682056427</t>
   </si>
   <si>
     <t xml:space="preserve">1.6540447473526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66272723674774</t>
+    <t xml:space="preserve">1.66272735595703</t>
   </si>
   <si>
     <t xml:space="preserve">1.72784733772278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76257789134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75389528274536</t>
+    <t xml:space="preserve">1.7625777721405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75389516353607</t>
   </si>
   <si>
     <t xml:space="preserve">1.78862583637238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80599093437195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77126049995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74521255493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83203899860382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79730844497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84072148799896</t>
+    <t xml:space="preserve">1.80599129199982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77126038074493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74521267414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83203876018524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79730832576752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84072172641754</t>
   </si>
   <si>
     <t xml:space="preserve">1.86676967144012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91018283367157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9535961151123</t>
+    <t xml:space="preserve">1.91018319129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359635353088</t>
   </si>
   <si>
     <t xml:space="preserve">1.94491350650787</t>
@@ -1310,49 +1310,49 @@
     <t xml:space="preserve">1.98832666873932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97096133232117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91886579990387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92754817008972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85808730125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84940457344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413488864899</t>
+    <t xml:space="preserve">1.97096157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91886568069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92754828929901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85808718204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84940433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8841347694397</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6504191160202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61919510364532</t>
+    <t xml:space="preserve">1.65041899681091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61919486522675</t>
   </si>
   <si>
     <t xml:space="preserve">1.6013525724411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61027371883392</t>
+    <t xml:space="preserve">1.61027359962463</t>
   </si>
   <si>
     <t xml:space="preserve">1.63703739643097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65487968921661</t>
+    <t xml:space="preserve">1.6548798084259</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365567684174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6459584236145</t>
+    <t xml:space="preserve">1.64595854282379</t>
   </si>
   <si>
     <t xml:space="preserve">1.64149785041809</t>
@@ -1367,31 +1367,31 @@
     <t xml:space="preserve">1.68610382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68164324760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63257682323456</t>
+    <t xml:space="preserve">1.68164312839508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63257694244385</t>
   </si>
   <si>
     <t xml:space="preserve">1.60581314563751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62811613082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61473429203033</t>
+    <t xml:space="preserve">1.62811625003815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61473441123962</t>
   </si>
   <si>
     <t xml:space="preserve">1.58351016044617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57904958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.552286028862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54336488246918</t>
+    <t xml:space="preserve">1.57904970645905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55228614807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54336476325989</t>
   </si>
   <si>
     <t xml:space="preserve">1.59243142604828</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">1.56120729446411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53890419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5567467212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57012832164764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58797085285187</t>
+    <t xml:space="preserve">1.53890442848206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55674660205841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57012856006622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58797073364258</t>
   </si>
   <si>
     <t xml:space="preserve">1.57458901405334</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">1.59689199924469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53444373607635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66380095481873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56566786766052</t>
+    <t xml:space="preserve">1.53444361686707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66380083560944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56566774845123</t>
   </si>
   <si>
     <t xml:space="preserve">1.54782545566559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52552258968353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50768005847931</t>
+    <t xml:space="preserve">1.52552235126495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5076801776886</t>
   </si>
   <si>
     <t xml:space="preserve">1.42738950252533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51660120487213</t>
+    <t xml:space="preserve">1.51660132408142</t>
   </si>
   <si>
     <t xml:space="preserve">1.48983764648438</t>
@@ -1451,31 +1451,31 @@
     <t xml:space="preserve">1.34709882736206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32479596138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19097805023193</t>
+    <t xml:space="preserve">1.32479584217072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19097816944122</t>
   </si>
   <si>
     <t xml:space="preserve">1.26680815219879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24450516700745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29803240299225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20436000823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27572917938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28465044498444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30695343017578</t>
+    <t xml:space="preserve">1.24450528621674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29803228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20435988903046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27572929859161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28465056419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30695354938507</t>
   </si>
   <si>
     <t xml:space="preserve">1.30249285697937</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">1.36494112014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35602009296417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36048054695129</t>
+    <t xml:space="preserve">1.35601997375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36048066616058</t>
   </si>
   <si>
     <t xml:space="preserve">1.40508663654327</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">1.44969236850739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4541529417038</t>
+    <t xml:space="preserve">1.45415306091309</t>
   </si>
   <si>
     <t xml:space="preserve">1.44523191452026</t>
@@ -1526,19 +1526,19 @@
     <t xml:space="preserve">1.38278353214264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33817756175995</t>
+    <t xml:space="preserve">1.38724410533905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33817768096924</t>
   </si>
   <si>
     <t xml:space="preserve">1.35155940055847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29357182979584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32925641536713</t>
+    <t xml:space="preserve">1.29357171058655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32925653457642</t>
   </si>
   <si>
     <t xml:space="preserve">1.33371698856354</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">1.3158745765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37386238574982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31141412258148</t>
+    <t xml:space="preserve">1.37386226654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31141400337219</t>
   </si>
   <si>
     <t xml:space="preserve">1.3203352689743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28018987178802</t>
+    <t xml:space="preserve">1.28018975257874</t>
   </si>
   <si>
     <t xml:space="preserve">1.40954720973969</t>
@@ -1571,25 +1571,25 @@
     <t xml:space="preserve">1.37832295894623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42292892932892</t>
+    <t xml:space="preserve">1.42292904853821</t>
   </si>
   <si>
     <t xml:space="preserve">1.28911113739014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27126860618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26234757900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24896585941315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46753478050232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44077134132385</t>
+    <t xml:space="preserve">1.2712687253952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26234745979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24896574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46753466129303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44077122211456</t>
   </si>
   <si>
     <t xml:space="preserve">1.48091650009155</t>
@@ -1610,70 +1610,70 @@
     <t xml:space="preserve">1.51214075088501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48537707328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52106189727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72178840637207</t>
+    <t xml:space="preserve">1.48537719249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52106201648712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72178852558136</t>
   </si>
   <si>
     <t xml:space="preserve">1.76639449596405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73963093757629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81992161273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87344861030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82884275913239</t>
+    <t xml:space="preserve">1.73963105678558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8734484910965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8288426399231</t>
   </si>
   <si>
     <t xml:space="preserve">1.83776390552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423678874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77531576156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73517036437988</t>
+    <t xml:space="preserve">1.78423690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77531564235687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73517024517059</t>
   </si>
   <si>
     <t xml:space="preserve">1.77085506916046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72624909877777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73070979118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74855208396912</t>
+    <t xml:space="preserve">1.72624897956848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73070991039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74855220317841</t>
   </si>
   <si>
     <t xml:space="preserve">1.79315805435181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71732783317566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74409162998199</t>
+    <t xml:space="preserve">1.71732795238495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74409151077271</t>
   </si>
   <si>
     <t xml:space="preserve">1.77977633476257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81100046634674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84668493270874</t>
+    <t xml:space="preserve">1.81100034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84668505191803</t>
   </si>
   <si>
     <t xml:space="preserve">1.86452746391296</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">1.80207920074463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75747334957123</t>
+    <t xml:space="preserve">1.75747323036194</t>
   </si>
   <si>
     <t xml:space="preserve">2.0340301990509</t>
@@ -1691,25 +1691,25 @@
     <t xml:space="preserve">2.02510857582092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96266031265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92697596549988</t>
+    <t xml:space="preserve">1.96266055107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92697608470917</t>
   </si>
   <si>
     <t xml:space="preserve">1.98050284385681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07863593101501</t>
+    <t xml:space="preserve">2.07863616943359</t>
   </si>
   <si>
     <t xml:space="preserve">2.10539937019348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05187249183655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06079363822937</t>
+    <t xml:space="preserve">2.05187225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06079339981079</t>
   </si>
   <si>
     <t xml:space="preserve">2.09647846221924</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">2.39087748527527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56037974357605</t>
+    <t xml:space="preserve">2.56037950515747</t>
   </si>
   <si>
     <t xml:space="preserve">2.60498571395874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65005493164062</t>
+    <t xml:space="preserve">2.65005469322205</t>
   </si>
   <si>
     <t xml:space="preserve">2.61399960517883</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">2.78526163101196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73117899894714</t>
+    <t xml:space="preserve">2.73117876052856</t>
   </si>
   <si>
     <t xml:space="preserve">2.90244102478027</t>
@@ -1757,25 +1757,25 @@
     <t xml:space="preserve">2.99257874488831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92948246002197</t>
+    <t xml:space="preserve">2.92948222160339</t>
   </si>
   <si>
     <t xml:space="preserve">2.84835815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76723408699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83934426307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87539958953857</t>
+    <t xml:space="preserve">2.76723384857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83934450149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87539982795715</t>
   </si>
   <si>
     <t xml:space="preserve">2.82131695747375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77624797821045</t>
+    <t xml:space="preserve">2.77624773979187</t>
   </si>
   <si>
     <t xml:space="preserve">2.72216510772705</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">2.55991697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53287529945374</t>
+    <t xml:space="preserve">2.53287553787231</t>
   </si>
   <si>
     <t xml:space="preserve">2.60498595237732</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.65906858444214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67709612846375</t>
+    <t xml:space="preserve">2.67709636688232</t>
   </si>
   <si>
     <t xml:space="preserve">2.52386164665222</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">2.57794427871704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597182273865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55090284347534</t>
+    <t xml:space="preserve">2.59597206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55090308189392</t>
   </si>
   <si>
     <t xml:space="preserve">2.51484799385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56893062591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79427528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83033061027527</t>
+    <t xml:space="preserve">2.56893086433411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79427552223206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83033084869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.71315121650696</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">2.54188919067383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4787929058075</t>
+    <t xml:space="preserve">2.47879266738892</t>
   </si>
   <si>
     <t xml:space="preserve">2.63202714920044</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">2.91145467758179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9745512008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95652365684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01060652732849</t>
+    <t xml:space="preserve">2.97455096244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95652389526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01060628890991</t>
   </si>
   <si>
     <t xml:space="preserve">3.01962018013</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">2.98356509208679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88441348075867</t>
+    <t xml:space="preserve">2.88441324234009</t>
   </si>
   <si>
     <t xml:space="preserve">2.94751000404358</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">2.68611025810242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23542046546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19035148620605</t>
+    <t xml:space="preserve">2.23542022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19035124778748</t>
   </si>
   <si>
     <t xml:space="preserve">2.28048944473267</t>
@@ -1937,10 +1937,10 @@
     <t xml:space="preserve">2.27147555351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26246166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28950309753418</t>
+    <t xml:space="preserve">2.26246190071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28950333595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.30753064155579</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">2.32555818557739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29851675033569</t>
+    <t xml:space="preserve">2.29851698875427</t>
   </si>
   <si>
     <t xml:space="preserve">2.343585729599</t>
@@ -70476,9 +70476,11 @@
       <c r="E2597" t="n">
         <v>1.99500000476837</v>
       </c>
-      <c r="F2597"/>
+      <c r="F2597" t="n">
+        <v>1.91999995708466</v>
+      </c>
       <c r="G2597" t="s">
-        <v>871</v>
+        <v>840</v>
       </c>
       <c r="H2597" t="s">
         <v>9</v>
@@ -70486,27 +70488,51 @@
     </row>
     <row r="2598">
       <c r="A2598" s="1" t="n">
-        <v>46101.6910185185</v>
+        <v>46104.3333333333</v>
       </c>
       <c r="B2598" t="n">
-        <v>6085</v>
+        <v>15909</v>
       </c>
       <c r="C2598" t="n">
-        <v>1.99500000476837</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="D2598" t="n">
         <v>1.91999995708466</v>
       </c>
       <c r="E2598" t="n">
-        <v>1.99500000476837</v>
-      </c>
-      <c r="F2598" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="F2598"/>
+      <c r="G2598" t="s">
+        <v>871</v>
+      </c>
+      <c r="H2598" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" s="1" t="n">
+        <v>46104.5588541667</v>
+      </c>
+      <c r="B2599" t="n">
+        <v>15909</v>
+      </c>
+      <c r="C2599" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="D2599" t="n">
         <v>1.91999995708466</v>
       </c>
-      <c r="G2598" t="s">
+      <c r="E2599" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="F2599" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G2599" t="s">
         <v>840</v>
       </c>
-      <c r="H2598" t="s">
+      <c r="H2599" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,85 +38,85 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034165382385</t>
+    <t xml:space="preserve">1.75034153461456</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538779258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69254732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245492458344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68429100513458</t>
+    <t xml:space="preserve">1.74538767337799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69254720211029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245516300201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68429088592529</t>
   </si>
   <si>
     <t xml:space="preserve">1.67603468894958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66612684726715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63888108730316</t>
+    <t xml:space="preserve">1.66612696647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63888132572174</t>
   </si>
   <si>
     <t xml:space="preserve">1.61163532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59347140789032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48613905906677</t>
+    <t xml:space="preserve">1.59347128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48613929748535</t>
   </si>
   <si>
     <t xml:space="preserve">1.59264588356018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59182012081146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58604049682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172784328461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521497249603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56044614315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51255941390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53980529308319</t>
+    <t xml:space="preserve">1.59182000160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58604097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521509170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56044602394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51255917549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5398051738739</t>
   </si>
   <si>
     <t xml:space="preserve">1.56539988517761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53567731380463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45311391353607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50595426559448</t>
+    <t xml:space="preserve">1.53567719459534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45311379432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50595438480377</t>
   </si>
   <si>
     <t xml:space="preserve">1.46137011051178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44238042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51833891868591</t>
+    <t xml:space="preserve">1.4423805475235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51833879947662</t>
   </si>
   <si>
     <t xml:space="preserve">1.65126574039459</t>
@@ -131,25 +131,25 @@
     <t xml:space="preserve">1.64300930500031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63723003864288</t>
+    <t xml:space="preserve">1.63722991943359</t>
   </si>
   <si>
     <t xml:space="preserve">1.64218378067017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63970685005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66777837276459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60503029823303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5984251499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870234012604</t>
+    <t xml:space="preserve">1.63970673084259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66777813434601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60503017902374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59842526912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870245933533</t>
   </si>
   <si>
     <t xml:space="preserve">1.64053249359131</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">1.63227617740631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60255324840546</t>
+    <t xml:space="preserve">1.60255336761475</t>
   </si>
   <si>
     <t xml:space="preserve">1.57283055782318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58934319019318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5843893289566</t>
+    <t xml:space="preserve">1.58934330940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58438956737518</t>
   </si>
   <si>
     <t xml:space="preserve">1.56787669658661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55714380741119</t>
+    <t xml:space="preserve">1.55714356899261</t>
   </si>
   <si>
     <t xml:space="preserve">1.53402590751648</t>
@@ -182,43 +182,43 @@
     <t xml:space="preserve">1.54310774803162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55466675758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5596204996109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55218982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55053842067719</t>
+    <t xml:space="preserve">1.55466651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962038040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55218970775604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55053865909576</t>
   </si>
   <si>
     <t xml:space="preserve">1.50265181064606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4869647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861610889435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237438201904</t>
+    <t xml:space="preserve">1.48696458339691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861587047577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237450122833</t>
   </si>
   <si>
     <t xml:space="preserve">1.49026715755463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5150363445282</t>
+    <t xml:space="preserve">1.51503622531891</t>
   </si>
   <si>
     <t xml:space="preserve">1.48779046535492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47623145580292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50760555267334</t>
+    <t xml:space="preserve">1.4762316942215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50760567188263</t>
   </si>
   <si>
     <t xml:space="preserve">1.50100064277649</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">1.49439537525177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48366236686707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45971858501434</t>
+    <t xml:space="preserve">1.48366212844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45971894264221</t>
   </si>
   <si>
     <t xml:space="preserve">1.45971870422363</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">1.45299994945526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46223878860474</t>
+    <t xml:space="preserve">1.46223866939545</t>
   </si>
   <si>
     <t xml:space="preserve">1.43284249305725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43536233901978</t>
+    <t xml:space="preserve">1.43536221981049</t>
   </si>
   <si>
     <t xml:space="preserve">1.43200266361237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42612361907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41100561618805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44040155410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43620216846466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4429212808609</t>
+    <t xml:space="preserve">1.42612338066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41100549697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44040167331696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43620228767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44292116165161</t>
   </si>
   <si>
     <t xml:space="preserve">1.44880044460297</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">1.47819626331329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44460105895996</t>
+    <t xml:space="preserve">1.44460093975067</t>
   </si>
   <si>
     <t xml:space="preserve">1.42360377311707</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">1.4303230047226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139872074127</t>
+    <t xml:space="preserve">1.46139860153198</t>
   </si>
   <si>
     <t xml:space="preserve">1.40260672569275</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">1.40848612785339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37825012207031</t>
+    <t xml:space="preserve">1.37825000286102</t>
   </si>
   <si>
     <t xml:space="preserve">1.42444372177124</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">1.46979737281799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42780339717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192399501801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47567665576935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44796049594879</t>
+    <t xml:space="preserve">1.42780315876007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192411422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47567677497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4479603767395</t>
   </si>
   <si>
     <t xml:space="preserve">1.47735631465912</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">1.4521598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48491525650024</t>
+    <t xml:space="preserve">1.48491549491882</t>
   </si>
   <si>
     <t xml:space="preserve">1.46391832828522</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">1.46643793582916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46895754337311</t>
+    <t xml:space="preserve">1.46895742416382</t>
   </si>
   <si>
     <t xml:space="preserve">1.48575532436371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45887899398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45635938644409</t>
+    <t xml:space="preserve">1.45887911319733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4563592672348</t>
   </si>
   <si>
     <t xml:space="preserve">1.45719933509827</t>
@@ -362,19 +362,19 @@
     <t xml:space="preserve">1.46727776527405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49835348129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50927221775055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50339269638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4949939250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48743510246277</t>
+    <t xml:space="preserve">1.4983537197113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50927197933197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50339305400848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49499404430389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48743498325348</t>
   </si>
   <si>
     <t xml:space="preserve">1.51011192798615</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">1.4991934299469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179170608521</t>
+    <t xml:space="preserve">1.51179182529449</t>
   </si>
   <si>
     <t xml:space="preserve">1.45048010349274</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">1.43872177600861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50003349781036</t>
+    <t xml:space="preserve">1.50003337860107</t>
   </si>
   <si>
     <t xml:space="preserve">1.48071610927582</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">1.49331426620483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47147750854492</t>
+    <t xml:space="preserve">1.47147715091705</t>
   </si>
   <si>
     <t xml:space="preserve">1.50087308883667</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">1.53194892406464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52690958976746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355015277863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5042325258255</t>
+    <t xml:space="preserve">1.52690970897675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50423276424408</t>
   </si>
   <si>
     <t xml:space="preserve">1.5126314163208</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">1.54538714885712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55294609069824</t>
+    <t xml:space="preserve">1.55294597148895</t>
   </si>
   <si>
     <t xml:space="preserve">1.52019047737122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5084320306778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59578001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53446865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56050515174866</t>
+    <t xml:space="preserve">1.50843214988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59578013420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53446853160858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56050503253937</t>
   </si>
   <si>
     <t xml:space="preserve">1.53026914596558</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">1.53110897541046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55126631259918</t>
+    <t xml:space="preserve">1.55126619338989</t>
   </si>
   <si>
     <t xml:space="preserve">1.55210614204407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55378603935242</t>
+    <t xml:space="preserve">1.55378580093384</t>
   </si>
   <si>
     <t xml:space="preserve">1.58654129505157</t>
@@ -494,34 +494,34 @@
     <t xml:space="preserve">1.56974363327026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57058370113373</t>
+    <t xml:space="preserve">1.57058358192444</t>
   </si>
   <si>
     <t xml:space="preserve">1.60333919525146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54958641529083</t>
+    <t xml:space="preserve">1.54958653450012</t>
   </si>
   <si>
     <t xml:space="preserve">1.55798530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57142341136932</t>
+    <t xml:space="preserve">1.57142353057861</t>
   </si>
   <si>
     <t xml:space="preserve">1.56470441818237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61089789867401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61173784732819</t>
+    <t xml:space="preserve">1.6108980178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61173808574677</t>
   </si>
   <si>
     <t xml:space="preserve">1.60417890548706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62517607212067</t>
+    <t xml:space="preserve">1.62517595291138</t>
   </si>
   <si>
     <t xml:space="preserve">1.62097656726837</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">1.61257779598236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5932605266571</t>
+    <t xml:space="preserve">1.59326028823853</t>
   </si>
   <si>
     <t xml:space="preserve">1.58822119235992</t>
@@ -545,49 +545,49 @@
     <t xml:space="preserve">1.61425757408142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71504366397858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77215576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76543664932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75367844104767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72512221336365</t>
+    <t xml:space="preserve">1.71504378318787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77215564250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76543653011322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75367856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72512245178223</t>
   </si>
   <si>
     <t xml:space="preserve">1.74527955055237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72176277637482</t>
+    <t xml:space="preserve">1.72176265716553</t>
   </si>
   <si>
     <t xml:space="preserve">1.70664501190186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73856055736542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69992566108704</t>
+    <t xml:space="preserve">1.73856043815613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69992554187775</t>
   </si>
   <si>
     <t xml:space="preserve">1.67892861366272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69656622409821</t>
+    <t xml:space="preserve">1.69656598567963</t>
   </si>
   <si>
     <t xml:space="preserve">1.69320666790009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70496487617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77383542060852</t>
+    <t xml:space="preserve">1.70496511459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77383553981781</t>
   </si>
   <si>
     <t xml:space="preserve">1.75871777534485</t>
@@ -596,127 +596,127 @@
     <t xml:space="preserve">1.68984723091125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69152688980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66801011562347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68816745281219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71336388587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73184144496918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535786151886</t>
+    <t xml:space="preserve">1.69152677059174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66800999641418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68816733360291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71336376667023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73184156417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535809993744</t>
   </si>
   <si>
     <t xml:space="preserve">1.7100043296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71672344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016154766083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047598361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375699043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031912326813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78895354270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74024021625519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76207733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73352098464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903197288513</t>
+    <t xml:space="preserve">1.71672308444977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016166687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74695932865143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77047634124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031900405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78895366191864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74024033546448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76207721233368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73352122306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903185367584</t>
   </si>
   <si>
     <t xml:space="preserve">1.78055453300476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82254874706268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86958229541779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86454319953918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84774553775787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391408920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90480947494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98488664627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34267687797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35119605064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24045157432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.180819272995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.364825963974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32223200798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34608459472656</t>
+    <t xml:space="preserve">1.82254886627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86958253383636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86454296112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84774541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391420841217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90480971336365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98488640785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34267735481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35119581222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24045133590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18081951141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36482620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32223224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34608507156372</t>
   </si>
   <si>
     <t xml:space="preserve">2.33415842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2489697933197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20296835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14163255691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07007479667664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01896166801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9593300819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01044273376465</t>
+    <t xml:space="preserve">2.24897003173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20296812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14163303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07007503509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01896142959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95932996273041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01044297218323</t>
   </si>
   <si>
     <t xml:space="preserve">2.06496357917786</t>
@@ -728,16 +728,16 @@
     <t xml:space="preserve">2.02407312393188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06155633926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04451823234558</t>
+    <t xml:space="preserve">2.06155610084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04451870918274</t>
   </si>
   <si>
     <t xml:space="preserve">2.0683708190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303740501404</t>
+    <t xml:space="preserve">2.05303716659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.04111075401306</t>
@@ -746,28 +746,28 @@
     <t xml:space="preserve">1.97977519035339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99340498447418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97636735439301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97125613689423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466373443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95081126689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93888485431671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92525494098663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92695844173431</t>
+    <t xml:space="preserve">1.99340522289276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97636747360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97125625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97466385364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95081114768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.938884973526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92525482177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9269585609436</t>
   </si>
   <si>
     <t xml:space="preserve">1.94229233264923</t>
@@ -782,34 +782,34 @@
     <t xml:space="preserve">1.92866230010986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97296011447906</t>
+    <t xml:space="preserve">1.97296023368835</t>
   </si>
   <si>
     <t xml:space="preserve">2.00703549385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01555442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98829424381256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9320695400238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673600673676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91332828998566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90821695327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93377351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94058847427368</t>
+    <t xml:space="preserve">2.01555418968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98829412460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93206965923309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673588752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91332852840424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90821707248688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93377363681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94058871269226</t>
   </si>
   <si>
     <t xml:space="preserve">2.13822555541992</t>
@@ -821,43 +821,43 @@
     <t xml:space="preserve">2.22341346740723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35971474647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27452659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41593909263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41253161430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36823391914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30860233306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31200933456421</t>
+    <t xml:space="preserve">2.3597149848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27452683448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41593885421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41253185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3682336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30860209465027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31200957298279</t>
   </si>
   <si>
     <t xml:space="preserve">2.31541705131531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28986072540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42445826530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41423535346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36993741989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39719748497009</t>
+    <t xml:space="preserve">2.28986048698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42445778846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41423559188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36993765830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39719772338867</t>
   </si>
   <si>
     <t xml:space="preserve">2.35801100730896</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">2.32052826881409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32904720306396</t>
+    <t xml:space="preserve">2.32904696464539</t>
   </si>
   <si>
     <t xml:space="preserve">2.31882452964783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3477885723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36312246322632</t>
+    <t xml:space="preserve">2.34778833389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36312222480774</t>
   </si>
   <si>
     <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32563972473145</t>
+    <t xml:space="preserve">2.32563996315002</t>
   </si>
   <si>
     <t xml:space="preserve">2.33926963806152</t>
@@ -899,70 +899,70 @@
     <t xml:space="preserve">2.38356757164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2711193561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25408148765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09392738342285</t>
+    <t xml:space="preserve">2.27111887931824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25408172607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09392762184143</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696716308594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10585355758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10415029525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12800288200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31712055206299</t>
+    <t xml:space="preserve">2.10585379600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10415005683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12800264358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31712079048157</t>
   </si>
   <si>
     <t xml:space="preserve">2.28304553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30349063873291</t>
+    <t xml:space="preserve">2.30349040031433</t>
   </si>
   <si>
     <t xml:space="preserve">2.29667544364929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28815674781799</t>
+    <t xml:space="preserve">2.28815698623657</t>
   </si>
   <si>
     <t xml:space="preserve">2.21659851074219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23874759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21489477157593</t>
+    <t xml:space="preserve">2.23874735832214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21489453315735</t>
   </si>
   <si>
     <t xml:space="preserve">2.25748920440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24556279182434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23193216323853</t>
+    <t xml:space="preserve">2.24556255340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23193192481995</t>
   </si>
   <si>
     <t xml:space="preserve">2.18933820724487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26260042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22511744499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23363614082336</t>
+    <t xml:space="preserve">2.26260018348694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22511720657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23363637924194</t>
   </si>
   <si>
     <t xml:space="preserve">2.23022866249084</t>
@@ -971,10 +971,10 @@
     <t xml:space="preserve">2.20637583732605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29156422615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39379000663757</t>
+    <t xml:space="preserve">2.29156446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39379024505615</t>
   </si>
   <si>
     <t xml:space="preserve">2.41934633255005</t>
@@ -986,22 +986,22 @@
     <t xml:space="preserve">2.5726854801178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5471293926239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58120441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50453495979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47045946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46194100379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3852710723877</t>
+    <t xml:space="preserve">2.54712891578674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5812041759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50453519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47045993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46194076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38527131080627</t>
   </si>
   <si>
     <t xml:space="preserve">2.41082787513733</t>
@@ -1013,31 +1013,31 @@
     <t xml:space="preserve">2.45342206954956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60676074028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61527967453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6493546962738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787386894226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43638443946838</t>
+    <t xml:space="preserve">2.60676097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61527991294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64935493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4363842010498</t>
   </si>
   <si>
     <t xml:space="preserve">2.52157258987427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53861021995544</t>
+    <t xml:space="preserve">2.53861045837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.55564785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48749709129333</t>
+    <t xml:space="preserve">2.48749732971191</t>
   </si>
   <si>
     <t xml:space="preserve">2.4449028968811</t>
@@ -1046,16 +1046,16 @@
     <t xml:space="preserve">2.26600790023804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14674425125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671034812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11856651306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066240310669</t>
+    <t xml:space="preserve">2.1467444896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671058654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1185667514801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066264152527</t>
   </si>
   <si>
     <t xml:space="preserve">2.29221940040588</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">2.24880599975586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26617121696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27485418319702</t>
+    <t xml:space="preserve">2.2661714553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27485370635986</t>
   </si>
   <si>
     <t xml:space="preserve">2.34431552886963</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">2.30958485603333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32695007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28353714942932</t>
+    <t xml:space="preserve">2.32695031166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28353691101074</t>
   </si>
   <si>
     <t xml:space="preserve">2.21407556533813</t>
@@ -1100,76 +1100,76 @@
     <t xml:space="preserve">2.20539307594299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15329694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13593173027039</t>
+    <t xml:space="preserve">2.15329718589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13593196868896</t>
   </si>
   <si>
     <t xml:space="preserve">2.10988402366638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18802762031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09251880645752</t>
+    <t xml:space="preserve">2.18802809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09251856803894</t>
   </si>
   <si>
     <t xml:space="preserve">2.22275829315186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07515358924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08383584022522</t>
+    <t xml:space="preserve">2.07515335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08383631706238</t>
   </si>
   <si>
     <t xml:space="preserve">2.10120129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04042267799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01437425613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05778789520264</t>
+    <t xml:space="preserve">2.0404224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01437449455261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05778765678406</t>
   </si>
   <si>
     <t xml:space="preserve">2.06647062301636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99700927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00569224357605</t>
+    <t xml:space="preserve">1.99700939655304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00569200515747</t>
   </si>
   <si>
     <t xml:space="preserve">1.97964406013489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9622790813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02305746078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04910492897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03173971176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93623101711273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87545228004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281785488129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82335650920868</t>
+    <t xml:space="preserve">1.96227896213531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02305722236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0491054058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03173995018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93623089790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87545251846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.892817735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8233562707901</t>
   </si>
   <si>
     <t xml:space="preserve">1.81467366218567</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">1.71916460990906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69311666488647</t>
+    <t xml:space="preserve">1.69311678409576</t>
   </si>
   <si>
     <t xml:space="preserve">1.62799680233002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63233816623688</t>
+    <t xml:space="preserve">1.63233804702759</t>
   </si>
   <si>
     <t xml:space="preserve">1.67575132846832</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">1.68443405628204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71048200130463</t>
+    <t xml:space="preserve">1.71048212051392</t>
   </si>
   <si>
     <t xml:space="preserve">1.6887754201889</t>
@@ -1205,22 +1205,22 @@
     <t xml:space="preserve">1.71482336521149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69745814800262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64536213874817</t>
+    <t xml:space="preserve">1.69745802879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64536201953888</t>
   </si>
   <si>
     <t xml:space="preserve">1.59760761260986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60629034042358</t>
+    <t xml:space="preserve">1.60629022121429</t>
   </si>
   <si>
     <t xml:space="preserve">1.61931419372559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61497294902802</t>
+    <t xml:space="preserve">1.61497282981873</t>
   </si>
   <si>
     <t xml:space="preserve">1.63667941093445</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">1.68009269237518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65838587284088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7017993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67140996456146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6670686006546</t>
+    <t xml:space="preserve">1.65838611125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70179927349091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67141008377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66706871986389</t>
   </si>
   <si>
     <t xml:space="preserve">1.57155954837799</t>
@@ -1256,37 +1256,37 @@
     <t xml:space="preserve">1.54551160335541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56287693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6540447473526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66272747516632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72784721851349</t>
+    <t xml:space="preserve">1.56287705898285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65404486656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66272735595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72784745693207</t>
   </si>
   <si>
     <t xml:space="preserve">1.76257789134979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75389540195465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78862583637238</t>
+    <t xml:space="preserve">1.75389516353607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78862571716309</t>
   </si>
   <si>
     <t xml:space="preserve">1.80599105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77126061916351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74521267414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83203911781311</t>
+    <t xml:space="preserve">1.77126049995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74521255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83203887939453</t>
   </si>
   <si>
     <t xml:space="preserve">1.79730844497681</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">1.84072172641754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8667699098587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91018307209015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359623432159</t>
+    <t xml:space="preserve">1.86676979064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91018295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9535961151123</t>
   </si>
   <si>
     <t xml:space="preserve">1.94491350650787</t>
@@ -1310,64 +1310,67 @@
     <t xml:space="preserve">1.98832666873932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97096145153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91886556148529</t>
+    <t xml:space="preserve">1.97096157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91886568069458</t>
   </si>
   <si>
     <t xml:space="preserve">1.92754828929901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85808706283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84940445423126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413488864899</t>
+    <t xml:space="preserve">1.85808718204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84940457344055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413512706757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62365543842316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6504191160202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61919498443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6013525724411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61027371883392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63703727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65487968921661</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65041923522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61919510364532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60135245323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61027371883392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63703727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65487968921661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6459584236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64149796962738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65934038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66826152801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68610382080078</t>
+    <t xml:space="preserve">1.64595854282379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64149808883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65934026241302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66826140880585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68610370159149</t>
   </si>
   <si>
     <t xml:space="preserve">1.68164312839508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63257670402527</t>
+    <t xml:space="preserve">1.63257682323456</t>
   </si>
   <si>
     <t xml:space="preserve">1.60581314563751</t>
@@ -1382,13 +1385,13 @@
     <t xml:space="preserve">1.58351016044617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57904958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55228614807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54336488246918</t>
+    <t xml:space="preserve">1.57904946804047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.552286028862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54336500167847</t>
   </si>
   <si>
     <t xml:space="preserve">1.59243130683899</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">1.56120717525482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53890430927277</t>
+    <t xml:space="preserve">1.53890442848206</t>
   </si>
   <si>
     <t xml:space="preserve">1.5567467212677</t>
@@ -1418,7 +1421,7 @@
     <t xml:space="preserve">1.53444385528564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66380083560944</t>
+    <t xml:space="preserve">1.66380095481873</t>
   </si>
   <si>
     <t xml:space="preserve">1.56566786766052</t>
@@ -1427,7 +1430,7 @@
     <t xml:space="preserve">1.54782557487488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52552258968353</t>
+    <t xml:space="preserve">1.52552270889282</t>
   </si>
   <si>
     <t xml:space="preserve">1.5076801776886</t>
@@ -1436,19 +1439,19 @@
     <t xml:space="preserve">1.42738950252533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51660144329071</t>
+    <t xml:space="preserve">1.51660132408142</t>
   </si>
   <si>
     <t xml:space="preserve">1.48983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34263825416565</t>
+    <t xml:space="preserve">1.34263813495636</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709882736206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32479596138</t>
+    <t xml:space="preserve">1.32479584217072</t>
   </si>
   <si>
     <t xml:space="preserve">1.19097816944122</t>
@@ -1463,7 +1466,7 @@
     <t xml:space="preserve">1.29803240299225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20435988903046</t>
+    <t xml:space="preserve">1.20436000823975</t>
   </si>
   <si>
     <t xml:space="preserve">1.27572929859161</t>
@@ -1472,25 +1475,25 @@
     <t xml:space="preserve">1.28465056419373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30695343017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30249285697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36940169334412</t>
+    <t xml:space="preserve">1.30695354938507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30249297618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36940181255341</t>
   </si>
   <si>
     <t xml:space="preserve">1.36494112014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35602009296417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.360480427742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40508663654327</t>
+    <t xml:space="preserve">1.35601985454559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36048066616058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40508639812469</t>
   </si>
   <si>
     <t xml:space="preserve">1.44969248771667</t>
@@ -1499,7 +1502,7 @@
     <t xml:space="preserve">1.45415306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44523191452026</t>
+    <t xml:space="preserve">1.44523203372955</t>
   </si>
   <si>
     <t xml:space="preserve">1.43631064891815</t>
@@ -1508,55 +1511,55 @@
     <t xml:space="preserve">1.41846835613251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46307420730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39170479774475</t>
+    <t xml:space="preserve">1.46307408809662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39170467853546</t>
   </si>
   <si>
     <t xml:space="preserve">1.40062594413757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41400766372681</t>
+    <t xml:space="preserve">1.4140077829361</t>
   </si>
   <si>
     <t xml:space="preserve">1.38278353214264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724398612976</t>
+    <t xml:space="preserve">1.38724410533905</t>
   </si>
   <si>
     <t xml:space="preserve">1.33817768096924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35155951976776</t>
+    <t xml:space="preserve">1.35155940055847</t>
   </si>
   <si>
     <t xml:space="preserve">1.29357171058655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32925641536713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33371722698212</t>
+    <t xml:space="preserve">1.32925653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33371698856354</t>
   </si>
   <si>
     <t xml:space="preserve">1.31587469577789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37386238574982</t>
+    <t xml:space="preserve">1.37386226654053</t>
   </si>
   <si>
     <t xml:space="preserve">1.31141412258148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3203352689743</t>
+    <t xml:space="preserve">1.32033538818359</t>
   </si>
   <si>
     <t xml:space="preserve">1.28018987178802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40954720973969</t>
+    <t xml:space="preserve">1.4095470905304</t>
   </si>
   <si>
     <t xml:space="preserve">1.39616537094116</t>
@@ -1565,7 +1568,7 @@
     <t xml:space="preserve">1.4586136341095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37832272052765</t>
+    <t xml:space="preserve">1.37832295894623</t>
   </si>
   <si>
     <t xml:space="preserve">1.42292892932892</t>
@@ -1577,13 +1580,13 @@
     <t xml:space="preserve">1.27126860618591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26234757900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24896562099457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46753478050232</t>
+    <t xml:space="preserve">1.26234745979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24896574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46753466129303</t>
   </si>
   <si>
     <t xml:space="preserve">1.44077134132385</t>
@@ -1592,25 +1595,25 @@
     <t xml:space="preserve">1.48091650009155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49429821968079</t>
+    <t xml:space="preserve">1.49429833889008</t>
   </si>
   <si>
     <t xml:space="preserve">1.50321936607361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52998304367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49875891208649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51214075088501</t>
+    <t xml:space="preserve">1.52998316287994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4987587928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51214063167572</t>
   </si>
   <si>
     <t xml:space="preserve">1.48537719249725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52106189727783</t>
+    <t xml:space="preserve">1.52106177806854</t>
   </si>
   <si>
     <t xml:space="preserve">1.72178852558136</t>
@@ -1625,7 +1628,7 @@
     <t xml:space="preserve">1.81992161273956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87344872951508</t>
+    <t xml:space="preserve">1.8734484910965</t>
   </si>
   <si>
     <t xml:space="preserve">1.82884275913239</t>
@@ -1637,13 +1640,13 @@
     <t xml:space="preserve">1.78423678874969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77531564235687</t>
+    <t xml:space="preserve">1.77531576156616</t>
   </si>
   <si>
     <t xml:space="preserve">1.73517036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085506916046</t>
+    <t xml:space="preserve">1.77085518836975</t>
   </si>
   <si>
     <t xml:space="preserve">1.72624909877777</t>
@@ -1652,79 +1655,79 @@
     <t xml:space="preserve">1.73070979118347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74855220317841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79315805435181</t>
+    <t xml:space="preserve">1.74855208396912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79315793514252</t>
   </si>
   <si>
     <t xml:space="preserve">1.71732783317566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74409162998199</t>
+    <t xml:space="preserve">1.74409151077271</t>
   </si>
   <si>
     <t xml:space="preserve">1.77977633476257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81100034713745</t>
+    <t xml:space="preserve">1.81100046634674</t>
   </si>
   <si>
     <t xml:space="preserve">1.84668505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86452734470367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80207931995392</t>
+    <t xml:space="preserve">1.86452722549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80207908153534</t>
   </si>
   <si>
     <t xml:space="preserve">1.75747334957123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03402996063232</t>
+    <t xml:space="preserve">2.0340301990509</t>
   </si>
   <si>
     <t xml:space="preserve">2.0251088142395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96266067028046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9269757270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9805029630661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07863593101501</t>
+    <t xml:space="preserve">1.96266055107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92697596549988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98050284385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07863569259644</t>
   </si>
   <si>
     <t xml:space="preserve">2.1053991317749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05187225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06079363822937</t>
+    <t xml:space="preserve">2.05187249183655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06079339981079</t>
   </si>
   <si>
     <t xml:space="preserve">2.09647822380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43548345565796</t>
+    <t xml:space="preserve">2.43548321723938</t>
   </si>
   <si>
     <t xml:space="preserve">2.46224689483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39087724685669</t>
+    <t xml:space="preserve">2.39087748527527</t>
   </si>
   <si>
     <t xml:space="preserve">2.56037974357605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60498571395874</t>
+    <t xml:space="preserve">2.60498595237732</t>
   </si>
   <si>
     <t xml:space="preserve">2.65005493164062</t>
@@ -1736,10 +1739,10 @@
     <t xml:space="preserve">2.64104104042053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74019289016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78526163101196</t>
+    <t xml:space="preserve">2.74019265174866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78526139259338</t>
   </si>
   <si>
     <t xml:space="preserve">2.73117876052856</t>
@@ -1748,19 +1751,19 @@
     <t xml:space="preserve">2.90244102478027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10074472427368</t>
+    <t xml:space="preserve">3.1007444858551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99257898330688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92948222160339</t>
+    <t xml:space="preserve">2.92948246002197</t>
   </si>
   <si>
     <t xml:space="preserve">2.84835839271545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76723408699036</t>
+    <t xml:space="preserve">2.76723432540894</t>
   </si>
   <si>
     <t xml:space="preserve">2.83934450149536</t>
@@ -1769,34 +1772,31 @@
     <t xml:space="preserve">2.87539958953857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82131671905518</t>
+    <t xml:space="preserve">2.82131695747375</t>
   </si>
   <si>
     <t xml:space="preserve">2.77624773979187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72216534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55991697311401</t>
+    <t xml:space="preserve">2.72216510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55991673469543</t>
   </si>
   <si>
     <t xml:space="preserve">2.53287553787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60498595237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58695816993713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67709636688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52386140823364</t>
+    <t xml:space="preserve">2.58695793151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65906858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67709612846375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52386164665222</t>
   </si>
   <si>
     <t xml:space="preserve">2.6230137348175</t>
@@ -1805,76 +1805,76 @@
     <t xml:space="preserve">2.57794451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55090308189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51484799385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56893038749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79427528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83033084869385</t>
+    <t xml:space="preserve">2.59597229957581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5509033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51484775543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56893062591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79427552223206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83033061027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.71315121650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70413732528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74920630455017</t>
+    <t xml:space="preserve">2.70413756370544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74920654296875</t>
   </si>
   <si>
     <t xml:space="preserve">2.80328917503357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86638569831848</t>
+    <t xml:space="preserve">2.86638593673706</t>
   </si>
   <si>
     <t xml:space="preserve">3.0015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09173035621643</t>
+    <t xml:space="preserve">3.09173059463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.96553754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93849635124207</t>
+    <t xml:space="preserve">2.93849611282349</t>
   </si>
   <si>
     <t xml:space="preserve">2.81230306625366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54188919067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47879242897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63202738761902</t>
+    <t xml:space="preserve">2.54188895225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47879266738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63202714920044</t>
   </si>
   <si>
     <t xml:space="preserve">2.91145467758179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97455096244812</t>
+    <t xml:space="preserve">2.9745512008667</t>
   </si>
   <si>
     <t xml:space="preserve">2.95652365684509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01060652732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01961994171143</t>
+    <t xml:space="preserve">3.01060628890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01962018013</t>
   </si>
   <si>
     <t xml:space="preserve">2.98356509208679</t>
@@ -1904,16 +1904,16 @@
     <t xml:space="preserve">2.19035148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28048920631409</t>
+    <t xml:space="preserve">2.28048944473267</t>
   </si>
   <si>
     <t xml:space="preserve">2.41569638252258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31654453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36161351203918</t>
+    <t xml:space="preserve">2.3165442943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36161327362061</t>
   </si>
   <si>
     <t xml:space="preserve">2.50583434104919</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">2.37964105606079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37062740325928</t>
+    <t xml:space="preserve">2.37062764167786</t>
   </si>
   <si>
     <t xml:space="preserve">2.27147555351257</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">2.26246166229248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28950333595276</t>
+    <t xml:space="preserve">2.28950309753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555818557739</t>
+    <t xml:space="preserve">2.32555842399597</t>
   </si>
   <si>
     <t xml:space="preserve">2.29851698875427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34358596801758</t>
+    <t xml:space="preserve">2.343585729599</t>
   </si>
   <si>
     <t xml:space="preserve">2.21739268302917</t>
@@ -25627,7 +25627,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G872" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25679,7 +25679,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G874" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25705,7 +25705,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G875" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25757,7 +25757,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G877" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25783,7 +25783,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G878" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25809,7 +25809,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G879" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25835,7 +25835,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G880" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25861,7 +25861,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G881" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25887,7 +25887,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G882" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25965,7 +25965,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G885" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25991,7 +25991,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G886" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26017,7 +26017,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G887" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26043,7 +26043,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G888" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26095,7 +26095,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G890" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26121,7 +26121,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G891" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26147,7 +26147,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G892" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26199,7 +26199,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G894" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26225,7 +26225,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G895" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26251,7 +26251,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G896" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26277,7 +26277,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26303,7 +26303,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G898" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26329,7 +26329,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G899" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26381,7 +26381,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G901" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26407,7 +26407,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G902" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26433,7 +26433,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G903" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26459,7 +26459,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G904" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26511,7 +26511,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G906" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26537,7 +26537,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G907" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26563,7 +26563,7 @@
         <v>1.75</v>
       </c>
       <c r="G908" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26589,7 +26589,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G909" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26615,7 +26615,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G910" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26641,7 +26641,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G911" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26667,7 +26667,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G912" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26693,7 +26693,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G913" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26719,7 +26719,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G914" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26745,7 +26745,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G915" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26771,7 +26771,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G916" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26797,7 +26797,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G917" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26823,7 +26823,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G918" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26849,7 +26849,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G919" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26875,7 +26875,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G920" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26901,7 +26901,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G921" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26927,7 +26927,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G922" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26979,7 +26979,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G924" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27005,7 +27005,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G925" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27031,7 +27031,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G926" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27109,7 +27109,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G929" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27135,7 +27135,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G930" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27161,7 +27161,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G931" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27187,7 +27187,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G932" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27239,7 +27239,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G934" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27265,7 +27265,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27291,7 +27291,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G936" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27317,7 +27317,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G937" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27343,7 +27343,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G938" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27369,7 +27369,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G939" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27395,7 +27395,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G940" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27421,7 +27421,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G941" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27447,7 +27447,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G942" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27473,7 +27473,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G943" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27525,7 +27525,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G945" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27551,7 +27551,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27577,7 +27577,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G947" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27603,7 +27603,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27629,7 +27629,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27655,7 +27655,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G950" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27681,7 +27681,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G951" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27707,7 +27707,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G952" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27733,7 +27733,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G953" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27759,7 +27759,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G954" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27785,7 +27785,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G955" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27811,7 +27811,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G956" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27837,7 +27837,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G957" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27863,7 +27863,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G958" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27889,7 +27889,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27915,7 +27915,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G960" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27941,7 +27941,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G961" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27967,7 +27967,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G962" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27993,7 +27993,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G963" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28071,7 +28071,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G966" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28097,7 +28097,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G967" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28123,7 +28123,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G968" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28175,7 +28175,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G970" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28227,7 +28227,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G972" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28253,7 +28253,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G973" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28279,7 +28279,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G974" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28305,7 +28305,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G975" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28357,7 +28357,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G977" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28383,7 +28383,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G978" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28409,7 +28409,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G979" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28435,7 +28435,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G980" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28539,7 +28539,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G984" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28565,7 +28565,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G985" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28591,7 +28591,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G986" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28617,7 +28617,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G987" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28643,7 +28643,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28669,7 +28669,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G989" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28695,7 +28695,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G990" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28721,7 +28721,7 @@
         <v>1.75</v>
       </c>
       <c r="G991" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28747,7 +28747,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G992" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28773,7 +28773,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G993" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28799,7 +28799,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G994" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28903,7 +28903,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G998" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28929,7 +28929,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G999" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29007,7 +29007,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1002" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29059,7 +29059,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1004" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29085,7 +29085,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1005" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29137,7 +29137,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1007" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29163,7 +29163,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29215,7 +29215,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1010" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29241,7 +29241,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1011" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29267,7 +29267,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1012" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29293,7 +29293,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1013" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29319,7 +29319,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1014" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29345,7 +29345,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1015" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29371,7 +29371,7 @@
         <v>1.75</v>
       </c>
       <c r="G1016" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29397,7 +29397,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1017" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29423,7 +29423,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1018" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29475,7 +29475,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1020" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29501,7 +29501,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1021" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29527,7 +29527,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1022" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29553,7 +29553,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1023" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29579,7 +29579,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1024" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29605,7 +29605,7 @@
         <v>1.75</v>
       </c>
       <c r="G1025" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29631,7 +29631,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1026" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29657,7 +29657,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1027" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29683,7 +29683,7 @@
         <v>1.75</v>
       </c>
       <c r="G1028" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29709,7 +29709,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1029" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29735,7 +29735,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1030" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29761,7 +29761,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1031" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29787,7 +29787,7 @@
         <v>1.75</v>
       </c>
       <c r="G1032" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29813,7 +29813,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1033" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29839,7 +29839,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1034" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29865,7 +29865,7 @@
         <v>1.75</v>
       </c>
       <c r="G1035" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29891,7 +29891,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29917,7 +29917,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1037" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29943,7 +29943,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1038" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29969,7 +29969,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1039" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29995,7 +29995,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1040" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30021,7 +30021,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1041" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30047,7 +30047,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1042" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30073,7 +30073,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1043" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30099,7 +30099,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1044" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30125,7 +30125,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1045" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30151,7 +30151,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1046" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30177,7 +30177,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1047" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30203,7 +30203,7 @@
         <v>1.75</v>
       </c>
       <c r="G1048" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30229,7 +30229,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1049" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30255,7 +30255,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1050" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30281,7 +30281,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1051" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30307,7 +30307,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30333,7 +30333,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1053" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30359,7 +30359,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1054" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30385,7 +30385,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1055" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30411,7 +30411,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1056" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30437,7 +30437,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30463,7 +30463,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1058" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30489,7 +30489,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1059" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30515,7 +30515,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1060" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30541,7 +30541,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30567,7 +30567,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1062" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30593,7 +30593,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1063" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30619,7 +30619,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1064" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30645,7 +30645,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1065" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30671,7 +30671,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1066" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30697,7 +30697,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30723,7 +30723,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30749,7 +30749,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1069" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30775,7 +30775,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1070" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30801,7 +30801,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1071" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30827,7 +30827,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1072" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30853,7 +30853,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1073" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30879,7 +30879,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1074" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30905,7 +30905,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1075" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30931,7 +30931,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1076" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30957,7 +30957,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1077" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30983,7 +30983,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1078" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31009,7 +31009,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1079" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31035,7 +31035,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1080" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31061,7 +31061,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1081" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31087,7 +31087,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1082" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31113,7 +31113,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1083" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31139,7 +31139,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1084" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31165,7 +31165,7 @@
         <v>1.625</v>
       </c>
       <c r="G1085" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31191,7 +31191,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1086" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31217,7 +31217,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1087" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31243,7 +31243,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1088" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31269,7 +31269,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1089" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31295,7 +31295,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1090" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31321,7 +31321,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1091" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31347,7 +31347,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1092" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31373,7 +31373,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1093" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31399,7 +31399,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1094" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31425,7 +31425,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1095" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31451,7 +31451,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1096" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31477,7 +31477,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1097" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31503,7 +31503,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31529,7 +31529,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1099" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31555,7 +31555,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1100" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31581,7 +31581,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1101" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31607,7 +31607,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1102" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31633,7 +31633,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1103" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31659,7 +31659,7 @@
         <v>1.5</v>
       </c>
       <c r="G1104" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31685,7 +31685,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1105" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31711,7 +31711,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1106" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31737,7 +31737,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1107" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31763,7 +31763,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1108" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31789,7 +31789,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1109" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31815,7 +31815,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1110" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31841,7 +31841,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1111" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31867,7 +31867,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1112" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31893,7 +31893,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1113" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31919,7 +31919,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1114" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31945,7 +31945,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1115" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31971,7 +31971,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1116" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31997,7 +31997,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1117" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32023,7 +32023,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1118" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32049,7 +32049,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1119" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32075,7 +32075,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1120" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32101,7 +32101,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1121" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32127,7 +32127,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1122" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32153,7 +32153,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1123" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32179,7 +32179,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1124" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32205,7 +32205,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1125" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32231,7 +32231,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1126" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32257,7 +32257,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1127" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32283,7 +32283,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1128" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32309,7 +32309,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1129" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32335,7 +32335,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1130" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32361,7 +32361,7 @@
         <v>1.5</v>
       </c>
       <c r="G1131" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32387,7 +32387,7 @@
         <v>1.5</v>
       </c>
       <c r="G1132" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32413,7 +32413,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1133" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32439,7 +32439,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1134" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32465,7 +32465,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1135" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32491,7 +32491,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1136" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32517,7 +32517,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1137" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32543,7 +32543,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1138" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32569,7 +32569,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1139" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32595,7 +32595,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1140" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32621,7 +32621,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1141" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32647,7 +32647,7 @@
         <v>1.5</v>
       </c>
       <c r="G1142" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32673,7 +32673,7 @@
         <v>1.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32699,7 +32699,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1144" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32725,7 +32725,7 @@
         <v>1.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32751,7 +32751,7 @@
         <v>1.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32777,7 +32777,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1147" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32803,7 +32803,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32829,7 +32829,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1149" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32855,7 +32855,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1150" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32881,7 +32881,7 @@
         <v>1.5</v>
       </c>
       <c r="G1151" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32907,7 +32907,7 @@
         <v>1.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32933,7 +32933,7 @@
         <v>1.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32959,7 +32959,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1154" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32985,7 +32985,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33011,7 +33011,7 @@
         <v>1.5</v>
       </c>
       <c r="G1156" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33037,7 +33037,7 @@
         <v>1.5</v>
       </c>
       <c r="G1157" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33063,7 +33063,7 @@
         <v>1.5</v>
       </c>
       <c r="G1158" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33089,7 +33089,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1159" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33115,7 +33115,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1160" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33141,7 +33141,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1161" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33167,7 +33167,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33193,7 +33193,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1163" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33219,7 +33219,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1164" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33245,7 +33245,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1165" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33271,7 +33271,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33297,7 +33297,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1167" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33323,7 +33323,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33349,7 +33349,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1169" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33375,7 +33375,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1170" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33401,7 +33401,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33427,7 +33427,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1172" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33453,7 +33453,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1173" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33479,7 +33479,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1174" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33505,7 +33505,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1175" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33531,7 +33531,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1176" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33557,7 +33557,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1177" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33583,7 +33583,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33609,7 +33609,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1179" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33635,7 +33635,7 @@
         <v>1.5</v>
       </c>
       <c r="G1180" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33661,7 +33661,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1181" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33687,7 +33687,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1182" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33713,7 +33713,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1183" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33739,7 +33739,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1184" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33765,7 +33765,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33791,7 +33791,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1186" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33817,7 +33817,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1187" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33843,7 +33843,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1188" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33869,7 +33869,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1189" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33895,7 +33895,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1190" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33921,7 +33921,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1191" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33947,7 +33947,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1192" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33973,7 +33973,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1193" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33999,7 +33999,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1194" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34025,7 +34025,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1195" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34051,7 +34051,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1196" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34077,7 +34077,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1197" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34103,7 +34103,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1198" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34129,7 +34129,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1199" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34155,7 +34155,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1200" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34181,7 +34181,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1201" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34207,7 +34207,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1202" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34233,7 +34233,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1203" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34259,7 +34259,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34285,7 +34285,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34311,7 +34311,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34337,7 +34337,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1207" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34363,7 +34363,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1208" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34389,7 +34389,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34415,7 +34415,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1210" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34441,7 +34441,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34467,7 +34467,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34493,7 +34493,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1213" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34519,7 +34519,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1214" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34545,7 +34545,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1215" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34571,7 +34571,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34597,7 +34597,7 @@
         <v>1.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34623,7 +34623,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1218" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34649,7 +34649,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1219" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34675,7 +34675,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1220" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34701,7 +34701,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1221" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34727,7 +34727,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1222" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34753,7 +34753,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1223" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34779,7 +34779,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34805,7 +34805,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1225" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34831,7 +34831,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1226" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34857,7 +34857,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1227" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34883,7 +34883,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1228" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34909,7 +34909,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1229" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34935,7 +34935,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1230" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34961,7 +34961,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1231" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34987,7 +34987,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35013,7 +35013,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1233" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35039,7 +35039,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1234" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35065,7 +35065,7 @@
         <v>1.5</v>
       </c>
       <c r="G1235" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35091,7 +35091,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1236" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35117,7 +35117,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35143,7 +35143,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35169,7 +35169,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1239" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35195,7 +35195,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35221,7 +35221,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35247,7 +35247,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1242" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35273,7 +35273,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35299,7 +35299,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1244" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35325,7 +35325,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35351,7 +35351,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1246" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35377,7 +35377,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1247" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35403,7 +35403,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35429,7 +35429,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1249" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35455,7 +35455,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1250" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35481,7 +35481,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1251" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35507,7 +35507,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35533,7 +35533,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35559,7 +35559,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1254" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35585,7 +35585,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1255" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35611,7 +35611,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1256" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35637,7 +35637,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1257" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35663,7 +35663,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1258" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35689,7 +35689,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1259" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35715,7 +35715,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1260" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35741,7 +35741,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1261" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35767,7 +35767,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1262" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35793,7 +35793,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1263" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35819,7 +35819,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1264" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35845,7 +35845,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1265" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35871,7 +35871,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1266" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35897,7 +35897,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35923,7 +35923,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35949,7 +35949,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1269" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35975,7 +35975,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36001,7 +36001,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1271" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36027,7 +36027,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1272" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36053,7 +36053,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1273" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36079,7 +36079,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1274" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36105,7 +36105,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1275" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36131,7 +36131,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36157,7 +36157,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1277" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36183,7 +36183,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36209,7 +36209,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1279" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36235,7 +36235,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1280" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36261,7 +36261,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1281" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36287,7 +36287,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1282" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36313,7 +36313,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1283" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36339,7 +36339,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1284" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36365,7 +36365,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1285" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36391,7 +36391,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1286" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36417,7 +36417,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1287" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36443,7 +36443,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36469,7 +36469,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1289" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36495,7 +36495,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1290" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36521,7 +36521,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1291" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36547,7 +36547,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1292" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36573,7 +36573,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1293" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36599,7 +36599,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1294" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36625,7 +36625,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1295" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36651,7 +36651,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1296" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36677,7 +36677,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1297" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36703,7 +36703,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1298" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36729,7 +36729,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1299" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36781,7 +36781,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1301" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36807,7 +36807,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1302" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36833,7 +36833,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1303" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36859,7 +36859,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1304" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36885,7 +36885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1305" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36911,7 +36911,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1306" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36937,7 +36937,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1307" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36963,7 +36963,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1308" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36989,7 +36989,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1309" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37015,7 +37015,7 @@
         <v>2</v>
       </c>
       <c r="G1310" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37041,7 +37041,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37067,7 +37067,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1312" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37093,7 +37093,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1313" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -37119,7 +37119,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1314" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37145,7 +37145,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1315" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37171,7 +37171,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1316" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37197,7 +37197,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1317" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37223,7 +37223,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1318" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37249,7 +37249,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37275,7 +37275,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37301,7 +37301,7 @@
         <v>2</v>
       </c>
       <c r="G1321" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37327,7 +37327,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1322" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37353,7 +37353,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1323" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37379,7 +37379,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1324" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37405,7 +37405,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1325" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37431,7 +37431,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1326" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37457,7 +37457,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1327" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37483,7 +37483,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1328" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37509,7 +37509,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1329" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37535,7 +37535,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1330" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37561,7 +37561,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1331" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37587,7 +37587,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1332" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37613,7 +37613,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1333" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37639,7 +37639,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1334" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37665,7 +37665,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37691,7 +37691,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1336" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37717,7 +37717,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1337" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37743,7 +37743,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1338" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37769,7 +37769,7 @@
         <v>2</v>
       </c>
       <c r="G1339" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37795,7 +37795,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1340" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37821,7 +37821,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1341" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37847,7 +37847,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1342" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37873,7 +37873,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1343" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37899,7 +37899,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37925,7 +37925,7 @@
         <v>2</v>
       </c>
       <c r="G1345" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37951,7 +37951,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1346" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37977,7 +37977,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38003,7 +38003,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38029,7 +38029,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -38055,7 +38055,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1350" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -38081,7 +38081,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1351" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -38107,7 +38107,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1352" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -38133,7 +38133,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1353" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -38159,7 +38159,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1354" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -38185,7 +38185,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1355" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -38211,7 +38211,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1356" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -38237,7 +38237,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1357" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38263,7 +38263,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1358" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38289,7 +38289,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1359" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38315,7 +38315,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1360" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38341,7 +38341,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1361" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38367,7 +38367,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1362" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38393,7 +38393,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1363" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38419,7 +38419,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1364" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38445,7 +38445,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1365" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38471,7 +38471,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1366" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38497,7 +38497,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38523,7 +38523,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38549,7 +38549,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1369" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38575,7 +38575,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1370" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38601,7 +38601,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1371" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38627,7 +38627,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38653,7 +38653,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1373" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38679,7 +38679,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1374" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38705,7 +38705,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1375" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38731,7 +38731,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1376" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38757,7 +38757,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1377" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38783,7 +38783,7 @@
         <v>3.25</v>
       </c>
       <c r="G1378" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38809,7 +38809,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1379" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38835,7 +38835,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1380" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38861,7 +38861,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1381" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38887,7 +38887,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38913,7 +38913,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38939,7 +38939,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1384" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38965,7 +38965,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1385" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38991,7 +38991,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1386" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -39017,7 +39017,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1387" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -39043,7 +39043,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1388" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -39069,7 +39069,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1389" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39095,7 +39095,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1390" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -39199,7 +39199,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1394" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -39225,7 +39225,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1395" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39303,7 +39303,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1398" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39329,7 +39329,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1399" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39355,7 +39355,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1400" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39381,7 +39381,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39485,7 +39485,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1405" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39797,7 +39797,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1417" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39823,7 +39823,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1418" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39901,7 +39901,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1421" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39927,7 +39927,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1422" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39979,7 +39979,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1424" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -40005,7 +40005,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1425" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -40057,7 +40057,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1427" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -40083,7 +40083,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1428" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -40161,7 +40161,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1431" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -40213,7 +40213,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1433" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -40239,7 +40239,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1434" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40317,7 +40317,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1437" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40343,7 +40343,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40395,7 +40395,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40421,7 +40421,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1441" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40447,7 +40447,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1442" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40473,7 +40473,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1443" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40499,7 +40499,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1444" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40525,7 +40525,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1445" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40551,7 +40551,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1446" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40759,7 +40759,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1454" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40837,7 +40837,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40863,7 +40863,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1458" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40889,7 +40889,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1459" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41227,7 +41227,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1472" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41253,7 +41253,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41305,7 +41305,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1475" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41357,7 +41357,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1477" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41409,7 +41409,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1479" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41669,7 +41669,7 @@
         <v>3.25</v>
       </c>
       <c r="G1489" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41695,7 +41695,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1490" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41903,7 +41903,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41981,7 +41981,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1501" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -42085,7 +42085,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1505" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -42111,7 +42111,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -42189,7 +42189,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -42215,7 +42215,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1510" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -42241,7 +42241,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1511" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42267,7 +42267,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1512" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42293,7 +42293,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1513" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42319,7 +42319,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1514" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42345,7 +42345,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1515" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42397,7 +42397,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42475,7 +42475,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1520" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42501,7 +42501,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42553,7 +42553,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1523" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42579,7 +42579,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42605,7 +42605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42657,7 +42657,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1527" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42761,7 +42761,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1531" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42865,7 +42865,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1535" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42943,7 +42943,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1538" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42969,7 +42969,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1539" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42995,7 +42995,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1540" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43047,7 +43047,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1542" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43125,7 +43125,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1545" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -43151,7 +43151,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1546" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -43385,7 +43385,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1555" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43411,7 +43411,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1556" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43463,7 +43463,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1558" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43489,7 +43489,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1559" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43567,7 +43567,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1562" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43697,7 +43697,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43723,7 +43723,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1568" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44009,7 +44009,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -44295,7 +44295,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1590" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44347,7 +44347,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -70525,9 +70525,11 @@
       <c r="E2599" t="n">
         <v>1.94500005245209</v>
       </c>
-      <c r="F2599"/>
+      <c r="F2599" t="n">
+        <v>1.94500005245209</v>
+      </c>
       <c r="G2599" t="s">
-        <v>870</v>
+        <v>845</v>
       </c>
       <c r="H2599" t="s">
         <v>9</v>
@@ -70535,27 +70537,51 @@
     </row>
     <row r="2600">
       <c r="A2600" s="1" t="n">
-        <v>46105.6356134259</v>
+        <v>46106.3333333333</v>
       </c>
       <c r="B2600" t="n">
-        <v>13326</v>
+        <v>9750</v>
       </c>
       <c r="C2600" t="n">
-        <v>1.9650000333786</v>
+        <v>1.97000002861023</v>
       </c>
       <c r="D2600" t="n">
-        <v>1.91999995708466</v>
+        <v>1.92999994754791</v>
       </c>
       <c r="E2600" t="n">
-        <v>1.94500005245209</v>
-      </c>
-      <c r="F2600" t="n">
-        <v>1.94500005245209</v>
-      </c>
+        <v>1.93499994277954</v>
+      </c>
+      <c r="F2600"/>
       <c r="G2600" t="s">
-        <v>845</v>
+        <v>870</v>
       </c>
       <c r="H2600" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" s="1" t="n">
+        <v>46106.6477430556</v>
+      </c>
+      <c r="B2601" t="n">
+        <v>9750</v>
+      </c>
+      <c r="C2601" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D2601" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="E2601" t="n">
+        <v>1.93499994277954</v>
+      </c>
+      <c r="F2601" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="G2601" t="s">
+        <v>847</v>
+      </c>
+      <c r="H2601" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,85 +38,85 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034141540527</t>
+    <t xml:space="preserve">1.75034153461456</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69254720211029</t>
+    <t xml:space="preserve">1.74538779258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69254732131958</t>
   </si>
   <si>
     <t xml:space="preserve">1.70245504379272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.684290766716</t>
+    <t xml:space="preserve">1.68429100513458</t>
   </si>
   <si>
     <t xml:space="preserve">1.6760345697403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66612684726715</t>
+    <t xml:space="preserve">1.66612708568573</t>
   </si>
   <si>
     <t xml:space="preserve">1.63888132572174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61163520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59347128868103</t>
+    <t xml:space="preserve">1.61163544654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59347140789032</t>
   </si>
   <si>
     <t xml:space="preserve">1.48613905906677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59264588356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59182024002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58604061603546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172784328461</t>
+    <t xml:space="preserve">1.5926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59182012081146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58604073524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172772407532</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521497249603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56044626235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51255929470062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5398051738739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56539988517761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53567719459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45311379432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50595438480377</t>
+    <t xml:space="preserve">1.56044614315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5125595331192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53980541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5654000043869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53567707538605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45311391353607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50595426559448</t>
   </si>
   <si>
     <t xml:space="preserve">1.46137011051178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4423805475235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51833856105804</t>
+    <t xml:space="preserve">1.44238042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51833868026733</t>
   </si>
   <si>
     <t xml:space="preserve">1.65126574039459</t>
@@ -131,85 +131,85 @@
     <t xml:space="preserve">1.64300942420959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6372298002243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64218378067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63970685005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66777837276459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60503017902374</t>
+    <t xml:space="preserve">1.63723027706146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64218366146088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63970673084259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6677782535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60503041744232</t>
   </si>
   <si>
     <t xml:space="preserve">1.5984251499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56870245933533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053237438202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227617740631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60255336761475</t>
+    <t xml:space="preserve">1.56870234012604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6322762966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60255324840546</t>
   </si>
   <si>
     <t xml:space="preserve">1.57283067703247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58934319019318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58438956737518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56787693500519</t>
+    <t xml:space="preserve">1.58934307098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58438968658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5678768157959</t>
   </si>
   <si>
     <t xml:space="preserve">1.55714356899261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5340256690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54310762882233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466663837433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5596204996109</t>
+    <t xml:space="preserve">1.53402578830719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54310786724091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466675758362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962038040161</t>
   </si>
   <si>
     <t xml:space="preserve">1.55218982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5505383014679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50265169143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696458339691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861622810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237462043762</t>
+    <t xml:space="preserve">1.55053853988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50265181064606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696482181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237450122833</t>
   </si>
   <si>
     <t xml:space="preserve">1.49026715755463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51503610610962</t>
+    <t xml:space="preserve">1.51503622531891</t>
   </si>
   <si>
     <t xml:space="preserve">1.48779034614563</t>
@@ -224,58 +224,58 @@
     <t xml:space="preserve">1.5010005235672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49439537525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48366224765778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45971882343292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45971870422363</t>
+    <t xml:space="preserve">1.49439549446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48366212844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45971894264221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4597190618515</t>
   </si>
   <si>
     <t xml:space="preserve">1.45299983024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46223866939545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43284249305725</t>
+    <t xml:space="preserve">1.46223855018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43284261226654</t>
   </si>
   <si>
     <t xml:space="preserve">1.43536221981049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43200254440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42612338066101</t>
+    <t xml:space="preserve">1.43200290203094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4261234998703</t>
   </si>
   <si>
     <t xml:space="preserve">1.41100573539734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44040167331696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43620216846466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44292140007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44880044460297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47819626331329</t>
+    <t xml:space="preserve">1.44040143489838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43620204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44292116165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44880032539368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47819638252258</t>
   </si>
   <si>
     <t xml:space="preserve">1.44460093975067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42360401153564</t>
+    <t xml:space="preserve">1.42360389232635</t>
   </si>
   <si>
     <t xml:space="preserve">1.43032288551331</t>
@@ -287,46 +287,46 @@
     <t xml:space="preserve">1.40260660648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40848588943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37825000286102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42444384098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41604483127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46979761123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42780327796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192411422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47567665576935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44796049594879</t>
+    <t xml:space="preserve">1.4084860086441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37825012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42444360256195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41604471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4697972536087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42780315876007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192399501801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47567677497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44796061515808</t>
   </si>
   <si>
     <t xml:space="preserve">1.47735631465912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43368244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45803892612457</t>
+    <t xml:space="preserve">1.43368256092072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45803880691528</t>
   </si>
   <si>
     <t xml:space="preserve">1.4521598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48491537570953</t>
+    <t xml:space="preserve">1.48491549491882</t>
   </si>
   <si>
     <t xml:space="preserve">1.46391832828522</t>
@@ -335,22 +335,22 @@
     <t xml:space="preserve">1.46643805503845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46895742416382</t>
+    <t xml:space="preserve">1.46895754337311</t>
   </si>
   <si>
     <t xml:space="preserve">1.48575532436371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45887911319733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4563592672348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45719909667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48827493190765</t>
+    <t xml:space="preserve">1.45887887477875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45635938644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45719921588898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48827481269836</t>
   </si>
   <si>
     <t xml:space="preserve">1.43956160545349</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">1.47399687767029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46727776527405</t>
+    <t xml:space="preserve">1.46727764606476</t>
   </si>
   <si>
     <t xml:space="preserve">1.49835360050201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50927209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50339269638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4949939250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48743498325348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51011192798615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4991934299469</t>
+    <t xml:space="preserve">1.50927197933197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5033928155899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49499404430389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48743510246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51011180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49919354915619</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179158687592</t>
@@ -389,46 +389,46 @@
     <t xml:space="preserve">1.45048010349274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44628059864044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43872165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5000331401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48071587085724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4815559387207</t>
+    <t xml:space="preserve">1.44628071784973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43872177600861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50003325939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48071610927582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48155581951141</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095187664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49583399295807</t>
+    <t xml:space="preserve">1.49583375453949</t>
   </si>
   <si>
     <t xml:space="preserve">1.50759220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49667358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47231721878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49331438541412</t>
+    <t xml:space="preserve">1.49667382240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47231709957123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49331426620483</t>
   </si>
   <si>
     <t xml:space="preserve">1.47147727012634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50087320804596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52774941921234</t>
+    <t xml:space="preserve">1.50087296962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52774965763092</t>
   </si>
   <si>
     <t xml:space="preserve">1.53194892406464</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">1.50423264503479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5126314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54454696178436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54538714885712</t>
+    <t xml:space="preserve">1.51263165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54454708099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54538726806641</t>
   </si>
   <si>
     <t xml:space="preserve">1.55294597148895</t>
@@ -458,25 +458,25 @@
     <t xml:space="preserve">1.52019047737122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50843214988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59578013420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53446865081787</t>
+    <t xml:space="preserve">1.50843226909637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59578001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53446853160858</t>
   </si>
   <si>
     <t xml:space="preserve">1.56050491333008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53026926517487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53110885620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55126631259918</t>
+    <t xml:space="preserve">1.53026914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53110897541046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55126619338989</t>
   </si>
   <si>
     <t xml:space="preserve">1.55210626125336</t>
@@ -491,34 +491,34 @@
     <t xml:space="preserve">1.56218469142914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56974363327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57058358192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60333919525146</t>
+    <t xml:space="preserve">1.56974375247955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57058346271515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60333907604218</t>
   </si>
   <si>
     <t xml:space="preserve">1.54958641529083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55798530578613</t>
+    <t xml:space="preserve">1.55798542499542</t>
   </si>
   <si>
     <t xml:space="preserve">1.57142353057861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56470453739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6108980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61173796653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60417890548706</t>
+    <t xml:space="preserve">1.56470441818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61089789867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61173820495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60417878627777</t>
   </si>
   <si>
     <t xml:space="preserve">1.62517595291138</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">1.61257767677307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59326028823853</t>
+    <t xml:space="preserve">1.59326040744781</t>
   </si>
   <si>
     <t xml:space="preserve">1.58822119235992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60753858089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63105523586273</t>
+    <t xml:space="preserve">1.60753846168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63105535507202</t>
   </si>
   <si>
     <t xml:space="preserve">1.61425757408142</t>
@@ -548,70 +548,70 @@
     <t xml:space="preserve">1.71504366397858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77215564250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76543653011322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7536780834198</t>
+    <t xml:space="preserve">1.77215588092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7654367685318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75367844104767</t>
   </si>
   <si>
     <t xml:space="preserve">1.72512233257294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74527955055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72176265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70664501190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73856043815613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69992566108704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67892861366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69656622409821</t>
+    <t xml:space="preserve">1.74527943134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72176277637482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70664489269257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73856055736542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69992554187775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67892873287201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69656610488892</t>
   </si>
   <si>
     <t xml:space="preserve">1.69320678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70496499538422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77383553981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75871777534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68984735012054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69152677059174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66801011562347</t>
+    <t xml:space="preserve">1.70496511459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77383542060852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75871789455414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68984711170197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69152700901031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66800999641418</t>
   </si>
   <si>
     <t xml:space="preserve">1.68816745281219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71336376667023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73184144496918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535786151886</t>
+    <t xml:space="preserve">1.71336388587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73184156417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535798072815</t>
   </si>
   <si>
     <t xml:space="preserve">1.7100043296814</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">1.73016154766083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74695909023285</t>
+    <t xml:space="preserve">1.74695920944214</t>
   </si>
   <si>
     <t xml:space="preserve">1.77047610282898</t>
@@ -632,49 +632,49 @@
     <t xml:space="preserve">1.76375687122345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75031900405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78895342350006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7402400970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76207745075226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73352098464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903209209442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78055441379547</t>
+    <t xml:space="preserve">1.75031876564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78895354270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74024033546448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76207733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73352110385895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78055453300476</t>
   </si>
   <si>
     <t xml:space="preserve">1.82254886627197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86958241462708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8645430803299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84774553775787</t>
+    <t xml:space="preserve">1.86958253383636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86454284191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84774541854858</t>
   </si>
   <si>
     <t xml:space="preserve">1.78391420841217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90480971336365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98488688468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34267735481262</t>
+    <t xml:space="preserve">1.90480959415436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98488640785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34267711639404</t>
   </si>
   <si>
     <t xml:space="preserve">2.35119605064392</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">2.180819272995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36482620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32223224639893</t>
+    <t xml:space="preserve">2.364825963974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32223200798035</t>
   </si>
   <si>
     <t xml:space="preserve">2.34608483314514</t>
@@ -701,40 +701,40 @@
     <t xml:space="preserve">2.24897003173828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20296859741211</t>
+    <t xml:space="preserve">2.20296835899353</t>
   </si>
   <si>
     <t xml:space="preserve">2.14163279533386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07007479667664</t>
+    <t xml:space="preserve">2.07007503509521</t>
   </si>
   <si>
     <t xml:space="preserve">2.01896166801453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95932996273041</t>
+    <t xml:space="preserve">1.95932984352112</t>
   </si>
   <si>
     <t xml:space="preserve">2.01044273376465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0649631023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00192427635193</t>
+    <t xml:space="preserve">2.06496334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00192403793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.02407336235046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06155633926392</t>
+    <t xml:space="preserve">2.06155610084534</t>
   </si>
   <si>
     <t xml:space="preserve">2.04451847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06837105751038</t>
+    <t xml:space="preserve">2.0683708190918</t>
   </si>
   <si>
     <t xml:space="preserve">2.05303716659546</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">1.97636759281158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97125649452209</t>
+    <t xml:space="preserve">1.97125625610352</t>
   </si>
   <si>
     <t xml:space="preserve">1.97466421127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95081102848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93888509273529</t>
+    <t xml:space="preserve">1.95081126689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93888485431671</t>
   </si>
   <si>
     <t xml:space="preserve">1.92525482177734</t>
@@ -770,34 +770,34 @@
     <t xml:space="preserve">1.92695832252502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94229257106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95762646198273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718099594116</t>
+    <t xml:space="preserve">1.94229233264923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95762622356415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718123435974</t>
   </si>
   <si>
     <t xml:space="preserve">1.92866218090057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97295987606049</t>
+    <t xml:space="preserve">1.97296011447906</t>
   </si>
   <si>
     <t xml:space="preserve">2.00703549385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01555418968201</t>
+    <t xml:space="preserve">2.01555442810059</t>
   </si>
   <si>
     <t xml:space="preserve">1.98829400539398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93206989765167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673564910889</t>
+    <t xml:space="preserve">1.93206965923309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673576831818</t>
   </si>
   <si>
     <t xml:space="preserve">1.91332828998566</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">1.90821719169617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93377351760864</t>
+    <t xml:space="preserve">1.93377327919006</t>
   </si>
   <si>
     <t xml:space="preserve">1.94058859348297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13822555541992</t>
+    <t xml:space="preserve">2.13822531700134</t>
   </si>
   <si>
     <t xml:space="preserve">2.2557852268219</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">2.22341370582581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3597149848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27452635765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41593909263611</t>
+    <t xml:space="preserve">2.35971474647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27452659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41593885421753</t>
   </si>
   <si>
     <t xml:space="preserve">2.41253161430359</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">2.36823391914368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30860185623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31200933456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31541728973389</t>
+    <t xml:space="preserve">2.30860161781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31200957298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31541705131531</t>
   </si>
   <si>
     <t xml:space="preserve">2.28986024856567</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">2.42445802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41423511505127</t>
+    <t xml:space="preserve">2.41423535346985</t>
   </si>
   <si>
     <t xml:space="preserve">2.36993765830994</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">2.39719748497009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35801100730896</t>
+    <t xml:space="preserve">2.35801076889038</t>
   </si>
   <si>
     <t xml:space="preserve">2.30519437789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32052826881409</t>
+    <t xml:space="preserve">2.32052803039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.32904696464539</t>
@@ -875,22 +875,22 @@
     <t xml:space="preserve">2.31882429122925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3477885723114</t>
+    <t xml:space="preserve">2.34778833389282</t>
   </si>
   <si>
     <t xml:space="preserve">2.36312246322632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3443808555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32563948631287</t>
+    <t xml:space="preserve">2.34438109397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">2.3392698764801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36652994155884</t>
+    <t xml:space="preserve">2.36652970314026</t>
   </si>
   <si>
     <t xml:space="preserve">2.3767523765564</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">2.27111887931824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25408148765564</t>
+    <t xml:space="preserve">2.25408124923706</t>
   </si>
   <si>
     <t xml:space="preserve">2.09392738342285</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">2.15696692466736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10585379600525</t>
+    <t xml:space="preserve">2.10585355758667</t>
   </si>
   <si>
     <t xml:space="preserve">2.10415005683899</t>
@@ -935,16 +935,16 @@
     <t xml:space="preserve">2.28815698623657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21659874916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23874735832214</t>
+    <t xml:space="preserve">2.21659851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23874759674072</t>
   </si>
   <si>
     <t xml:space="preserve">2.21489453315735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25748872756958</t>
+    <t xml:space="preserve">2.25748896598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.24556255340576</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">2.22511720657349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23363590240479</t>
+    <t xml:space="preserve">2.23363614082336</t>
   </si>
   <si>
     <t xml:space="preserve">2.23022866249084</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">2.41934657096863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53009152412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57268524169922</t>
+    <t xml:space="preserve">2.53009176254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5726854801178</t>
   </si>
   <si>
     <t xml:space="preserve">2.54712915420532</t>
@@ -995,43 +995,43 @@
     <t xml:space="preserve">2.50453495979309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47045946121216</t>
+    <t xml:space="preserve">2.47045969963074</t>
   </si>
   <si>
     <t xml:space="preserve">2.46194100379944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38527154922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41082763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30008292198181</t>
+    <t xml:space="preserve">2.38527131080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41082787513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30008339881897</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342206954956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60676097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61527967453003</t>
+    <t xml:space="preserve">2.60676074028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61527991294861</t>
   </si>
   <si>
     <t xml:space="preserve">2.6493546962738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6578733921051</t>
+    <t xml:space="preserve">2.65787363052368</t>
   </si>
   <si>
     <t xml:space="preserve">2.43638443946838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52157282829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53861045837402</t>
+    <t xml:space="preserve">2.52157258987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53861021995544</t>
   </si>
   <si>
     <t xml:space="preserve">2.55564785003662</t>
@@ -1040,28 +1040,28 @@
     <t xml:space="preserve">2.48749732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44490337371826</t>
+    <t xml:space="preserve">2.44490313529968</t>
   </si>
   <si>
     <t xml:space="preserve">2.26600766181946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1467444896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671034812927</t>
+    <t xml:space="preserve">2.14674425125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671010971069</t>
   </si>
   <si>
     <t xml:space="preserve">2.1185667514801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17066216468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29221987724304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24880623817444</t>
+    <t xml:space="preserve">2.17066240310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29221963882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24880599975586</t>
   </si>
   <si>
     <t xml:space="preserve">2.2661714553833</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.3009021282196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30958485603333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32695007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28353691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21407556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17934513092041</t>
+    <t xml:space="preserve">2.3095850944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32695031166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28353714942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21407580375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17934489250183</t>
   </si>
   <si>
     <t xml:space="preserve">2.20539307594299</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">2.10120153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04042267799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01437497138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05778813362122</t>
+    <t xml:space="preserve">2.0404224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01437473297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05778789520264</t>
   </si>
   <si>
     <t xml:space="preserve">2.06647062301636</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">1.97964406013489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9622790813446</t>
+    <t xml:space="preserve">1.96227884292603</t>
   </si>
   <si>
     <t xml:space="preserve">2.02305746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04910516738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03174018859863</t>
+    <t xml:space="preserve">2.0491054058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03173995018005</t>
   </si>
   <si>
     <t xml:space="preserve">1.93623089790344</t>
@@ -1172,25 +1172,25 @@
     <t xml:space="preserve">1.81467366218567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77994310855865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71916472911835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69311690330505</t>
+    <t xml:space="preserve">1.77994322776794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71916460990906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69311678409576</t>
   </si>
   <si>
     <t xml:space="preserve">1.62799680233002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63233816623688</t>
+    <t xml:space="preserve">1.63233804702759</t>
   </si>
   <si>
     <t xml:space="preserve">1.67575132846832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68443417549133</t>
+    <t xml:space="preserve">1.68443405628204</t>
   </si>
   <si>
     <t xml:space="preserve">1.71048200130463</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">1.69745802879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64536213874817</t>
+    <t xml:space="preserve">1.64536201953888</t>
   </si>
   <si>
     <t xml:space="preserve">1.59760761260986</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">1.60629022121429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6193140745163</t>
+    <t xml:space="preserve">1.61931419372559</t>
   </si>
   <si>
     <t xml:space="preserve">1.61497294902802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63667953014374</t>
+    <t xml:space="preserve">1.63667941093445</t>
   </si>
   <si>
     <t xml:space="preserve">1.64970350265503</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">1.65838611125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7017993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67141008377075</t>
+    <t xml:space="preserve">1.70179951190948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67140996456146</t>
   </si>
   <si>
     <t xml:space="preserve">1.6670686006546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5715594291687</t>
+    <t xml:space="preserve">1.57155966758728</t>
   </si>
   <si>
     <t xml:space="preserve">1.52814638614655</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">1.72784733772278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76257789134979</t>
+    <t xml:space="preserve">1.7625777721405</t>
   </si>
   <si>
     <t xml:space="preserve">1.75389528274536</t>
@@ -1274,37 +1274,37 @@
     <t xml:space="preserve">1.78862583637238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80599093437195</t>
+    <t xml:space="preserve">1.80599105358124</t>
   </si>
   <si>
     <t xml:space="preserve">1.77126038074493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74521243572235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83203887939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79730832576752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84072160720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86676979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91018271446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359599590302</t>
+    <t xml:space="preserve">1.74521255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83203899860382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79730844497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84072184562683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8667699098587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91018319129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359635353088</t>
   </si>
   <si>
     <t xml:space="preserve">1.94491362571716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98832678794861</t>
+    <t xml:space="preserve">1.98832654953003</t>
   </si>
   <si>
     <t xml:space="preserve">1.97096157073975</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">1.91886568069458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92754817008972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85808706283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84940433502197</t>
+    <t xml:space="preserve">1.9275484085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8580869436264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84940445423126</t>
   </si>
   <si>
     <t xml:space="preserve">1.88413500785828</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">1.6013525724411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61027371883392</t>
+    <t xml:space="preserve">1.61027359962463</t>
   </si>
   <si>
     <t xml:space="preserve">1.63703727722168</t>
@@ -1346,6 +1346,9 @@
     <t xml:space="preserve">1.65487957000732</t>
   </si>
   <si>
+    <t xml:space="preserve">1.62365555763245</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.6459584236145</t>
   </si>
   <si>
@@ -1361,7 +1364,7 @@
     <t xml:space="preserve">1.68610382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68164336681366</t>
+    <t xml:space="preserve">1.68164324760437</t>
   </si>
   <si>
     <t xml:space="preserve">1.63257670402527</t>
@@ -1373,7 +1376,7 @@
     <t xml:space="preserve">1.62811613082886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61473417282104</t>
+    <t xml:space="preserve">1.61473441123962</t>
   </si>
   <si>
     <t xml:space="preserve">1.58351016044617</t>
@@ -1385,10 +1388,10 @@
     <t xml:space="preserve">1.55228590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54336488246918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59243130683899</t>
+    <t xml:space="preserve">1.54336476325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59243142604828</t>
   </si>
   <si>
     <t xml:space="preserve">1.56120717525482</t>
@@ -1412,10 +1415,10 @@
     <t xml:space="preserve">1.5968918800354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53444373607635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66380071640015</t>
+    <t xml:space="preserve">1.53444385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66380083560944</t>
   </si>
   <si>
     <t xml:space="preserve">1.56566774845123</t>
@@ -1427,10 +1430,10 @@
     <t xml:space="preserve">1.52552258968353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5076801776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738938331604</t>
+    <t xml:space="preserve">1.50768005847931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738950252533</t>
   </si>
   <si>
     <t xml:space="preserve">1.51660132408142</t>
@@ -1442,7 +1445,7 @@
     <t xml:space="preserve">1.34263813495636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34709882736206</t>
+    <t xml:space="preserve">1.34709894657135</t>
   </si>
   <si>
     <t xml:space="preserve">1.32479596138</t>
@@ -1457,7 +1460,7 @@
     <t xml:space="preserve">1.24450528621674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29803228378296</t>
+    <t xml:space="preserve">1.29803240299225</t>
   </si>
   <si>
     <t xml:space="preserve">1.20435976982117</t>
@@ -1481,19 +1484,19 @@
     <t xml:space="preserve">1.36494112014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35601997375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36048066616058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40508639812469</t>
+    <t xml:space="preserve">1.35602009296417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36048054695129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40508651733398</t>
   </si>
   <si>
     <t xml:space="preserve">1.44969236850739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45415306091309</t>
+    <t xml:space="preserve">1.45415318012238</t>
   </si>
   <si>
     <t xml:space="preserve">1.44523179531097</t>
@@ -1508,7 +1511,7 @@
     <t xml:space="preserve">1.46307420730591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39170467853546</t>
+    <t xml:space="preserve">1.39170479774475</t>
   </si>
   <si>
     <t xml:space="preserve">1.40062606334686</t>
@@ -1517,13 +1520,13 @@
     <t xml:space="preserve">1.41400766372681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38278329372406</t>
+    <t xml:space="preserve">1.38278341293335</t>
   </si>
   <si>
     <t xml:space="preserve">1.38724410533905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33817768096924</t>
+    <t xml:space="preserve">1.33817756175995</t>
   </si>
   <si>
     <t xml:space="preserve">1.35155928134918</t>
@@ -1535,10 +1538,10 @@
     <t xml:space="preserve">1.32925641536713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33371698856354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31587469577789</t>
+    <t xml:space="preserve">1.33371710777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3158745765686</t>
   </si>
   <si>
     <t xml:space="preserve">1.37386226654053</t>
@@ -1550,7 +1553,7 @@
     <t xml:space="preserve">1.3203352689743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28018999099731</t>
+    <t xml:space="preserve">1.28018987178802</t>
   </si>
   <si>
     <t xml:space="preserve">1.40954720973969</t>
@@ -1559,7 +1562,7 @@
     <t xml:space="preserve">1.39616525173187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45861375331879</t>
+    <t xml:space="preserve">1.4586136341095</t>
   </si>
   <si>
     <t xml:space="preserve">1.37832295894623</t>
@@ -1568,7 +1571,7 @@
     <t xml:space="preserve">1.42292892932892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28911125659943</t>
+    <t xml:space="preserve">1.28911113739014</t>
   </si>
   <si>
     <t xml:space="preserve">1.27126860618591</t>
@@ -1577,7 +1580,7 @@
     <t xml:space="preserve">1.26234757900238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24896574020386</t>
+    <t xml:space="preserve">1.24896562099457</t>
   </si>
   <si>
     <t xml:space="preserve">1.46753478050232</t>
@@ -1589,34 +1592,34 @@
     <t xml:space="preserve">1.48091661930084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49429833889008</t>
+    <t xml:space="preserve">1.49429821968079</t>
   </si>
   <si>
     <t xml:space="preserve">1.5032194852829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52998304367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49875891208649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51214075088501</t>
+    <t xml:space="preserve">1.52998292446136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4987587928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5121408700943</t>
   </si>
   <si>
     <t xml:space="preserve">1.48537719249725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52106201648712</t>
+    <t xml:space="preserve">1.52106189727783</t>
   </si>
   <si>
     <t xml:space="preserve">1.72178852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76639449596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73963105678558</t>
+    <t xml:space="preserve">1.76639437675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73963093757629</t>
   </si>
   <si>
     <t xml:space="preserve">1.81992149353027</t>
@@ -1625,13 +1628,13 @@
     <t xml:space="preserve">1.87344872951508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82884275913239</t>
+    <t xml:space="preserve">1.82884287834167</t>
   </si>
   <si>
     <t xml:space="preserve">1.83776390552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423678874969</t>
+    <t xml:space="preserve">1.78423690795898</t>
   </si>
   <si>
     <t xml:space="preserve">1.77531564235687</t>
@@ -1646,16 +1649,16 @@
     <t xml:space="preserve">1.72624921798706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73070979118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74855220317841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79315793514252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71732807159424</t>
+    <t xml:space="preserve">1.73070967197418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7485523223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79315805435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71732795238495</t>
   </si>
   <si>
     <t xml:space="preserve">1.74409151077271</t>
@@ -1664,10 +1667,10 @@
     <t xml:space="preserve">1.77977633476257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81100046634674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84668493270874</t>
+    <t xml:space="preserve">1.81100034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84668505191803</t>
   </si>
   <si>
     <t xml:space="preserve">1.86452734470367</t>
@@ -1685,19 +1688,19 @@
     <t xml:space="preserve">2.02510905265808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96266031265259</t>
+    <t xml:space="preserve">1.96266078948975</t>
   </si>
   <si>
     <t xml:space="preserve">1.92697584629059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050272464752</t>
+    <t xml:space="preserve">1.9805029630661</t>
   </si>
   <si>
     <t xml:space="preserve">2.07863593101501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10539937019348</t>
+    <t xml:space="preserve">2.10539960861206</t>
   </si>
   <si>
     <t xml:space="preserve">2.05187225341797</t>
@@ -1706,19 +1709,19 @@
     <t xml:space="preserve">2.06079363822937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09647822380066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43548321723938</t>
+    <t xml:space="preserve">2.09647798538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43548345565796</t>
   </si>
   <si>
     <t xml:space="preserve">2.46224689483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39087724685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56037998199463</t>
+    <t xml:space="preserve">2.39087748527527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56037974357605</t>
   </si>
   <si>
     <t xml:space="preserve">2.60498595237732</t>
@@ -1733,7 +1736,7 @@
     <t xml:space="preserve">2.64104104042053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74019265174866</t>
+    <t xml:space="preserve">2.74019289016724</t>
   </si>
   <si>
     <t xml:space="preserve">2.78526163101196</t>
@@ -1745,7 +1748,7 @@
     <t xml:space="preserve">2.90244102478027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1007444858551</t>
+    <t xml:space="preserve">3.10074472427368</t>
   </si>
   <si>
     <t xml:space="preserve">2.99257898330688</t>
@@ -1760,7 +1763,7 @@
     <t xml:space="preserve">2.76723408699036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83934426307678</t>
+    <t xml:space="preserve">2.83934450149536</t>
   </si>
   <si>
     <t xml:space="preserve">2.87539958953857</t>
@@ -1772,7 +1775,7 @@
     <t xml:space="preserve">2.77624773979187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72216510772705</t>
+    <t xml:space="preserve">2.72216534614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.55991697311401</t>
@@ -1781,22 +1784,19 @@
     <t xml:space="preserve">2.53287553787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6049861907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58695840835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65906858444214</t>
+    <t xml:space="preserve">2.58695816993713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.67709636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52386164665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62301349639893</t>
+    <t xml:space="preserve">2.52386140823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6230137348175</t>
   </si>
   <si>
     <t xml:space="preserve">2.57794451713562</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">2.56893038749695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7942750453949</t>
+    <t xml:space="preserve">2.79427528381348</t>
   </si>
   <si>
     <t xml:space="preserve">2.83033084869385</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">2.71315121650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70413756370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74920654296875</t>
+    <t xml:space="preserve">2.70413732528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74920630455017</t>
   </si>
   <si>
     <t xml:space="preserve">2.80328917503357</t>
@@ -1838,22 +1838,22 @@
     <t xml:space="preserve">3.0015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09173059463501</t>
+    <t xml:space="preserve">3.09173035621643</t>
   </si>
   <si>
     <t xml:space="preserve">2.96553754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93849611282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81230282783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54188942909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4787929058075</t>
+    <t xml:space="preserve">2.93849635124207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81230306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54188919067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47879242897034</t>
   </si>
   <si>
     <t xml:space="preserve">2.63202738761902</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">2.91145467758179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9745512008667</t>
+    <t xml:space="preserve">2.97455096244812</t>
   </si>
   <si>
     <t xml:space="preserve">2.95652365684509</t>
@@ -1871,16 +1871,16 @@
     <t xml:space="preserve">3.01060652732849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01962018013</t>
+    <t xml:space="preserve">3.01961994171143</t>
   </si>
   <si>
     <t xml:space="preserve">2.98356509208679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88441324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94751024246216</t>
+    <t xml:space="preserve">2.88441348075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94751000404358</t>
   </si>
   <si>
     <t xml:space="preserve">2.92046856880188</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">2.19035148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28048944473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.415696144104</t>
+    <t xml:space="preserve">2.28048920631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41569638252258</t>
   </si>
   <si>
     <t xml:space="preserve">2.31654453277588</t>
@@ -1922,34 +1922,34 @@
     <t xml:space="preserve">2.4427375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37964129447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3706271648407</t>
+    <t xml:space="preserve">2.37964105606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37062740325928</t>
   </si>
   <si>
     <t xml:space="preserve">2.27147555351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26246190071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28950309753418</t>
+    <t xml:space="preserve">2.26246166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28950333595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.30753064155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32555794715881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.343585729599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21739292144775</t>
+    <t xml:space="preserve">2.32555818557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851698875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34358596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21739268302917</t>
   </si>
   <si>
     <t xml:space="preserve">2.20837903022766</t>
@@ -25624,7 +25624,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G872" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25676,7 +25676,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G874" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25702,7 +25702,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G875" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25754,7 +25754,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G877" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25780,7 +25780,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G878" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25806,7 +25806,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G879" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25832,7 +25832,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G880" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25858,7 +25858,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G881" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25884,7 +25884,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G882" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25962,7 +25962,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G885" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25988,7 +25988,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G886" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26014,7 +26014,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G887" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26040,7 +26040,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G888" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26092,7 +26092,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G890" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26118,7 +26118,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G891" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26144,7 +26144,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G892" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26196,7 +26196,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G894" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26222,7 +26222,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G895" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26248,7 +26248,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G896" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26274,7 +26274,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26300,7 +26300,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G898" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26326,7 +26326,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G899" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26378,7 +26378,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G901" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26404,7 +26404,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G902" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26430,7 +26430,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G903" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26456,7 +26456,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G904" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26508,7 +26508,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G906" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26534,7 +26534,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G907" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26560,7 +26560,7 @@
         <v>1.75</v>
       </c>
       <c r="G908" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26586,7 +26586,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G909" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26612,7 +26612,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G910" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26638,7 +26638,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G911" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26664,7 +26664,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G912" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26690,7 +26690,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G913" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26716,7 +26716,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G914" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26742,7 +26742,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G915" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26768,7 +26768,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G916" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26794,7 +26794,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G917" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26820,7 +26820,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G918" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26846,7 +26846,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G919" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26872,7 +26872,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G920" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26898,7 +26898,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G921" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26924,7 +26924,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G922" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26976,7 +26976,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G924" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27002,7 +27002,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G925" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27028,7 +27028,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G926" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27106,7 +27106,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G929" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27132,7 +27132,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G930" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27158,7 +27158,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G931" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27184,7 +27184,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G932" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27236,7 +27236,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G934" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27262,7 +27262,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27288,7 +27288,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G936" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27314,7 +27314,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G937" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27340,7 +27340,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G938" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27366,7 +27366,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G939" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27392,7 +27392,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G940" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27418,7 +27418,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G941" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27444,7 +27444,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G942" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27470,7 +27470,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G943" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27522,7 +27522,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G945" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27548,7 +27548,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27574,7 +27574,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G947" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27600,7 +27600,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27626,7 +27626,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27652,7 +27652,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G950" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27678,7 +27678,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G951" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27704,7 +27704,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G952" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27730,7 +27730,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G953" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27756,7 +27756,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G954" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27782,7 +27782,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G955" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27808,7 +27808,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G956" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27834,7 +27834,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G957" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27860,7 +27860,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G958" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27886,7 +27886,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27912,7 +27912,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G960" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27938,7 +27938,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G961" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27964,7 +27964,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G962" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27990,7 +27990,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G963" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28068,7 +28068,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G966" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28094,7 +28094,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G967" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28120,7 +28120,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G968" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28172,7 +28172,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G970" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28224,7 +28224,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G972" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28250,7 +28250,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G973" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28276,7 +28276,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G974" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28302,7 +28302,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G975" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28354,7 +28354,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G977" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28380,7 +28380,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G978" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28406,7 +28406,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G979" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28432,7 +28432,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G980" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28536,7 +28536,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G984" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28562,7 +28562,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G985" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28588,7 +28588,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G986" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28614,7 +28614,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G987" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28640,7 +28640,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28666,7 +28666,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G989" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28692,7 +28692,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G990" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28718,7 +28718,7 @@
         <v>1.75</v>
       </c>
       <c r="G991" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28744,7 +28744,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G992" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28770,7 +28770,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G993" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28796,7 +28796,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G994" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28900,7 +28900,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G998" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28926,7 +28926,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G999" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29004,7 +29004,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1002" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29056,7 +29056,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1004" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29082,7 +29082,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1005" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29134,7 +29134,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1007" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29160,7 +29160,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29212,7 +29212,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1010" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29238,7 +29238,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1011" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29264,7 +29264,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1012" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29290,7 +29290,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1013" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29316,7 +29316,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1014" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29342,7 +29342,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1015" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29368,7 +29368,7 @@
         <v>1.75</v>
       </c>
       <c r="G1016" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29394,7 +29394,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1017" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29420,7 +29420,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1018" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29472,7 +29472,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1020" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29498,7 +29498,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1021" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29524,7 +29524,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1022" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29550,7 +29550,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1023" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29576,7 +29576,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1024" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29602,7 +29602,7 @@
         <v>1.75</v>
       </c>
       <c r="G1025" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29628,7 +29628,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1026" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29654,7 +29654,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1027" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29680,7 +29680,7 @@
         <v>1.75</v>
       </c>
       <c r="G1028" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29706,7 +29706,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1029" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29732,7 +29732,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1030" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29758,7 +29758,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1031" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29784,7 +29784,7 @@
         <v>1.75</v>
       </c>
       <c r="G1032" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29810,7 +29810,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1033" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29836,7 +29836,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1034" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29862,7 +29862,7 @@
         <v>1.75</v>
       </c>
       <c r="G1035" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29888,7 +29888,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29914,7 +29914,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1037" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29940,7 +29940,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1038" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29966,7 +29966,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1039" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29992,7 +29992,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1040" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30018,7 +30018,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1041" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30044,7 +30044,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1042" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30070,7 +30070,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1043" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30096,7 +30096,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1044" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30122,7 +30122,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1045" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30148,7 +30148,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1046" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30174,7 +30174,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1047" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30200,7 +30200,7 @@
         <v>1.75</v>
       </c>
       <c r="G1048" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30226,7 +30226,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1049" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30252,7 +30252,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1050" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30278,7 +30278,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1051" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30304,7 +30304,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30330,7 +30330,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1053" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30356,7 +30356,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1054" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30382,7 +30382,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1055" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30408,7 +30408,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1056" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30434,7 +30434,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30460,7 +30460,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1058" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30486,7 +30486,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1059" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30512,7 +30512,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1060" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30538,7 +30538,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30564,7 +30564,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1062" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30590,7 +30590,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1063" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30616,7 +30616,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1064" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30642,7 +30642,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1065" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30668,7 +30668,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1066" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30694,7 +30694,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30720,7 +30720,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30746,7 +30746,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1069" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30772,7 +30772,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1070" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30798,7 +30798,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1071" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30824,7 +30824,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1072" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30850,7 +30850,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1073" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30876,7 +30876,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1074" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30902,7 +30902,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1075" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30928,7 +30928,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1076" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30954,7 +30954,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1077" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30980,7 +30980,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1078" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31006,7 +31006,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1079" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31032,7 +31032,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1080" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31058,7 +31058,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1081" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31084,7 +31084,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1082" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31110,7 +31110,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1083" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31136,7 +31136,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1084" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31162,7 +31162,7 @@
         <v>1.625</v>
       </c>
       <c r="G1085" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31188,7 +31188,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1086" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31214,7 +31214,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1087" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31240,7 +31240,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1088" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31266,7 +31266,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1089" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31292,7 +31292,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1090" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31318,7 +31318,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1091" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31344,7 +31344,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1092" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31370,7 +31370,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1093" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31396,7 +31396,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1094" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31422,7 +31422,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1095" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31448,7 +31448,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1096" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31474,7 +31474,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1097" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31500,7 +31500,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31526,7 +31526,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1099" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31552,7 +31552,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1100" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31578,7 +31578,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1101" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31604,7 +31604,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1102" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31630,7 +31630,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1103" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31656,7 +31656,7 @@
         <v>1.5</v>
       </c>
       <c r="G1104" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31682,7 +31682,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1105" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31708,7 +31708,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1106" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31734,7 +31734,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1107" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31760,7 +31760,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1108" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31786,7 +31786,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1109" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31812,7 +31812,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1110" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31838,7 +31838,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1111" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31864,7 +31864,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1112" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31890,7 +31890,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1113" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31916,7 +31916,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1114" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31942,7 +31942,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1115" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31968,7 +31968,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1116" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31994,7 +31994,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1117" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32020,7 +32020,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1118" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32046,7 +32046,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1119" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32072,7 +32072,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1120" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32098,7 +32098,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1121" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32124,7 +32124,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1122" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32150,7 +32150,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1123" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32176,7 +32176,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1124" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32202,7 +32202,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1125" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32228,7 +32228,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1126" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32254,7 +32254,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1127" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32280,7 +32280,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1128" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32306,7 +32306,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1129" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32332,7 +32332,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1130" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32358,7 +32358,7 @@
         <v>1.5</v>
       </c>
       <c r="G1131" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32384,7 +32384,7 @@
         <v>1.5</v>
       </c>
       <c r="G1132" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32410,7 +32410,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1133" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32436,7 +32436,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1134" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32462,7 +32462,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1135" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32488,7 +32488,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1136" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32514,7 +32514,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1137" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32540,7 +32540,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1138" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32566,7 +32566,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1139" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32592,7 +32592,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1140" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32618,7 +32618,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1141" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32644,7 +32644,7 @@
         <v>1.5</v>
       </c>
       <c r="G1142" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32670,7 +32670,7 @@
         <v>1.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32696,7 +32696,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1144" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32722,7 +32722,7 @@
         <v>1.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32748,7 +32748,7 @@
         <v>1.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32774,7 +32774,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1147" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32800,7 +32800,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32826,7 +32826,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1149" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32852,7 +32852,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1150" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32878,7 +32878,7 @@
         <v>1.5</v>
       </c>
       <c r="G1151" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32904,7 +32904,7 @@
         <v>1.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32930,7 +32930,7 @@
         <v>1.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32956,7 +32956,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1154" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32982,7 +32982,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33008,7 +33008,7 @@
         <v>1.5</v>
       </c>
       <c r="G1156" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33034,7 +33034,7 @@
         <v>1.5</v>
       </c>
       <c r="G1157" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33060,7 +33060,7 @@
         <v>1.5</v>
       </c>
       <c r="G1158" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33086,7 +33086,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1159" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33112,7 +33112,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1160" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33138,7 +33138,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1161" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33164,7 +33164,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33190,7 +33190,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1163" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33216,7 +33216,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1164" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33242,7 +33242,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1165" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33268,7 +33268,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33294,7 +33294,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1167" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33320,7 +33320,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33346,7 +33346,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1169" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33372,7 +33372,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1170" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33398,7 +33398,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33424,7 +33424,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1172" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33450,7 +33450,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1173" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33476,7 +33476,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1174" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33502,7 +33502,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1175" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33528,7 +33528,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1176" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33554,7 +33554,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1177" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33580,7 +33580,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33606,7 +33606,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1179" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33632,7 +33632,7 @@
         <v>1.5</v>
       </c>
       <c r="G1180" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33658,7 +33658,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1181" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33684,7 +33684,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1182" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33710,7 +33710,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1183" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33736,7 +33736,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1184" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33762,7 +33762,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33788,7 +33788,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1186" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33814,7 +33814,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1187" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33840,7 +33840,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1188" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33866,7 +33866,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1189" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33892,7 +33892,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1190" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33918,7 +33918,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1191" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33944,7 +33944,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1192" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33970,7 +33970,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1193" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33996,7 +33996,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1194" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34022,7 +34022,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1195" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34048,7 +34048,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1196" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34074,7 +34074,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1197" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34100,7 +34100,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1198" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34126,7 +34126,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1199" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34152,7 +34152,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1200" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34178,7 +34178,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1201" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34204,7 +34204,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1202" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34230,7 +34230,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1203" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34256,7 +34256,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34282,7 +34282,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34308,7 +34308,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34334,7 +34334,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34360,7 +34360,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34386,7 +34386,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34412,7 +34412,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34438,7 +34438,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34464,7 +34464,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34490,7 +34490,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1213" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34516,7 +34516,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1214" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34542,7 +34542,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1215" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34568,7 +34568,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34594,7 +34594,7 @@
         <v>1.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34620,7 +34620,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1218" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34646,7 +34646,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1219" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34672,7 +34672,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1220" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34698,7 +34698,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1221" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34724,7 +34724,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1222" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34750,7 +34750,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34776,7 +34776,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34802,7 +34802,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1225" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34828,7 +34828,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1226" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34854,7 +34854,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1227" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34880,7 +34880,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1228" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34906,7 +34906,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1229" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34932,7 +34932,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1230" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34958,7 +34958,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1231" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34984,7 +34984,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35010,7 +35010,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1233" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35036,7 +35036,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1234" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35062,7 +35062,7 @@
         <v>1.5</v>
       </c>
       <c r="G1235" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35088,7 +35088,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1236" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35114,7 +35114,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35140,7 +35140,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35166,7 +35166,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1239" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35192,7 +35192,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35218,7 +35218,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35244,7 +35244,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1242" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35270,7 +35270,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35296,7 +35296,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1244" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35322,7 +35322,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35348,7 +35348,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1246" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35374,7 +35374,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1247" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35400,7 +35400,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35426,7 +35426,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1249" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35452,7 +35452,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1250" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35478,7 +35478,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1251" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35504,7 +35504,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35530,7 +35530,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35556,7 +35556,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1254" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35582,7 +35582,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1255" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35608,7 +35608,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1256" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35634,7 +35634,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1257" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35660,7 +35660,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1258" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35686,7 +35686,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1259" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35712,7 +35712,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1260" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35738,7 +35738,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1261" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35764,7 +35764,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35790,7 +35790,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1263" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35816,7 +35816,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1264" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35842,7 +35842,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1265" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35868,7 +35868,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1266" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35894,7 +35894,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35920,7 +35920,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35946,7 +35946,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1269" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35972,7 +35972,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35998,7 +35998,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1271" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36024,7 +36024,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1272" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36050,7 +36050,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1273" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36076,7 +36076,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1274" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36102,7 +36102,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1275" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36128,7 +36128,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36154,7 +36154,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1277" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36180,7 +36180,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36206,7 +36206,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1279" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36232,7 +36232,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1280" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36258,7 +36258,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1281" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36284,7 +36284,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1282" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36310,7 +36310,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1283" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36336,7 +36336,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1284" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36362,7 +36362,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1285" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36388,7 +36388,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1286" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36414,7 +36414,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1287" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36440,7 +36440,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36466,7 +36466,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1289" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36492,7 +36492,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1290" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36518,7 +36518,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1291" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36544,7 +36544,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1292" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36570,7 +36570,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1293" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36596,7 +36596,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1294" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36622,7 +36622,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1295" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36648,7 +36648,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1296" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36674,7 +36674,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1297" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36700,7 +36700,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1298" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36726,7 +36726,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1299" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36778,7 +36778,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1301" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36804,7 +36804,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1302" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36830,7 +36830,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1303" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36856,7 +36856,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1304" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36882,7 +36882,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1305" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36908,7 +36908,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1306" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36934,7 +36934,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1307" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36960,7 +36960,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1308" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36986,7 +36986,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1309" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37012,7 +37012,7 @@
         <v>2</v>
       </c>
       <c r="G1310" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37038,7 +37038,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37064,7 +37064,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1312" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37090,7 +37090,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1313" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -37116,7 +37116,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1314" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37142,7 +37142,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1315" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37168,7 +37168,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1316" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37194,7 +37194,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1317" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37220,7 +37220,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1318" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37246,7 +37246,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37272,7 +37272,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37298,7 +37298,7 @@
         <v>2</v>
       </c>
       <c r="G1321" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37324,7 +37324,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1322" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37350,7 +37350,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1323" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37376,7 +37376,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1324" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37402,7 +37402,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1325" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37428,7 +37428,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1326" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37454,7 +37454,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1327" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37480,7 +37480,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1328" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37506,7 +37506,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1329" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37532,7 +37532,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1330" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37558,7 +37558,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1331" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37584,7 +37584,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1332" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37610,7 +37610,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1333" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37636,7 +37636,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1334" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37662,7 +37662,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37688,7 +37688,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1336" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37714,7 +37714,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1337" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37740,7 +37740,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1338" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37766,7 +37766,7 @@
         <v>2</v>
       </c>
       <c r="G1339" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37792,7 +37792,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1340" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37818,7 +37818,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1341" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37844,7 +37844,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1342" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37870,7 +37870,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1343" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37896,7 +37896,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37922,7 +37922,7 @@
         <v>2</v>
       </c>
       <c r="G1345" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37948,7 +37948,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1346" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37974,7 +37974,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38000,7 +38000,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38026,7 +38026,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -38052,7 +38052,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1350" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -38078,7 +38078,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1351" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -38104,7 +38104,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1352" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -38130,7 +38130,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1353" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -38156,7 +38156,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1354" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -38182,7 +38182,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1355" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -38208,7 +38208,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1356" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -38234,7 +38234,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1357" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38260,7 +38260,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1358" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38286,7 +38286,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1359" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38312,7 +38312,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1360" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38338,7 +38338,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1361" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38364,7 +38364,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1362" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38390,7 +38390,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1363" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38416,7 +38416,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1364" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38442,7 +38442,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1365" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38468,7 +38468,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1366" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38494,7 +38494,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38520,7 +38520,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38546,7 +38546,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1369" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38572,7 +38572,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1370" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38598,7 +38598,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1371" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38624,7 +38624,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38650,7 +38650,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1373" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38676,7 +38676,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1374" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38702,7 +38702,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1375" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38728,7 +38728,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1376" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38754,7 +38754,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1377" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38780,7 +38780,7 @@
         <v>3.25</v>
       </c>
       <c r="G1378" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38806,7 +38806,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1379" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38832,7 +38832,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1380" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38858,7 +38858,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1381" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38884,7 +38884,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38910,7 +38910,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38936,7 +38936,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1384" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38962,7 +38962,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1385" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38988,7 +38988,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1386" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -39014,7 +39014,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1387" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -39040,7 +39040,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1388" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -39066,7 +39066,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1389" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39092,7 +39092,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1390" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -39196,7 +39196,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1394" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -39222,7 +39222,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1395" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39300,7 +39300,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1398" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39326,7 +39326,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1399" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39352,7 +39352,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1400" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39378,7 +39378,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39482,7 +39482,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1405" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39794,7 +39794,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1417" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39820,7 +39820,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1418" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39898,7 +39898,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1421" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39924,7 +39924,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1422" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39976,7 +39976,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1424" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -40002,7 +40002,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1425" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -40054,7 +40054,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1427" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -40080,7 +40080,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1428" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -40158,7 +40158,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1431" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -40210,7 +40210,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1433" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -40236,7 +40236,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1434" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40314,7 +40314,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1437" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40340,7 +40340,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40392,7 +40392,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40418,7 +40418,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1441" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40444,7 +40444,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1442" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40470,7 +40470,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1443" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40496,7 +40496,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1444" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40522,7 +40522,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1445" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40548,7 +40548,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1446" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40756,7 +40756,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1454" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40834,7 +40834,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40860,7 +40860,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1458" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40886,7 +40886,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1459" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41224,7 +41224,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1472" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41250,7 +41250,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41302,7 +41302,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1475" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41354,7 +41354,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1477" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41406,7 +41406,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1479" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41666,7 +41666,7 @@
         <v>3.25</v>
       </c>
       <c r="G1489" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41692,7 +41692,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1490" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41900,7 +41900,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41978,7 +41978,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1501" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -42082,7 +42082,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1505" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -42108,7 +42108,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -42186,7 +42186,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -42212,7 +42212,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1510" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -42238,7 +42238,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1511" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42264,7 +42264,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1512" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42290,7 +42290,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1513" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42316,7 +42316,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1514" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42342,7 +42342,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1515" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42394,7 +42394,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42472,7 +42472,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1520" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42498,7 +42498,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42550,7 +42550,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1523" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42576,7 +42576,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42602,7 +42602,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42654,7 +42654,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1527" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42758,7 +42758,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1531" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42862,7 +42862,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1535" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42940,7 +42940,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1538" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42966,7 +42966,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1539" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42992,7 +42992,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1540" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43044,7 +43044,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1542" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43122,7 +43122,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1545" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -43148,7 +43148,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1546" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -43382,7 +43382,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1555" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43408,7 +43408,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1556" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43460,7 +43460,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1558" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43486,7 +43486,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1559" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43564,7 +43564,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1562" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43694,7 +43694,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43720,7 +43720,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1568" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44006,7 +44006,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -44292,7 +44292,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1590" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44344,7 +44344,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -70945,6 +70945,32 @@
         <v>859</v>
       </c>
       <c r="H2615" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2616">
+      <c r="A2616" s="1" t="n">
+        <v>46132.2916666667</v>
+      </c>
+      <c r="B2616" t="n">
+        <v>41574</v>
+      </c>
+      <c r="C2616" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2616" t="n">
+        <v>2.17000007629395</v>
+      </c>
+      <c r="E2616" t="n">
+        <v>2.19000005722046</v>
+      </c>
+      <c r="F2616" t="n">
+        <v>2.21000003814697</v>
+      </c>
+      <c r="G2616" t="s">
+        <v>856</v>
+      </c>
+      <c r="H2616" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034153461456</t>
+    <t xml:space="preserve">1.75034165382385</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538779258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69254732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245504379272</t>
+    <t xml:space="preserve">1.74538767337799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69254744052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245492458344</t>
   </si>
   <si>
     <t xml:space="preserve">1.68429100513458</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">1.6760345697403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66612708568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63888132572174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61163544654846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59347140789032</t>
+    <t xml:space="preserve">1.66612684726715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63888120651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61163532733917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59347128868103</t>
   </si>
   <si>
     <t xml:space="preserve">1.48613905906677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5926456451416</t>
+    <t xml:space="preserve">1.59264588356018</t>
   </si>
   <si>
     <t xml:space="preserve">1.59182012081146</t>
@@ -83,55 +83,55 @@
     <t xml:space="preserve">1.58604073524475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172772407532</t>
+    <t xml:space="preserve">1.60172784328461</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521497249603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56044614315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5125595331192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53980541229248</t>
+    <t xml:space="preserve">1.56044590473175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51255941390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53980505466461</t>
   </si>
   <si>
     <t xml:space="preserve">1.5654000043869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53567707538605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45311391353607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50595426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46137011051178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44238042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51833868026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65126574039459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63475298881531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65621960163116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64300942420959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63723027706146</t>
+    <t xml:space="preserve">1.53567719459534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45311379432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50595438480377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46136999130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44238066673279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51833879947662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6512656211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6347531080246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65621972084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64300918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63723015785217</t>
   </si>
   <si>
     <t xml:space="preserve">1.64218366146088</t>
@@ -140,67 +140,67 @@
     <t xml:space="preserve">1.63970673084259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6677782535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60503041744232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5984251499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56870234012604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6322762966156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60255324840546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57283067703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58934307098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58438968658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5678768157959</t>
+    <t xml:space="preserve">1.66777837276459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60503017902374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59842538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56870245933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6405326128006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60255336761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57283043861389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58934319019318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58438956737518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56787693500519</t>
   </si>
   <si>
     <t xml:space="preserve">1.55714356899261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53402578830719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54310786724091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466675758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962038040161</t>
+    <t xml:space="preserve">1.53402590751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54310774803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5596204996109</t>
   </si>
   <si>
     <t xml:space="preserve">1.55218982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55053853988647</t>
+    <t xml:space="preserve">1.55053842067719</t>
   </si>
   <si>
     <t xml:space="preserve">1.50265181064606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48696482181549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861598968506</t>
+    <t xml:space="preserve">1.4869647026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861587047577</t>
   </si>
   <si>
     <t xml:space="preserve">1.53237450122833</t>
@@ -209,49 +209,46 @@
     <t xml:space="preserve">1.49026715755463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51503622531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779034614563</t>
+    <t xml:space="preserve">1.5150363445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779058456421</t>
   </si>
   <si>
     <t xml:space="preserve">1.47623157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50760555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5010005235672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49439549446106</t>
+    <t xml:space="preserve">1.50760567188263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50100040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49439537525177</t>
   </si>
   <si>
     <t xml:space="preserve">1.48366212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45971894264221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4597190618515</t>
+    <t xml:space="preserve">1.45971882343292</t>
   </si>
   <si>
     <t xml:space="preserve">1.45299983024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46223855018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43284261226654</t>
+    <t xml:space="preserve">1.46223866939545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43284249305725</t>
   </si>
   <si>
     <t xml:space="preserve">1.43536221981049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43200290203094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4261234998703</t>
+    <t xml:space="preserve">1.43200266361237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42612338066101</t>
   </si>
   <si>
     <t xml:space="preserve">1.41100573539734</t>
@@ -266,67 +263,67 @@
     <t xml:space="preserve">1.44292116165161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44880032539368</t>
+    <t xml:space="preserve">1.44880044460297</t>
   </si>
   <si>
     <t xml:space="preserve">1.47819638252258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44460093975067</t>
+    <t xml:space="preserve">1.44460082054138</t>
   </si>
   <si>
     <t xml:space="preserve">1.42360389232635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43032288551331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46139872074127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40260660648346</t>
+    <t xml:space="preserve">1.4303230047226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46139860153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40260648727417</t>
   </si>
   <si>
     <t xml:space="preserve">1.4084860086441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37825012207031</t>
+    <t xml:space="preserve">1.37825000286102</t>
   </si>
   <si>
     <t xml:space="preserve">1.42444360256195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604471206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4697972536087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42780315876007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192399501801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47567677497864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44796061515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47735631465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43368256092072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45803880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4521598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48491549491882</t>
+    <t xml:space="preserve">1.41604483127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46979737281799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42780339717865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192387580872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47567665576935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44796049594879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47735643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43368244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45803904533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45215976238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48491537570953</t>
   </si>
   <si>
     <t xml:space="preserve">1.46391832828522</t>
@@ -335,7 +332,7 @@
     <t xml:space="preserve">1.46643805503845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46895754337311</t>
+    <t xml:space="preserve">1.4689576625824</t>
   </si>
   <si>
     <t xml:space="preserve">1.48575532436371</t>
@@ -344,7 +341,7 @@
     <t xml:space="preserve">1.45887887477875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45635938644409</t>
+    <t xml:space="preserve">1.4563592672348</t>
   </si>
   <si>
     <t xml:space="preserve">1.45719921588898</t>
@@ -353,22 +350,22 @@
     <t xml:space="preserve">1.48827481269836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43956160545349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47399687767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46727764606476</t>
+    <t xml:space="preserve">1.43956172466278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47399699687958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46727776527405</t>
   </si>
   <si>
     <t xml:space="preserve">1.49835360050201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50927197933197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5033928155899</t>
+    <t xml:space="preserve">1.50927209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50339257717133</t>
   </si>
   <si>
     <t xml:space="preserve">1.49499404430389</t>
@@ -380,16 +377,16 @@
     <t xml:space="preserve">1.51011180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49919354915619</t>
+    <t xml:space="preserve">1.49919319152832</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179158687592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45048010349274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44628071784973</t>
+    <t xml:space="preserve">1.45048022270203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44628083705902</t>
   </si>
   <si>
     <t xml:space="preserve">1.43872177600861</t>
@@ -398,25 +395,25 @@
     <t xml:space="preserve">1.50003325939178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48071610927582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48155581951141</t>
+    <t xml:space="preserve">1.48071587085724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4815559387207</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095187664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49583375453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50759220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49667382240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47231709957123</t>
+    <t xml:space="preserve">1.49583387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5075923204422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49667394161224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47231698036194</t>
   </si>
   <si>
     <t xml:space="preserve">1.49331426620483</t>
@@ -425,10 +422,10 @@
     <t xml:space="preserve">1.47147727012634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50087296962738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52774965763092</t>
+    <t xml:space="preserve">1.50087308883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52774941921234</t>
   </si>
   <si>
     <t xml:space="preserve">1.53194892406464</t>
@@ -437,37 +434,37 @@
     <t xml:space="preserve">1.52690958976746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52355003356934</t>
+    <t xml:space="preserve">1.52354991436005</t>
   </si>
   <si>
     <t xml:space="preserve">1.50423264503479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51263165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54454708099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54538726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55294597148895</t>
+    <t xml:space="preserve">1.51263153553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54454720020294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54538714885712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55294609069824</t>
   </si>
   <si>
     <t xml:space="preserve">1.52019047737122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50843226909637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59578001499176</t>
+    <t xml:space="preserve">1.50843214988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59578013420105</t>
   </si>
   <si>
     <t xml:space="preserve">1.53446853160858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56050491333008</t>
+    <t xml:space="preserve">1.56050503253937</t>
   </si>
   <si>
     <t xml:space="preserve">1.53026914596558</t>
@@ -476,7 +473,7 @@
     <t xml:space="preserve">1.53110897541046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55126619338989</t>
+    <t xml:space="preserve">1.55126631259918</t>
   </si>
   <si>
     <t xml:space="preserve">1.55210626125336</t>
@@ -485,13 +482,13 @@
     <t xml:space="preserve">1.55378592014313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58654129505157</t>
+    <t xml:space="preserve">1.58654153347015</t>
   </si>
   <si>
     <t xml:space="preserve">1.56218469142914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56974375247955</t>
+    <t xml:space="preserve">1.56974363327026</t>
   </si>
   <si>
     <t xml:space="preserve">1.57058346271515</t>
@@ -500,10 +497,10 @@
     <t xml:space="preserve">1.60333907604218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54958641529083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55798542499542</t>
+    <t xml:space="preserve">1.54958653450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55798530578613</t>
   </si>
   <si>
     <t xml:space="preserve">1.57142353057861</t>
@@ -515,7 +512,7 @@
     <t xml:space="preserve">1.61089789867401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61173820495605</t>
+    <t xml:space="preserve">1.61173808574677</t>
   </si>
   <si>
     <t xml:space="preserve">1.60417878627777</t>
@@ -530,25 +527,25 @@
     <t xml:space="preserve">1.61257767677307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59326040744781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58822119235992</t>
+    <t xml:space="preserve">1.5932605266571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58822107315063</t>
   </si>
   <si>
     <t xml:space="preserve">1.60753846168518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63105535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61425757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71504366397858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77215588092804</t>
+    <t xml:space="preserve">1.63105523586273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71504354476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77215552330017</t>
   </si>
   <si>
     <t xml:space="preserve">1.7654367685318</t>
@@ -557,49 +554,49 @@
     <t xml:space="preserve">1.75367844104767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72512233257294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74527943134308</t>
+    <t xml:space="preserve">1.72512209415436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74527966976166</t>
   </si>
   <si>
     <t xml:space="preserve">1.72176277637482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70664489269257</t>
+    <t xml:space="preserve">1.70664477348328</t>
   </si>
   <si>
     <t xml:space="preserve">1.73856055736542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69992554187775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67892873287201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69656610488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69320678710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70496511459351</t>
+    <t xml:space="preserve">1.69992578029633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67892861366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69656622409821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69320666790009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70496487617493</t>
   </si>
   <si>
     <t xml:space="preserve">1.77383542060852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75871789455414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68984711170197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69152700901031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66800999641418</t>
+    <t xml:space="preserve">1.75871765613556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68984723091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69152677059174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6680098772049</t>
   </si>
   <si>
     <t xml:space="preserve">1.68816745281219</t>
@@ -608,10 +605,10 @@
     <t xml:space="preserve">1.71336388587952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73184156417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535798072815</t>
+    <t xml:space="preserve">1.73184144496918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535809993744</t>
   </si>
   <si>
     <t xml:space="preserve">1.7100043296814</t>
@@ -620,55 +617,55 @@
     <t xml:space="preserve">1.71672332286835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73016154766083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047610282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375687122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031876564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78895354270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74024033546448</t>
+    <t xml:space="preserve">1.73016142845154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74695932865143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7704758644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375699043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031888484955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78895366191864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74024021625519</t>
   </si>
   <si>
     <t xml:space="preserve">1.76207733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73352110385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78055453300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254886627197</t>
+    <t xml:space="preserve">1.73352098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903209209442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78055465221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254862785339</t>
   </si>
   <si>
     <t xml:space="preserve">1.86958253383636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86454284191132</t>
+    <t xml:space="preserve">1.8645430803299</t>
   </si>
   <si>
     <t xml:space="preserve">1.84774541854858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78391420841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90480959415436</t>
+    <t xml:space="preserve">1.78391432762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90480971336365</t>
   </si>
   <si>
     <t xml:space="preserve">1.98488640785217</t>
@@ -677,16 +674,16 @@
     <t xml:space="preserve">2.34267711639404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35119605064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24045157432556</t>
+    <t xml:space="preserve">2.3511962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24045133590698</t>
   </si>
   <si>
     <t xml:space="preserve">2.180819272995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.364825963974</t>
+    <t xml:space="preserve">2.36482620239258</t>
   </si>
   <si>
     <t xml:space="preserve">2.32223200798035</t>
@@ -695,7 +692,7 @@
     <t xml:space="preserve">2.34608483314514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33415818214417</t>
+    <t xml:space="preserve">2.33415842056274</t>
   </si>
   <si>
     <t xml:space="preserve">2.24897003173828</t>
@@ -707,25 +704,25 @@
     <t xml:space="preserve">2.14163279533386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07007503509521</t>
+    <t xml:space="preserve">2.07007479667664</t>
   </si>
   <si>
     <t xml:space="preserve">2.01896166801453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95932984352112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01044273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06496334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00192403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02407336235046</t>
+    <t xml:space="preserve">1.9593300819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01044297218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06496357917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00192427635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02407312393188</t>
   </si>
   <si>
     <t xml:space="preserve">2.06155610084534</t>
@@ -734,52 +731,52 @@
     <t xml:space="preserve">2.04451847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0683708190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303716659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111075401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9797750711441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99340534210205</t>
+    <t xml:space="preserve">2.06837105751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303740501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04111051559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97977495193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99340546131134</t>
   </si>
   <si>
     <t xml:space="preserve">1.97636759281158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97125625610352</t>
+    <t xml:space="preserve">1.97125637531281</t>
   </si>
   <si>
     <t xml:space="preserve">1.97466421127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95081126689911</t>
+    <t xml:space="preserve">1.95081150531769</t>
   </si>
   <si>
     <t xml:space="preserve">1.93888485431671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92525482177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92695832252502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94229233264923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95762622356415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93718123435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92866218090057</t>
+    <t xml:space="preserve">1.92525470256805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92695844173431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94229221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95762658119202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93718111515045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92866194248199</t>
   </si>
   <si>
     <t xml:space="preserve">1.97296011447906</t>
@@ -788,94 +785,94 @@
     <t xml:space="preserve">2.00703549385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01555442810059</t>
+    <t xml:space="preserve">2.01555418968201</t>
   </si>
   <si>
     <t xml:space="preserve">1.98829400539398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93206965923309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673576831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91332828998566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90821719169617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93377327919006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94058859348297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822531700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2557852268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22341370582581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35971474647522</t>
+    <t xml:space="preserve">1.93206977844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673600673676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91332817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90821707248688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93377351760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94058847427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822555541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25578498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22341346740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3597149848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.27452659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41593885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41253161430359</t>
+    <t xml:space="preserve">2.41593933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41253137588501</t>
   </si>
   <si>
     <t xml:space="preserve">2.36823391914368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30860161781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31200957298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31541705131531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28986024856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42445802688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41423535346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36993765830994</t>
+    <t xml:space="preserve">2.30860185623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31200933456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31541728973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28986048698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42445778846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41423511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36993741989136</t>
   </si>
   <si>
     <t xml:space="preserve">2.39719748497009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35801076889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30519437789917</t>
+    <t xml:space="preserve">2.35801148414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30519461631775</t>
   </si>
   <si>
     <t xml:space="preserve">2.32052803039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32904696464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31882429122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34778833389282</t>
+    <t xml:space="preserve">2.32904720306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31882452964783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3477885723114</t>
   </si>
   <si>
     <t xml:space="preserve">2.36312246322632</t>
@@ -884,16 +881,16 @@
     <t xml:space="preserve">2.34438109397888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32563972473145</t>
+    <t xml:space="preserve">2.32563948631287</t>
   </si>
   <si>
     <t xml:space="preserve">2.3392698764801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36652970314026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3767523765564</t>
+    <t xml:space="preserve">2.36653017997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37675261497498</t>
   </si>
   <si>
     <t xml:space="preserve">2.38356757164001</t>
@@ -914,7 +911,7 @@
     <t xml:space="preserve">2.10585355758667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10415005683899</t>
+    <t xml:space="preserve">2.10415029525757</t>
   </si>
   <si>
     <t xml:space="preserve">2.12800288200378</t>
@@ -926,184 +923,187 @@
     <t xml:space="preserve">2.28304553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30349063873291</t>
+    <t xml:space="preserve">2.30349087715149</t>
   </si>
   <si>
     <t xml:space="preserve">2.29667568206787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28815698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21659851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23874759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21489453315735</t>
+    <t xml:space="preserve">2.28815722465515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21659874916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23874735832214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21489477157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25748920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24556279182434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23193216323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933820724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26260018348694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22511744499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23363614082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23022866249084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20637583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29156398773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39379024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41934680938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53009152412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5726854801178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54712915420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58120441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50453495979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47045969963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46194076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38527131080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41082787513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30008316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45342206954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60676074028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61527943611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6493546962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6578733921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43638467788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52157258987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53861045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55564761161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48749756813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44490313529968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26600766181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14674401283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671058654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11856651306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066216468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29221963882446</t>
   </si>
   <si>
     <t xml:space="preserve">2.25748896598816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24556255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23193264007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933820724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26260018348694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22511720657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23363614082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23022866249084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20637583732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29156422615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39379000663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41934657096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53009176254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5726854801178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54712915420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5812041759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50453495979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47045969963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46194100379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38527131080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41082787513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30008339881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45342206954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60676074028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61527991294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6493546962738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43638443946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52157258987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53861021995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55564785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48749732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44490313529968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26600766181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14674425125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671010971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1185667514801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066240310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29221963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24880599975586</t>
+    <t xml:space="preserve">2.24880623817444</t>
   </si>
   <si>
     <t xml:space="preserve">2.2661714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2748544216156</t>
+    <t xml:space="preserve">2.27485394477844</t>
   </si>
   <si>
     <t xml:space="preserve">2.34431552886963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35299801826477</t>
+    <t xml:space="preserve">2.35299777984619</t>
   </si>
   <si>
     <t xml:space="preserve">2.3009021282196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3095850944519</t>
+    <t xml:space="preserve">2.30958485603333</t>
   </si>
   <si>
     <t xml:space="preserve">2.32695031166077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28353714942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21407580375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17934489250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20539307594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15329718589783</t>
+    <t xml:space="preserve">2.28353691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21407532691956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17934513092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20539283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15329694747925</t>
   </si>
   <si>
     <t xml:space="preserve">2.13593173027039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10988402366638</t>
+    <t xml:space="preserve">2.1098837852478</t>
   </si>
   <si>
     <t xml:space="preserve">2.18802762031555</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.09251880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22275829315186</t>
+    <t xml:space="preserve">2.22275853157043</t>
   </si>
   <si>
     <t xml:space="preserve">2.07515358924866</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">2.10120153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0404224395752</t>
+    <t xml:space="preserve">2.04042267799377</t>
   </si>
   <si>
     <t xml:space="preserve">2.01437473297119</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">2.06647062301636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99700927734375</t>
+    <t xml:space="preserve">1.99700951576233</t>
   </si>
   <si>
     <t xml:space="preserve">2.00569224357605</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">2.02305746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0491054058075</t>
+    <t xml:space="preserve">2.04910516738892</t>
   </si>
   <si>
     <t xml:space="preserve">2.03173995018005</t>
@@ -1160,19 +1160,19 @@
     <t xml:space="preserve">1.93623089790344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87545228004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281761646271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82335650920868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81467366218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77994322776794</t>
+    <t xml:space="preserve">1.87545239925385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.892817735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8233562707901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81467378139496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77994310855865</t>
   </si>
   <si>
     <t xml:space="preserve">1.71916460990906</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">1.62799680233002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63233804702759</t>
+    <t xml:space="preserve">1.63233816623688</t>
   </si>
   <si>
     <t xml:space="preserve">1.67575132846832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68443405628204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71048200130463</t>
+    <t xml:space="preserve">1.68443417549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71048188209534</t>
   </si>
   <si>
     <t xml:space="preserve">1.6887754201889</t>
@@ -1205,49 +1205,49 @@
     <t xml:space="preserve">1.69745802879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64536201953888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59760761260986</t>
+    <t xml:space="preserve">1.64536213874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59760737419128</t>
   </si>
   <si>
     <t xml:space="preserve">1.60629022121429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61931419372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61497294902802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63667941093445</t>
+    <t xml:space="preserve">1.61931431293488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61497282981873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63667953014374</t>
   </si>
   <si>
     <t xml:space="preserve">1.64970350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68009281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65838611125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70179951190948</t>
+    <t xml:space="preserve">1.68009269237518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65838599205017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7017993927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.67140996456146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6670686006546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57155966758728</t>
+    <t xml:space="preserve">1.66706871986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57155954837799</t>
   </si>
   <si>
     <t xml:space="preserve">1.52814638614655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5107809305191</t>
+    <t xml:space="preserve">1.51078104972839</t>
   </si>
   <si>
     <t xml:space="preserve">1.54551160335541</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">1.56287693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6540447473526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66272735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72784733772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7625777721405</t>
+    <t xml:space="preserve">1.65404486656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66272747516632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72784721851349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76257801055908</t>
   </si>
   <si>
     <t xml:space="preserve">1.75389528274536</t>
@@ -1289,85 +1289,85 @@
     <t xml:space="preserve">1.79730844497681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84072184562683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8667699098587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91018319129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95359635353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94491362571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98832654953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97096157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91886568069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9275484085083</t>
+    <t xml:space="preserve">1.84072160720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86676967144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91018283367157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359623432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94491338729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98832666873932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97096145153046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.918865442276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92754805088043</t>
   </si>
   <si>
     <t xml:space="preserve">1.8580869436264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84940445423126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413500785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62365543842316</t>
+    <t xml:space="preserve">1.84940469264984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413488864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62365531921387</t>
   </si>
   <si>
     <t xml:space="preserve">1.6504191160202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61919498443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6013525724411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61027359962463</t>
+    <t xml:space="preserve">1.61919486522675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60135245323181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61027371883392</t>
   </si>
   <si>
     <t xml:space="preserve">1.63703727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65487957000732</t>
+    <t xml:space="preserve">1.65487968921661</t>
   </si>
   <si>
     <t xml:space="preserve">1.62365555763245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6459584236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64149796962738</t>
+    <t xml:space="preserve">1.64595854282379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6414977312088</t>
   </si>
   <si>
     <t xml:space="preserve">1.65934026241302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66826140880585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68610382080078</t>
+    <t xml:space="preserve">1.66826128959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68610394001007</t>
   </si>
   <si>
     <t xml:space="preserve">1.68164324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63257670402527</t>
+    <t xml:space="preserve">1.63257682323456</t>
   </si>
   <si>
     <t xml:space="preserve">1.60581314563751</t>
@@ -1376,61 +1376,61 @@
     <t xml:space="preserve">1.62811613082886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61473441123962</t>
+    <t xml:space="preserve">1.61473429203033</t>
   </si>
   <si>
     <t xml:space="preserve">1.58351016044617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57904970645905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55228590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54336476325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59243142604828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56120717525482</t>
+    <t xml:space="preserve">1.57904958724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.552286028862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54336488246918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59243130683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56120729446411</t>
   </si>
   <si>
     <t xml:space="preserve">1.53890430927277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5567467212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57012856006622</t>
+    <t xml:space="preserve">1.55674660205841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57012844085693</t>
   </si>
   <si>
     <t xml:space="preserve">1.58797073364258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57458889484406</t>
+    <t xml:space="preserve">1.57458901405334</t>
   </si>
   <si>
     <t xml:space="preserve">1.5968918800354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53444385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66380083560944</t>
+    <t xml:space="preserve">1.53444373607635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66380095481873</t>
   </si>
   <si>
     <t xml:space="preserve">1.56566774845123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54782557487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52552258968353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50768005847931</t>
+    <t xml:space="preserve">1.54782545566559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52552247047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50768029689789</t>
   </si>
   <si>
     <t xml:space="preserve">1.42738950252533</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">1.48983776569366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34263813495636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709894657135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32479596138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19097816944122</t>
+    <t xml:space="preserve">1.34263825416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709882736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32479584217072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19097805023193</t>
   </si>
   <si>
     <t xml:space="preserve">1.26680815219879</t>
@@ -1463,28 +1463,28 @@
     <t xml:space="preserve">1.29803240299225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20435976982117</t>
+    <t xml:space="preserve">1.20435988903046</t>
   </si>
   <si>
     <t xml:space="preserve">1.2757294178009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28465056419373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30695354938507</t>
+    <t xml:space="preserve">1.28465044498444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30695366859436</t>
   </si>
   <si>
     <t xml:space="preserve">1.30249297618866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36940181255341</t>
+    <t xml:space="preserve">1.36940157413483</t>
   </si>
   <si>
     <t xml:space="preserve">1.36494112014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35602009296417</t>
+    <t xml:space="preserve">1.35601997375488</t>
   </si>
   <si>
     <t xml:space="preserve">1.36048054695129</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.44523179531097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43631064891815</t>
+    <t xml:space="preserve">1.43631052970886</t>
   </si>
   <si>
     <t xml:space="preserve">1.41846823692322</t>
@@ -1511,40 +1511,40 @@
     <t xml:space="preserve">1.46307420730591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39170479774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40062606334686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41400766372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38278341293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38724410533905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33817756175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35155928134918</t>
+    <t xml:space="preserve">1.39170467853546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40062582492828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4140077829361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38278353214264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38724398612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33817768096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35155940055847</t>
   </si>
   <si>
     <t xml:space="preserve">1.29357171058655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32925641536713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33371710777283</t>
+    <t xml:space="preserve">1.32925653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33371698856354</t>
   </si>
   <si>
     <t xml:space="preserve">1.3158745765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37386226654053</t>
+    <t xml:space="preserve">1.37386238574982</t>
   </si>
   <si>
     <t xml:space="preserve">1.31141412258148</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">1.3203352689743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28018987178802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40954720973969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39616525173187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4586136341095</t>
+    <t xml:space="preserve">1.28018999099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4095470905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39616537094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45861375331879</t>
   </si>
   <si>
     <t xml:space="preserve">1.37832295894623</t>
@@ -1574,37 +1574,37 @@
     <t xml:space="preserve">1.28911113739014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27126860618591</t>
+    <t xml:space="preserve">1.2712687253952</t>
   </si>
   <si>
     <t xml:space="preserve">1.26234757900238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24896562099457</t>
+    <t xml:space="preserve">1.24896574020386</t>
   </si>
   <si>
     <t xml:space="preserve">1.46753478050232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44077122211456</t>
+    <t xml:space="preserve">1.44077110290527</t>
   </si>
   <si>
     <t xml:space="preserve">1.48091661930084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49429821968079</t>
+    <t xml:space="preserve">1.49429833889008</t>
   </si>
   <si>
     <t xml:space="preserve">1.5032194852829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52998292446136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4987587928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5121408700943</t>
+    <t xml:space="preserve">1.52998328208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49875903129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51214075088501</t>
   </si>
   <si>
     <t xml:space="preserve">1.48537719249725</t>
@@ -1616,25 +1616,25 @@
     <t xml:space="preserve">1.72178852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76639437675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73963093757629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87344872951508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82884287834167</t>
+    <t xml:space="preserve">1.76639449596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73963105678558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81992137432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8734484910965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8288426399231</t>
   </si>
   <si>
     <t xml:space="preserve">1.83776390552521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423690795898</t>
+    <t xml:space="preserve">1.78423678874969</t>
   </si>
   <si>
     <t xml:space="preserve">1.77531564235687</t>
@@ -1646,19 +1646,19 @@
     <t xml:space="preserve">1.77085506916046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72624921798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73070967197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7485523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79315805435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71732795238495</t>
+    <t xml:space="preserve">1.72624909877777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73070991039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74855220317841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79315793514252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71732783317566</t>
   </si>
   <si>
     <t xml:space="preserve">1.74409151077271</t>
@@ -1667,52 +1667,52 @@
     <t xml:space="preserve">1.77977633476257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81100034713745</t>
+    <t xml:space="preserve">1.81100046634674</t>
   </si>
   <si>
     <t xml:space="preserve">1.84668505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86452734470367</t>
+    <t xml:space="preserve">1.86452746391296</t>
   </si>
   <si>
     <t xml:space="preserve">1.80207920074463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75747334957123</t>
+    <t xml:space="preserve">1.75747323036194</t>
   </si>
   <si>
     <t xml:space="preserve">2.03402996063232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02510905265808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96266078948975</t>
+    <t xml:space="preserve">2.0251088142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96266043186188</t>
   </si>
   <si>
     <t xml:space="preserve">1.92697584629059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9805029630661</t>
+    <t xml:space="preserve">1.98050272464752</t>
   </si>
   <si>
     <t xml:space="preserve">2.07863593101501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10539960861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05187225341797</t>
+    <t xml:space="preserve">2.10539937019348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05187249183655</t>
   </si>
   <si>
     <t xml:space="preserve">2.06079363822937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09647798538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43548345565796</t>
+    <t xml:space="preserve">2.09647822380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4354829788208</t>
   </si>
   <si>
     <t xml:space="preserve">2.46224689483643</t>
@@ -1721,19 +1721,19 @@
     <t xml:space="preserve">2.39087748527527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56037974357605</t>
+    <t xml:space="preserve">2.56037998199463</t>
   </si>
   <si>
     <t xml:space="preserve">2.60498595237732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65005493164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61399960517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64104104042053</t>
+    <t xml:space="preserve">2.65005469322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61399984359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64104127883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.74019289016724</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">2.73117876052856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90244102478027</t>
+    <t xml:space="preserve">2.90244078636169</t>
   </si>
   <si>
     <t xml:space="preserve">3.10074472427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99257898330688</t>
+    <t xml:space="preserve">2.99257874488831</t>
   </si>
   <si>
     <t xml:space="preserve">2.92948222160339</t>
@@ -1769,34 +1769,34 @@
     <t xml:space="preserve">2.87539958953857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82131671905518</t>
+    <t xml:space="preserve">2.82131695747375</t>
   </si>
   <si>
     <t xml:space="preserve">2.77624773979187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72216534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55991697311401</t>
+    <t xml:space="preserve">2.72216510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55991673469543</t>
   </si>
   <si>
     <t xml:space="preserve">2.53287553787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58695816993713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67709636688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52386140823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6230137348175</t>
+    <t xml:space="preserve">2.58695840835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65906858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67709612846375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5238618850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62301349639893</t>
   </si>
   <si>
     <t xml:space="preserve">2.57794451713562</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">2.51484799385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56893038749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79427528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83033084869385</t>
+    <t xml:space="preserve">2.56893062591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79427552223206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83033061027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.71315121650696</t>
@@ -1829,64 +1829,64 @@
     <t xml:space="preserve">2.74920630455017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80328917503357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86638569831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0015926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09173035621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96553754806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93849635124207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81230306625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54188919067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47879242897034</t>
+    <t xml:space="preserve">2.80328893661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86638593673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00159287452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09173059463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96553730964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93849611282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81230282783508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54188942909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4787929058075</t>
   </si>
   <si>
     <t xml:space="preserve">2.63202738761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91145467758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97455096244812</t>
+    <t xml:space="preserve">2.91145443916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97455143928528</t>
   </si>
   <si>
     <t xml:space="preserve">2.95652365684509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01060652732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01961994171143</t>
+    <t xml:space="preserve">3.01060628890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01962041854858</t>
   </si>
   <si>
     <t xml:space="preserve">2.98356509208679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88441348075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94751000404358</t>
+    <t xml:space="preserve">2.88441324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94751024246216</t>
   </si>
   <si>
     <t xml:space="preserve">2.92046856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85737204551697</t>
+    <t xml:space="preserve">2.85737180709839</t>
   </si>
   <si>
     <t xml:space="preserve">2.75822019577026</t>
@@ -1901,25 +1901,25 @@
     <t xml:space="preserve">2.19035148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28048920631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41569638252258</t>
+    <t xml:space="preserve">2.28048944473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.415696144104</t>
   </si>
   <si>
     <t xml:space="preserve">2.31654453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36161351203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50583434104919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48780655860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4427375793457</t>
+    <t xml:space="preserve">2.36161327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50583410263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48780679702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44273734092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.37964105606079</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">2.27147555351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26246166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28950333595276</t>
+    <t xml:space="preserve">2.26246190071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28950309753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.30753064155579</t>
@@ -1943,13 +1943,13 @@
     <t xml:space="preserve">2.32555818557739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29851698875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34358596801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21739268302917</t>
+    <t xml:space="preserve">2.29851675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.343585729599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21739292144775</t>
   </si>
   <si>
     <t xml:space="preserve">2.20837903022766</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">2.23598384857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21758079528809</t>
+    <t xml:space="preserve">2.21758055686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.24518537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18077397346497</t>
+    <t xml:space="preserve">2.18077421188354</t>
   </si>
   <si>
     <t xml:space="preserve">2.16237092018127</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">2.1715726852417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11636304855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08875846862793</t>
+    <t xml:space="preserve">2.11636328697205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08875823020935</t>
   </si>
   <si>
     <t xml:space="preserve">2.07035541534424</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">2.05195212364197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97833967208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98754107952118</t>
+    <t xml:space="preserve">1.97833955287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98754119873047</t>
   </si>
   <si>
     <t xml:space="preserve">2.07955694198608</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">2.09795999526978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13476610183716</t>
+    <t xml:space="preserve">2.13476634025574</t>
   </si>
   <si>
     <t xml:space="preserve">2.10716152191162</t>
@@ -2021,25 +2021,25 @@
     <t xml:space="preserve">2.14396786689758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12556481361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99674272537231</t>
+    <t xml:space="preserve">2.12556457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99674260616302</t>
   </si>
   <si>
     <t xml:space="preserve">1.9691379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95073485374451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00594425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93233156204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91392838954926</t>
+    <t xml:space="preserve">1.95073461532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00594449043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93233144283295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91392827033997</t>
   </si>
   <si>
     <t xml:space="preserve">1.90472686290741</t>
@@ -2048,19 +2048,19 @@
     <t xml:space="preserve">1.9231299161911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94153296947479</t>
+    <t xml:space="preserve">1.94153320789337</t>
   </si>
   <si>
     <t xml:space="preserve">1.88632369041443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86792051792145</t>
+    <t xml:space="preserve">1.86792063713074</t>
   </si>
   <si>
     <t xml:space="preserve">1.84951746463776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89552521705627</t>
+    <t xml:space="preserve">1.89552533626556</t>
   </si>
   <si>
     <t xml:space="preserve">1.8587189912796</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">1.87712204456329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83111417293549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271111965179</t>
+    <t xml:space="preserve">1.83111429214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8127110004425</t>
   </si>
   <si>
     <t xml:space="preserve">1.80350959300995</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">1.8357150554657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82651352882385</t>
+    <t xml:space="preserve">1.82651340961456</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031581878662</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">1.82191264629364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02434754371643</t>
+    <t xml:space="preserve">2.02434730529785</t>
   </si>
   <si>
     <t xml:space="preserve">2.31879782676697</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">2.25438690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30959630012512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28199172019958</t>
+    <t xml:space="preserve">2.3095965385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28199148178101</t>
   </si>
   <si>
     <t xml:space="preserve">2.26358842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30039477348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27278995513916</t>
+    <t xml:space="preserve">2.3003945350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27279019355774</t>
   </si>
   <si>
     <t xml:space="preserve">2.33720111846924</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">2.15316939353943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23669123649597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1989414691925</t>
+    <t xml:space="preserve">2.23669147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19894123077393</t>
   </si>
   <si>
     <t xml:space="preserve">2.18006634712219</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">2.20837879180908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11400365829468</t>
+    <t xml:space="preserve">2.11400389671326</t>
   </si>
   <si>
     <t xml:space="preserve">2.09512877464294</t>
@@ -2165,25 +2165,25 @@
     <t xml:space="preserve">1.98187851905823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91581583023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94412839412689</t>
+    <t xml:space="preserve">1.91581594944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94412851333618</t>
   </si>
   <si>
     <t xml:space="preserve">1.93469095230103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00075364112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03850364685059</t>
+    <t xml:space="preserve">2.00075340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03850388526917</t>
   </si>
   <si>
     <t xml:space="preserve">2.0101912021637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01962852478027</t>
+    <t xml:space="preserve">2.01962876319885</t>
   </si>
   <si>
     <t xml:space="preserve">2.0573787689209</t>
@@ -2192,19 +2192,19 @@
     <t xml:space="preserve">2.16119122505188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17062878608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22725391387939</t>
+    <t xml:space="preserve">2.17062902450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22725367546082</t>
   </si>
   <si>
     <t xml:space="preserve">2.24612903594971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26500415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.368816614151</t>
+    <t xml:space="preserve">2.26500391960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36881685256958</t>
   </si>
   <si>
     <t xml:space="preserve">2.34994173049927</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18950366973877</t>
+    <t xml:space="preserve">2.18950390815735</t>
   </si>
   <si>
     <t xml:space="preserve">2.21781635284424</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">1.95356595516205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97244083881378</t>
+    <t xml:space="preserve">1.97244107723236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92525339126587</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">1.85447204113007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86862826347351</t>
+    <t xml:space="preserve">1.8686283826828</t>
   </si>
   <si>
     <t xml:space="preserve">1.79312813282013</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.82144069671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8450345993042</t>
+    <t xml:space="preserve">1.84503448009491</t>
   </si>
   <si>
     <t xml:space="preserve">1.81672191619873</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">1.80256569385529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82615947723389</t>
+    <t xml:space="preserve">1.8261593580246</t>
   </si>
   <si>
     <t xml:space="preserve">1.83559703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87334716320038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83087825775146</t>
+    <t xml:space="preserve">1.87334704399109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83087837696075</t>
   </si>
   <si>
     <t xml:space="preserve">1.85919082164764</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">1.75537812709808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74594068527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76481556892395</t>
+    <t xml:space="preserve">1.74594056606293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76481568813324</t>
   </si>
   <si>
     <t xml:space="preserve">1.76009690761566</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">1.71290934085846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73178434371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70347166061401</t>
+    <t xml:space="preserve">1.73178446292877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7034717798233</t>
   </si>
   <si>
     <t xml:space="preserve">1.67987787723541</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">1.69875299930573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74122178554535</t>
+    <t xml:space="preserve">1.74122190475464</t>
   </si>
   <si>
     <t xml:space="preserve">1.7270655632019</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">1.78840935230255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77897191047668</t>
+    <t xml:space="preserve">1.7789717912674</t>
   </si>
   <si>
     <t xml:space="preserve">1.77425312995911</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">1.96300339698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02906632423401</t>
+    <t xml:space="preserve">2.02906608581543</t>
   </si>
   <si>
     <t xml:space="preserve">2.07625389099121</t>
@@ -5552,7 +5552,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G100" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H100" t="s">
         <v>9</v>
@@ -5578,7 +5578,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G101" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H101" t="s">
         <v>9</v>
@@ -5604,7 +5604,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G102" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H102" t="s">
         <v>9</v>
@@ -5630,7 +5630,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G103" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H103" t="s">
         <v>9</v>
@@ -5656,7 +5656,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G104" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H104" t="s">
         <v>9</v>
@@ -5682,7 +5682,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G105" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H105" t="s">
         <v>9</v>
@@ -5708,7 +5708,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G106" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H106" t="s">
         <v>9</v>
@@ -5734,7 +5734,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G107" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H107" t="s">
         <v>9</v>
@@ -5760,7 +5760,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G108" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H108" t="s">
         <v>9</v>
@@ -5786,7 +5786,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G109" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H109" t="s">
         <v>9</v>
@@ -5812,7 +5812,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G110" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s">
         <v>9</v>
@@ -5838,7 +5838,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G111" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H111" t="s">
         <v>9</v>
@@ -5864,7 +5864,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G112" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H112" t="s">
         <v>9</v>
@@ -5890,7 +5890,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G113" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s">
         <v>9</v>
@@ -5916,7 +5916,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G114" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H114" t="s">
         <v>9</v>
@@ -5942,7 +5942,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G115" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H115" t="s">
         <v>9</v>
@@ -5968,7 +5968,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G116" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H116" t="s">
         <v>9</v>
@@ -5994,7 +5994,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G117" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H117" t="s">
         <v>9</v>
@@ -6020,7 +6020,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G118" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H118" t="s">
         <v>9</v>
@@ -6046,7 +6046,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G119" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -6072,7 +6072,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G120" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -6098,7 +6098,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G121" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -6124,7 +6124,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G122" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -6150,7 +6150,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G123" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -6176,7 +6176,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G124" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -6202,7 +6202,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G125" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -6228,7 +6228,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G126" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -6254,7 +6254,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G127" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -6280,7 +6280,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G128" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -6306,7 +6306,7 @@
         <v>1.75</v>
       </c>
       <c r="G129" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -6332,7 +6332,7 @@
         <v>1.75</v>
       </c>
       <c r="G130" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -6358,7 +6358,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G131" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -6384,7 +6384,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G132" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -6410,7 +6410,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G133" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -6436,7 +6436,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G134" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -6462,7 +6462,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G135" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -6488,7 +6488,7 @@
         <v>1.75</v>
       </c>
       <c r="G136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6514,7 +6514,7 @@
         <v>1.75</v>
       </c>
       <c r="G137" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6540,7 +6540,7 @@
         <v>1.75</v>
       </c>
       <c r="G138" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6566,7 +6566,7 @@
         <v>1.75</v>
       </c>
       <c r="G139" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6592,7 +6592,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G140" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6618,7 +6618,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G141" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6644,7 +6644,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G142" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -6670,7 +6670,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G143" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6696,7 +6696,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G144" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6722,7 +6722,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G145" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6748,7 +6748,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G146" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6774,7 +6774,7 @@
         <v>1.75</v>
       </c>
       <c r="G147" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6800,7 +6800,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G148" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6826,7 +6826,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G149" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6852,7 +6852,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G150" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6878,7 +6878,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G151" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6904,7 +6904,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G152" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6930,7 +6930,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G153" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6956,7 +6956,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G154" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6982,7 +6982,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G155" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -7008,7 +7008,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G156" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -7034,7 +7034,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G157" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -7060,7 +7060,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -7086,7 +7086,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G159" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -7112,7 +7112,7 @@
         <v>1.75</v>
       </c>
       <c r="G160" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -7138,7 +7138,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G161" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -7164,7 +7164,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G162" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -7190,7 +7190,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G163" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -7216,7 +7216,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G164" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -7242,7 +7242,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G165" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7268,7 +7268,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G166" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7294,7 +7294,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G167" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7320,7 +7320,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G168" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7346,7 +7346,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G169" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7372,7 +7372,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G170" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7398,7 +7398,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G171" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7424,7 +7424,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G172" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7450,7 +7450,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G173" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7476,7 +7476,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G174" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7502,7 +7502,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G175" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7528,7 +7528,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G176" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7554,7 +7554,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G177" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7580,7 +7580,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G178" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7606,7 +7606,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G179" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7632,7 +7632,7 @@
         <v>1.75</v>
       </c>
       <c r="G180" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7658,7 +7658,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G181" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7684,7 +7684,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G182" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7710,7 +7710,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G183" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7736,7 +7736,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G184" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7762,7 +7762,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G185" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7788,7 +7788,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G186" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7814,7 +7814,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G187" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7840,7 +7840,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G188" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7866,7 +7866,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7892,7 +7892,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G190" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7918,7 +7918,7 @@
         <v>1.75</v>
       </c>
       <c r="G191" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7944,7 +7944,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G192" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7970,7 +7970,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G193" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7996,7 +7996,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G194" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -8022,7 +8022,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G195" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -8048,7 +8048,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G196" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -8074,7 +8074,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G197" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -8100,7 +8100,7 @@
         <v>1.75</v>
       </c>
       <c r="G198" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -8126,7 +8126,7 @@
         <v>1.75</v>
       </c>
       <c r="G199" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -8152,7 +8152,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G200" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -8178,7 +8178,7 @@
         <v>1.75</v>
       </c>
       <c r="G201" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -8204,7 +8204,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G202" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -8230,7 +8230,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G203" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8256,7 +8256,7 @@
         <v>1.75</v>
       </c>
       <c r="G204" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8282,7 +8282,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G205" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8308,7 +8308,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G206" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8334,7 +8334,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G207" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8360,7 +8360,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G208" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8386,7 +8386,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G209" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8412,7 +8412,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G210" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8438,7 +8438,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G211" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8464,7 +8464,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G212" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8490,7 +8490,7 @@
         <v>1.75</v>
       </c>
       <c r="G213" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8516,7 +8516,7 @@
         <v>1.75</v>
       </c>
       <c r="G214" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8542,7 +8542,7 @@
         <v>1.75</v>
       </c>
       <c r="G215" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8568,7 +8568,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G216" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8594,7 +8594,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G217" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8620,7 +8620,7 @@
         <v>1.75</v>
       </c>
       <c r="G218" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8646,7 +8646,7 @@
         <v>1.75</v>
       </c>
       <c r="G219" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8672,7 +8672,7 @@
         <v>1.75</v>
       </c>
       <c r="G220" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8698,7 +8698,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G221" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8724,7 +8724,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G222" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8750,7 +8750,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G223" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8776,7 +8776,7 @@
         <v>1.75</v>
       </c>
       <c r="G224" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8802,7 +8802,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G225" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8828,7 +8828,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G226" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8854,7 +8854,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G227" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8880,7 +8880,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G228" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8906,7 +8906,7 @@
         <v>1.75</v>
       </c>
       <c r="G229" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8932,7 +8932,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G230" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8958,7 +8958,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G231" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8984,7 +8984,7 @@
         <v>1.75</v>
       </c>
       <c r="G232" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -9010,7 +9010,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9036,7 +9036,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G234" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9062,7 +9062,7 @@
         <v>1.75</v>
       </c>
       <c r="G235" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9088,7 +9088,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G236" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9114,7 +9114,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G237" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9140,7 +9140,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G238" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -9166,7 +9166,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G239" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -9192,7 +9192,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G240" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9218,7 +9218,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G241" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9244,7 +9244,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G242" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9270,7 +9270,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G243" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9296,7 +9296,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G244" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9322,7 +9322,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G245" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9348,7 +9348,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G246" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9374,7 +9374,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G247" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9400,7 +9400,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G248" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9426,7 +9426,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G249" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9452,7 +9452,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G250" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9478,7 +9478,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G251" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9504,7 +9504,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G252" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9530,7 +9530,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G253" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9556,7 +9556,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G254" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9582,7 +9582,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G255" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9608,7 +9608,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G256" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9634,7 +9634,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G257" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9660,7 +9660,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G258" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9686,7 +9686,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G259" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9712,7 +9712,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G260" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9738,7 +9738,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G261" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9764,7 +9764,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G262" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9790,7 +9790,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9816,7 +9816,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G264" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9842,7 +9842,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G265" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9868,7 +9868,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G266" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9894,7 +9894,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G267" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9920,7 +9920,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G268" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9946,7 +9946,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G269" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9972,7 +9972,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G270" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9998,7 +9998,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G271" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10024,7 +10024,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G272" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10050,7 +10050,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G273" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10076,7 +10076,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G274" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10102,7 +10102,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G275" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10128,7 +10128,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G276" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10154,7 +10154,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G277" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10180,7 +10180,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G278" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10206,7 +10206,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G279" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10232,7 +10232,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G280" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10258,7 +10258,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G281" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10284,7 +10284,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G282" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10310,7 +10310,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G283" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10336,7 +10336,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G284" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10362,7 +10362,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G285" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10388,7 +10388,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G286" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10414,7 +10414,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G287" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10440,7 +10440,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G288" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10466,7 +10466,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G289" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10492,7 +10492,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G290" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10518,7 +10518,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G291" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10544,7 +10544,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G292" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10570,7 +10570,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G293" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10596,7 +10596,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G294" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10622,7 +10622,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G295" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10648,7 +10648,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G296" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10674,7 +10674,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G297" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10700,7 +10700,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G298" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10726,7 +10726,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G299" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10752,7 +10752,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G300" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10778,7 +10778,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G301" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10804,7 +10804,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G302" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10830,7 +10830,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G303" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10856,7 +10856,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G304" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10882,7 +10882,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G305" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10908,7 +10908,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G306" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10934,7 +10934,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G307" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10960,7 +10960,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10986,7 +10986,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G309" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11012,7 +11012,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G310" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11038,7 +11038,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G311" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11064,7 +11064,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G312" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11090,7 +11090,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G313" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11116,7 +11116,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G314" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11142,7 +11142,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G315" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11168,7 +11168,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11194,7 +11194,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G317" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11220,7 +11220,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G318" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11246,7 +11246,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G319" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11272,7 +11272,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G320" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11298,7 +11298,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G321" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11324,7 +11324,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G322" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11350,7 +11350,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G323" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11376,7 +11376,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G324" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11402,7 +11402,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G325" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11428,7 +11428,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G326" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11454,7 +11454,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G327" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11480,7 +11480,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G328" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11506,7 +11506,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G329" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11532,7 +11532,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G330" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11558,7 +11558,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G331" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11584,7 +11584,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G332" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11610,7 +11610,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G333" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11636,7 +11636,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G334" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11662,7 +11662,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G335" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11688,7 +11688,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G336" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11714,7 +11714,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G337" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -11740,7 +11740,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G338" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11766,7 +11766,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G339" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11792,7 +11792,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G340" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11818,7 +11818,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G341" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11844,7 +11844,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G342" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11870,7 +11870,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G343" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11896,7 +11896,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G344" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11922,7 +11922,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G345" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11948,7 +11948,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G346" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11974,7 +11974,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G347" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -12000,7 +12000,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G348" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12026,7 +12026,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G349" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12052,7 +12052,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G350" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12078,7 +12078,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G351" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12104,7 +12104,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G352" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12130,7 +12130,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G353" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12156,7 +12156,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G354" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12182,7 +12182,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G355" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12208,7 +12208,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G356" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12234,7 +12234,7 @@
         <v>2.75</v>
       </c>
       <c r="G357" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12260,7 +12260,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G358" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12286,7 +12286,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G359" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12312,7 +12312,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G360" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12338,7 +12338,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G361" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12364,7 +12364,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G362" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12390,7 +12390,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G363" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12416,7 +12416,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G364" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12442,7 +12442,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G365" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12468,7 +12468,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G366" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12494,7 +12494,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G367" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12520,7 +12520,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G368" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12546,7 +12546,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G369" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12572,7 +12572,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G370" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12598,7 +12598,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G371" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12624,7 +12624,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G372" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12650,7 +12650,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G373" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12676,7 +12676,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G374" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12702,7 +12702,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G375" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12728,7 +12728,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G376" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12754,7 +12754,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G377" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12780,7 +12780,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G378" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12806,7 +12806,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G379" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12832,7 +12832,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G380" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12858,7 +12858,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G381" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12884,7 +12884,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G382" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12910,7 +12910,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G383" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12936,7 +12936,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G384" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12962,7 +12962,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G385" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12988,7 +12988,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G386" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13014,7 +13014,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G387" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13040,7 +13040,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G388" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13066,7 +13066,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G389" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13092,7 +13092,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G390" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13118,7 +13118,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G391" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13144,7 +13144,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G392" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13170,7 +13170,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G393" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13196,7 +13196,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G394" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13222,7 +13222,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G395" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13248,7 +13248,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G396" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13274,7 +13274,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G397" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13300,7 +13300,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G398" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13326,7 +13326,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13352,7 +13352,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13378,7 +13378,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G401" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13404,7 +13404,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G402" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13430,7 +13430,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G403" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13456,7 +13456,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G404" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13482,7 +13482,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G405" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13508,7 +13508,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G406" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13534,7 +13534,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G407" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13560,7 +13560,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G408" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13586,7 +13586,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G409" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13612,7 +13612,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G410" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13638,7 +13638,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G411" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13664,7 +13664,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G412" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13690,7 +13690,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G413" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13716,7 +13716,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G414" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13742,7 +13742,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G415" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13768,7 +13768,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G416" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13794,7 +13794,7 @@
         <v>2.25</v>
       </c>
       <c r="G417" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13820,7 +13820,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G418" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13846,7 +13846,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G419" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13872,7 +13872,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G420" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13898,7 +13898,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G421" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13924,7 +13924,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G422" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13950,7 +13950,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13976,7 +13976,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G424" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14002,7 +14002,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G425" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14028,7 +14028,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G426" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14054,7 +14054,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G427" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14080,7 +14080,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14106,7 +14106,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G429" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14132,7 +14132,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G430" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14158,7 +14158,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G431" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14184,7 +14184,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G432" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14210,7 +14210,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G433" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14236,7 +14236,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G434" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14262,7 +14262,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G435" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14288,7 +14288,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G436" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14314,7 +14314,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G437" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14340,7 +14340,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G438" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14366,7 +14366,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14392,7 +14392,7 @@
         <v>2.75</v>
       </c>
       <c r="G440" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14418,7 +14418,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G441" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14444,7 +14444,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G442" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14470,7 +14470,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G443" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14496,7 +14496,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G444" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14522,7 +14522,7 @@
         <v>2.75</v>
       </c>
       <c r="G445" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14548,7 +14548,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G446" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14574,7 +14574,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G447" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14600,7 +14600,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G448" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14626,7 +14626,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G449" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14652,7 +14652,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G450" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14678,7 +14678,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G451" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14704,7 +14704,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G452" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14730,7 +14730,7 @@
         <v>2.75</v>
       </c>
       <c r="G453" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14756,7 +14756,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G454" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14782,7 +14782,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G455" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14808,7 +14808,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G456" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14834,7 +14834,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G457" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14860,7 +14860,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G458" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14886,7 +14886,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G459" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14912,7 +14912,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G460" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14938,7 +14938,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G461" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14964,7 +14964,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G462" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14990,7 +14990,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G463" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15016,7 +15016,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15042,7 +15042,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G465" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15068,7 +15068,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G466" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15094,7 +15094,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G467" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15120,7 +15120,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G468" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15146,7 +15146,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G469" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15172,7 +15172,7 @@
         <v>2.75</v>
       </c>
       <c r="G470" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15198,7 +15198,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G471" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15224,7 +15224,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G472" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15250,7 +15250,7 @@
         <v>2.75</v>
       </c>
       <c r="G473" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15276,7 +15276,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G474" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15302,7 +15302,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G475" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15328,7 +15328,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G476" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15354,7 +15354,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G477" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15380,7 +15380,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G478" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15406,7 +15406,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G479" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15432,7 +15432,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G480" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15458,7 +15458,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G481" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15484,7 +15484,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G482" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15510,7 +15510,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G483" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15536,7 +15536,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G484" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15562,7 +15562,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G485" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15588,7 +15588,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G486" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15614,7 +15614,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G487" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15640,7 +15640,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G488" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15666,7 +15666,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G489" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15692,7 +15692,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G490" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15718,7 +15718,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G491" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15744,7 +15744,7 @@
         <v>2.75</v>
       </c>
       <c r="G492" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15770,7 +15770,7 @@
         <v>2.75</v>
       </c>
       <c r="G493" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15796,7 +15796,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G494" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15822,7 +15822,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G495" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15848,7 +15848,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G496" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15874,7 +15874,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G497" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15900,7 +15900,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G498" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15926,7 +15926,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G499" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15952,7 +15952,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G500" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15978,7 +15978,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G501" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16004,7 +16004,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G502" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16030,7 +16030,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G503" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16056,7 +16056,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G504" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16082,7 +16082,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G505" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16108,7 +16108,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G506" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16134,7 +16134,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G507" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16160,7 +16160,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G508" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16186,7 +16186,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G509" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16212,7 +16212,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G510" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16238,7 +16238,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G511" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16264,7 +16264,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G512" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16290,7 +16290,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G513" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16316,7 +16316,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G514" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16342,7 +16342,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G515" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16368,7 +16368,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G516" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16394,7 +16394,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G517" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16420,7 +16420,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16446,7 +16446,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16472,7 +16472,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16498,7 +16498,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G521" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16524,7 +16524,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G522" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16550,7 +16550,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16576,7 +16576,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G524" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16602,7 +16602,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G525" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16628,7 +16628,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G526" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16654,7 +16654,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G527" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16680,7 +16680,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G528" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16706,7 +16706,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G529" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16732,7 +16732,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G530" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16758,7 +16758,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G531" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16784,7 +16784,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G532" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16810,7 +16810,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G533" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16836,7 +16836,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G534" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16862,7 +16862,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G535" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16888,7 +16888,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G536" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16914,7 +16914,7 @@
         <v>2.75</v>
       </c>
       <c r="G537" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16940,7 +16940,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G538" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16966,7 +16966,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G539" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16992,7 +16992,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G540" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17018,7 +17018,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G541" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17044,7 +17044,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G542" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17070,7 +17070,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G543" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17096,7 +17096,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17122,7 +17122,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G545" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17148,7 +17148,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G546" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17174,7 +17174,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G547" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17200,7 +17200,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G548" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17226,7 +17226,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G549" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17252,7 +17252,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G550" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17278,7 +17278,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G551" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17304,7 +17304,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G552" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17330,7 +17330,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G553" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17356,7 +17356,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G554" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17382,7 +17382,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G555" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17408,7 +17408,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G556" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17434,7 +17434,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G557" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17460,7 +17460,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G558" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17486,7 +17486,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G559" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17512,7 +17512,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G560" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17538,7 +17538,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17564,7 +17564,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17590,7 +17590,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G563" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17616,7 +17616,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G564" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17642,7 +17642,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G565" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17668,7 +17668,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G566" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17694,7 +17694,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G567" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17720,7 +17720,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G568" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17746,7 +17746,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G569" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17772,7 +17772,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G570" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17798,7 +17798,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G571" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17824,7 +17824,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17850,7 +17850,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G573" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17876,7 +17876,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G574" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17902,7 +17902,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G575" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17928,7 +17928,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G576" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17954,7 +17954,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G577" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17980,7 +17980,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G578" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18006,7 +18006,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G579" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18032,7 +18032,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18058,7 +18058,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18084,7 +18084,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G582" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18110,7 +18110,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G583" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18136,7 +18136,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G584" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18162,7 +18162,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G585" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18188,7 +18188,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G586" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18214,7 +18214,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G587" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18240,7 +18240,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G588" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18266,7 +18266,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G589" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18292,7 +18292,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G590" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18318,7 +18318,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G591" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18344,7 +18344,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G592" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18370,7 +18370,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G593" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18396,7 +18396,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G594" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18422,7 +18422,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G595" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18448,7 +18448,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G596" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18474,7 +18474,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G597" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18500,7 +18500,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G598" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18526,7 +18526,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G599" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18552,7 +18552,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G600" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18578,7 +18578,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G601" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18604,7 +18604,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G602" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18630,7 +18630,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18656,7 +18656,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G604" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18682,7 +18682,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G605" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18708,7 +18708,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G606" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18734,7 +18734,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G607" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18760,7 +18760,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G608" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18786,7 +18786,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G609" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18812,7 +18812,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G610" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18838,7 +18838,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18864,7 +18864,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G612" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18890,7 +18890,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G613" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18916,7 +18916,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G614" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18942,7 +18942,7 @@
         <v>2.5</v>
       </c>
       <c r="G615" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18968,7 +18968,7 @@
         <v>2.5</v>
       </c>
       <c r="G616" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18994,7 +18994,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G617" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19020,7 +19020,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G618" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19072,7 +19072,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G620" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19514,7 +19514,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19540,7 +19540,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19670,7 +19670,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G643" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19774,7 +19774,7 @@
         <v>2.5</v>
       </c>
       <c r="G647" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19852,7 +19852,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G650" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19878,7 +19878,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G651" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19904,7 +19904,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G652" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19956,7 +19956,7 @@
         <v>2.5</v>
       </c>
       <c r="G654" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20086,7 +20086,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20216,7 +20216,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G664" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -70971,6 +70971,32 @@
         <v>856</v>
       </c>
       <c r="H2616" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2617">
+      <c r="A2617" s="1" t="n">
+        <v>46133.2916666667</v>
+      </c>
+      <c r="B2617" t="n">
+        <v>3302</v>
+      </c>
+      <c r="C2617" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D2617" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="E2617" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="F2617" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G2617" t="s">
+        <v>858</v>
+      </c>
+      <c r="H2617" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRC.MI.xlsx
+++ b/data/IRC.MI.xlsx
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75034129619598</t>
+    <t xml:space="preserve">1.75034153461456</t>
   </si>
   <si>
     <t xml:space="preserve">IRC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74538779258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69254744052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245492458344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67603468894958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66612708568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63888120651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61163520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59347140789032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48613917827606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59264600276947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59182035923004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58604061603546</t>
+    <t xml:space="preserve">1.74538791179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69254732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245480537415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68429100513458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67603433132172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66612696647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63888108730316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61163532733917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59347128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48613905906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59264576435089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59182012081146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58604049682617</t>
   </si>
   <si>
     <t xml:space="preserve">1.60172784328461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58521497249603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56044602394104</t>
+    <t xml:space="preserve">1.58521509170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56044590473175</t>
   </si>
   <si>
     <t xml:space="preserve">1.51255929470062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53980529308319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56539976596832</t>
+    <t xml:space="preserve">1.53980541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5654000043869</t>
   </si>
   <si>
     <t xml:space="preserve">1.53567707538605</t>
@@ -107,73 +107,73 @@
     <t xml:space="preserve">1.45311379432678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50595438480377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46137011051178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44238042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51833891868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6512656211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6347531080246</t>
+    <t xml:space="preserve">1.50595426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46137022972107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44238078594208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51833879947662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65126574039459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63475298881531</t>
   </si>
   <si>
     <t xml:space="preserve">1.65621960163116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64300930500031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6372298002243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64218378067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63970685005188</t>
+    <t xml:space="preserve">1.64300942420959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63723015785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64218366146088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63970673084259</t>
   </si>
   <si>
     <t xml:space="preserve">1.66777837276459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60503041744232</t>
+    <t xml:space="preserve">1.60503017902374</t>
   </si>
   <si>
     <t xml:space="preserve">1.5984251499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56870222091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64053249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227605819702</t>
+    <t xml:space="preserve">1.56870245933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64053237438202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227617740631</t>
   </si>
   <si>
     <t xml:space="preserve">1.60255324840546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57283055782318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58934319019318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5843893289566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56787669658661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55714344978333</t>
+    <t xml:space="preserve">1.57283043861389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58934330940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58438944816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56787693500519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55714356899261</t>
   </si>
   <si>
     <t xml:space="preserve">1.53402590751648</t>
@@ -182,82 +182,82 @@
     <t xml:space="preserve">1.54310774803162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55466663837433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5596204996109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55218970775604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55053865909576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50265192985535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696494102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48861598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237462043762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49026727676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51503622531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48779046535492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623145580292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50760567188263</t>
+    <t xml:space="preserve">1.55466651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962038040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55218958854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55053853988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50265181064606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696482181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48861587047577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237450122833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49026715755463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5150363445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48779034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47623133659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50760543346405</t>
   </si>
   <si>
     <t xml:space="preserve">1.5010005235672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49439537525177</t>
+    <t xml:space="preserve">1.49439549446106</t>
   </si>
   <si>
     <t xml:space="preserve">1.48366236686707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45971894264221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45299983024597</t>
+    <t xml:space="preserve">1.45971882343292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45299971103668</t>
   </si>
   <si>
     <t xml:space="preserve">1.46223855018616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43284237384796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43536198139191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43200278282166</t>
+    <t xml:space="preserve">1.43284273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43536221981049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43200266361237</t>
   </si>
   <si>
     <t xml:space="preserve">1.4261234998703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41100561618805</t>
+    <t xml:space="preserve">1.41100537776947</t>
   </si>
   <si>
     <t xml:space="preserve">1.44040167331696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43620204925537</t>
+    <t xml:space="preserve">1.43620193004608</t>
   </si>
   <si>
     <t xml:space="preserve">1.4429212808609</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">1.44880044460297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.478196144104</t>
+    <t xml:space="preserve">1.47819626331329</t>
   </si>
   <si>
     <t xml:space="preserve">1.44460093975067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42360401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43032288551331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46139860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40260672569275</t>
+    <t xml:space="preserve">1.42360389232635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43032276630402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46139872074127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40260648727417</t>
   </si>
   <si>
     <t xml:space="preserve">1.4084860086441</t>
@@ -290,43 +290,43 @@
     <t xml:space="preserve">1.37825000286102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42444372177124</t>
+    <t xml:space="preserve">1.42444360256195</t>
   </si>
   <si>
     <t xml:space="preserve">1.41604483127594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46979737281799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42780315876007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192411422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47567665576935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4479603767395</t>
+    <t xml:space="preserve">1.46979749202728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42780327796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192387580872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47567677497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44796049594879</t>
   </si>
   <si>
     <t xml:space="preserve">1.47735631465912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43368232250214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45803916454315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4521598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48491549491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46391820907593</t>
+    <t xml:space="preserve">1.43368256092072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45803892612457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45215976238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48491537570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46391832828522</t>
   </si>
   <si>
     <t xml:space="preserve">1.46643793582916</t>
@@ -338,31 +338,31 @@
     <t xml:space="preserve">1.48575520515442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45887911319733</t>
+    <t xml:space="preserve">1.45887899398804</t>
   </si>
   <si>
     <t xml:space="preserve">1.4563592672348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45719933509827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48827493190765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43956160545349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47399699687958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46727776527405</t>
+    <t xml:space="preserve">1.45719921588898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48827469348907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43956172466278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.473996758461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46727788448334</t>
   </si>
   <si>
     <t xml:space="preserve">1.4983537197113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50927209854126</t>
+    <t xml:space="preserve">1.50927221775055</t>
   </si>
   <si>
     <t xml:space="preserve">1.5033928155899</t>
@@ -371,76 +371,76 @@
     <t xml:space="preserve">1.4949939250946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48743510246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51011192798615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4991934299469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179170608521</t>
+    <t xml:space="preserve">1.48743498325348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51011180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49919331073761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179158687592</t>
   </si>
   <si>
     <t xml:space="preserve">1.45048010349274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44628071784973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4387218952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50003337860107</t>
+    <t xml:space="preserve">1.44628059864044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43872165679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50003325939178</t>
   </si>
   <si>
     <t xml:space="preserve">1.48071599006653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4815559387207</t>
+    <t xml:space="preserve">1.48155581951141</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095187664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49583387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5075923204422</t>
+    <t xml:space="preserve">1.49583375453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50759208202362</t>
   </si>
   <si>
     <t xml:space="preserve">1.49667370319366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47231721878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49331438541412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47147715091705</t>
+    <t xml:space="preserve">1.47231709957123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49331426620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47147727012634</t>
   </si>
   <si>
     <t xml:space="preserve">1.50087320804596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52774953842163</t>
+    <t xml:space="preserve">1.52774941921234</t>
   </si>
   <si>
     <t xml:space="preserve">1.53194892406464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52690970897675</t>
+    <t xml:space="preserve">1.52690958976746</t>
   </si>
   <si>
     <t xml:space="preserve">1.52355003356934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50423264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51263153553009</t>
+    <t xml:space="preserve">1.50423276424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51263165473938</t>
   </si>
   <si>
     <t xml:space="preserve">1.54454720020294</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">1.54538702964783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55294597148895</t>
+    <t xml:space="preserve">1.55294585227966</t>
   </si>
   <si>
     <t xml:space="preserve">1.52019047737122</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">1.59578013420105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53446853160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56050503253937</t>
+    <t xml:space="preserve">1.53446865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56050491333008</t>
   </si>
   <si>
     <t xml:space="preserve">1.53026914596558</t>
@@ -473,43 +473,43 @@
     <t xml:space="preserve">1.53110909461975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55126631259918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55210614204407</t>
+    <t xml:space="preserve">1.55126619338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55210626125336</t>
   </si>
   <si>
     <t xml:space="preserve">1.55378580093384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58654153347015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56218481063843</t>
+    <t xml:space="preserve">1.58654129505157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56218469142914</t>
   </si>
   <si>
     <t xml:space="preserve">1.56974363327026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57058370113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60333919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54958641529083</t>
+    <t xml:space="preserve">1.57058358192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60333895683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54958653450012</t>
   </si>
   <si>
     <t xml:space="preserve">1.55798530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57142353057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56470441818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61089777946472</t>
+    <t xml:space="preserve">1.57142341136932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56470429897308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61089789867401</t>
   </si>
   <si>
     <t xml:space="preserve">1.61173796653748</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">1.60417890548706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62517607212067</t>
+    <t xml:space="preserve">1.62517583370209</t>
   </si>
   <si>
     <t xml:space="preserve">1.62097644805908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61257755756378</t>
+    <t xml:space="preserve">1.61257791519165</t>
   </si>
   <si>
     <t xml:space="preserve">1.59326028823853</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">1.58822131156921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60753870010376</t>
+    <t xml:space="preserve">1.60753846168518</t>
   </si>
   <si>
     <t xml:space="preserve">1.63105535507202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61425769329071</t>
+    <t xml:space="preserve">1.61425757408142</t>
   </si>
   <si>
     <t xml:space="preserve">1.71504378318787</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">1.76543664932251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75367844104767</t>
+    <t xml:space="preserve">1.75367856025696</t>
   </si>
   <si>
     <t xml:space="preserve">1.72512221336365</t>
@@ -563,52 +563,52 @@
     <t xml:space="preserve">1.72176277637482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70664489269257</t>
+    <t xml:space="preserve">1.70664501190186</t>
   </si>
   <si>
     <t xml:space="preserve">1.73856043815613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69992542266846</t>
+    <t xml:space="preserve">1.69992578029633</t>
   </si>
   <si>
     <t xml:space="preserve">1.67892849445343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69656610488892</t>
+    <t xml:space="preserve">1.69656622409821</t>
   </si>
   <si>
     <t xml:space="preserve">1.69320666790009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70496499538422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77383553981781</t>
+    <t xml:space="preserve">1.70496487617493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7738356590271</t>
   </si>
   <si>
     <t xml:space="preserve">1.75871777534485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68984723091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69152677059174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66801011562347</t>
+    <t xml:space="preserve">1.68984711170197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69152688980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66800999641418</t>
   </si>
   <si>
     <t xml:space="preserve">1.68816733360291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71336376667023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73184156417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535821914673</t>
+    <t xml:space="preserve">1.71336388587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73184132575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535798072815</t>
   </si>
   <si>
     <t xml:space="preserve">1.7100043296814</t>
@@ -620,58 +620,58 @@
     <t xml:space="preserve">1.73016166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77047622203827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76375687122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031876564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78895354270935</t>
+    <t xml:space="preserve">1.74695932865143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77047598361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76375699043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031888484955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78895366191864</t>
   </si>
   <si>
     <t xml:space="preserve">1.74024021625519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76207733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73352110385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903197288513</t>
+    <t xml:space="preserve">1.76207721233368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73352098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903221130371</t>
   </si>
   <si>
     <t xml:space="preserve">1.78055453300476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82254886627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86958253383636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86454272270203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84774529933929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78391444683075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90480971336365</t>
+    <t xml:space="preserve">1.82254898548126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8695821762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86454331874847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84774553775787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78391408920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90480959415436</t>
   </si>
   <si>
     <t xml:space="preserve">1.98488664627075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34267711639404</t>
+    <t xml:space="preserve">2.34267735481262</t>
   </si>
   <si>
     <t xml:space="preserve">2.35119605064392</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">2.24045157432556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18081974983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36482644081116</t>
+    <t xml:space="preserve">2.180819272995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.364825963974</t>
   </si>
   <si>
     <t xml:space="preserve">2.32223224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34608483314514</t>
+    <t xml:space="preserve">2.34608459472656</t>
   </si>
   <si>
     <t xml:space="preserve">2.33415842056274</t>
@@ -701,67 +701,67 @@
     <t xml:space="preserve">2.20296835899353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14163303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07007503509521</t>
+    <t xml:space="preserve">2.14163279533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07007479667664</t>
   </si>
   <si>
     <t xml:space="preserve">2.01896166801453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95933020114899</t>
+    <t xml:space="preserve">1.95932996273041</t>
   </si>
   <si>
     <t xml:space="preserve">2.01044273376465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06496357917786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00192403793335</t>
+    <t xml:space="preserve">2.0649631023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00192427635193</t>
   </si>
   <si>
     <t xml:space="preserve">2.02407312393188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06155586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04451823234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837105751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303764343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111051559448</t>
+    <t xml:space="preserve">2.06155610084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04451847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837129592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303716659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0411102771759</t>
   </si>
   <si>
     <t xml:space="preserve">1.97977519035339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99340522289276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97636771202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97125625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97466385364532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95081114768982</t>
+    <t xml:space="preserve">1.99340510368347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97636735439301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97125649452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9746640920639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9508113861084</t>
   </si>
   <si>
     <t xml:space="preserve">1.938884973526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92525482177734</t>
+    <t xml:space="preserve">1.92525458335876</t>
   </si>
   <si>
     <t xml:space="preserve">1.9269585609436</t>
@@ -773,43 +773,43 @@
     <t xml:space="preserve">1.95762634277344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93718099594116</t>
+    <t xml:space="preserve">1.93718075752258</t>
   </si>
   <si>
     <t xml:space="preserve">1.92866230010986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97296023368835</t>
+    <t xml:space="preserve">1.97295999526978</t>
   </si>
   <si>
     <t xml:space="preserve">2.00703525543213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01555418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98829412460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93206989765167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91673588752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91332828998566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90821719169617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93377339839935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94058871269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13822555541992</t>
+    <t xml:space="preserve">2.01555442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98829400539398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93206965923309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91673624515533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91332840919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90821695327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93377351760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94058883190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13822507858276</t>
   </si>
   <si>
     <t xml:space="preserve">2.2557852268219</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">2.22341346740723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35971522331238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27452683448792</t>
+    <t xml:space="preserve">2.35971450805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27452659606934</t>
   </si>
   <si>
     <t xml:space="preserve">2.41593909263611</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">2.41253161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3682336807251</t>
+    <t xml:space="preserve">2.36823391914368</t>
   </si>
   <si>
     <t xml:space="preserve">2.30860185623169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31200957298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31541657447815</t>
+    <t xml:space="preserve">2.31200933456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31541681289673</t>
   </si>
   <si>
     <t xml:space="preserve">2.28986048698425</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">2.42445802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41423583030701</t>
+    <t xml:space="preserve">2.41423535346985</t>
   </si>
   <si>
     <t xml:space="preserve">2.36993741989136</t>
@@ -857,55 +857,55 @@
     <t xml:space="preserve">2.39719772338867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35801100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30519413948059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32052826881409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32904720306396</t>
+    <t xml:space="preserve">2.35801124572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30519437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32052803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32904696464539</t>
   </si>
   <si>
     <t xml:space="preserve">2.31882452964783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3477885723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36312198638916</t>
+    <t xml:space="preserve">2.34778833389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36312246322632</t>
   </si>
   <si>
     <t xml:space="preserve">2.3443808555603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32563972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33926963806152</t>
+    <t xml:space="preserve">2.32563948631287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33927011489868</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653017997742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37675261497498</t>
+    <t xml:space="preserve">2.37675213813782</t>
   </si>
   <si>
     <t xml:space="preserve">2.38356757164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27111864089966</t>
+    <t xml:space="preserve">2.27111887931824</t>
   </si>
   <si>
     <t xml:space="preserve">2.25408148765564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09392738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15696668624878</t>
+    <t xml:space="preserve">2.09392714500427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15696692466736</t>
   </si>
   <si>
     <t xml:space="preserve">2.10585379600525</t>
@@ -917,19 +917,19 @@
     <t xml:space="preserve">2.12800264358521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31712055206299</t>
+    <t xml:space="preserve">2.31712079048157</t>
   </si>
   <si>
     <t xml:space="preserve">2.28304529190063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30349040031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29667568206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28815674781799</t>
+    <t xml:space="preserve">2.30349063873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29667544364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28815698623657</t>
   </si>
   <si>
     <t xml:space="preserve">2.21659851074219</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">2.23874759674072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21489453315735</t>
+    <t xml:space="preserve">2.21489477157593</t>
   </si>
   <si>
     <t xml:space="preserve">2.25748920440674</t>
@@ -950,52 +950,52 @@
     <t xml:space="preserve">2.23193216323853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18933820724487</t>
+    <t xml:space="preserve">2.18933844566345</t>
   </si>
   <si>
     <t xml:space="preserve">2.26260018348694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22511720657349</t>
+    <t xml:space="preserve">2.22511744499207</t>
   </si>
   <si>
     <t xml:space="preserve">2.23363637924194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23022890090942</t>
+    <t xml:space="preserve">2.23022866249084</t>
   </si>
   <si>
     <t xml:space="preserve">2.20637607574463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29156446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39379024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41934657096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53009152412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5726854801178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54712915420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5812041759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50453495979309</t>
+    <t xml:space="preserve">2.29156398773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39378976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41934680938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53009128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57268571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54712891578674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58120441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50453519821167</t>
   </si>
   <si>
     <t xml:space="preserve">2.47045993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46194076538086</t>
+    <t xml:space="preserve">2.46194052696228</t>
   </si>
   <si>
     <t xml:space="preserve">2.38527131080627</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">2.41082787513733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30008316040039</t>
+    <t xml:space="preserve">2.30008292198181</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342206954956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60676074028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61527991294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64935493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65787386894226</t>
+    <t xml:space="preserve">2.60676050186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61527943611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6493546962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65787410736084</t>
   </si>
   <si>
     <t xml:space="preserve">2.43638396263123</t>
@@ -1031,34 +1031,34 @@
     <t xml:space="preserve">2.53861021995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55564832687378</t>
+    <t xml:space="preserve">2.55564785003662</t>
   </si>
   <si>
     <t xml:space="preserve">2.48749732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4449028968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26600790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14674401283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19671058654785</t>
+    <t xml:space="preserve">2.44490265846252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26600766181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14674425125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19671034812927</t>
   </si>
   <si>
     <t xml:space="preserve">2.11856651306152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17066216468811</t>
+    <t xml:space="preserve">2.17066240310669</t>
   </si>
   <si>
     <t xml:space="preserve">2.29221963882446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25748872756958</t>
+    <t xml:space="preserve">2.25748896598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.24880623817444</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">2.27485394477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34431552886963</t>
+    <t xml:space="preserve">2.34431529045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.35299801826477</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">2.30090236663818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30958485603333</t>
+    <t xml:space="preserve">2.30958461761475</t>
   </si>
   <si>
     <t xml:space="preserve">2.32695007324219</t>
@@ -1091,52 +1091,52 @@
     <t xml:space="preserve">2.21407580375671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17934513092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20539307594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15329718589783</t>
+    <t xml:space="preserve">2.17934465408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20539283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15329742431641</t>
   </si>
   <si>
     <t xml:space="preserve">2.13593196868896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10988402366638</t>
+    <t xml:space="preserve">2.1098837852478</t>
   </si>
   <si>
     <t xml:space="preserve">2.18802762031555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0925190448761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22275853157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0751531124115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08383584022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10120105743408</t>
+    <t xml:space="preserve">2.09251856803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22275829315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07515335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0838360786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10120129585266</t>
   </si>
   <si>
     <t xml:space="preserve">2.0404224395752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01437473297119</t>
+    <t xml:space="preserve">2.01437449455261</t>
   </si>
   <si>
     <t xml:space="preserve">2.05778789520264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06647062301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700963497162</t>
+    <t xml:space="preserve">2.06647086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700939655304</t>
   </si>
   <si>
     <t xml:space="preserve">2.00569224357605</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">1.97964406013489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96227896213531</t>
+    <t xml:space="preserve">1.96227872371674</t>
   </si>
   <si>
     <t xml:space="preserve">2.02305746078491</t>
@@ -1154,31 +1154,31 @@
     <t xml:space="preserve">2.04910516738892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03173995018005</t>
+    <t xml:space="preserve">2.03173971176147</t>
   </si>
   <si>
     <t xml:space="preserve">1.93623101711273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87545263767242</t>
+    <t xml:space="preserve">1.87545228004456</t>
   </si>
   <si>
     <t xml:space="preserve">1.892817735672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82335650920868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81467390060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77994322776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71916472911835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69311666488647</t>
+    <t xml:space="preserve">1.82335638999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81467366218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77994310855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71916460990906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69311678409576</t>
   </si>
   <si>
     <t xml:space="preserve">1.62799680233002</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">1.68443417549133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71048212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6887754201889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71482336521149</t>
+    <t xml:space="preserve">1.71048200130463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68877530097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7148232460022</t>
   </si>
   <si>
     <t xml:space="preserve">1.69745790958405</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">1.60629022121429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61931419372559</t>
+    <t xml:space="preserve">1.61931431293488</t>
   </si>
   <si>
     <t xml:space="preserve">1.61497282981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63667929172516</t>
+    <t xml:space="preserve">1.63667941093445</t>
   </si>
   <si>
     <t xml:space="preserve">1.64970338344574</t>
@@ -1232,58 +1232,58 @@
     <t xml:space="preserve">1.65838611125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70179927349091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67140996456146</t>
+    <t xml:space="preserve">1.7017993927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67141020298004</t>
   </si>
   <si>
     <t xml:space="preserve">1.66706871986389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5715594291687</t>
+    <t xml:space="preserve">1.57155954837799</t>
   </si>
   <si>
     <t xml:space="preserve">1.52814626693726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51078104972839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551148414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56287705898285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65404486656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66272723674774</t>
+    <t xml:space="preserve">1.51078116893768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551160335541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56287682056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6540447473526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66272735595703</t>
   </si>
   <si>
     <t xml:space="preserve">1.72784721851349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76257789134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75389528274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78862595558167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80599093437195</t>
+    <t xml:space="preserve">1.76257765293121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75389516353607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78862583637238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80599117279053</t>
   </si>
   <si>
     <t xml:space="preserve">1.77126049995422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74521267414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83203899860382</t>
+    <t xml:space="preserve">1.74521255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83203911781311</t>
   </si>
   <si>
     <t xml:space="preserve">1.79730844497681</t>
@@ -1292,60 +1292,63 @@
     <t xml:space="preserve">1.84072160720825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86676979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91018319129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9535961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94491362571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98832666873932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97096133232117</t>
+    <t xml:space="preserve">1.86676967144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91018295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95359635353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94491326808929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98832678794861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97096145153046</t>
   </si>
   <si>
     <t xml:space="preserve">1.91886556148529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92754828929901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85808718204498</t>
+    <t xml:space="preserve">1.9275484085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8580869436264</t>
   </si>
   <si>
     <t xml:space="preserve">1.84940445423126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88413512706757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62365567684174</t>
+    <t xml:space="preserve">1.88413488864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62365543842316</t>
   </si>
   <si>
     <t xml:space="preserve">1.6504191160202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61919486522675</t>
+    <t xml:space="preserve">1.61919510364532</t>
   </si>
   <si>
     <t xml:space="preserve">1.6013525724411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61027359962463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63703739643097</t>
+    <t xml:space="preserve">1.61027371883392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63703727722168</t>
   </si>
   <si>
     <t xml:space="preserve">1.65487968921661</t>
   </si>
   <si>
+    <t xml:space="preserve">1.62365555763245</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.64595854282379</t>
   </si>
   <si>
@@ -1355,7 +1358,7 @@
     <t xml:space="preserve">1.65934026241302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66826152801514</t>
+    <t xml:space="preserve">1.66826140880585</t>
   </si>
   <si>
     <t xml:space="preserve">1.68610382080078</t>
@@ -1364,7 +1367,7 @@
     <t xml:space="preserve">1.68164312839508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63257670402527</t>
+    <t xml:space="preserve">1.63257658481598</t>
   </si>
   <si>
     <t xml:space="preserve">1.60581314563751</t>
@@ -1373,22 +1376,22 @@
     <t xml:space="preserve">1.62811613082886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61473429203033</t>
+    <t xml:space="preserve">1.61473417282104</t>
   </si>
   <si>
     <t xml:space="preserve">1.58351027965546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57904958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55228590965271</t>
+    <t xml:space="preserve">1.57904970645905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.552286028862</t>
   </si>
   <si>
     <t xml:space="preserve">1.54336488246918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59243154525757</t>
+    <t xml:space="preserve">1.59243130683899</t>
   </si>
   <si>
     <t xml:space="preserve">1.56120717525482</t>
@@ -1397,19 +1400,19 @@
     <t xml:space="preserve">1.53890430927277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5567467212677</t>
+    <t xml:space="preserve">1.55674660205841</t>
   </si>
   <si>
     <t xml:space="preserve">1.57012832164764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58797061443329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57458913326263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5968918800354</t>
+    <t xml:space="preserve">1.58797085285187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57458901405334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59689199924469</t>
   </si>
   <si>
     <t xml:space="preserve">1.53444373607635</t>
@@ -1421,28 +1424,28 @@
     <t xml:space="preserve">1.56566786766052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54782557487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52552247047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50768005847931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738962173462</t>
+    <t xml:space="preserve">1.54782545566559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52552258968353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50768029689789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738950252533</t>
   </si>
   <si>
     <t xml:space="preserve">1.51660132408142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48983752727509</t>
+    <t xml:space="preserve">1.48983776569366</t>
   </si>
   <si>
     <t xml:space="preserve">1.34263813495636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34709882736206</t>
+    <t xml:space="preserve">1.34709870815277</t>
   </si>
   <si>
     <t xml:space="preserve">1.32479584217072</t>
@@ -1451,97 +1454,97 @@
     <t xml:space="preserve">1.19097816944122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2668080329895</t>
+    <t xml:space="preserve">1.26680815219879</t>
   </si>
   <si>
     <t xml:space="preserve">1.24450528621674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29803240299225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20435988903046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27572929859161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28465056419373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30695343017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30249285697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36940181255341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36494112014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35601997375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36048054695129</t>
+    <t xml:space="preserve">1.29803228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20435976982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27572917938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28465068340302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30695354938507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30249297618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36940169334412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36494123935699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35602021217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36048066616058</t>
   </si>
   <si>
     <t xml:space="preserve">1.40508651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44969248771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45415306091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44523191452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43631088733673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4184684753418</t>
+    <t xml:space="preserve">1.44969236850739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4541529417038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44523179531097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43631064891815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41846835613251</t>
   </si>
   <si>
     <t xml:space="preserve">1.46307420730591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39170479774475</t>
+    <t xml:space="preserve">1.39170467853546</t>
   </si>
   <si>
     <t xml:space="preserve">1.40062594413757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41400766372681</t>
+    <t xml:space="preserve">1.4140077829361</t>
   </si>
   <si>
     <t xml:space="preserve">1.38278